--- a/data/master_links.xlsx
+++ b/data/master_links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6A10845-2F88-4C9D-882C-239EA4CECDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999B3949-FE84-4B41-8AC4-C326B0788D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" tabRatio="314" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,6 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main_links!$A$1:$L$158</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="810">
   <si>
     <t>https://xhamster18.desi/videos/nubile-films-seductive-games-of-passion-3267609</t>
   </si>
@@ -989,9 +990,6 @@
     <t>amy brooke</t>
   </si>
   <si>
-    <t>enema</t>
-  </si>
-  <si>
     <t>undressing at 3m,enema at 41m,ruthless flogging while on crotch chain</t>
   </si>
   <si>
@@ -2421,6 +2419,81 @@
   </si>
   <si>
     <t>strip pole,on knees</t>
+  </si>
+  <si>
+    <t>ball gag,gangbang,pretzel,fisting</t>
+  </si>
+  <si>
+    <t>missionary,laying down,pretzel</t>
+  </si>
+  <si>
+    <t>general type of common bdsm videos with woman on woman as well</t>
+  </si>
+  <si>
+    <t>pegging,humiliation,2f-1m,chastity</t>
+  </si>
+  <si>
+    <t>doggy,missionary,laying down</t>
+  </si>
+  <si>
+    <t>decent low and mid quality femdom porn no studios</t>
+  </si>
+  <si>
+    <t>standing,doggy,</t>
+  </si>
+  <si>
+    <t>pegging,humiliation,2f-1m,chastity,milking,latex,humbler</t>
+  </si>
+  <si>
+    <t>general femdom kinky videos,some large studios but overall mid to high quality</t>
+  </si>
+  <si>
+    <t>teen,fingering,butt plug,spanking,side fuck,anal</t>
+  </si>
+  <si>
+    <t>doggy,side fuck,full nelson</t>
+  </si>
+  <si>
+    <t>spanking at 3m,full nelson at end</t>
+  </si>
+  <si>
+    <t>spanking,wedgie,enema,oiled,vibrator,strapon</t>
+  </si>
+  <si>
+    <t>spanking at 1m,wedgie at 2m,hair tied to wedgie,enema at 3m,inverted pussy over face at 5m,missionary at 9m</t>
+  </si>
+  <si>
+    <t>standing,inverted pussy over face,missionary</t>
+  </si>
+  <si>
+    <t>sitting</t>
+  </si>
+  <si>
+    <t>malice jade from reddit,uncage at 2m</t>
+  </si>
+  <si>
+    <t>chastity,gloves,condoms,edging</t>
+  </si>
+  <si>
+    <t>standing,doggy,laying down</t>
+  </si>
+  <si>
+    <t>body clothespin,wax,face dildo,spitroast,ice</t>
+  </si>
+  <si>
+    <t>octavia red</t>
+  </si>
+  <si>
+    <t>balls tied to ground at 8m,ice on back at 19m,spitroast at 31m,face dildo at 39m</t>
+  </si>
+  <si>
+    <t>standing,laying down</t>
+  </si>
+  <si>
+    <t>cunnilingus,flogging,nipple bite,ball clamps,face dildo,pegging,face underground</t>
+  </si>
+  <si>
+    <t>cunnilingus at 10m,flogging at 14m,nipple bite at 15m.ball clamp at 18m,pussy on chastity at 24m,face dildo at 27m,pegging at 32m,face underground</t>
   </si>
 </sst>
 </file>
@@ -2919,7 +2992,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L158"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2939,7 +3011,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>77</v>
@@ -2951,16 +3023,16 @@
         <v>80</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>82</v>
       </c>
       <c r="G1" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="H1" s="17" t="s">
         <v>490</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>491</v>
       </c>
       <c r="I1" s="17" t="s">
         <v>81</v>
@@ -2975,9 +3047,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:12" s="15" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="str">
-        <f>IF(ISBLANK(I2)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A2:A8" si="0">IF(ISBLANK(I2)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B2" s="17" t="s">
@@ -2990,16 +3062,16 @@
         <v>115</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F2" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I2" s="17" t="s">
         <v>84</v>
@@ -3008,20 +3080,20 @@
         <v>8</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L2" s="17" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.REGEXEXTRACT(B2,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="3" spans="1:12" s="15" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
-        <f>IF(ISBLANK(I3)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C3" s="17">
         <v>57</v>
@@ -3030,16 +3102,16 @@
         <v>289</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F3" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="I3" s="17" t="s">
         <v>84</v>
@@ -3048,16 +3120,16 @@
         <v>8</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="L3" s="17" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.REGEXEXTRACT(B3,"(?&lt;=//)[^/]+")</f>
         <v>www.eporner.com</v>
       </c>
     </row>
-    <row r="4" spans="1:12" s="15" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
-        <f>IF(ISBLANK(I4)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B4" s="17" t="s">
@@ -3067,19 +3139,19 @@
         <v>0</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F4" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="I4" s="17" t="s">
         <v>84</v>
@@ -3088,38 +3160,38 @@
         <v>8</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="L4" s="17" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.REGEXEXTRACT(B4,"(?&lt;=//)[^/]+")</f>
         <v>tube.perverzija.com</v>
       </c>
     </row>
-    <row r="5" spans="1:12" s="15" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
-        <f>IF(ISBLANK(I5)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C5" s="17">
         <v>0</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F5" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="I5" s="17" t="s">
         <v>84</v>
@@ -3128,38 +3200,38 @@
         <v>8</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L5" s="17" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.REGEXEXTRACT(B5,"(?&lt;=//)[^/]+")</f>
         <v>www.fuq.com</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="15" customFormat="1" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="str">
-        <f>IF(ISBLANK(I6)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C6" s="17">
         <v>0</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F6" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="I6" s="17" t="s">
         <v>84</v>
@@ -3168,118 +3240,118 @@
         <v>8</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="L6" s="17" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.REGEXEXTRACT(B6,"(?&lt;=//)[^/]+")</f>
         <v>www.tubebdsm.com</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="str">
-        <f>IF(ISBLANK(#REF!)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>67</v>
+        <v>479</v>
       </c>
       <c r="C7" s="17">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>413</v>
+        <v>446</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>413</v>
+        <v>343</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>528</v>
+        <v>792</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>668</v>
+        <v>791</v>
       </c>
       <c r="I7" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J7" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>366</v>
+        <v>793</v>
       </c>
       <c r="L7" s="17" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.REGEXEXTRACT(B7,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="str">
-        <f t="shared" ref="A8:A39" si="0">IF(ISBLANK(I8)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>66</v>
+        <v>475</v>
       </c>
       <c r="C8" s="17">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>270</v>
+        <v>150</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>492</v>
+        <v>412</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>529</v>
+        <v>797</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>669</v>
+        <v>799</v>
       </c>
       <c r="I8" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J8" s="17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>139</v>
+        <v>798</v>
       </c>
       <c r="L8" s="17" t="str" cm="1">
         <f t="array" ref="L8">_xlfn.REGEXEXTRACT(B8,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(#REF!)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>358</v>
+        <v>67</v>
       </c>
       <c r="C9" s="17">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>197</v>
+        <v>412</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>360</v>
+        <v>412</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="I9" s="17" t="s">
         <v>84</v>
@@ -3288,38 +3360,38 @@
         <v>7</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="L9" s="17" t="str" cm="1">
         <f t="array" ref="L9">_xlfn.REGEXEXTRACT(B9,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="A10:A41" si="1">IF(ISBLANK(I10)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="C10" s="17">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>98</v>
+        <v>270</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>322</v>
+        <v>491</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="I10" s="17" t="s">
         <v>84</v>
@@ -3328,38 +3400,38 @@
         <v>7</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>325</v>
+        <v>139</v>
       </c>
       <c r="L10" s="17" t="str" cm="1">
         <f t="array" ref="L10">_xlfn.REGEXEXTRACT(B10,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>45</v>
+        <v>357</v>
       </c>
       <c r="C11" s="17">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>98</v>
+        <v>197</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>273</v>
+        <v>359</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="I11" s="17" t="s">
         <v>84</v>
@@ -3368,38 +3440,38 @@
         <v>7</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>104</v>
+        <v>360</v>
       </c>
       <c r="L11" s="17" t="str" cm="1">
         <f t="array" ref="L11">_xlfn.REGEXEXTRACT(B11,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C12" s="17">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D12" s="17" t="s">
         <v>98</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="I12" s="17" t="s">
         <v>84</v>
@@ -3408,38 +3480,38 @@
         <v>7</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="L12" s="17" t="str" cm="1">
         <f t="array" ref="L12">_xlfn.REGEXEXTRACT(B12,"(?&lt;=//)[^/]+")</f>
         <v>m.hqporner.com</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>126</v>
+        <v>45</v>
       </c>
       <c r="C13" s="17">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>133</v>
+        <v>273</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>134</v>
+        <v>671</v>
       </c>
       <c r="I13" s="17" t="s">
         <v>84</v>
@@ -3448,38 +3520,38 @@
         <v>7</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="L13" s="17" t="str" cm="1">
         <f t="array" ref="L13">_xlfn.REGEXEXTRACT(B13,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="C14" s="17">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>239</v>
+        <v>307</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="I14" s="17" t="s">
         <v>84</v>
@@ -3488,38 +3560,38 @@
         <v>7</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="L14" s="17" t="str" cm="1">
         <f t="array" ref="L14">_xlfn.REGEXEXTRACT(B14,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>408</v>
+        <v>126</v>
       </c>
       <c r="C15" s="17">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>322</v>
+        <v>133</v>
       </c>
       <c r="F15" s="17" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>675</v>
+        <v>134</v>
       </c>
       <c r="I15" s="17" t="s">
         <v>84</v>
@@ -3528,38 +3600,38 @@
         <v>7</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>444</v>
+        <v>147</v>
       </c>
       <c r="L15" s="17" t="str" cm="1">
         <f t="array" ref="L15">_xlfn.REGEXEXTRACT(B15,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>448</v>
+        <v>177</v>
       </c>
       <c r="C16" s="17">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>110</v>
+        <v>212</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>344</v>
+        <v>239</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="I16" s="17" t="s">
         <v>84</v>
@@ -3568,38 +3640,38 @@
         <v>7</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>449</v>
+        <v>298</v>
       </c>
       <c r="L16" s="17" t="str" cm="1">
         <f t="array" ref="L16">_xlfn.REGEXEXTRACT(B16,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>168</v>
+        <v>407</v>
       </c>
       <c r="C17" s="17">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>447</v>
+        <v>110</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>169</v>
+        <v>321</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="I17" s="17" t="s">
         <v>84</v>
@@ -3608,20 +3680,20 @@
         <v>7</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>171</v>
+        <v>443</v>
       </c>
       <c r="L17" s="17" t="str" cm="1">
         <f t="array" ref="L17">_xlfn.REGEXEXTRACT(B17,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>379</v>
+        <v>447</v>
       </c>
       <c r="C18" s="17">
         <v>0</v>
@@ -3630,16 +3702,16 @@
         <v>110</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="I18" s="17" t="s">
         <v>84</v>
@@ -3648,38 +3720,38 @@
         <v>7</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>380</v>
+        <v>448</v>
       </c>
       <c r="L18" s="17" t="str" cm="1">
         <f t="array" ref="L18">_xlfn.REGEXEXTRACT(B18,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>399</v>
+        <v>168</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>344</v>
+        <v>169</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="I19" s="17" t="s">
         <v>84</v>
@@ -3688,36 +3760,38 @@
         <v>7</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>422</v>
+        <v>171</v>
       </c>
       <c r="L19" s="17" t="str" cm="1">
         <f t="array" ref="L19">_xlfn.REGEXEXTRACT(B19,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C20" s="17">
         <v>0</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>447</v>
+        <v>110</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="G20" s="17"/>
+        <v>112</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>538</v>
+      </c>
       <c r="H20" s="17" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="I20" s="17" t="s">
         <v>84</v>
@@ -3726,36 +3800,38 @@
         <v>7</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>433</v>
+        <v>379</v>
       </c>
       <c r="L20" s="17" t="str" cm="1">
         <f t="array" ref="L20">_xlfn.REGEXEXTRACT(B20,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C21" s="17">
         <v>0</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="G21" s="17"/>
+        <v>112</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>539</v>
+      </c>
       <c r="H21" s="17" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="I21" s="17" t="s">
         <v>84</v>
@@ -3764,38 +3840,36 @@
         <v>7</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="L21" s="17" t="str" cm="1">
         <f t="array" ref="L21">_xlfn.REGEXEXTRACT(B21,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>466</v>
+        <v>395</v>
       </c>
       <c r="C22" s="17">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>102</v>
+        <v>446</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>493</v>
+        <v>343</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>541</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="G22" s="17"/>
       <c r="H22" s="17" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="I22" s="17" t="s">
         <v>84</v>
@@ -3804,38 +3878,36 @@
         <v>7</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>469</v>
+        <v>432</v>
       </c>
       <c r="L22" s="17" t="str" cm="1">
         <f t="array" ref="L22">_xlfn.REGEXEXTRACT(B22,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>477</v>
+        <v>396</v>
       </c>
       <c r="C23" s="17">
         <v>0</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="G23" s="17" t="s">
-        <v>542</v>
-      </c>
+        <v>418</v>
+      </c>
+      <c r="G23" s="17"/>
       <c r="H23" s="17" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="I23" s="17" t="s">
         <v>84</v>
@@ -3844,158 +3916,158 @@
         <v>7</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>484</v>
+        <v>433</v>
       </c>
       <c r="L23" s="17" t="str" cm="1">
         <f t="array" ref="L23">_xlfn.REGEXEXTRACT(B23,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>393</v>
+        <v>465</v>
       </c>
       <c r="C24" s="17">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>413</v>
+        <v>102</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>413</v>
+        <v>492</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="J24" s="17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="L24" s="17" t="str" cm="1">
         <f t="array" ref="L24">_xlfn.REGEXEXTRACT(B24,"(?&lt;=//)[^/]+")</f>
-        <v>abjav.com</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>114</v>
+        <v>476</v>
       </c>
       <c r="C25" s="17">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>115</v>
+        <v>446</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>273</v>
+        <v>343</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="I25" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J25" s="17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>144</v>
+        <v>483</v>
       </c>
       <c r="L25" s="17" t="str" cm="1">
         <f t="array" ref="L25">_xlfn.REGEXEXTRACT(B25,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>34</v>
+        <v>392</v>
       </c>
       <c r="C26" s="17">
-        <v>66</v>
+        <v>113</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>102</v>
+        <v>412</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>350</v>
+        <v>412</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="J26" s="17">
         <v>6</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>353</v>
+        <v>441</v>
       </c>
       <c r="L26" s="17" t="str" cm="1">
         <f t="array" ref="L26">_xlfn.REGEXEXTRACT(B26,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>abjav.com</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="C27" s="17">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>303</v>
+        <v>115</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>326</v>
+        <v>273</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="I27" s="17" t="s">
         <v>84</v>
@@ -4004,38 +4076,38 @@
         <v>6</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>327</v>
+        <v>144</v>
       </c>
       <c r="L27" s="17" t="str" cm="1">
         <f t="array" ref="L27">_xlfn.REGEXEXTRACT(B27,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C28" s="17">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="I28" s="17" t="s">
         <v>84</v>
@@ -4044,38 +4116,38 @@
         <v>6</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="L28" s="17" t="str" cm="1">
         <f t="array" ref="L28">_xlfn.REGEXEXTRACT(B28,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="C29" s="17">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>274</v>
+        <v>325</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="I29" s="17" t="s">
         <v>84</v>
@@ -4084,38 +4156,38 @@
         <v>6</v>
       </c>
       <c r="K29" s="17" t="s">
-        <v>136</v>
+        <v>326</v>
       </c>
       <c r="L29" s="17" t="str" cm="1">
         <f t="array" ref="L29">_xlfn.REGEXEXTRACT(B29,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C30" s="17">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>494</v>
+        <v>318</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="I30" s="17" t="s">
         <v>84</v>
@@ -4124,38 +4196,38 @@
         <v>6</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>135</v>
+        <v>319</v>
       </c>
       <c r="L30" s="17" t="str" cm="1">
         <f t="array" ref="L30">_xlfn.REGEXEXTRACT(B30,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="C31" s="17">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>106</v>
+        <v>274</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="I31" s="17" t="s">
         <v>84</v>
@@ -4164,38 +4236,38 @@
         <v>6</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="L31" s="17" t="str" cm="1">
         <f t="array" ref="L31">_xlfn.REGEXEXTRACT(B31,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>abxxx.com</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="C32" s="17">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>212</v>
+        <v>91</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>301</v>
+        <v>493</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="I32" s="17" t="s">
         <v>84</v>
@@ -4204,38 +4276,38 @@
         <v>6</v>
       </c>
       <c r="K32" s="17" t="s">
-        <v>302</v>
+        <v>135</v>
       </c>
       <c r="L32" s="17" t="str" cm="1">
         <f t="array" ref="L32">_xlfn.REGEXEXTRACT(B32,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="C33" s="17">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>211</v>
+        <v>106</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="I33" s="17" t="s">
         <v>84</v>
@@ -4244,38 +4316,38 @@
         <v>6</v>
       </c>
       <c r="K33" s="17" t="s">
-        <v>324</v>
+        <v>141</v>
       </c>
       <c r="L33" s="17" t="str" cm="1">
         <f t="array" ref="L33">_xlfn.REGEXEXTRACT(B33,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>163</v>
+        <v>5</v>
       </c>
       <c r="C34" s="17">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>289</v>
+        <v>212</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>211</v>
+        <v>301</v>
       </c>
       <c r="F34" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="I34" s="17" t="s">
         <v>84</v>
@@ -4284,38 +4356,38 @@
         <v>6</v>
       </c>
       <c r="K34" s="17" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="L34" s="17" t="str" cm="1">
         <f t="array" ref="L34">_xlfn.REGEXEXTRACT(B34,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B35" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C35" s="17">
         <v>46</v>
       </c>
-      <c r="C35" s="17">
-        <v>44</v>
-      </c>
       <c r="D35" s="17" t="s">
-        <v>267</v>
+        <v>132</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="I35" s="17" t="s">
         <v>84</v>
@@ -4324,38 +4396,38 @@
         <v>6</v>
       </c>
       <c r="K35" s="17" t="s">
-        <v>269</v>
+        <v>323</v>
       </c>
       <c r="L35" s="17" t="str" cm="1">
         <f t="array" ref="L35">_xlfn.REGEXEXTRACT(B35,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="C36" s="17">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>256</v>
+        <v>289</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>225</v>
+        <v>93</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="I36" s="17" t="s">
         <v>84</v>
@@ -4364,38 +4436,38 @@
         <v>6</v>
       </c>
       <c r="K36" s="17" t="s">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="L36" s="17" t="str" cm="1">
         <f t="array" ref="L36">_xlfn.REGEXEXTRACT(B36,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C37" s="17">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>101</v>
+        <v>267</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="I37" s="17" t="s">
         <v>84</v>
@@ -4404,78 +4476,78 @@
         <v>6</v>
       </c>
       <c r="K37" s="17" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="L37" s="17" t="str" cm="1">
         <f t="array" ref="L37">_xlfn.REGEXEXTRACT(B37,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>365</v>
+        <v>186</v>
       </c>
       <c r="C38" s="17">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>413</v>
+        <v>256</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>413</v>
+        <v>223</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>370</v>
+        <v>84</v>
       </c>
       <c r="J38" s="17">
         <v>6</v>
       </c>
       <c r="K38" s="17" t="s">
-        <v>371</v>
+        <v>257</v>
       </c>
       <c r="L38" s="17" t="str" cm="1">
         <f t="array" ref="L38">_xlfn.REGEXEXTRACT(B38,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.tnaflix.com</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>191</v>
+        <v>15</v>
       </c>
       <c r="C39" s="17">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>447</v>
+        <v>101</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>224</v>
+        <v>93</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="I39" s="17" t="s">
         <v>84</v>
@@ -4484,78 +4556,78 @@
         <v>6</v>
       </c>
       <c r="K39" s="17" t="s">
-        <v>343</v>
+        <v>255</v>
       </c>
       <c r="L39" s="17" t="str" cm="1">
         <f t="array" ref="L39">_xlfn.REGEXEXTRACT(B39,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="str">
-        <f t="shared" ref="A40:A71" si="1">IF(ISBLANK(I40)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="C40" s="17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>382</v>
+        <v>412</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>344</v>
+        <v>412</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>84</v>
+        <v>369</v>
       </c>
       <c r="J40" s="17">
         <v>6</v>
       </c>
       <c r="K40" s="17" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="L40" s="17" t="str" cm="1">
         <f t="array" ref="L40">_xlfn.REGEXEXTRACT(B40,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="str">
         <f t="shared" si="1"/>
         <v>Done</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>384</v>
+        <v>191</v>
       </c>
       <c r="C41" s="17">
         <v>0</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>289</v>
+        <v>446</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>344</v>
+        <v>249</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>93</v>
+        <v>224</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="I41" s="17" t="s">
         <v>84</v>
@@ -4564,38 +4636,38 @@
         <v>6</v>
       </c>
       <c r="K41" s="17" t="s">
-        <v>387</v>
+        <v>342</v>
       </c>
       <c r="L41" s="17" t="str" cm="1">
         <f t="array" ref="L41">_xlfn.REGEXEXTRACT(B41,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="A42:A73" si="2">IF(ISBLANK(I42)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>398</v>
+        <v>380</v>
       </c>
       <c r="C42" s="17">
         <v>0</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>447</v>
+        <v>381</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="I42" s="17" t="s">
         <v>84</v>
@@ -4604,38 +4676,38 @@
         <v>6</v>
       </c>
       <c r="K42" s="17" t="s">
-        <v>420</v>
+        <v>382</v>
       </c>
       <c r="L42" s="17" t="str" cm="1">
         <f t="array" ref="L42">_xlfn.REGEXEXTRACT(B42,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="C43" s="17">
         <v>0</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>447</v>
+        <v>289</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="I43" s="17" t="s">
         <v>84</v>
@@ -4644,38 +4716,38 @@
         <v>6</v>
       </c>
       <c r="K43" s="17" t="s">
-        <v>424</v>
+        <v>386</v>
       </c>
       <c r="L43" s="17" t="str" cm="1">
         <f t="array" ref="L43">_xlfn.REGEXEXTRACT(B43,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C44" s="17">
         <v>0</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F44" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="I44" s="17" t="s">
         <v>84</v>
@@ -4684,38 +4756,38 @@
         <v>6</v>
       </c>
       <c r="K44" s="17" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="L44" s="17" t="str" cm="1">
         <f t="array" ref="L44">_xlfn.REGEXEXTRACT(B44,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C45" s="17">
         <v>0</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F45" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="I45" s="17" t="s">
         <v>84</v>
@@ -4724,38 +4796,38 @@
         <v>6</v>
       </c>
       <c r="K45" s="17" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="L45" s="17" t="str" cm="1">
         <f t="array" ref="L45">_xlfn.REGEXEXTRACT(B45,"(?&lt;=//)[^/]+")</f>
         <v>www.fuq.com</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>450</v>
+        <v>402</v>
       </c>
       <c r="C46" s="17">
         <v>0</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>382</v>
+        <v>446</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="I46" s="17" t="s">
         <v>84</v>
@@ -4764,38 +4836,38 @@
         <v>6</v>
       </c>
       <c r="K46" s="17" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="L46" s="17" t="str" cm="1">
         <f t="array" ref="L46">_xlfn.REGEXEXTRACT(B46,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>453</v>
+        <v>403</v>
       </c>
       <c r="C47" s="17">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>382</v>
+        <v>446</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>459</v>
+        <v>343</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="I47" s="17" t="s">
         <v>84</v>
@@ -4804,318 +4876,318 @@
         <v>6</v>
       </c>
       <c r="K47" s="17" t="s">
-        <v>460</v>
+        <v>426</v>
       </c>
       <c r="L47" s="17" t="str" cm="1">
         <f t="array" ref="L47">_xlfn.REGEXEXTRACT(B47,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>21</v>
+        <v>449</v>
       </c>
       <c r="C48" s="17">
-        <v>129</v>
+        <v>0</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>495</v>
+        <v>343</v>
       </c>
       <c r="F48" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="I48" s="17" t="s">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="J48" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K48" s="17" t="s">
-        <v>375</v>
+        <v>450</v>
       </c>
       <c r="L48" s="17" t="str" cm="1">
         <f t="array" ref="L48">_xlfn.REGEXEXTRACT(B48,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="C49" s="17">
-        <v>128</v>
+        <v>51</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>413</v>
+        <v>381</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>495</v>
+        <v>458</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>237</v>
+        <v>112</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="I49" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J49" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K49" s="17" t="s">
-        <v>378</v>
+        <v>459</v>
       </c>
       <c r="L49" s="17" t="str" cm="1">
         <f t="array" ref="L49">_xlfn.REGEXEXTRACT(B49,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>38</v>
+        <v>473</v>
       </c>
       <c r="C50" s="17">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>367</v>
+        <v>446</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>368</v>
+        <v>343</v>
       </c>
       <c r="F50" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>569</v>
+        <v>785</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>710</v>
+        <v>786</v>
       </c>
       <c r="I50" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J50" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K50" s="17" t="s">
-        <v>369</v>
+        <v>787</v>
       </c>
       <c r="L50" s="17" t="str" cm="1">
         <f t="array" ref="L50">_xlfn.REGEXEXTRACT(B50,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>14</v>
+        <v>478</v>
       </c>
       <c r="C51" s="17">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>98</v>
+        <v>446</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>496</v>
+        <v>343</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>570</v>
+        <v>788</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>711</v>
+        <v>789</v>
       </c>
       <c r="I51" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J51" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K51" s="17" t="s">
-        <v>364</v>
+        <v>790</v>
       </c>
       <c r="L51" s="17" t="str" cm="1">
         <f t="array" ref="L51">_xlfn.REGEXEXTRACT(B51,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.tubebdsm.com</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>27</v>
+        <v>474</v>
       </c>
       <c r="C52" s="17">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>102</v>
+        <v>412</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>336</v>
+        <v>412</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>571</v>
+        <v>794</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>712</v>
+        <v>795</v>
       </c>
       <c r="I52" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J52" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K52" s="17" t="s">
-        <v>342</v>
+        <v>796</v>
       </c>
       <c r="L52" s="17" t="str" cm="1">
         <f t="array" ref="L52">_xlfn.REGEXEXTRACT(B52,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>abbdsm.com</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>19</v>
+        <v>480</v>
       </c>
       <c r="C53" s="17">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>102</v>
+        <v>481</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>335</v>
+        <v>481</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>572</v>
+        <v>802</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>713</v>
+        <v>800</v>
       </c>
       <c r="I53" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J53" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K53" s="17" t="s">
-        <v>338</v>
+        <v>801</v>
       </c>
       <c r="L53" s="17" t="str" cm="1">
         <f t="array" ref="L53">_xlfn.REGEXEXTRACT(B53,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C54" s="17">
-        <v>60</v>
+        <v>129</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>303</v>
+        <v>371</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>333</v>
+        <v>494</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>714</v>
+        <v>707</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="J54" s="17">
         <v>5</v>
       </c>
       <c r="K54" s="17" t="s">
-        <v>334</v>
+        <v>374</v>
       </c>
       <c r="L54" s="17" t="str" cm="1">
         <f t="array" ref="L54">_xlfn.REGEXEXTRACT(B54,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>30</v>
+        <v>417</v>
       </c>
       <c r="C55" s="17">
-        <v>58</v>
+        <v>128</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>98</v>
+        <v>412</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>93</v>
+        <v>237</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>121</v>
+        <v>708</v>
       </c>
       <c r="I55" s="17" t="s">
         <v>84</v>
@@ -5124,38 +5196,38 @@
         <v>5</v>
       </c>
       <c r="K55" s="17" t="s">
-        <v>123</v>
+        <v>377</v>
       </c>
       <c r="L55" s="17" t="str" cm="1">
         <f t="array" ref="L55">_xlfn.REGEXEXTRACT(B55,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C56" s="17">
-        <v>57</v>
+        <v>116</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>110</v>
+        <v>366</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>276</v>
+        <v>367</v>
       </c>
       <c r="F56" s="17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="I56" s="17" t="s">
         <v>84</v>
@@ -5164,38 +5236,38 @@
         <v>5</v>
       </c>
       <c r="K56" s="17" t="s">
-        <v>143</v>
+        <v>368</v>
       </c>
       <c r="L56" s="17" t="str" cm="1">
         <f t="array" ref="L56">_xlfn.REGEXEXTRACT(B56,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>punishworld.com</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
       <c r="C57" s="17">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="D57" s="17" t="s">
         <v>98</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>245</v>
+        <v>495</v>
       </c>
       <c r="F57" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
       <c r="I57" s="17" t="s">
         <v>84</v>
@@ -5204,38 +5276,38 @@
         <v>5</v>
       </c>
       <c r="K57" s="17" t="s">
-        <v>316</v>
+        <v>363</v>
       </c>
       <c r="L57" s="17" t="str" cm="1">
         <f t="array" ref="L57">_xlfn.REGEXEXTRACT(B57,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C58" s="17">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>413</v>
+        <v>102</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>413</v>
+        <v>335</v>
       </c>
       <c r="F58" s="17" t="s">
         <v>94</v>
       </c>
       <c r="G58" s="17" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="I58" s="17" t="s">
         <v>84</v>
@@ -5244,38 +5316,38 @@
         <v>5</v>
       </c>
       <c r="K58" s="17" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="L58" s="17" t="str" cm="1">
         <f t="array" ref="L58">_xlfn.REGEXEXTRACT(B58,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C59" s="17">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D59" s="17" t="s">
         <v>102</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>305</v>
+        <v>334</v>
       </c>
       <c r="F59" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G59" s="17" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="I59" s="17" t="s">
         <v>84</v>
@@ -5284,38 +5356,38 @@
         <v>5</v>
       </c>
       <c r="K59" s="17" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="L59" s="17" t="str" cm="1">
         <f t="array" ref="L59">_xlfn.REGEXEXTRACT(B59,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="C60" s="17">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D60" s="17" t="s">
         <v>303</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>273</v>
+        <v>332</v>
       </c>
       <c r="F60" s="17" t="s">
         <v>94</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="I60" s="17" t="s">
         <v>84</v>
@@ -5324,38 +5396,38 @@
         <v>5</v>
       </c>
       <c r="K60" s="17" t="s">
-        <v>304</v>
+        <v>333</v>
       </c>
       <c r="L60" s="17" t="str" cm="1">
         <f t="array" ref="L60">_xlfn.REGEXEXTRACT(B60,"(?&lt;=//)[^/]+")</f>
-        <v>hcbdsm.com</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C61" s="17">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="D61" s="17" t="s">
         <v>98</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>294</v>
+        <v>496</v>
       </c>
       <c r="F61" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>720</v>
+        <v>121</v>
       </c>
       <c r="I61" s="17" t="s">
         <v>84</v>
@@ -5364,38 +5436,38 @@
         <v>5</v>
       </c>
       <c r="K61" s="17" t="s">
-        <v>295</v>
+        <v>123</v>
       </c>
       <c r="L61" s="17" t="str" cm="1">
         <f t="array" ref="L61">_xlfn.REGEXEXTRACT(B61,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>431</v>
+        <v>76</v>
       </c>
       <c r="C62" s="17">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>289</v>
+        <v>110</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>432</v>
+        <v>276</v>
       </c>
       <c r="F62" s="17" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>721</v>
+        <v>714</v>
       </c>
       <c r="I62" s="17" t="s">
         <v>84</v>
@@ -5404,38 +5476,38 @@
         <v>5</v>
       </c>
       <c r="K62" s="17" t="s">
-        <v>446</v>
+        <v>143</v>
       </c>
       <c r="L62" s="17" t="str" cm="1">
         <f t="array" ref="L62">_xlfn.REGEXEXTRACT(B62,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntrex.com</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="C63" s="17">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>498</v>
+        <v>245</v>
       </c>
       <c r="F63" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>722</v>
+        <v>715</v>
       </c>
       <c r="I63" s="17" t="s">
         <v>84</v>
@@ -5444,38 +5516,38 @@
         <v>5</v>
       </c>
       <c r="K63" s="17" t="s">
-        <v>266</v>
+        <v>315</v>
       </c>
       <c r="L63" s="17" t="str" cm="1">
         <f t="array" ref="L63">_xlfn.REGEXEXTRACT(B63,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="C64" s="17">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>258</v>
+        <v>412</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>499</v>
+        <v>412</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>237</v>
+        <v>94</v>
       </c>
       <c r="G64" s="17" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>723</v>
+        <v>716</v>
       </c>
       <c r="I64" s="17" t="s">
         <v>84</v>
@@ -5484,38 +5556,38 @@
         <v>5</v>
       </c>
       <c r="K64" s="17" t="s">
-        <v>259</v>
+        <v>317</v>
       </c>
       <c r="L64" s="17" t="str" cm="1">
         <f t="array" ref="L64">_xlfn.REGEXEXTRACT(B64,"(?&lt;=//)[^/]+")</f>
         <v>spankbang.com</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
       <c r="C65" s="17">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>247</v>
+        <v>102</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>500</v>
+        <v>305</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>724</v>
+        <v>717</v>
       </c>
       <c r="I65" s="17" t="s">
         <v>84</v>
@@ -5524,38 +5596,38 @@
         <v>5</v>
       </c>
       <c r="K65" s="17" t="s">
-        <v>248</v>
+        <v>306</v>
       </c>
       <c r="L65" s="17" t="str" cm="1">
         <f t="array" ref="L65">_xlfn.REGEXEXTRACT(B65,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="C66" s="17">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>101</v>
+        <v>303</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>107</v>
+        <v>273</v>
       </c>
       <c r="F66" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="I66" s="17" t="s">
         <v>84</v>
@@ -5564,38 +5636,38 @@
         <v>5</v>
       </c>
       <c r="K66" s="17" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="L66" s="17" t="str" cm="1">
         <f t="array" ref="L66">_xlfn.REGEXEXTRACT(B66,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>hcbdsm.com</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C67" s="17">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>501</v>
+        <v>294</v>
       </c>
       <c r="F67" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="H67" s="17" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="I67" s="17" t="s">
         <v>84</v>
@@ -5604,38 +5676,38 @@
         <v>5</v>
       </c>
       <c r="K67" s="17" t="s">
-        <v>138</v>
+        <v>295</v>
       </c>
       <c r="L67" s="17" t="str" cm="1">
         <f t="array" ref="L67">_xlfn.REGEXEXTRACT(B67,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>405</v>
+        <v>430</v>
       </c>
       <c r="C68" s="17">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>413</v>
+        <v>289</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="F68" s="17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>727</v>
+        <v>720</v>
       </c>
       <c r="I68" s="17" t="s">
         <v>84</v>
@@ -5644,38 +5716,38 @@
         <v>5</v>
       </c>
       <c r="K68" s="17" t="s">
-        <v>406</v>
+        <v>445</v>
       </c>
       <c r="L68" s="17" t="str" cm="1">
         <f t="array" ref="L68">_xlfn.REGEXEXTRACT(B68,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.porntrex.com</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>407</v>
+        <v>176</v>
       </c>
       <c r="C69" s="17">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>439</v>
+        <v>102</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>413</v>
+        <v>497</v>
       </c>
       <c r="F69" s="17" t="s">
-        <v>440</v>
+        <v>93</v>
       </c>
       <c r="G69" s="17" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="H69" s="17" t="s">
-        <v>96</v>
+        <v>721</v>
       </c>
       <c r="I69" s="17" t="s">
         <v>84</v>
@@ -5684,38 +5756,38 @@
         <v>5</v>
       </c>
       <c r="K69" s="17" t="s">
-        <v>441</v>
+        <v>266</v>
       </c>
       <c r="L69" s="17" t="str" cm="1">
         <f t="array" ref="L69">_xlfn.REGEXEXTRACT(B69,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>194</v>
+        <v>8</v>
       </c>
       <c r="C70" s="17">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>200</v>
+        <v>258</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>201</v>
+        <v>498</v>
       </c>
       <c r="F70" s="17" t="s">
-        <v>93</v>
+        <v>237</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="H70" s="17" t="s">
-        <v>148</v>
+        <v>722</v>
       </c>
       <c r="I70" s="17" t="s">
         <v>84</v>
@@ -5724,38 +5796,38 @@
         <v>5</v>
       </c>
       <c r="K70" s="17" t="s">
-        <v>321</v>
+        <v>259</v>
       </c>
       <c r="L70" s="17" t="str" cm="1">
         <f t="array" ref="L70">_xlfn.REGEXEXTRACT(B70,"(?&lt;=//)[^/]+")</f>
         <v>spankbang.com</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="C71" s="17">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>198</v>
+        <v>499</v>
       </c>
       <c r="F71" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="H71" s="17" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="I71" s="17" t="s">
         <v>84</v>
@@ -5764,78 +5836,78 @@
         <v>5</v>
       </c>
       <c r="K71" s="17" t="s">
-        <v>199</v>
+        <v>248</v>
       </c>
       <c r="L71" s="17" t="str" cm="1">
         <f t="array" ref="L71">_xlfn.REGEXEXTRACT(B71,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="str">
-        <f t="shared" ref="A72:A103" si="2">IF(ISBLANK(I72)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>392</v>
+        <v>22</v>
       </c>
       <c r="C72" s="17">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>413</v>
+        <v>101</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>413</v>
+        <v>107</v>
       </c>
       <c r="F72" s="17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G72" s="17" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="H72" s="17" t="s">
-        <v>421</v>
+        <v>724</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="J72" s="17">
         <v>5</v>
       </c>
       <c r="K72" s="17" t="s">
-        <v>435</v>
+        <v>140</v>
       </c>
       <c r="L72" s="17" t="str" cm="1">
         <f t="array" ref="L72">_xlfn.REGEXEXTRACT(B72,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="str">
         <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>385</v>
+        <v>44</v>
       </c>
       <c r="C73" s="17">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>386</v>
+        <v>101</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>394</v>
+        <v>500</v>
       </c>
       <c r="F73" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G73" s="17" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="I73" s="17" t="s">
         <v>84</v>
@@ -5844,38 +5916,38 @@
         <v>5</v>
       </c>
       <c r="K73" s="17" t="s">
-        <v>388</v>
+        <v>138</v>
       </c>
       <c r="L73" s="17" t="str" cm="1">
         <f t="array" ref="L73">_xlfn.REGEXEXTRACT(B73,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A74:A105" si="3">IF(ISBLANK(I74)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C74" s="17">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>447</v>
+        <v>412</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>344</v>
+        <v>412</v>
       </c>
       <c r="F74" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="I74" s="17" t="s">
         <v>84</v>
@@ -5884,38 +5956,38 @@
         <v>5</v>
       </c>
       <c r="K74" s="17" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="L74" s="17" t="str" cm="1">
         <f t="array" ref="L74">_xlfn.REGEXEXTRACT(B74,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>beeg.com</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>456</v>
+        <v>406</v>
       </c>
       <c r="C75" s="17">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>382</v>
+        <v>438</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>461</v>
+        <v>412</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>112</v>
+        <v>439</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>731</v>
+        <v>96</v>
       </c>
       <c r="I75" s="17" t="s">
         <v>84</v>
@@ -5924,38 +5996,38 @@
         <v>5</v>
       </c>
       <c r="K75" s="17" t="s">
-        <v>463</v>
+        <v>440</v>
       </c>
       <c r="L75" s="17" t="str" cm="1">
         <f t="array" ref="L75">_xlfn.REGEXEXTRACT(B75,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>454</v>
+        <v>194</v>
       </c>
       <c r="C76" s="17">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>382</v>
+        <v>200</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>502</v>
+        <v>201</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>732</v>
+        <v>148</v>
       </c>
       <c r="I76" s="17" t="s">
         <v>84</v>
@@ -5964,38 +6036,38 @@
         <v>5</v>
       </c>
       <c r="K76" s="17" t="s">
-        <v>465</v>
+        <v>320</v>
       </c>
       <c r="L76" s="17" t="str" cm="1">
         <f t="array" ref="L76">_xlfn.REGEXEXTRACT(B76,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>467</v>
+        <v>180</v>
       </c>
       <c r="C77" s="17">
-        <v>54</v>
+        <v>4</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>468</v>
+        <v>198</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="I77" s="17" t="s">
         <v>84</v>
@@ -6004,278 +6076,278 @@
         <v>5</v>
       </c>
       <c r="K77" s="17" t="s">
-        <v>470</v>
+        <v>199</v>
       </c>
       <c r="L77" s="17" t="str" cm="1">
         <f t="array" ref="L77">_xlfn.REGEXEXTRACT(B77,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>txxx.com</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>68</v>
+        <v>391</v>
       </c>
       <c r="C78" s="17">
-        <v>182</v>
+        <v>1</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>734</v>
+        <v>420</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="J78" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K78" s="17" t="s">
-        <v>377</v>
+        <v>434</v>
       </c>
       <c r="L78" s="17" t="str" cm="1">
         <f t="array" ref="L78">_xlfn.REGEXEXTRACT(B78,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>xhamster44.desi</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>69</v>
+        <v>384</v>
       </c>
       <c r="C79" s="17">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>503</v>
+        <v>393</v>
       </c>
       <c r="F79" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="H79" s="17" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="I79" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J79" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K79" s="17" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="L79" s="17" t="str" cm="1">
         <f t="array" ref="L79">_xlfn.REGEXEXTRACT(B79,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>153</v>
+        <v>401</v>
       </c>
       <c r="C80" s="17">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>150</v>
+        <v>446</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>504</v>
+        <v>343</v>
       </c>
       <c r="F80" s="17" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="G80" s="17" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="H80" s="17" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="I80" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J80" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K80" s="17" t="s">
-        <v>154</v>
+        <v>424</v>
       </c>
       <c r="L80" s="17" t="str" cm="1">
         <f t="array" ref="L80">_xlfn.REGEXEXTRACT(B80,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>63</v>
+        <v>455</v>
       </c>
       <c r="C81" s="17">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>110</v>
+        <v>381</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>111</v>
+        <v>460</v>
       </c>
       <c r="F81" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="I81" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J81" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K81" s="17" t="s">
-        <v>113</v>
+        <v>462</v>
       </c>
       <c r="L81" s="17" t="str" cm="1">
         <f t="array" ref="L81">_xlfn.REGEXEXTRACT(B81,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>164</v>
+        <v>453</v>
       </c>
       <c r="C82" s="17">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>355</v>
+        <v>501</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="H82" s="17" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="I82" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J82" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K82" s="17" t="s">
-        <v>356</v>
+        <v>464</v>
       </c>
       <c r="L82" s="17" t="str" cm="1">
         <f t="array" ref="L82">_xlfn.REGEXEXTRACT(B82,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>175</v>
+        <v>466</v>
       </c>
       <c r="C83" s="17">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>197</v>
+        <v>110</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>505</v>
+        <v>467</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="H83" s="17" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="I83" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J83" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K83" s="17" t="s">
-        <v>337</v>
+        <v>469</v>
       </c>
       <c r="L83" s="17" t="str" cm="1">
         <f t="array" ref="L83">_xlfn.REGEXEXTRACT(B83,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="C84" s="17">
-        <v>59</v>
+        <v>182</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>151</v>
+        <v>412</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>506</v>
+        <v>412</v>
       </c>
       <c r="F84" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G84" s="17" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="H84" s="17" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="I84" s="17" t="s">
         <v>84</v>
@@ -6284,38 +6356,38 @@
         <v>4</v>
       </c>
       <c r="K84" s="17" t="s">
-        <v>97</v>
+        <v>376</v>
       </c>
       <c r="L84" s="17" t="str" cm="1">
         <f t="array" ref="L84">_xlfn.REGEXEXTRACT(B84,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>punishbang.com</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="C85" s="17">
-        <v>58</v>
+        <v>170</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>98</v>
+        <v>372</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="F85" s="17" t="s">
         <v>94</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="H85" s="17" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="I85" s="17" t="s">
         <v>84</v>
@@ -6324,38 +6396,38 @@
         <v>4</v>
       </c>
       <c r="K85" s="17" t="s">
-        <v>332</v>
+        <v>373</v>
       </c>
       <c r="L85" s="17" t="str" cm="1">
         <f t="array" ref="L85">_xlfn.REGEXEXTRACT(B85,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>punishbang.com</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>29</v>
+        <v>153</v>
       </c>
       <c r="C86" s="17">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>101</v>
+        <v>150</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>275</v>
+        <v>503</v>
       </c>
       <c r="F86" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="I86" s="17" t="s">
         <v>84</v>
@@ -6364,38 +6436,38 @@
         <v>4</v>
       </c>
       <c r="K86" s="17" t="s">
-        <v>103</v>
+        <v>154</v>
       </c>
       <c r="L86" s="17" t="str" cm="1">
         <f t="array" ref="L86">_xlfn.REGEXEXTRACT(B86,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C87" s="17">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>267</v>
+        <v>110</v>
       </c>
       <c r="E87" s="17" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="F87" s="17" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="G87" s="17" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="I87" s="17" t="s">
         <v>84</v>
@@ -6404,38 +6476,38 @@
         <v>4</v>
       </c>
       <c r="K87" s="17" t="s">
-        <v>314</v>
+        <v>113</v>
       </c>
       <c r="L87" s="17" t="str" cm="1">
         <f t="array" ref="L87">_xlfn.REGEXEXTRACT(B87,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="C88" s="17">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>102</v>
+        <v>353</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>313</v>
+        <v>354</v>
       </c>
       <c r="F88" s="17" t="s">
-        <v>93</v>
+        <v>224</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="H88" s="17" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="I88" s="17" t="s">
         <v>84</v>
@@ -6444,38 +6516,38 @@
         <v>4</v>
       </c>
       <c r="K88" s="17" t="s">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="L88" s="17" t="str" cm="1">
         <f t="array" ref="L88">_xlfn.REGEXEXTRACT(B88,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>7</v>
+        <v>175</v>
       </c>
       <c r="C89" s="17">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="E89" s="17" t="s">
-        <v>413</v>
+        <v>504</v>
       </c>
       <c r="F89" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="I89" s="17" t="s">
         <v>84</v>
@@ -6484,38 +6556,38 @@
         <v>4</v>
       </c>
       <c r="K89" s="17" t="s">
-        <v>310</v>
+        <v>336</v>
       </c>
       <c r="L89" s="17" t="str" cm="1">
         <f t="array" ref="L89">_xlfn.REGEXEXTRACT(B89,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.party</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C90" s="17">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="E90" s="17" t="s">
-        <v>292</v>
+        <v>505</v>
       </c>
       <c r="F90" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G90" s="17" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="I90" s="17" t="s">
         <v>84</v>
@@ -6524,38 +6596,38 @@
         <v>4</v>
       </c>
       <c r="K90" s="17" t="s">
-        <v>293</v>
+        <v>97</v>
       </c>
       <c r="L90" s="17" t="str" cm="1">
         <f t="array" ref="L90">_xlfn.REGEXEXTRACT(B90,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="C91" s="17">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>285</v>
+        <v>506</v>
       </c>
       <c r="F91" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="I91" s="17" t="s">
         <v>84</v>
@@ -6564,38 +6636,38 @@
         <v>4</v>
       </c>
       <c r="K91" s="17" t="s">
-        <v>286</v>
+        <v>331</v>
       </c>
       <c r="L91" s="17" t="str" cm="1">
         <f t="array" ref="L91">_xlfn.REGEXEXTRACT(B91,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C92" s="17">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D92" s="17" t="s">
         <v>101</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F92" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G92" s="17" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="I92" s="17" t="s">
         <v>84</v>
@@ -6604,38 +6676,38 @@
         <v>4</v>
       </c>
       <c r="K92" s="17" t="s">
-        <v>279</v>
+        <v>103</v>
       </c>
       <c r="L92" s="17" t="str" cm="1">
         <f t="array" ref="L92">_xlfn.REGEXEXTRACT(B92,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>173</v>
+        <v>49</v>
       </c>
       <c r="C93" s="17">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>413</v>
+        <v>267</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>508</v>
+        <v>120</v>
       </c>
       <c r="F93" s="17" t="s">
-        <v>282</v>
+        <v>94</v>
       </c>
       <c r="G93" s="17" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="H93" s="17" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="I93" s="17" t="s">
         <v>84</v>
@@ -6644,38 +6716,38 @@
         <v>4</v>
       </c>
       <c r="K93" s="17" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="L93" s="17" t="str" cm="1">
         <f t="array" ref="L93">_xlfn.REGEXEXTRACT(B93,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>159</v>
+        <v>18</v>
       </c>
       <c r="C94" s="17">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>260</v>
+        <v>312</v>
       </c>
       <c r="F94" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="H94" s="17" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="I94" s="17" t="s">
         <v>84</v>
@@ -6684,38 +6756,38 @@
         <v>4</v>
       </c>
       <c r="K94" s="17" t="s">
-        <v>262</v>
+        <v>314</v>
       </c>
       <c r="L94" s="17" t="str" cm="1">
         <f t="array" ref="L94">_xlfn.REGEXEXTRACT(B94,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C95" s="17">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>120</v>
+        <v>412</v>
       </c>
       <c r="F95" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="H95" s="17" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="I95" s="17" t="s">
         <v>84</v>
@@ -6724,38 +6796,38 @@
         <v>4</v>
       </c>
       <c r="K95" s="17" t="s">
-        <v>196</v>
+        <v>309</v>
       </c>
       <c r="L95" s="17" t="str" cm="1">
         <f t="array" ref="L95">_xlfn.REGEXEXTRACT(B95,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>spankbang.party</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A96" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="C96" s="17">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>220</v>
+        <v>101</v>
       </c>
       <c r="E96" s="17" t="s">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="F96" s="17" t="s">
-        <v>224</v>
+        <v>93</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="H96" s="17" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="I96" s="17" t="s">
         <v>84</v>
@@ -6764,38 +6836,38 @@
         <v>4</v>
       </c>
       <c r="K96" s="17" t="s">
-        <v>250</v>
+        <v>293</v>
       </c>
       <c r="L96" s="17" t="str" cm="1">
         <f t="array" ref="L96">_xlfn.REGEXEXTRACT(B96,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="C97" s="17">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>241</v>
+        <v>102</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>242</v>
+        <v>285</v>
       </c>
       <c r="F97" s="17" t="s">
-        <v>237</v>
+        <v>93</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="H97" s="17" t="s">
-        <v>109</v>
+        <v>746</v>
       </c>
       <c r="I97" s="17" t="s">
         <v>84</v>
@@ -6804,38 +6876,38 @@
         <v>4</v>
       </c>
       <c r="K97" s="17" t="s">
-        <v>243</v>
+        <v>286</v>
       </c>
       <c r="L97" s="17" t="str" cm="1">
         <f t="array" ref="L97">_xlfn.REGEXEXTRACT(B97,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.me</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B98" s="17" t="s">
-        <v>162</v>
+        <v>16</v>
       </c>
       <c r="C98" s="17">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>509</v>
+        <v>278</v>
       </c>
       <c r="F98" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="H98" s="17" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
       <c r="I98" s="17" t="s">
         <v>84</v>
@@ -6844,38 +6916,38 @@
         <v>4</v>
       </c>
       <c r="K98" s="17" t="s">
-        <v>219</v>
+        <v>279</v>
       </c>
       <c r="L98" s="17" t="str" cm="1">
         <f t="array" ref="L98">_xlfn.REGEXEXTRACT(B98,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>410</v>
+        <v>173</v>
       </c>
       <c r="C99" s="17">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>156</v>
+        <v>412</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>412</v>
+        <v>507</v>
       </c>
       <c r="F99" s="17" t="s">
-        <v>112</v>
+        <v>282</v>
       </c>
       <c r="G99" s="17" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="H99" s="17" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="I99" s="17" t="s">
         <v>84</v>
@@ -6884,38 +6956,38 @@
         <v>4</v>
       </c>
       <c r="K99" s="17" t="s">
-        <v>443</v>
+        <v>283</v>
       </c>
       <c r="L99" s="17" t="str" cm="1">
         <f t="array" ref="L99">_xlfn.REGEXEXTRACT(B99,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>txxx.com</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="C100" s="17">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="E100" s="17" t="s">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="F100" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G100" s="17" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="H100" s="17" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="I100" s="17" t="s">
         <v>84</v>
@@ -6924,38 +6996,38 @@
         <v>4</v>
       </c>
       <c r="K100" s="17" t="s">
-        <v>214</v>
+        <v>262</v>
       </c>
       <c r="L100" s="17" t="str" cm="1">
         <f t="array" ref="L100">_xlfn.REGEXEXTRACT(B100,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="C101" s="17">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="D101" s="17" t="s">
-        <v>212</v>
+        <v>105</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="F101" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G101" s="17" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="H101" s="17" t="s">
-        <v>261</v>
+        <v>750</v>
       </c>
       <c r="I101" s="17" t="s">
         <v>84</v>
@@ -6964,38 +7036,38 @@
         <v>4</v>
       </c>
       <c r="K101" s="17" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="L101" s="17" t="str" cm="1">
         <f t="array" ref="L101">_xlfn.REGEXEXTRACT(B101,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C102" s="17">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>106</v>
+        <v>249</v>
       </c>
       <c r="F102" s="17" t="s">
         <v>224</v>
       </c>
       <c r="G102" s="17" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="H102" s="17" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="I102" s="17" t="s">
         <v>84</v>
@@ -7004,38 +7076,38 @@
         <v>4</v>
       </c>
       <c r="K102" s="17" t="s">
-        <v>207</v>
+        <v>250</v>
       </c>
       <c r="L102" s="17" t="str" cm="1">
         <f t="array" ref="L102">_xlfn.REGEXEXTRACT(B102,"(?&lt;=//)[^/]+")</f>
-        <v>www.porndead.org</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="C103" s="17">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="D103" s="17" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>201</v>
+        <v>242</v>
       </c>
       <c r="F103" s="17" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="G103" s="17" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="H103" s="17" t="s">
-        <v>757</v>
+        <v>109</v>
       </c>
       <c r="I103" s="17" t="s">
         <v>84</v>
@@ -7044,38 +7116,38 @@
         <v>4</v>
       </c>
       <c r="K103" s="17" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="L103" s="17" t="str" cm="1">
         <f t="array" ref="L103">_xlfn.REGEXEXTRACT(B103,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster18.desi</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+        <v>txxx.me</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="str">
-        <f t="shared" ref="A104:A135" si="3">IF(ISBLANK(I104)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>9</v>
+        <v>162</v>
       </c>
       <c r="C104" s="17">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>447</v>
+        <v>98</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>344</v>
+        <v>508</v>
       </c>
       <c r="F104" s="17" t="s">
-        <v>419</v>
+        <v>93</v>
       </c>
       <c r="G104" s="17" t="s">
-        <v>522</v>
+        <v>616</v>
       </c>
       <c r="H104" s="17" t="s">
-        <v>522</v>
+        <v>752</v>
       </c>
       <c r="I104" s="17" t="s">
         <v>84</v>
@@ -7084,38 +7156,38 @@
         <v>4</v>
       </c>
       <c r="K104" s="17" t="s">
-        <v>349</v>
+        <v>219</v>
       </c>
       <c r="L104" s="17" t="str" cm="1">
         <f t="array" ref="L104">_xlfn.REGEXEXTRACT(B104,"(?&lt;=//)[^/]+")</f>
-        <v>netfapx.net</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="str">
         <f t="shared" si="3"/>
         <v>Done</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>10</v>
+        <v>409</v>
       </c>
       <c r="C105" s="17">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>447</v>
+        <v>156</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>344</v>
+        <v>411</v>
       </c>
       <c r="F105" s="17" t="s">
-        <v>419</v>
+        <v>112</v>
       </c>
       <c r="G105" s="17" t="s">
-        <v>522</v>
+        <v>617</v>
       </c>
       <c r="H105" s="17" t="s">
-        <v>522</v>
+        <v>753</v>
       </c>
       <c r="I105" s="17" t="s">
         <v>84</v>
@@ -7124,78 +7196,78 @@
         <v>4</v>
       </c>
       <c r="K105" s="17" t="s">
-        <v>352</v>
+        <v>442</v>
       </c>
       <c r="L105" s="17" t="str" cm="1">
         <f t="array" ref="L105">_xlfn.REGEXEXTRACT(B105,"(?&lt;=//)[^/]+")</f>
-        <v>pornzog</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="A106:A137" si="4">IF(ISBLANK(I106)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>389</v>
+        <v>185</v>
       </c>
       <c r="C106" s="17">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>447</v>
+        <v>212</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>344</v>
+        <v>211</v>
       </c>
       <c r="F106" s="17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G106" s="17" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="J106" s="17">
         <v>4</v>
       </c>
       <c r="K106" s="17" t="s">
-        <v>390</v>
+        <v>214</v>
       </c>
       <c r="L106" s="17" t="str" cm="1">
         <f t="array" ref="L106">_xlfn.REGEXEXTRACT(B106,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubegalore.com</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>452</v>
+        <v>4</v>
       </c>
       <c r="C107" s="17">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>382</v>
+        <v>212</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>457</v>
+        <v>210</v>
       </c>
       <c r="F107" s="17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G107" s="17" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="H107" s="17" t="s">
-        <v>733</v>
+        <v>261</v>
       </c>
       <c r="I107" s="17" t="s">
         <v>84</v>
@@ -7204,38 +7276,38 @@
         <v>4</v>
       </c>
       <c r="K107" s="17" t="s">
-        <v>458</v>
+        <v>213</v>
       </c>
       <c r="L107" s="17" t="str" cm="1">
         <f t="array" ref="L107">_xlfn.REGEXEXTRACT(B107,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>455</v>
+        <v>192</v>
       </c>
       <c r="C108" s="17">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>382</v>
+        <v>206</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>510</v>
+        <v>106</v>
       </c>
       <c r="F108" s="17" t="s">
-        <v>112</v>
+        <v>224</v>
       </c>
       <c r="G108" s="17" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="H108" s="17" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="I108" s="17" t="s">
         <v>84</v>
@@ -7244,318 +7316,318 @@
         <v>4</v>
       </c>
       <c r="K108" s="17" t="s">
-        <v>464</v>
+        <v>207</v>
       </c>
       <c r="L108" s="17" t="str" cm="1">
         <f t="array" ref="L108">_xlfn.REGEXEXTRACT(B108,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.porndead.org</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>391</v>
+        <v>0</v>
       </c>
       <c r="C109" s="17">
-        <v>106</v>
+        <v>9</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>413</v>
+        <v>271</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>495</v>
+        <v>201</v>
       </c>
       <c r="F109" s="17" t="s">
-        <v>112</v>
+        <v>225</v>
       </c>
       <c r="G109" s="17" t="s">
-        <v>626</v>
+        <v>621</v>
       </c>
       <c r="H109" s="17" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>376</v>
+        <v>84</v>
       </c>
       <c r="J109" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K109" s="17" t="s">
-        <v>395</v>
+        <v>202</v>
       </c>
       <c r="L109" s="17" t="str" cm="1">
         <f t="array" ref="L109">_xlfn.REGEXEXTRACT(B109,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>xhamster18.desi</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C110" s="17">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>152</v>
+        <v>446</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>277</v>
+        <v>343</v>
       </c>
       <c r="F110" s="17" t="s">
-        <v>93</v>
+        <v>418</v>
       </c>
       <c r="G110" s="17" t="s">
-        <v>627</v>
+        <v>521</v>
       </c>
       <c r="H110" s="17" t="s">
-        <v>761</v>
+        <v>521</v>
       </c>
       <c r="I110" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J110" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K110" s="17" t="s">
-        <v>137</v>
+        <v>348</v>
       </c>
       <c r="L110" s="17" t="str" cm="1">
         <f t="array" ref="L110">_xlfn.REGEXEXTRACT(B110,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>netfapx.net</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>188</v>
+        <v>10</v>
       </c>
       <c r="C111" s="17">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>98</v>
+        <v>446</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>245</v>
+        <v>343</v>
       </c>
       <c r="F111" s="17" t="s">
-        <v>93</v>
+        <v>418</v>
       </c>
       <c r="G111" s="17" t="s">
-        <v>628</v>
+        <v>521</v>
       </c>
       <c r="H111" s="17" t="s">
-        <v>109</v>
+        <v>521</v>
       </c>
       <c r="I111" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J111" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K111" s="17" t="s">
-        <v>317</v>
+        <v>351</v>
       </c>
       <c r="L111" s="17" t="str" cm="1">
         <f t="array" ref="L111">_xlfn.REGEXEXTRACT(B111,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>pornzog</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>62</v>
+        <v>388</v>
       </c>
       <c r="C112" s="17">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>101</v>
+        <v>446</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>357</v>
+        <v>343</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="H112" s="17" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="J112" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K112" s="17" t="s">
-        <v>359</v>
+        <v>389</v>
       </c>
       <c r="L112" s="17" t="str" cm="1">
         <f t="array" ref="L112">_xlfn.REGEXEXTRACT(B112,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="113" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.tubegalore.com</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>64</v>
+        <v>451</v>
       </c>
       <c r="C113" s="17">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>270</v>
+        <v>381</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>511</v>
+        <v>456</v>
       </c>
       <c r="F113" s="17" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="G113" s="17" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="H113" s="17" t="s">
-        <v>763</v>
+        <v>732</v>
       </c>
       <c r="I113" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J113" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K113" s="17" t="s">
-        <v>142</v>
+        <v>457</v>
       </c>
       <c r="L113" s="17" t="str" cm="1">
         <f t="array" ref="L113">_xlfn.REGEXEXTRACT(B113,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>311</v>
+        <v>454</v>
       </c>
       <c r="C114" s="17">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>110</v>
+        <v>381</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>312</v>
+        <v>509</v>
       </c>
       <c r="F114" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="H114" s="17" t="s">
-        <v>706</v>
+        <v>758</v>
       </c>
       <c r="I114" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J114" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K114" s="17" t="s">
-        <v>417</v>
+        <v>463</v>
       </c>
       <c r="L114" s="17" t="str" cm="1">
         <f t="array" ref="L114">_xlfn.REGEXEXTRACT(B114,"(?&lt;=//)[^/]+")</f>
-        <v>pervtube.net</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>116</v>
+        <v>390</v>
       </c>
       <c r="C115" s="17">
-        <v>49</v>
+        <v>106</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>110</v>
+        <v>412</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>117</v>
+        <v>494</v>
       </c>
       <c r="F115" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G115" s="17" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="H115" s="17" t="s">
-        <v>733</v>
+        <v>759</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>84</v>
+        <v>375</v>
       </c>
       <c r="J115" s="17">
         <v>3</v>
       </c>
       <c r="K115" s="17" t="s">
-        <v>145</v>
+        <v>394</v>
       </c>
       <c r="L115" s="17" t="str" cm="1">
         <f t="array" ref="L115">_xlfn.REGEXEXTRACT(B115,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B116" s="17" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C116" s="17">
-        <v>46</v>
+        <v>102</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="F116" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G116" s="17" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="H116" s="17" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="I116" s="17" t="s">
         <v>84</v>
@@ -7564,38 +7636,38 @@
         <v>3</v>
       </c>
       <c r="K116" s="17" t="s">
-        <v>291</v>
+        <v>137</v>
       </c>
       <c r="L116" s="17" t="str" cm="1">
         <f t="array" ref="L116">_xlfn.REGEXEXTRACT(B116,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="117" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>416</v>
+        <v>188</v>
       </c>
       <c r="C117" s="17">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>413</v>
+        <v>98</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>512</v>
+        <v>245</v>
       </c>
       <c r="F117" s="17" t="s">
-        <v>237</v>
+        <v>93</v>
       </c>
       <c r="G117" s="17" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="H117" s="17" t="s">
-        <v>765</v>
+        <v>109</v>
       </c>
       <c r="I117" s="17" t="s">
         <v>84</v>
@@ -7604,78 +7676,78 @@
         <v>3</v>
       </c>
       <c r="K117" s="17" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="L117" s="17" t="str" cm="1">
         <f t="array" ref="L117">_xlfn.REGEXEXTRACT(B117,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>122</v>
+        <v>62</v>
       </c>
       <c r="C118" s="17">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="E118" s="17" t="s">
-        <v>124</v>
+        <v>356</v>
       </c>
       <c r="F118" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G118" s="17" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="H118" s="17" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="I118" s="17" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="J118" s="17">
         <v>3</v>
       </c>
       <c r="K118" s="17" t="s">
-        <v>146</v>
+        <v>358</v>
       </c>
       <c r="L118" s="17" t="str" cm="1">
         <f t="array" ref="L118">_xlfn.REGEXEXTRACT(B118,"(?&lt;=//)[^/]+")</f>
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="C119" s="17">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>239</v>
+        <v>510</v>
       </c>
       <c r="F119" s="17" t="s">
-        <v>224</v>
+        <v>92</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="H119" s="17" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="I119" s="17" t="s">
         <v>84</v>
@@ -7684,38 +7756,38 @@
         <v>3</v>
       </c>
       <c r="K119" s="17" t="s">
-        <v>281</v>
+        <v>142</v>
       </c>
       <c r="L119" s="17" t="str" cm="1">
         <f t="array" ref="L119">_xlfn.REGEXEXTRACT(B119,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="120" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>1</v>
+        <v>310</v>
       </c>
       <c r="C120" s="17">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>263</v>
+        <v>110</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>106</v>
+        <v>311</v>
       </c>
       <c r="F120" s="17" t="s">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="G120" s="17" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="H120" s="17" t="s">
-        <v>768</v>
+        <v>705</v>
       </c>
       <c r="I120" s="17" t="s">
         <v>84</v>
@@ -7724,38 +7796,38 @@
         <v>3</v>
       </c>
       <c r="K120" s="17" t="s">
-        <v>264</v>
+        <v>416</v>
       </c>
       <c r="L120" s="17" t="str" cm="1">
         <f t="array" ref="L120">_xlfn.REGEXEXTRACT(B120,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="121" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>pervtube.net</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c r="C121" s="17">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>251</v>
+        <v>110</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>252</v>
+        <v>117</v>
       </c>
       <c r="F121" s="17" t="s">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="G121" s="17" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="H121" s="17" t="s">
-        <v>769</v>
+        <v>732</v>
       </c>
       <c r="I121" s="17" t="s">
         <v>84</v>
@@ -7764,38 +7836,38 @@
         <v>3</v>
       </c>
       <c r="K121" s="17" t="s">
-        <v>253</v>
+        <v>145</v>
       </c>
       <c r="L121" s="17" t="str" cm="1">
         <f t="array" ref="L121">_xlfn.REGEXEXTRACT(B121,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="122" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="C122" s="17">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>128</v>
+        <v>197</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>513</v>
+        <v>290</v>
       </c>
       <c r="F122" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G122" s="17" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="H122" s="17" t="s">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="I122" s="17" t="s">
         <v>84</v>
@@ -7804,38 +7876,38 @@
         <v>3</v>
       </c>
       <c r="K122" s="17" t="s">
-        <v>244</v>
+        <v>291</v>
       </c>
       <c r="L122" s="17" t="str" cm="1">
         <f t="array" ref="L122">_xlfn.REGEXEXTRACT(B122,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>74</v>
+        <v>415</v>
       </c>
       <c r="C123" s="17">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>222</v>
+        <v>412</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="F123" s="17" t="s">
         <v>237</v>
       </c>
       <c r="G123" s="17" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="H123" s="17" t="s">
-        <v>771</v>
+        <v>764</v>
       </c>
       <c r="I123" s="17" t="s">
         <v>84</v>
@@ -7844,78 +7916,78 @@
         <v>3</v>
       </c>
       <c r="K123" s="17" t="s">
-        <v>236</v>
+        <v>297</v>
       </c>
       <c r="L123" s="17" t="str" cm="1">
         <f t="array" ref="L123">_xlfn.REGEXEXTRACT(B123,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="C124" s="17">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>238</v>
+        <v>115</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>239</v>
+        <v>124</v>
       </c>
       <c r="F124" s="17" t="s">
-        <v>225</v>
+        <v>92</v>
       </c>
       <c r="G124" s="17" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="H124" s="17" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="I124" s="17" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="J124" s="17">
         <v>3</v>
       </c>
       <c r="K124" s="17" t="s">
-        <v>240</v>
+        <v>146</v>
       </c>
       <c r="L124" s="17" t="str" cm="1">
         <f t="array" ref="L124">_xlfn.REGEXEXTRACT(B124,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>2</v>
+        <v>178</v>
       </c>
       <c r="C125" s="17">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D125" s="17" t="s">
-        <v>220</v>
+        <v>280</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>106</v>
+        <v>239</v>
       </c>
       <c r="F125" s="17" t="s">
         <v>224</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="H125" s="17" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="I125" s="17" t="s">
         <v>84</v>
@@ -7924,38 +7996,38 @@
         <v>3</v>
       </c>
       <c r="K125" s="17" t="s">
-        <v>221</v>
+        <v>281</v>
       </c>
       <c r="L125" s="17" t="str" cm="1">
         <f t="array" ref="L125">_xlfn.REGEXEXTRACT(B125,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>161</v>
+        <v>1</v>
       </c>
       <c r="C126" s="17">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="D126" s="17" t="s">
-        <v>98</v>
+        <v>263</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>273</v>
+        <v>106</v>
       </c>
       <c r="F126" s="17" t="s">
-        <v>93</v>
+        <v>224</v>
       </c>
       <c r="G126" s="17" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="H126" s="17" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="I126" s="17" t="s">
         <v>84</v>
@@ -7964,38 +8036,38 @@
         <v>3</v>
       </c>
       <c r="K126" s="17" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="L126" s="17" t="str" cm="1">
         <f t="array" ref="L126">_xlfn.REGEXEXTRACT(B126,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>127</v>
+        <v>193</v>
       </c>
       <c r="C127" s="17">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>128</v>
+        <v>251</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>515</v>
+        <v>252</v>
       </c>
       <c r="F127" s="17" t="s">
-        <v>94</v>
+        <v>224</v>
       </c>
       <c r="G127" s="17" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="H127" s="17" t="s">
-        <v>148</v>
+        <v>768</v>
       </c>
       <c r="I127" s="17" t="s">
         <v>84</v>
@@ -8004,38 +8076,38 @@
         <v>3</v>
       </c>
       <c r="K127" s="17" t="s">
-        <v>149</v>
+        <v>253</v>
       </c>
       <c r="L127" s="17" t="str" cm="1">
         <f t="array" ref="L127">_xlfn.REGEXEXTRACT(B127,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="C128" s="17">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>212</v>
+        <v>128</v>
       </c>
       <c r="E128" s="17" t="s">
-        <v>215</v>
+        <v>512</v>
       </c>
       <c r="F128" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="H128" s="17" t="s">
-        <v>95</v>
+        <v>769</v>
       </c>
       <c r="I128" s="17" t="s">
         <v>84</v>
@@ -8044,38 +8116,38 @@
         <v>3</v>
       </c>
       <c r="K128" s="17" t="s">
-        <v>216</v>
+        <v>244</v>
       </c>
       <c r="L128" s="17" t="str" cm="1">
         <f t="array" ref="L128">_xlfn.REGEXEXTRACT(B128,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>189</v>
+        <v>74</v>
       </c>
       <c r="C129" s="17">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="D129" s="17" t="s">
-        <v>203</v>
+        <v>222</v>
       </c>
       <c r="E129" s="17" t="s">
-        <v>204</v>
+        <v>513</v>
       </c>
       <c r="F129" s="17" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="G129" s="17" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="H129" s="17" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="I129" s="17" t="s">
         <v>84</v>
@@ -8084,38 +8156,38 @@
         <v>3</v>
       </c>
       <c r="K129" s="17" t="s">
-        <v>205</v>
+        <v>236</v>
       </c>
       <c r="L129" s="17" t="str" cm="1">
         <f t="array" ref="L129">_xlfn.REGEXEXTRACT(B129,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B130" s="17" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C130" s="17">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="D130" s="17" t="s">
-        <v>89</v>
+        <v>238</v>
       </c>
       <c r="E130" s="17" t="s">
-        <v>272</v>
+        <v>239</v>
       </c>
       <c r="F130" s="17" t="s">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="G130" s="17" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="H130" s="17" t="s">
-        <v>88</v>
+        <v>771</v>
       </c>
       <c r="I130" s="17" t="s">
         <v>84</v>
@@ -8124,78 +8196,78 @@
         <v>3</v>
       </c>
       <c r="K130" s="17" t="s">
-        <v>90</v>
+        <v>240</v>
       </c>
       <c r="L130" s="17" t="str" cm="1">
         <f t="array" ref="L130">_xlfn.REGEXEXTRACT(B130,"(?&lt;=//)[^/]+")</f>
-        <v>anyporn.com</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>428</v>
+        <v>2</v>
       </c>
       <c r="C131" s="17">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>413</v>
+        <v>220</v>
       </c>
       <c r="E131" s="17" t="s">
-        <v>413</v>
+        <v>106</v>
       </c>
       <c r="F131" s="17" t="s">
-        <v>112</v>
+        <v>224</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="H131" s="17" t="s">
-        <v>265</v>
+        <v>772</v>
       </c>
       <c r="I131" s="17" t="s">
-        <v>437</v>
+        <v>84</v>
       </c>
       <c r="J131" s="17">
         <v>3</v>
       </c>
       <c r="K131" s="17" t="s">
-        <v>438</v>
+        <v>221</v>
       </c>
       <c r="L131" s="17" t="str" cm="1">
         <f t="array" ref="L131">_xlfn.REGEXEXTRACT(B131,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" ht="90" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>409</v>
+        <v>161</v>
       </c>
       <c r="C132" s="17">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="E132" s="17" t="s">
-        <v>411</v>
+        <v>273</v>
       </c>
       <c r="F132" s="17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G132" s="17" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="H132" s="17" t="s">
-        <v>109</v>
+        <v>773</v>
       </c>
       <c r="I132" s="17" t="s">
         <v>84</v>
@@ -8204,38 +8276,38 @@
         <v>3</v>
       </c>
       <c r="K132" s="17" t="s">
-        <v>436</v>
+        <v>218</v>
       </c>
       <c r="L132" s="17" t="str" cm="1">
         <f t="array" ref="L132">_xlfn.REGEXEXTRACT(B132,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntopedia.com</v>
-      </c>
-    </row>
-    <row r="133" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>184</v>
+        <v>127</v>
       </c>
       <c r="C133" s="17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>447</v>
+        <v>128</v>
       </c>
       <c r="E133" s="17" t="s">
-        <v>211</v>
+        <v>514</v>
       </c>
       <c r="F133" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G133" s="17" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="H133" s="17" t="s">
-        <v>776</v>
+        <v>148</v>
       </c>
       <c r="I133" s="17" t="s">
         <v>84</v>
@@ -8244,38 +8316,38 @@
         <v>3</v>
       </c>
       <c r="K133" s="17" t="s">
-        <v>347</v>
+        <v>149</v>
       </c>
       <c r="L133" s="17" t="str" cm="1">
         <f t="array" ref="L133">_xlfn.REGEXEXTRACT(B133,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>183</v>
+        <v>6</v>
       </c>
       <c r="C134" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>447</v>
+        <v>212</v>
       </c>
       <c r="E134" s="17" t="s">
-        <v>245</v>
+        <v>215</v>
       </c>
       <c r="F134" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G134" s="17" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="H134" s="17" t="s">
-        <v>777</v>
+        <v>95</v>
       </c>
       <c r="I134" s="17" t="s">
         <v>84</v>
@@ -8284,226 +8356,226 @@
         <v>3</v>
       </c>
       <c r="K134" s="17" t="s">
-        <v>348</v>
+        <v>216</v>
       </c>
       <c r="L134" s="17" t="str" cm="1">
         <f t="array" ref="L134">_xlfn.REGEXEXTRACT(B134,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="135" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="C135" s="17">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>339</v>
+        <v>203</v>
       </c>
       <c r="E135" s="17" t="s">
-        <v>341</v>
+        <v>204</v>
       </c>
       <c r="F135" s="17" t="s">
         <v>224</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="H135" s="17" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="I135" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J135" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K135" s="17" t="s">
-        <v>340</v>
+        <v>205</v>
       </c>
       <c r="L135" s="17" t="str" cm="1">
         <f t="array" ref="L135">_xlfn.REGEXEXTRACT(B135,"(?&lt;=//)[^/]+")</f>
-        <v>www.peekvids.com</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.tnaflix.com</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A136" s="17" t="str">
-        <f t="shared" ref="A136:A158" si="4">IF(ISBLANK(I136)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="C136" s="17">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>328</v>
+        <v>89</v>
       </c>
       <c r="E136" s="17" t="s">
-        <v>329</v>
+        <v>272</v>
       </c>
       <c r="F136" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G136" s="17" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="H136" s="17" t="s">
-        <v>779</v>
+        <v>88</v>
       </c>
       <c r="I136" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J136" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K136" s="17" t="s">
-        <v>330</v>
+        <v>90</v>
       </c>
       <c r="L136" s="17" t="str" cm="1">
         <f t="array" ref="L136">_xlfn.REGEXEXTRACT(B136,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>anyporn.com</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="str">
         <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>187</v>
+        <v>427</v>
       </c>
       <c r="C137" s="17">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>289</v>
+        <v>412</v>
       </c>
       <c r="E137" s="17" t="s">
-        <v>516</v>
+        <v>412</v>
       </c>
       <c r="F137" s="17" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="G137" s="17" t="s">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="H137" s="17" t="s">
-        <v>780</v>
+        <v>265</v>
       </c>
       <c r="I137" s="17" t="s">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="J137" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K137" s="17" t="s">
-        <v>331</v>
+        <v>437</v>
       </c>
       <c r="L137" s="17" t="str" cm="1">
         <f t="array" ref="L137">_xlfn.REGEXEXTRACT(B137,"(?&lt;=//)[^/]+")</f>
-        <v>www.omg.xxx</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A138" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="A138:A154" si="5">IF(ISBLANK(I138)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>166</v>
+        <v>408</v>
       </c>
       <c r="C138" s="17">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="E138" s="17" t="s">
-        <v>517</v>
+        <v>410</v>
       </c>
       <c r="F138" s="17" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="G138" s="17" t="s">
-        <v>655</v>
+        <v>648</v>
       </c>
       <c r="H138" s="17" t="s">
-        <v>781</v>
+        <v>109</v>
       </c>
       <c r="I138" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J138" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K138" s="17" t="s">
-        <v>299</v>
+        <v>435</v>
       </c>
       <c r="L138" s="17" t="str" cm="1">
         <f t="array" ref="L138">_xlfn.REGEXEXTRACT(B138,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.porntopedia.com</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Done</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>48</v>
+        <v>184</v>
       </c>
       <c r="C139" s="17">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>101</v>
+        <v>446</v>
       </c>
       <c r="E139" s="17" t="s">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="F139" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G139" s="17" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="H139" s="17" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="I139" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J139" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K139" s="17" t="s">
-        <v>284</v>
+        <v>346</v>
       </c>
       <c r="L139" s="17" t="str" cm="1">
         <f t="array" ref="L139">_xlfn.REGEXEXTRACT(B139,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="140" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Done</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C140" s="17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>98</v>
+        <v>446</v>
       </c>
       <c r="E140" s="17" t="s">
         <v>245</v>
@@ -8512,50 +8584,50 @@
         <v>93</v>
       </c>
       <c r="G140" s="17" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="H140" s="17" t="s">
-        <v>323</v>
+        <v>776</v>
       </c>
       <c r="I140" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J140" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K140" s="17" t="s">
-        <v>246</v>
+        <v>347</v>
       </c>
       <c r="L140" s="17" t="str" cm="1">
         <f t="array" ref="L140">_xlfn.REGEXEXTRACT(B140,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="141" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Done</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>195</v>
+        <v>172</v>
       </c>
       <c r="C141" s="17">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>128</v>
+        <v>338</v>
       </c>
       <c r="E141" s="17" t="s">
-        <v>518</v>
+        <v>340</v>
       </c>
       <c r="F141" s="17" t="s">
-        <v>94</v>
+        <v>224</v>
       </c>
       <c r="G141" s="17" t="s">
-        <v>658</v>
+        <v>651</v>
       </c>
       <c r="H141" s="17" t="s">
-        <v>109</v>
+        <v>777</v>
       </c>
       <c r="I141" s="17" t="s">
         <v>84</v>
@@ -8564,38 +8636,38 @@
         <v>2</v>
       </c>
       <c r="K141" s="17" t="s">
-        <v>217</v>
+        <v>339</v>
       </c>
       <c r="L141" s="17" t="str" cm="1">
         <f t="array" ref="L141">_xlfn.REGEXEXTRACT(B141,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.peekvids.com</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Done</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>158</v>
+        <v>71</v>
       </c>
       <c r="C142" s="17">
-        <v>18</v>
+        <v>57</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>413</v>
+        <v>327</v>
       </c>
       <c r="E142" s="17" t="s">
-        <v>519</v>
+        <v>328</v>
       </c>
       <c r="F142" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G142" s="17" t="s">
-        <v>659</v>
+        <v>652</v>
       </c>
       <c r="H142" s="17" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="I142" s="17" t="s">
         <v>84</v>
@@ -8604,38 +8676,38 @@
         <v>2</v>
       </c>
       <c r="K142" s="17" t="s">
-        <v>415</v>
+        <v>329</v>
       </c>
       <c r="L142" s="17" t="str" cm="1">
         <f t="array" ref="L142">_xlfn.REGEXEXTRACT(B142,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Done</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>155</v>
+        <v>187</v>
       </c>
       <c r="C143" s="17">
-        <v>14</v>
+        <v>57</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>156</v>
+        <v>289</v>
       </c>
       <c r="E143" s="17" t="s">
-        <v>157</v>
+        <v>515</v>
       </c>
       <c r="F143" s="17" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="G143" s="17" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="H143" s="17" t="s">
-        <v>109</v>
+        <v>779</v>
       </c>
       <c r="I143" s="17" t="s">
         <v>84</v>
@@ -8644,344 +8716,380 @@
         <v>2</v>
       </c>
       <c r="K143" s="17" t="s">
-        <v>414</v>
+        <v>330</v>
       </c>
       <c r="L143" s="17" t="str" cm="1">
         <f t="array" ref="L143">_xlfn.REGEXEXTRACT(B143,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="144" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>www.omg.xxx</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Done</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C144" s="17">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="E144" s="17" t="s">
-        <v>128</v>
+        <v>516</v>
       </c>
       <c r="F144" s="17" t="s">
         <v>94</v>
       </c>
       <c r="G144" s="17" t="s">
-        <v>296</v>
+        <v>654</v>
       </c>
       <c r="H144" s="17" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="I144" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J144" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K144" s="17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L144" s="17" t="str" cm="1">
         <f t="array" ref="L144">_xlfn.REGEXEXTRACT(B144,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Done</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>125</v>
+        <v>48</v>
       </c>
       <c r="C145" s="17">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>128</v>
+        <v>101</v>
       </c>
       <c r="E145" s="17" t="s">
-        <v>515</v>
+        <v>120</v>
       </c>
       <c r="F145" s="17" t="s">
         <v>94</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="H145" s="17" t="s">
-        <v>129</v>
+        <v>781</v>
       </c>
       <c r="I145" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J145" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K145" s="17" t="s">
-        <v>130</v>
+        <v>284</v>
       </c>
       <c r="L145" s="17" t="str" cm="1">
         <f t="array" ref="L145">_xlfn.REGEXEXTRACT(B145,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Done</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>3</v>
+        <v>181</v>
       </c>
       <c r="C146" s="17">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>208</v>
+        <v>98</v>
       </c>
       <c r="E146" s="17" t="s">
-        <v>106</v>
+        <v>245</v>
       </c>
       <c r="F146" s="17" t="s">
-        <v>224</v>
+        <v>93</v>
       </c>
       <c r="G146" s="17" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="H146" s="17" t="s">
-        <v>785</v>
+        <v>322</v>
       </c>
       <c r="I146" s="17" t="s">
         <v>84</v>
       </c>
       <c r="J146" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K146" s="17" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="L146" s="17" t="str" cm="1">
         <f t="array" ref="L146">_xlfn.REGEXEXTRACT(B146,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>Pending</v>
+        <f t="shared" si="5"/>
+        <v>Done</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>474</v>
+        <v>195</v>
       </c>
       <c r="C147" s="17">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>447</v>
+        <v>128</v>
       </c>
       <c r="E147" s="17" t="s">
-        <v>344</v>
+        <v>517</v>
       </c>
       <c r="F147" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G147" s="17" t="s">
-        <v>522</v>
+        <v>657</v>
       </c>
       <c r="H147" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="I147" s="17"/>
-      <c r="J147" s="17"/>
-      <c r="K147" s="17"/>
+        <v>109</v>
+      </c>
+      <c r="I147" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J147" s="17">
+        <v>2</v>
+      </c>
+      <c r="K147" s="17" t="s">
+        <v>217</v>
+      </c>
       <c r="L147" s="17" t="str" cm="1">
         <f t="array" ref="L147">_xlfn.REGEXEXTRACT(B147,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>Pending</v>
+        <f t="shared" si="5"/>
+        <v>Done</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>479</v>
+        <v>158</v>
       </c>
       <c r="C148" s="17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>447</v>
+        <v>412</v>
       </c>
       <c r="E148" s="17" t="s">
-        <v>344</v>
+        <v>518</v>
       </c>
       <c r="F148" s="17" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="G148" s="17" t="s">
-        <v>522</v>
+        <v>658</v>
       </c>
       <c r="H148" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="I148" s="17"/>
-      <c r="J148" s="17"/>
-      <c r="K148" s="17"/>
+        <v>782</v>
+      </c>
+      <c r="I148" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J148" s="17">
+        <v>2</v>
+      </c>
+      <c r="K148" s="17" t="s">
+        <v>414</v>
+      </c>
       <c r="L148" s="17" t="str" cm="1">
         <f t="array" ref="L148">_xlfn.REGEXEXTRACT(B148,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="149" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>Pending</v>
+        <f t="shared" si="5"/>
+        <v>Done</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>480</v>
+        <v>155</v>
       </c>
       <c r="C149" s="17">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>447</v>
+        <v>156</v>
       </c>
       <c r="E149" s="17" t="s">
-        <v>344</v>
+        <v>157</v>
       </c>
       <c r="F149" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G149" s="17" t="s">
-        <v>522</v>
+        <v>659</v>
       </c>
       <c r="H149" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="I149" s="17"/>
-      <c r="J149" s="17"/>
-      <c r="K149" s="17"/>
+        <v>109</v>
+      </c>
+      <c r="I149" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J149" s="17">
+        <v>2</v>
+      </c>
+      <c r="K149" s="17" t="s">
+        <v>413</v>
+      </c>
       <c r="L149" s="17" t="str" cm="1">
         <f t="array" ref="L149">_xlfn.REGEXEXTRACT(B149,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="150" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>Pending</v>
+        <f t="shared" si="5"/>
+        <v>Done</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>475</v>
+        <v>160</v>
       </c>
       <c r="C150" s="17">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>413</v>
+        <v>128</v>
       </c>
       <c r="E150" s="17" t="s">
-        <v>413</v>
+        <v>128</v>
       </c>
       <c r="F150" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>522</v>
+        <v>296</v>
       </c>
       <c r="H150" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="I150" s="17"/>
-      <c r="J150" s="17"/>
-      <c r="K150" s="17"/>
+        <v>783</v>
+      </c>
+      <c r="I150" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J150" s="17">
+        <v>1</v>
+      </c>
+      <c r="K150" s="17" t="s">
+        <v>300</v>
+      </c>
       <c r="L150" s="17" t="str" cm="1">
         <f t="array" ref="L150">_xlfn.REGEXEXTRACT(B150,"(?&lt;=//)[^/]+")</f>
-        <v>abbdsm.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="151" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>Pending</v>
+        <f t="shared" si="5"/>
+        <v>Done</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>476</v>
+        <v>125</v>
       </c>
       <c r="C151" s="17">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="E151" s="17" t="s">
-        <v>413</v>
+        <v>514</v>
       </c>
       <c r="F151" s="17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G151" s="17" t="s">
-        <v>308</v>
+        <v>660</v>
       </c>
       <c r="H151" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="I151" s="17"/>
-      <c r="J151" s="17"/>
-      <c r="K151" s="17"/>
+        <v>129</v>
+      </c>
+      <c r="I151" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J151" s="17">
+        <v>1</v>
+      </c>
+      <c r="K151" s="17" t="s">
+        <v>130</v>
+      </c>
       <c r="L151" s="17" t="str" cm="1">
         <f t="array" ref="L151">_xlfn.REGEXEXTRACT(B151,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>Pending</v>
+        <f t="shared" si="5"/>
+        <v>Done</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>481</v>
+        <v>3</v>
       </c>
       <c r="C152" s="17">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>482</v>
+        <v>208</v>
       </c>
       <c r="E152" s="17" t="s">
-        <v>482</v>
+        <v>106</v>
       </c>
       <c r="F152" s="17" t="s">
-        <v>112</v>
+        <v>224</v>
       </c>
       <c r="G152" s="17" t="s">
-        <v>522</v>
+        <v>661</v>
       </c>
       <c r="H152" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="I152" s="17"/>
-      <c r="J152" s="17"/>
-      <c r="K152" s="17"/>
+        <v>784</v>
+      </c>
+      <c r="I152" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J152" s="17">
+        <v>1</v>
+      </c>
+      <c r="K152" s="17" t="s">
+        <v>209</v>
+      </c>
       <c r="L152" s="17" t="str" cm="1">
         <f t="array" ref="L152">_xlfn.REGEXEXTRACT(B152,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
+        <v>www.pornhub.com</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A153" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>Pending</v>
+        <f t="shared" si="5"/>
+        <v>Done</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C153" s="17">
         <v>44</v>
@@ -8990,20 +9098,26 @@
         <v>110</v>
       </c>
       <c r="E153" s="17" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F153" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G153" s="17" t="s">
-        <v>522</v>
+        <v>808</v>
       </c>
       <c r="H153" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="I153" s="17"/>
-      <c r="J153" s="17"/>
-      <c r="K153" s="17"/>
+        <v>807</v>
+      </c>
+      <c r="I153" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J153" s="17">
+        <v>7</v>
+      </c>
+      <c r="K153" s="17" t="s">
+        <v>809</v>
+      </c>
       <c r="L153" s="17" t="str" cm="1">
         <f t="array" ref="L153">_xlfn.REGEXEXTRACT(B153,"(?&lt;=//)[^/]+")</f>
         <v>www.fapcat.com</v>
@@ -9011,33 +9125,39 @@
     </row>
     <row r="154" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="17" t="str">
-        <f t="shared" si="4"/>
-        <v>Pending</v>
+        <f t="shared" si="5"/>
+        <v>Done</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C154" s="17">
         <v>50</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E154" s="17" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F154" s="17" t="s">
         <v>112</v>
       </c>
       <c r="G154" s="17" t="s">
-        <v>522</v>
+        <v>804</v>
       </c>
       <c r="H154" s="17" t="s">
-        <v>522</v>
-      </c>
-      <c r="I154" s="17"/>
-      <c r="J154" s="17"/>
-      <c r="K154" s="17"/>
+        <v>803</v>
+      </c>
+      <c r="I154" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="J154" s="17">
+        <v>6</v>
+      </c>
+      <c r="K154" s="17" t="s">
+        <v>806</v>
+      </c>
       <c r="L154" s="17" t="str" cm="1">
         <f t="array" ref="L154">_xlfn.REGEXEXTRACT(B154,"(?&lt;=//)[^/]+")</f>
         <v>tube.perverzija.com</v>
@@ -9045,11 +9165,11 @@
     </row>
     <row r="155" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I155)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C155" s="17">
         <v>51</v>
@@ -9058,16 +9178,16 @@
         <v>151</v>
       </c>
       <c r="E155" s="17" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F155" s="17" t="s">
         <v>94</v>
       </c>
       <c r="G155" s="17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H155" s="17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I155" s="17"/>
       <c r="J155" s="17"/>
@@ -9079,11 +9199,11 @@
     </row>
     <row r="156" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A156" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I156)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C156" s="17">
         <v>53</v>
@@ -9092,7 +9212,7 @@
         <v>197</v>
       </c>
       <c r="E156" s="17" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F156" s="17" t="s">
         <v>93</v>
@@ -9101,7 +9221,7 @@
         <v>100</v>
       </c>
       <c r="H156" s="17" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I156" s="17"/>
       <c r="J156" s="17"/>
@@ -9113,20 +9233,20 @@
     </row>
     <row r="157" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I157)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C157" s="17">
         <v>54</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E157" s="17" t="s">
-        <v>522</v>
+        <v>805</v>
       </c>
       <c r="F157" s="17" t="s">
         <v>93</v>
@@ -9135,7 +9255,7 @@
         <v>288</v>
       </c>
       <c r="H157" s="17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I157" s="17"/>
       <c r="J157" s="17"/>
@@ -9147,29 +9267,29 @@
     </row>
     <row r="158" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I158)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C158" s="17">
         <v>99</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E158" s="17" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F158" s="17" t="s">
         <v>93</v>
       </c>
       <c r="G158" s="17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H158" s="17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="I158" s="17"/>
       <c r="J158" s="17"/>
@@ -9181,17 +9301,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:L158" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Pending"/>
-      </filters>
-    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A155:L158">
+      <sortCondition ref="C1:C158"/>
+    </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L158">
     <sortCondition descending="1" ref="J1:J158"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="I3:L125 H1:L2 A1:G1048576 H159:XFD1048576 H3:H158 I126:XFD158">
+  <conditionalFormatting sqref="H1:L2 I3:L125 H159:XFD1048576 A1:G1048576 H3:H158 I126:XFD158">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>

--- a/data/master_links.xlsx
+++ b/data/master_links.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Crypto\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999B3949-FE84-4B41-8AC4-C326B0788D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB3F5C23-0F34-49C8-B1C6-D5CE2ADC65C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15960" tabRatio="314" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,10 +18,9 @@
     <sheet name="bdsmvilla" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main_links!$A$1:$L$158</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">main_links!$A$1:$L$166</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -64,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1398" uniqueCount="829">
   <si>
     <t>https://xhamster18.desi/videos/nubile-films-seductive-games-of-passion-3267609</t>
   </si>
@@ -93,12 +92,6 @@
     <t>https://spankbang.com/73cu4/video/riley+reid+and+melissa+moore+hot+stepsisters</t>
   </si>
   <si>
-    <t>https://netfapx.net/63721/</t>
-  </si>
-  <si>
-    <t>https://pornzog</t>
-  </si>
-  <si>
     <t>https://heavyfetish.com/videos/2325/wired-pussy-annabelle-lee/</t>
   </si>
   <si>
@@ -1095,9 +1088,6 @@
     <t>several innocent high videos of length from 20 to 50 mins</t>
   </si>
   <si>
-    <t>zstar</t>
-  </si>
-  <si>
     <t>kink.com</t>
   </si>
   <si>
@@ -1245,9 +1235,6 @@
     <t>https://abjav.com/video/114433/japanese-femdom-pt3/?campaign_id=251311668</t>
   </si>
   <si>
-    <t>dani daniels</t>
-  </si>
-  <si>
     <t>ass eating at 14m,foot licking at 35m</t>
   </si>
   <si>
@@ -1404,9 +1391,6 @@
     <t>stripping at 6m,tit flogging at 6m,oiled at 15m</t>
   </si>
   <si>
-    <t>websitelink</t>
-  </si>
-  <si>
     <t>https://www.pornhits.com/videos.php?p=1&amp;s=l&amp;spon=divine-bitches-kink</t>
   </si>
   <si>
@@ -2103,12 +2087,6 @@
     <t>doggy,kneeling,doggy</t>
   </si>
   <si>
-    <t>side fuck,reverse cowgirl,prone bone</t>
-  </si>
-  <si>
-    <t>prone bone,side fuck,doggy</t>
-  </si>
-  <si>
     <t>wooden horse,bent,doggy</t>
   </si>
   <si>
@@ -2494,6 +2472,84 @@
   </si>
   <si>
     <t>cunnilingus at 10m,flogging at 14m,nipple bite at 15m.ball clamp at 18m,pussy on chastity at 24m,face dildo at 27m,pegging at 32m,face underground</t>
+  </si>
+  <si>
+    <t>https://www.pornhits.com/video/487013/leigh-raven-going-for-gold/</t>
+  </si>
+  <si>
+    <t>https://www.pornhits.com/video/55779/19-year-old-s-fierce-introduced-to-the-bitches/</t>
+  </si>
+  <si>
+    <t>https://www.pornhits.com/video/55501/basement-bitch-cuckold/</t>
+  </si>
+  <si>
+    <t>https://www.pornhits.com/video/100335/new-male-sub-falls-deep-into-sub-space-like-never-seen-before-on-divine-bitches/</t>
+  </si>
+  <si>
+    <t>https://www.pornhits.com/video/452951/all-for-me/</t>
+  </si>
+  <si>
+    <t>https://www.pornhits.com/video/56131/chastity-woes-episode-2/</t>
+  </si>
+  <si>
+    <t>https://www.pornhits.com/videos.php?p=1&amp;q=Divine%20Bitches%20Chastity%20Videos</t>
+  </si>
+  <si>
+    <t>leigh raven</t>
+  </si>
+  <si>
+    <t>haley wilde,isis love</t>
+  </si>
+  <si>
+    <t>aiden star</t>
+  </si>
+  <si>
+    <t>dia zerva</t>
+  </si>
+  <si>
+    <t>amber snow</t>
+  </si>
+  <si>
+    <t>chanel preston</t>
+  </si>
+  <si>
+    <t>z-nstars</t>
+  </si>
+  <si>
+    <t>z-nstars,presley dawson</t>
+  </si>
+  <si>
+    <t>z-nstars,dani daniels</t>
+  </si>
+  <si>
+    <t>general-website-link</t>
+  </si>
+  <si>
+    <t>tube porn site</t>
+  </si>
+  <si>
+    <t>https://netfapx.net/</t>
+  </si>
+  <si>
+    <t>https://pornzog.com</t>
+  </si>
+  <si>
+    <t>https://www.pornhits.com/videos.php?p=1&amp;q=Divine%20Bitches%20Couple%20Dominated</t>
+  </si>
+  <si>
+    <t>pegging,cbt,gangbang,vibrator,flogging,canning</t>
+  </si>
+  <si>
+    <t>doggy,lay down,suspended</t>
+  </si>
+  <si>
+    <t>good quality divine bitches femdom porn</t>
+  </si>
+  <si>
+    <t>good quality divine bitches femdom porn with chastity</t>
+  </si>
+  <si>
+    <t>chastity,cbt,pegging,flogging,canning,vibrator</t>
   </si>
 </sst>
 </file>
@@ -2694,19 +2750,19 @@
   </cellStyles>
   <dxfs count="2">
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6161"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF6161"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2992,95 +3048,96 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-  <dimension ref="A1:L158"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:L166"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.85546875" style="16" customWidth="1"/>
     <col min="2" max="2" width="46.28515625" style="16" customWidth="1"/>
     <col min="3" max="3" width="14.7109375" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.28515625" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" style="16" customWidth="1"/>
     <col min="6" max="6" width="21.5703125" style="16" customWidth="1"/>
     <col min="7" max="7" width="58" style="16" customWidth="1"/>
     <col min="8" max="9" width="21.5703125" style="16" customWidth="1"/>
     <col min="10" max="10" width="10.5703125" style="16" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="53.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.28515625" style="16" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="35.140625" style="16" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B1" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C1" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>483</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="I1" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="D1" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>488</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>489</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>490</v>
-      </c>
-      <c r="I1" s="17" t="s">
-        <v>81</v>
-      </c>
       <c r="J1" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K1" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L1" s="17" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="17" t="str">
-        <f t="shared" ref="A2:A8" si="0">IF(ISBLANK(I2)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I2)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C2" s="17">
         <v>87</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F2" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="I2" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J2" s="17">
         <v>8</v>
       </c>
       <c r="K2" s="17" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="L2" s="17" t="str" cm="1">
         <f t="array" ref="L2">_xlfn.REGEXEXTRACT(B2,"(?&lt;=//)[^/]+")</f>
@@ -3089,38 +3146,38 @@
     </row>
     <row r="3" spans="1:12" s="15" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I3)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C3" s="17">
         <v>57</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="F3" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="I3" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J3" s="17">
         <v>8</v>
       </c>
       <c r="K3" s="17" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="L3" s="17" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.REGEXEXTRACT(B3,"(?&lt;=//)[^/]+")</f>
@@ -3129,38 +3186,38 @@
     </row>
     <row r="4" spans="1:12" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I4)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C4" s="17">
         <v>0</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J4" s="17">
         <v>8</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="L4" s="17" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.REGEXEXTRACT(B4,"(?&lt;=//)[^/]+")</f>
@@ -3169,38 +3226,38 @@
     </row>
     <row r="5" spans="1:12" s="15" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I5)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C5" s="17">
         <v>0</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F5" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
       <c r="I5" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J5" s="17">
         <v>8</v>
       </c>
       <c r="K5" s="17" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="L5" s="17" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.REGEXEXTRACT(B5,"(?&lt;=//)[^/]+")</f>
@@ -3209,38 +3266,38 @@
     </row>
     <row r="6" spans="1:12" s="15" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I6)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C6" s="17">
         <v>0</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>666</v>
+        <v>661</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J6" s="17">
         <v>8</v>
       </c>
       <c r="K6" s="17" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="L6" s="17" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.REGEXEXTRACT(B6,"(?&lt;=//)[^/]+")</f>
@@ -3249,38 +3306,38 @@
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I7)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J7" s="17">
         <v>8</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="L7" s="17" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.REGEXEXTRACT(B7,"(?&lt;=//)[^/]+")</f>
@@ -3289,38 +3346,38 @@
     </row>
     <row r="8" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I8)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C8" s="17">
         <v>11</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G8" s="17" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="I8" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J8" s="17">
         <v>8</v>
       </c>
       <c r="K8" s="17" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="L8" s="17" t="str" cm="1">
         <f t="array" ref="L8">_xlfn.REGEXEXTRACT(B8,"(?&lt;=//)[^/]+")</f>
@@ -3333,34 +3390,34 @@
         <v>Done</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C9" s="17">
         <v>111</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="I9" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J9" s="17">
         <v>7</v>
       </c>
       <c r="K9" s="17" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="L9" s="17" t="str" cm="1">
         <f t="array" ref="L9">_xlfn.REGEXEXTRACT(B9,"(?&lt;=//)[^/]+")</f>
@@ -3369,38 +3426,38 @@
     </row>
     <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="str">
-        <f t="shared" ref="A10:A41" si="1">IF(ISBLANK(I10)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I10)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C10" s="17">
         <v>85</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>668</v>
+        <v>663</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J10" s="17">
         <v>7</v>
       </c>
       <c r="K10" s="17" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="L10" s="17" t="str" cm="1">
         <f t="array" ref="L10">_xlfn.REGEXEXTRACT(B10,"(?&lt;=//)[^/]+")</f>
@@ -3409,38 +3466,38 @@
     </row>
     <row r="11" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I11)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C11" s="17">
         <v>73</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="I11" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J11" s="17">
         <v>7</v>
       </c>
       <c r="K11" s="17" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L11" s="17" t="str" cm="1">
         <f t="array" ref="L11">_xlfn.REGEXEXTRACT(B11,"(?&lt;=//)[^/]+")</f>
@@ -3449,38 +3506,38 @@
     </row>
     <row r="12" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I12)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C12" s="17">
         <v>56</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J12" s="17">
         <v>7</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="L12" s="17" t="str" cm="1">
         <f t="array" ref="L12">_xlfn.REGEXEXTRACT(B12,"(?&lt;=//)[^/]+")</f>
@@ -3489,38 +3546,38 @@
     </row>
     <row r="13" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I13)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" s="17">
         <v>53</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J13" s="17">
         <v>7</v>
       </c>
       <c r="K13" s="17" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="L13" s="17" t="str" cm="1">
         <f t="array" ref="L13">_xlfn.REGEXEXTRACT(B13,"(?&lt;=//)[^/]+")</f>
@@ -3529,38 +3586,38 @@
     </row>
     <row r="14" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I14)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C14" s="17">
         <v>51</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F14" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="I14" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J14" s="17">
         <v>7</v>
       </c>
       <c r="K14" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="L14" s="17" t="str" cm="1">
         <f t="array" ref="L14">_xlfn.REGEXEXTRACT(B14,"(?&lt;=//)[^/]+")</f>
@@ -3569,38 +3626,38 @@
     </row>
     <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I15)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C15" s="17">
         <v>48</v>
       </c>
       <c r="D15" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="H15" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="E15" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="G15" s="17" t="s">
-        <v>533</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>134</v>
-      </c>
       <c r="I15" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J15" s="17">
         <v>7</v>
       </c>
       <c r="K15" s="17" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L15" s="17" t="str" cm="1">
         <f t="array" ref="L15">_xlfn.REGEXEXTRACT(B15,"(?&lt;=//)[^/]+")</f>
@@ -3609,38 +3666,38 @@
     </row>
     <row r="16" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I16)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C16" s="17">
         <v>47</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F16" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="H16" s="17" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="I16" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J16" s="17">
         <v>7</v>
       </c>
       <c r="K16" s="17" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L16" s="17" t="str" cm="1">
         <f t="array" ref="L16">_xlfn.REGEXEXTRACT(B16,"(?&lt;=//)[^/]+")</f>
@@ -3649,38 +3706,38 @@
     </row>
     <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I17)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C17" s="17">
         <v>46</v>
       </c>
       <c r="D17" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="F17" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E17" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>112</v>
-      </c>
       <c r="G17" s="17" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="H17" s="17" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="I17" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J17" s="17">
         <v>7</v>
       </c>
       <c r="K17" s="17" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="L17" s="17" t="str" cm="1">
         <f t="array" ref="L17">_xlfn.REGEXEXTRACT(B17,"(?&lt;=//)[^/]+")</f>
@@ -3689,38 +3746,38 @@
     </row>
     <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I18)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C18" s="17">
         <v>0</v>
       </c>
       <c r="D18" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>816</v>
+      </c>
+      <c r="F18" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E18" s="17" t="s">
-        <v>343</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>112</v>
-      </c>
       <c r="G18" s="17" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J18" s="17">
         <v>7</v>
       </c>
       <c r="K18" s="17" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="L18" s="17" t="str" cm="1">
         <f t="array" ref="L18">_xlfn.REGEXEXTRACT(B18,"(?&lt;=//)[^/]+")</f>
@@ -3729,38 +3786,38 @@
     </row>
     <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I19)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C19" s="17">
         <v>0</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="H19" s="17" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="I19" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J19" s="17">
         <v>7</v>
       </c>
       <c r="K19" s="17" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="L19" s="17" t="str" cm="1">
         <f t="array" ref="L19">_xlfn.REGEXEXTRACT(B19,"(?&lt;=//)[^/]+")</f>
@@ -3769,38 +3826,38 @@
     </row>
     <row r="20" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A20" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I20)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C20" s="17">
         <v>0</v>
       </c>
       <c r="D20" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>816</v>
+      </c>
+      <c r="F20" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E20" s="17" t="s">
-        <v>343</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>112</v>
-      </c>
       <c r="G20" s="17" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="I20" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J20" s="17">
         <v>7</v>
       </c>
       <c r="K20" s="17" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L20" s="17" t="str" cm="1">
         <f t="array" ref="L20">_xlfn.REGEXEXTRACT(B20,"(?&lt;=//)[^/]+")</f>
@@ -3809,38 +3866,38 @@
     </row>
     <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I21)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="C21" s="17">
         <v>0</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J21" s="17">
         <v>7</v>
       </c>
       <c r="K21" s="17" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="L21" s="17" t="str" cm="1">
         <f t="array" ref="L21">_xlfn.REGEXEXTRACT(B21,"(?&lt;=//)[^/]+")</f>
@@ -3849,36 +3906,38 @@
     </row>
     <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I22)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C22" s="17">
         <v>0</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="G22" s="17"/>
+        <v>414</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>820</v>
+      </c>
       <c r="H22" s="17" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="I22" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J22" s="17">
         <v>7</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="L22" s="17" t="str" cm="1">
         <f t="array" ref="L22">_xlfn.REGEXEXTRACT(B22,"(?&lt;=//)[^/]+")</f>
@@ -3887,36 +3946,38 @@
     </row>
     <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I23)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="C23" s="17">
         <v>0</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="G23" s="17"/>
+        <v>414</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>820</v>
+      </c>
       <c r="H23" s="17" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="I23" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J23" s="17">
         <v>7</v>
       </c>
       <c r="K23" s="17" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L23" s="17" t="str" cm="1">
         <f t="array" ref="L23">_xlfn.REGEXEXTRACT(B23,"(?&lt;=//)[^/]+")</f>
@@ -3925,38 +3986,38 @@
     </row>
     <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I24)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C24" s="17">
         <v>46</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="H24" s="17" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J24" s="17">
         <v>7</v>
       </c>
       <c r="K24" s="17" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="L24" s="17" t="str" cm="1">
         <f t="array" ref="L24">_xlfn.REGEXEXTRACT(B24,"(?&lt;=//)[^/]+")</f>
@@ -3965,358 +4026,358 @@
     </row>
     <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I25)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C25" s="17">
         <v>0</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>682</v>
+        <v>675</v>
       </c>
       <c r="I25" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J25" s="17">
         <v>7</v>
       </c>
       <c r="K25" s="17" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="L25" s="17" t="str" cm="1">
         <f t="array" ref="L25">_xlfn.REGEXEXTRACT(B25,"(?&lt;=//)[^/]+")</f>
         <v>www.tubebdsm.com</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I26)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>392</v>
+        <v>477</v>
       </c>
       <c r="C26" s="17">
-        <v>113</v>
+        <v>44</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>412</v>
+        <v>108</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>542</v>
+        <v>801</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>683</v>
+        <v>800</v>
       </c>
       <c r="I26" s="17" t="s">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="J26" s="17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K26" s="17" t="s">
-        <v>441</v>
+        <v>802</v>
       </c>
       <c r="L26" s="17" t="str" cm="1">
         <f t="array" ref="L26">_xlfn.REGEXEXTRACT(B26,"(?&lt;=//)[^/]+")</f>
-        <v>abjav.com</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>www.fapcat.com</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I27)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>114</v>
+        <v>389</v>
       </c>
       <c r="C27" s="17">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>115</v>
+        <v>408</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>273</v>
+        <v>408</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="J27" s="17">
         <v>6</v>
       </c>
       <c r="K27" s="17" t="s">
-        <v>144</v>
+        <v>437</v>
       </c>
       <c r="L27" s="17" t="str" cm="1">
         <f t="array" ref="L27">_xlfn.REGEXEXTRACT(B27,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>abjav.com</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I28)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
       <c r="C28" s="17">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>349</v>
+        <v>271</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="I28" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J28" s="17">
         <v>6</v>
       </c>
       <c r="K28" s="17" t="s">
-        <v>352</v>
+        <v>142</v>
       </c>
       <c r="L28" s="17" t="str" cm="1">
         <f t="array" ref="L28">_xlfn.REGEXEXTRACT(B28,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I29)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C29" s="17">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>303</v>
+        <v>100</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="F29" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G29" s="17" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J29" s="17">
         <v>6</v>
       </c>
       <c r="K29" s="17" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="L29" s="17" t="str" cm="1">
         <f t="array" ref="L29">_xlfn.REGEXEXTRACT(B29,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I30)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C30" s="17">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>98</v>
+        <v>301</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G30" s="17" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J30" s="17">
         <v>6</v>
       </c>
       <c r="K30" s="17" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="L30" s="17" t="str" cm="1">
         <f t="array" ref="L30">_xlfn.REGEXEXTRACT(B30,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I31)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>99</v>
+        <v>11</v>
       </c>
       <c r="C31" s="17">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>274</v>
+        <v>316</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>688</v>
+        <v>680</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J31" s="17">
         <v>6</v>
       </c>
       <c r="K31" s="17" t="s">
-        <v>136</v>
+        <v>317</v>
       </c>
       <c r="L31" s="17" t="str" cm="1">
         <f t="array" ref="L31">_xlfn.REGEXEXTRACT(B31,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I32)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="C32" s="17">
         <v>53</v>
       </c>
       <c r="D32" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="F32" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="E32" s="17" t="s">
-        <v>493</v>
-      </c>
-      <c r="F32" s="17" t="s">
-        <v>92</v>
-      </c>
       <c r="G32" s="17" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>689</v>
+        <v>681</v>
       </c>
       <c r="I32" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J32" s="17">
         <v>6</v>
       </c>
       <c r="K32" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L32" s="17" t="str" cm="1">
         <f t="array" ref="L32">_xlfn.REGEXEXTRACT(B32,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>abxxx.com</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I33)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="C33" s="17">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>106</v>
+        <v>488</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>690</v>
+        <v>682</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J33" s="17">
         <v>6</v>
       </c>
       <c r="K33" s="17" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="L33" s="17" t="str" cm="1">
         <f t="array" ref="L33">_xlfn.REGEXEXTRACT(B33,"(?&lt;=//)[^/]+")</f>
@@ -4325,232 +4386,232 @@
     </row>
     <row r="34" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I34)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
       <c r="C34" s="17">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>212</v>
+        <v>106</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>301</v>
+        <v>104</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>691</v>
+        <v>683</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J34" s="17">
         <v>6</v>
       </c>
       <c r="K34" s="17" t="s">
-        <v>302</v>
+        <v>139</v>
       </c>
       <c r="L34" s="17" t="str" cm="1">
         <f t="array" ref="L34">_xlfn.REGEXEXTRACT(B34,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I35)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C35" s="17">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>132</v>
+        <v>210</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>211</v>
+        <v>299</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J35" s="17">
         <v>6</v>
       </c>
       <c r="K35" s="17" t="s">
-        <v>323</v>
+        <v>300</v>
       </c>
       <c r="L35" s="17" t="str" cm="1">
         <f t="array" ref="L35">_xlfn.REGEXEXTRACT(B35,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I36)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>163</v>
+        <v>15</v>
       </c>
       <c r="C36" s="17">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>289</v>
+        <v>130</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>693</v>
+        <v>685</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J36" s="17">
         <v>6</v>
       </c>
       <c r="K36" s="17" t="s">
-        <v>287</v>
+        <v>321</v>
       </c>
       <c r="L36" s="17" t="str" cm="1">
         <f t="array" ref="L36">_xlfn.REGEXEXTRACT(B36,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I37)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>46</v>
+        <v>161</v>
       </c>
       <c r="C37" s="17">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>268</v>
+        <v>209</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>694</v>
+        <v>686</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J37" s="17">
         <v>6</v>
       </c>
       <c r="K37" s="17" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="L37" s="17" t="str" cm="1">
         <f t="array" ref="L37">_xlfn.REGEXEXTRACT(B37,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I38)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="C38" s="17">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>223</v>
+        <v>266</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>225</v>
+        <v>91</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J38" s="17">
         <v>6</v>
       </c>
       <c r="K38" s="17" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="L38" s="17" t="str" cm="1">
         <f t="array" ref="L38">_xlfn.REGEXEXTRACT(B38,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I39)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>15</v>
+        <v>184</v>
       </c>
       <c r="C39" s="17">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>101</v>
+        <v>254</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>93</v>
+        <v>223</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J39" s="17">
         <v>6</v>
@@ -4560,163 +4621,163 @@
       </c>
       <c r="L39" s="17" t="str" cm="1">
         <f t="array" ref="L39">_xlfn.REGEXEXTRACT(B39,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>www.tnaflix.com</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I40)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>364</v>
+        <v>13</v>
       </c>
       <c r="C40" s="17">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>412</v>
+        <v>99</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>412</v>
+        <v>252</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>697</v>
+        <v>689</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>369</v>
+        <v>82</v>
       </c>
       <c r="J40" s="17">
         <v>6</v>
       </c>
       <c r="K40" s="17" t="s">
-        <v>370</v>
+        <v>253</v>
       </c>
       <c r="L40" s="17" t="str" cm="1">
         <f t="array" ref="L40">_xlfn.REGEXEXTRACT(B40,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I41)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>191</v>
+        <v>361</v>
       </c>
       <c r="C41" s="17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>249</v>
+        <v>408</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="H41" s="17" t="s">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>84</v>
+        <v>366</v>
       </c>
       <c r="J41" s="17">
         <v>6</v>
       </c>
       <c r="K41" s="17" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="L41" s="17" t="str" cm="1">
         <f t="array" ref="L41">_xlfn.REGEXEXTRACT(B41,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>punishworld.com</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="17" t="str">
-        <f t="shared" ref="A42:A73" si="2">IF(ISBLANK(I42)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I42)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>380</v>
+        <v>189</v>
       </c>
       <c r="C42" s="17">
         <v>0</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>381</v>
+        <v>819</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>343</v>
+        <v>817</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="G42" s="17" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="H42" s="17" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J42" s="17">
         <v>6</v>
       </c>
       <c r="K42" s="17" t="s">
-        <v>382</v>
+        <v>340</v>
       </c>
       <c r="L42" s="17" t="str" cm="1">
         <f t="array" ref="L42">_xlfn.REGEXEXTRACT(B42,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I43)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="C43" s="17">
         <v>0</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>289</v>
+        <v>378</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G43" s="17" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>700</v>
+        <v>692</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J43" s="17">
         <v>6</v>
       </c>
       <c r="K43" s="17" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="L43" s="17" t="str" cm="1">
         <f t="array" ref="L43">_xlfn.REGEXEXTRACT(B43,"(?&lt;=//)[^/]+")</f>
@@ -4725,118 +4786,118 @@
     </row>
     <row r="44" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I44)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="C44" s="17">
         <v>0</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>446</v>
+        <v>287</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J44" s="17">
         <v>6</v>
       </c>
       <c r="K44" s="17" t="s">
-        <v>419</v>
+        <v>383</v>
       </c>
       <c r="L44" s="17" t="str" cm="1">
         <f t="array" ref="L44">_xlfn.REGEXEXTRACT(B44,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
+        <v>www.txxx.porn</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I45)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="C45" s="17">
         <v>0</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F45" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G45" s="17" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>702</v>
+        <v>694</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J45" s="17">
         <v>6</v>
       </c>
       <c r="K45" s="17" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="L45" s="17" t="str" cm="1">
         <f t="array" ref="L45">_xlfn.REGEXEXTRACT(B45,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
+        <v>beeg.com</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I46)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C46" s="17">
         <v>0</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J46" s="17">
         <v>6</v>
       </c>
       <c r="K46" s="17" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="L46" s="17" t="str" cm="1">
         <f t="array" ref="L46">_xlfn.REGEXEXTRACT(B46,"(?&lt;=//)[^/]+")</f>
@@ -4845,1878 +4906,1878 @@
     </row>
     <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I47)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C47" s="17">
         <v>0</v>
       </c>
       <c r="D47" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>704</v>
+        <v>696</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J47" s="17">
         <v>6</v>
       </c>
       <c r="K47" s="17" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="L47" s="17" t="str" cm="1">
         <f t="array" ref="L47">_xlfn.REGEXEXTRACT(B47,"(?&lt;=//)[^/]+")</f>
         <v>www.fuq.com</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I48)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="C48" s="17">
         <v>0</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>381</v>
+        <v>819</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="I48" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J48" s="17">
         <v>6</v>
       </c>
       <c r="K48" s="17" t="s">
-        <v>450</v>
+        <v>422</v>
       </c>
       <c r="L48" s="17" t="str" cm="1">
         <f t="array" ref="L48">_xlfn.REGEXEXTRACT(B48,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>www.fuq.com</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I49)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="C49" s="17">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>458</v>
+        <v>816</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J49" s="17">
         <v>6</v>
       </c>
       <c r="K49" s="17" t="s">
-        <v>459</v>
+        <v>445</v>
       </c>
       <c r="L49" s="17" t="str" cm="1">
         <f t="array" ref="L49">_xlfn.REGEXEXTRACT(B49,"(?&lt;=//)[^/]+")</f>
         <v>www.porntry.com</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I50)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="C50" s="17">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>446</v>
+        <v>378</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>343</v>
+        <v>453</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>785</v>
+        <v>560</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>786</v>
+        <v>699</v>
       </c>
       <c r="I50" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J50" s="17">
         <v>6</v>
       </c>
       <c r="K50" s="17" t="s">
-        <v>787</v>
+        <v>454</v>
       </c>
       <c r="L50" s="17" t="str" cm="1">
         <f t="array" ref="L50">_xlfn.REGEXEXTRACT(B50,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I51)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="C51" s="17">
         <v>0</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>446</v>
+        <v>819</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>343</v>
+        <v>816</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>788</v>
+        <v>778</v>
       </c>
       <c r="H51" s="17" t="s">
-        <v>789</v>
+        <v>779</v>
       </c>
       <c r="I51" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J51" s="17">
         <v>6</v>
       </c>
       <c r="K51" s="17" t="s">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="L51" s="17" t="str" cm="1">
         <f t="array" ref="L51">_xlfn.REGEXEXTRACT(B51,"(?&lt;=//)[^/]+")</f>
         <v>www.tubebdsm.com</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I52)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C52" s="17">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>412</v>
+        <v>819</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>412</v>
+        <v>816</v>
       </c>
       <c r="F52" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G52" s="17" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>795</v>
+        <v>782</v>
       </c>
       <c r="I52" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J52" s="17">
         <v>6</v>
       </c>
       <c r="K52" s="17" t="s">
-        <v>796</v>
+        <v>783</v>
       </c>
       <c r="L52" s="17" t="str" cm="1">
         <f t="array" ref="L52">_xlfn.REGEXEXTRACT(B52,"(?&lt;=//)[^/]+")</f>
-        <v>abbdsm.com</v>
+        <v>www.tubebdsm.com</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I53)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="C53" s="17">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D53" s="17" t="s">
-        <v>481</v>
+        <v>408</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>481</v>
+        <v>408</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G53" s="17" t="s">
-        <v>802</v>
+        <v>787</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>800</v>
+        <v>788</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J53" s="17">
         <v>6</v>
       </c>
       <c r="K53" s="17" t="s">
-        <v>801</v>
+        <v>789</v>
       </c>
       <c r="L53" s="17" t="str" cm="1">
         <f t="array" ref="L53">_xlfn.REGEXEXTRACT(B53,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>abbdsm.com</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A54" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I54)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B54" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="C54" s="17">
         <v>21</v>
       </c>
-      <c r="C54" s="17">
-        <v>129</v>
-      </c>
       <c r="D54" s="17" t="s">
-        <v>371</v>
+        <v>476</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>494</v>
+        <v>476</v>
       </c>
       <c r="F54" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G54" s="17" t="s">
-        <v>566</v>
+        <v>795</v>
       </c>
       <c r="H54" s="17" t="s">
-        <v>707</v>
+        <v>793</v>
       </c>
       <c r="I54" s="17" t="s">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="J54" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K54" s="17" t="s">
-        <v>374</v>
+        <v>794</v>
       </c>
       <c r="L54" s="17" t="str" cm="1">
         <f t="array" ref="L54">_xlfn.REGEXEXTRACT(B54,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>xhamster44.desi</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I55)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B55" s="17" t="s">
-        <v>417</v>
+        <v>466</v>
       </c>
       <c r="C55" s="17">
-        <v>128</v>
+        <v>50</v>
       </c>
       <c r="D55" s="17" t="s">
-        <v>412</v>
+        <v>378</v>
       </c>
       <c r="E55" s="17" t="s">
-        <v>494</v>
+        <v>514</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>237</v>
+        <v>110</v>
       </c>
       <c r="G55" s="17" t="s">
-        <v>567</v>
+        <v>797</v>
       </c>
       <c r="H55" s="17" t="s">
-        <v>708</v>
+        <v>796</v>
       </c>
       <c r="I55" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J55" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K55" s="17" t="s">
-        <v>377</v>
+        <v>799</v>
       </c>
       <c r="L55" s="17" t="str" cm="1">
         <f t="array" ref="L55">_xlfn.REGEXEXTRACT(B55,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I56)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B56" s="17" t="s">
-        <v>38</v>
+        <v>823</v>
       </c>
       <c r="C56" s="17">
-        <v>116</v>
+        <v>0</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>366</v>
+        <v>108</v>
       </c>
       <c r="E56" s="17" t="s">
-        <v>367</v>
+        <v>816</v>
       </c>
       <c r="F56" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G56" s="17" t="s">
-        <v>568</v>
+        <v>824</v>
       </c>
       <c r="H56" s="17" t="s">
-        <v>709</v>
+        <v>825</v>
       </c>
       <c r="I56" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J56" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K56" s="17" t="s">
-        <v>368</v>
+        <v>826</v>
       </c>
       <c r="L56" s="17" t="str" cm="1">
         <f t="array" ref="L56">_xlfn.REGEXEXTRACT(B56,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
+        <v>www.pornhits.com</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I57)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B57" s="17" t="s">
-        <v>14</v>
+        <v>809</v>
       </c>
       <c r="C57" s="17">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="D57" s="17" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E57" s="17" t="s">
-        <v>495</v>
+        <v>816</v>
       </c>
       <c r="F57" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G57" s="17" t="s">
-        <v>569</v>
+        <v>828</v>
       </c>
       <c r="H57" s="17" t="s">
-        <v>710</v>
+        <v>825</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J57" s="17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K57" s="17" t="s">
-        <v>363</v>
+        <v>827</v>
       </c>
       <c r="L57" s="17" t="str" cm="1">
         <f t="array" ref="L57">_xlfn.REGEXEXTRACT(B57,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I58)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B58" s="17" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C58" s="17">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>102</v>
+        <v>368</v>
       </c>
       <c r="E58" s="17" t="s">
-        <v>335</v>
+        <v>489</v>
       </c>
       <c r="F58" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G58" s="17" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="H58" s="17" t="s">
-        <v>711</v>
+        <v>700</v>
       </c>
       <c r="I58" s="17" t="s">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="J58" s="17">
         <v>5</v>
       </c>
       <c r="K58" s="17" t="s">
-        <v>341</v>
+        <v>371</v>
       </c>
       <c r="L58" s="17" t="str" cm="1">
         <f t="array" ref="L58">_xlfn.REGEXEXTRACT(B58,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I59)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B59" s="17" t="s">
-        <v>19</v>
+        <v>413</v>
       </c>
       <c r="C59" s="17">
-        <v>62</v>
+        <v>128</v>
       </c>
       <c r="D59" s="17" t="s">
-        <v>102</v>
+        <v>408</v>
       </c>
       <c r="E59" s="17" t="s">
-        <v>334</v>
+        <v>489</v>
       </c>
       <c r="F59" s="17" t="s">
-        <v>93</v>
+        <v>235</v>
       </c>
       <c r="G59" s="17" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
       <c r="H59" s="17" t="s">
-        <v>712</v>
+        <v>701</v>
       </c>
       <c r="I59" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J59" s="17">
         <v>5</v>
       </c>
       <c r="K59" s="17" t="s">
-        <v>337</v>
+        <v>374</v>
       </c>
       <c r="L59" s="17" t="str" cm="1">
         <f t="array" ref="L59">_xlfn.REGEXEXTRACT(B59,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A60" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I60)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B60" s="17" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="C60" s="17">
-        <v>60</v>
+        <v>116</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>303</v>
+        <v>363</v>
       </c>
       <c r="E60" s="17" t="s">
-        <v>332</v>
+        <v>364</v>
       </c>
       <c r="F60" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G60" s="17" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="H60" s="17" t="s">
-        <v>713</v>
+        <v>702</v>
       </c>
       <c r="I60" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J60" s="17">
         <v>5</v>
       </c>
       <c r="K60" s="17" t="s">
-        <v>333</v>
+        <v>365</v>
       </c>
       <c r="L60" s="17" t="str" cm="1">
         <f t="array" ref="L60">_xlfn.REGEXEXTRACT(B60,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>punishworld.com</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I61)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B61" s="17" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C61" s="17">
-        <v>58</v>
+        <v>89</v>
       </c>
       <c r="D61" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E61" s="17" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="F61" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G61" s="17" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="H61" s="17" t="s">
-        <v>121</v>
+        <v>703</v>
       </c>
       <c r="I61" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J61" s="17">
         <v>5</v>
       </c>
       <c r="K61" s="17" t="s">
-        <v>123</v>
+        <v>360</v>
       </c>
       <c r="L61" s="17" t="str" cm="1">
         <f t="array" ref="L61">_xlfn.REGEXEXTRACT(B61,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A62" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I62)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B62" s="17" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C62" s="17">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="E62" s="17" t="s">
-        <v>276</v>
+        <v>333</v>
       </c>
       <c r="F62" s="17" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="G62" s="17" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="H62" s="17" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="I62" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J62" s="17">
         <v>5</v>
       </c>
       <c r="K62" s="17" t="s">
-        <v>143</v>
+        <v>339</v>
       </c>
       <c r="L62" s="17" t="str" cm="1">
         <f t="array" ref="L62">_xlfn.REGEXEXTRACT(B62,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I63)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B63" s="17" t="s">
-        <v>182</v>
+        <v>17</v>
       </c>
       <c r="C63" s="17">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D63" s="17" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E63" s="17" t="s">
-        <v>245</v>
+        <v>332</v>
       </c>
       <c r="F63" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G63" s="17" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="H63" s="17" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="I63" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J63" s="17">
         <v>5</v>
       </c>
       <c r="K63" s="17" t="s">
-        <v>315</v>
+        <v>335</v>
       </c>
       <c r="L63" s="17" t="str" cm="1">
         <f t="array" ref="L63">_xlfn.REGEXEXTRACT(B63,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I64)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B64" s="17" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C64" s="17">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>412</v>
+        <v>301</v>
       </c>
       <c r="E64" s="17" t="s">
-        <v>412</v>
+        <v>330</v>
       </c>
       <c r="F64" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G64" s="17" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="H64" s="17" t="s">
-        <v>716</v>
+        <v>706</v>
       </c>
       <c r="I64" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J64" s="17">
         <v>5</v>
       </c>
       <c r="K64" s="17" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="L64" s="17" t="str" cm="1">
         <f t="array" ref="L64">_xlfn.REGEXEXTRACT(B64,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I65)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B65" s="17" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C65" s="17">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D65" s="17" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="E65" s="17" t="s">
-        <v>305</v>
+        <v>491</v>
       </c>
       <c r="F65" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G65" s="17" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="H65" s="17" t="s">
-        <v>717</v>
+        <v>119</v>
       </c>
       <c r="I65" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J65" s="17">
         <v>5</v>
       </c>
       <c r="K65" s="17" t="s">
-        <v>306</v>
+        <v>121</v>
       </c>
       <c r="L65" s="17" t="str" cm="1">
         <f t="array" ref="L65">_xlfn.REGEXEXTRACT(B65,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I66)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B66" s="17" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="C66" s="17">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>303</v>
+        <v>108</v>
       </c>
       <c r="E66" s="17" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F66" s="17" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="G66" s="17" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="H66" s="17" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="I66" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J66" s="17">
         <v>5</v>
       </c>
       <c r="K66" s="17" t="s">
-        <v>304</v>
+        <v>141</v>
       </c>
       <c r="L66" s="17" t="str" cm="1">
         <f t="array" ref="L66">_xlfn.REGEXEXTRACT(B66,"(?&lt;=//)[^/]+")</f>
-        <v>hcbdsm.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I67)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B67" s="17" t="s">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="C67" s="17">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D67" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E67" s="17" t="s">
-        <v>294</v>
+        <v>243</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G67" s="17" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
       <c r="H67" s="17" t="s">
-        <v>719</v>
+        <v>708</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J67" s="17">
         <v>5</v>
       </c>
       <c r="K67" s="17" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="L67" s="17" t="str" cm="1">
         <f t="array" ref="L67">_xlfn.REGEXEXTRACT(B67,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A68" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I68)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B68" s="17" t="s">
-        <v>430</v>
+        <v>41</v>
       </c>
       <c r="C68" s="17">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>289</v>
+        <v>408</v>
       </c>
       <c r="E68" s="17" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
       <c r="F68" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G68" s="17" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="H68" s="17" t="s">
-        <v>720</v>
+        <v>709</v>
       </c>
       <c r="I68" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J68" s="17">
         <v>5</v>
       </c>
       <c r="K68" s="17" t="s">
-        <v>445</v>
+        <v>315</v>
       </c>
       <c r="L68" s="17" t="str" cm="1">
         <f t="array" ref="L68">_xlfn.REGEXEXTRACT(B68,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntrex.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I69)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B69" s="17" t="s">
-        <v>176</v>
+        <v>23</v>
       </c>
       <c r="C69" s="17">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="D69" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E69" s="17" t="s">
-        <v>497</v>
+        <v>303</v>
       </c>
       <c r="F69" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G69" s="17" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="H69" s="17" t="s">
-        <v>721</v>
+        <v>710</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J69" s="17">
         <v>5</v>
       </c>
       <c r="K69" s="17" t="s">
-        <v>266</v>
+        <v>304</v>
       </c>
       <c r="L69" s="17" t="str" cm="1">
         <f t="array" ref="L69">_xlfn.REGEXEXTRACT(B69,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I70)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B70" s="17" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="C70" s="17">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>258</v>
+        <v>301</v>
       </c>
       <c r="E70" s="17" t="s">
-        <v>498</v>
+        <v>271</v>
       </c>
       <c r="F70" s="17" t="s">
-        <v>237</v>
+        <v>92</v>
       </c>
       <c r="G70" s="17" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="H70" s="17" t="s">
-        <v>722</v>
+        <v>711</v>
       </c>
       <c r="I70" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J70" s="17">
         <v>5</v>
       </c>
       <c r="K70" s="17" t="s">
-        <v>259</v>
+        <v>302</v>
       </c>
       <c r="L70" s="17" t="str" cm="1">
         <f t="array" ref="L70">_xlfn.REGEXEXTRACT(B70,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>hcbdsm.com</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I71)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B71" s="17" t="s">
-        <v>73</v>
+        <v>26</v>
       </c>
       <c r="C71" s="17">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D71" s="17" t="s">
-        <v>247</v>
+        <v>96</v>
       </c>
       <c r="E71" s="17" t="s">
-        <v>499</v>
+        <v>292</v>
       </c>
       <c r="F71" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G71" s="17" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="H71" s="17" t="s">
-        <v>723</v>
+        <v>712</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J71" s="17">
         <v>5</v>
       </c>
       <c r="K71" s="17" t="s">
-        <v>248</v>
+        <v>293</v>
       </c>
       <c r="L71" s="17" t="str" cm="1">
         <f t="array" ref="L71">_xlfn.REGEXEXTRACT(B71,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I72)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B72" s="17" t="s">
-        <v>22</v>
+        <v>426</v>
       </c>
       <c r="C72" s="17">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>101</v>
+        <v>287</v>
       </c>
       <c r="E72" s="17" t="s">
-        <v>107</v>
+        <v>427</v>
       </c>
       <c r="F72" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G72" s="17" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="H72" s="17" t="s">
-        <v>724</v>
+        <v>713</v>
       </c>
       <c r="I72" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J72" s="17">
         <v>5</v>
       </c>
       <c r="K72" s="17" t="s">
-        <v>140</v>
+        <v>441</v>
       </c>
       <c r="L72" s="17" t="str" cm="1">
         <f t="array" ref="L72">_xlfn.REGEXEXTRACT(B72,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>www.porntrex.com</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I73)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B73" s="17" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="C73" s="17">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E73" s="17" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="F73" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G73" s="17" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="H73" s="17" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="I73" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J73" s="17">
         <v>5</v>
       </c>
       <c r="K73" s="17" t="s">
-        <v>138</v>
+        <v>264</v>
       </c>
       <c r="L73" s="17" t="str" cm="1">
         <f t="array" ref="L73">_xlfn.REGEXEXTRACT(B73,"(?&lt;=//)[^/]+")</f>
         <v>bdsmstreak.com</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A74" s="17" t="str">
-        <f t="shared" ref="A74:A105" si="3">IF(ISBLANK(I74)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I74)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B74" s="17" t="s">
-        <v>404</v>
+        <v>8</v>
       </c>
       <c r="C74" s="17">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>412</v>
+        <v>256</v>
       </c>
       <c r="E74" s="17" t="s">
-        <v>412</v>
+        <v>493</v>
       </c>
       <c r="F74" s="17" t="s">
-        <v>112</v>
+        <v>235</v>
       </c>
       <c r="G74" s="17" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="H74" s="17" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="I74" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J74" s="17">
         <v>5</v>
       </c>
       <c r="K74" s="17" t="s">
-        <v>405</v>
+        <v>257</v>
       </c>
       <c r="L74" s="17" t="str" cm="1">
         <f t="array" ref="L74">_xlfn.REGEXEXTRACT(B74,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I75)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B75" s="17" t="s">
-        <v>406</v>
+        <v>71</v>
       </c>
       <c r="C75" s="17">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D75" s="17" t="s">
-        <v>438</v>
+        <v>245</v>
       </c>
       <c r="E75" s="17" t="s">
-        <v>412</v>
+        <v>494</v>
       </c>
       <c r="F75" s="17" t="s">
-        <v>439</v>
+        <v>92</v>
       </c>
       <c r="G75" s="17" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="H75" s="17" t="s">
-        <v>96</v>
+        <v>716</v>
       </c>
       <c r="I75" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J75" s="17">
         <v>5</v>
       </c>
       <c r="K75" s="17" t="s">
-        <v>440</v>
+        <v>246</v>
       </c>
       <c r="L75" s="17" t="str" cm="1">
         <f t="array" ref="L75">_xlfn.REGEXEXTRACT(B75,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A76" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I76)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B76" s="17" t="s">
-        <v>194</v>
+        <v>20</v>
       </c>
       <c r="C76" s="17">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>200</v>
+        <v>99</v>
       </c>
       <c r="E76" s="17" t="s">
-        <v>201</v>
+        <v>105</v>
       </c>
       <c r="F76" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G76" s="17" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="H76" s="17" t="s">
-        <v>148</v>
+        <v>717</v>
       </c>
       <c r="I76" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J76" s="17">
         <v>5</v>
       </c>
       <c r="K76" s="17" t="s">
-        <v>320</v>
+        <v>138</v>
       </c>
       <c r="L76" s="17" t="str" cm="1">
         <f t="array" ref="L76">_xlfn.REGEXEXTRACT(B76,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I77)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B77" s="17" t="s">
-        <v>180</v>
+        <v>42</v>
       </c>
       <c r="C77" s="17">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>197</v>
+        <v>99</v>
       </c>
       <c r="E77" s="17" t="s">
-        <v>198</v>
+        <v>495</v>
       </c>
       <c r="F77" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G77" s="17" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="H77" s="17" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="I77" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J77" s="17">
         <v>5</v>
       </c>
       <c r="K77" s="17" t="s">
-        <v>199</v>
+        <v>136</v>
       </c>
       <c r="L77" s="17" t="str" cm="1">
         <f t="array" ref="L77">_xlfn.REGEXEXTRACT(B77,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I78)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B78" s="17" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="C78" s="17">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E78" s="17" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="F78" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G78" s="17" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="H78" s="17" t="s">
-        <v>420</v>
+        <v>719</v>
       </c>
       <c r="I78" s="17" t="s">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="J78" s="17">
         <v>5</v>
       </c>
       <c r="K78" s="17" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="L78" s="17" t="str" cm="1">
         <f t="array" ref="L78">_xlfn.REGEXEXTRACT(B78,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
+        <v>beeg.com</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I79)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B79" s="17" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="C79" s="17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>385</v>
+        <v>434</v>
       </c>
       <c r="E79" s="17" t="s">
-        <v>393</v>
+        <v>408</v>
       </c>
       <c r="F79" s="17" t="s">
-        <v>93</v>
+        <v>435</v>
       </c>
       <c r="G79" s="17" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="H79" s="17" t="s">
-        <v>728</v>
+        <v>94</v>
       </c>
       <c r="I79" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J79" s="17">
         <v>5</v>
       </c>
       <c r="K79" s="17" t="s">
-        <v>387</v>
+        <v>436</v>
       </c>
       <c r="L79" s="17" t="str" cm="1">
         <f t="array" ref="L79">_xlfn.REGEXEXTRACT(B79,"(?&lt;=//)[^/]+")</f>
-        <v>www.txxx.porn</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I80)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B80" s="17" t="s">
-        <v>401</v>
+        <v>192</v>
       </c>
       <c r="C80" s="17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>446</v>
+        <v>198</v>
       </c>
       <c r="E80" s="17" t="s">
-        <v>343</v>
+        <v>199</v>
       </c>
       <c r="F80" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G80" s="17" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="H80" s="17" t="s">
-        <v>729</v>
+        <v>146</v>
       </c>
       <c r="I80" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J80" s="17">
         <v>5</v>
       </c>
       <c r="K80" s="17" t="s">
-        <v>424</v>
+        <v>318</v>
       </c>
       <c r="L80" s="17" t="str" cm="1">
         <f t="array" ref="L80">_xlfn.REGEXEXTRACT(B80,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I81)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B81" s="17" t="s">
-        <v>455</v>
+        <v>178</v>
       </c>
       <c r="C81" s="17">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>381</v>
+        <v>195</v>
       </c>
       <c r="E81" s="17" t="s">
-        <v>460</v>
+        <v>196</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G81" s="17" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="H81" s="17" t="s">
-        <v>730</v>
+        <v>720</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J81" s="17">
         <v>5</v>
       </c>
       <c r="K81" s="17" t="s">
-        <v>462</v>
+        <v>197</v>
       </c>
       <c r="L81" s="17" t="str" cm="1">
         <f t="array" ref="L81">_xlfn.REGEXEXTRACT(B81,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>txxx.com</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I82)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B82" s="17" t="s">
-        <v>453</v>
+        <v>388</v>
       </c>
       <c r="C82" s="17">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="E82" s="17" t="s">
-        <v>501</v>
+        <v>408</v>
       </c>
       <c r="F82" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G82" s="17" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="H82" s="17" t="s">
-        <v>731</v>
+        <v>416</v>
       </c>
       <c r="I82" s="17" t="s">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="J82" s="17">
         <v>5</v>
       </c>
       <c r="K82" s="17" t="s">
-        <v>464</v>
+        <v>430</v>
       </c>
       <c r="L82" s="17" t="str" cm="1">
         <f t="array" ref="L82">_xlfn.REGEXEXTRACT(B82,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
+        <v>xhamster44.desi</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I83)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B83" s="17" t="s">
-        <v>466</v>
+        <v>381</v>
       </c>
       <c r="C83" s="17">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>110</v>
+        <v>382</v>
       </c>
       <c r="E83" s="17" t="s">
-        <v>467</v>
+        <v>818</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G83" s="17" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="H83" s="17" t="s">
-        <v>732</v>
+        <v>721</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J83" s="17">
         <v>5</v>
       </c>
       <c r="K83" s="17" t="s">
-        <v>469</v>
+        <v>384</v>
       </c>
       <c r="L83" s="17" t="str" cm="1">
         <f t="array" ref="L83">_xlfn.REGEXEXTRACT(B83,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>www.txxx.porn</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I84)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B84" s="17" t="s">
-        <v>68</v>
+        <v>397</v>
       </c>
       <c r="C84" s="17">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>412</v>
+        <v>819</v>
       </c>
       <c r="E84" s="17" t="s">
-        <v>412</v>
+        <v>816</v>
       </c>
       <c r="F84" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G84" s="17" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
       <c r="H84" s="17" t="s">
-        <v>733</v>
+        <v>722</v>
       </c>
       <c r="I84" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J84" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K84" s="17" t="s">
-        <v>376</v>
+        <v>420</v>
       </c>
       <c r="L84" s="17" t="str" cm="1">
         <f t="array" ref="L84">_xlfn.REGEXEXTRACT(B84,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>www.fuq.com</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I85)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B85" s="17" t="s">
-        <v>69</v>
+        <v>450</v>
       </c>
       <c r="C85" s="17">
-        <v>170</v>
+        <v>47</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="E85" s="17" t="s">
-        <v>502</v>
+        <v>455</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="G85" s="17" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="H85" s="17" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J85" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K85" s="17" t="s">
-        <v>373</v>
+        <v>457</v>
       </c>
       <c r="L85" s="17" t="str" cm="1">
         <f t="array" ref="L85">_xlfn.REGEXEXTRACT(B85,"(?&lt;=//)[^/]+")</f>
-        <v>punishbang.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I86)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B86" s="17" t="s">
-        <v>153</v>
+        <v>448</v>
       </c>
       <c r="C86" s="17">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>150</v>
+        <v>378</v>
       </c>
       <c r="E86" s="17" t="s">
-        <v>503</v>
+        <v>496</v>
       </c>
       <c r="F86" s="17" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="G86" s="17" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="H86" s="17" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="I86" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J86" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K86" s="17" t="s">
-        <v>154</v>
+        <v>459</v>
       </c>
       <c r="L86" s="17" t="str" cm="1">
         <f t="array" ref="L86">_xlfn.REGEXEXTRACT(B86,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I87)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B87" s="17" t="s">
-        <v>63</v>
+        <v>461</v>
       </c>
       <c r="C87" s="17">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D87" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E87" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="F87" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E87" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="F87" s="17" t="s">
-        <v>112</v>
-      </c>
       <c r="G87" s="17" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="H87" s="17" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="I87" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J87" s="17">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K87" s="17" t="s">
-        <v>113</v>
+        <v>464</v>
       </c>
       <c r="L87" s="17" t="str" cm="1">
         <f t="array" ref="L87">_xlfn.REGEXEXTRACT(B87,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A88" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I88)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B88" s="17" t="s">
-        <v>164</v>
+        <v>66</v>
       </c>
       <c r="C88" s="17">
-        <v>66</v>
+        <v>182</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>353</v>
+        <v>408</v>
       </c>
       <c r="E88" s="17" t="s">
-        <v>354</v>
+        <v>408</v>
       </c>
       <c r="F88" s="17" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="G88" s="17" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="H88" s="17" t="s">
-        <v>737</v>
+        <v>726</v>
       </c>
       <c r="I88" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J88" s="17">
         <v>4</v>
       </c>
       <c r="K88" s="17" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="L88" s="17" t="str" cm="1">
         <f t="array" ref="L88">_xlfn.REGEXEXTRACT(B88,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>punishbang.com</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I89)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B89" s="17" t="s">
-        <v>175</v>
+        <v>67</v>
       </c>
       <c r="C89" s="17">
-        <v>60</v>
+        <v>170</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>197</v>
+        <v>369</v>
       </c>
       <c r="E89" s="17" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="F89" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G89" s="17" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="H89" s="17" t="s">
-        <v>738</v>
+        <v>727</v>
       </c>
       <c r="I89" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J89" s="17">
         <v>4</v>
       </c>
       <c r="K89" s="17" t="s">
-        <v>336</v>
+        <v>370</v>
       </c>
       <c r="L89" s="17" t="str" cm="1">
         <f t="array" ref="L89">_xlfn.REGEXEXTRACT(B89,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>punishbang.com</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I90)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B90" s="17" t="s">
-        <v>24</v>
+        <v>151</v>
       </c>
       <c r="C90" s="17">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E90" s="17" t="s">
-        <v>505</v>
+        <v>498</v>
       </c>
       <c r="F90" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G90" s="17" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="H90" s="17" t="s">
-        <v>739</v>
+        <v>728</v>
       </c>
       <c r="I90" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J90" s="17">
         <v>4</v>
       </c>
       <c r="K90" s="17" t="s">
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="L90" s="17" t="str" cm="1">
         <f t="array" ref="L90">_xlfn.REGEXEXTRACT(B90,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I91)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B91" s="17" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="C91" s="17">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="E91" s="17" t="s">
-        <v>506</v>
+        <v>109</v>
       </c>
       <c r="F91" s="17" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="G91" s="17" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="H91" s="17" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="I91" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J91" s="17">
         <v>4</v>
       </c>
       <c r="K91" s="17" t="s">
-        <v>331</v>
+        <v>111</v>
       </c>
       <c r="L91" s="17" t="str" cm="1">
         <f t="array" ref="L91">_xlfn.REGEXEXTRACT(B91,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I92)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B92" s="17" t="s">
-        <v>29</v>
+        <v>162</v>
       </c>
       <c r="C92" s="17">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>101</v>
+        <v>350</v>
       </c>
       <c r="E92" s="17" t="s">
-        <v>275</v>
+        <v>351</v>
       </c>
       <c r="F92" s="17" t="s">
-        <v>93</v>
+        <v>222</v>
       </c>
       <c r="G92" s="17" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="H92" s="17" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="I92" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J92" s="17">
         <v>4</v>
       </c>
       <c r="K92" s="17" t="s">
-        <v>103</v>
+        <v>352</v>
       </c>
       <c r="L92" s="17" t="str" cm="1">
         <f t="array" ref="L92">_xlfn.REGEXEXTRACT(B92,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>m.hqporner.com</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I93)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B93" s="17" t="s">
-        <v>49</v>
+        <v>173</v>
       </c>
       <c r="C93" s="17">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>267</v>
+        <v>195</v>
       </c>
       <c r="E93" s="17" t="s">
-        <v>120</v>
+        <v>499</v>
       </c>
       <c r="F93" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G93" s="17" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="H93" s="17" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="I93" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J93" s="17">
         <v>4</v>
       </c>
       <c r="K93" s="17" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="L93" s="17" t="str" cm="1">
         <f t="array" ref="L93">_xlfn.REGEXEXTRACT(B93,"(?&lt;=//)[^/]+")</f>
@@ -6725,158 +6786,158 @@
     </row>
     <row r="94" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I94)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B94" s="17" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C94" s="17">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="E94" s="17" t="s">
-        <v>312</v>
+        <v>500</v>
       </c>
       <c r="F94" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G94" s="17" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="H94" s="17" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="I94" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J94" s="17">
         <v>4</v>
       </c>
       <c r="K94" s="17" t="s">
-        <v>314</v>
+        <v>95</v>
       </c>
       <c r="L94" s="17" t="str" cm="1">
         <f t="array" ref="L94">_xlfn.REGEXEXTRACT(B94,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I95)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B95" s="17" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C95" s="17">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>212</v>
+        <v>96</v>
       </c>
       <c r="E95" s="17" t="s">
-        <v>412</v>
+        <v>501</v>
       </c>
       <c r="F95" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G95" s="17" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="H95" s="17" t="s">
-        <v>744</v>
+        <v>733</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J95" s="17">
         <v>4</v>
       </c>
       <c r="K95" s="17" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="L95" s="17" t="str" cm="1">
         <f t="array" ref="L95">_xlfn.REGEXEXTRACT(B95,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.party</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I96)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B96" s="17" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="C96" s="17">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E96" s="17" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="F96" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G96" s="17" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="H96" s="17" t="s">
-        <v>745</v>
+        <v>734</v>
       </c>
       <c r="I96" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J96" s="17">
         <v>4</v>
       </c>
       <c r="K96" s="17" t="s">
-        <v>293</v>
+        <v>101</v>
       </c>
       <c r="L96" s="17" t="str" cm="1">
         <f t="array" ref="L96">_xlfn.REGEXEXTRACT(B96,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I97)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B97" s="17" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C97" s="17">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="D97" s="17" t="s">
-        <v>102</v>
+        <v>265</v>
       </c>
       <c r="E97" s="17" t="s">
-        <v>285</v>
+        <v>118</v>
       </c>
       <c r="F97" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G97" s="17" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="H97" s="17" t="s">
-        <v>746</v>
+        <v>735</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J97" s="17">
         <v>4</v>
       </c>
       <c r="K97" s="17" t="s">
-        <v>286</v>
+        <v>311</v>
       </c>
       <c r="L97" s="17" t="str" cm="1">
         <f t="array" ref="L97">_xlfn.REGEXEXTRACT(B97,"(?&lt;=//)[^/]+")</f>
@@ -6885,1318 +6946,1318 @@
     </row>
     <row r="98" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I98)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B98" s="17" t="s">
         <v>16</v>
       </c>
       <c r="C98" s="17">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D98" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E98" s="17" t="s">
-        <v>278</v>
+        <v>310</v>
       </c>
       <c r="F98" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G98" s="17" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="H98" s="17" t="s">
-        <v>747</v>
+        <v>736</v>
       </c>
       <c r="I98" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J98" s="17">
         <v>4</v>
       </c>
       <c r="K98" s="17" t="s">
-        <v>279</v>
+        <v>312</v>
       </c>
       <c r="L98" s="17" t="str" cm="1">
         <f t="array" ref="L98">_xlfn.REGEXEXTRACT(B98,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I99)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B99" s="17" t="s">
-        <v>173</v>
+        <v>7</v>
       </c>
       <c r="C99" s="17">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="D99" s="17" t="s">
-        <v>412</v>
+        <v>210</v>
       </c>
       <c r="E99" s="17" t="s">
-        <v>507</v>
+        <v>408</v>
       </c>
       <c r="F99" s="17" t="s">
-        <v>282</v>
+        <v>91</v>
       </c>
       <c r="G99" s="17" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
       <c r="H99" s="17" t="s">
-        <v>748</v>
+        <v>737</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J99" s="17">
         <v>4</v>
       </c>
       <c r="K99" s="17" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="L99" s="17" t="str" cm="1">
         <f t="array" ref="L99">_xlfn.REGEXEXTRACT(B99,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.com</v>
+        <v>spankbang.party</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I100)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B100" s="17" t="s">
-        <v>159</v>
+        <v>58</v>
       </c>
       <c r="C100" s="17">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D100" s="17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E100" s="17" t="s">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="F100" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G100" s="17" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="H100" s="17" t="s">
-        <v>749</v>
+        <v>738</v>
       </c>
       <c r="I100" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J100" s="17">
         <v>4</v>
       </c>
       <c r="K100" s="17" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="L100" s="17" t="str" cm="1">
         <f t="array" ref="L100">_xlfn.REGEXEXTRACT(B100,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I101)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B101" s="17" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C101" s="17">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D101" s="17" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E101" s="17" t="s">
-        <v>120</v>
+        <v>283</v>
       </c>
       <c r="F101" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G101" s="17" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="H101" s="17" t="s">
-        <v>750</v>
+        <v>739</v>
       </c>
       <c r="I101" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J101" s="17">
         <v>4</v>
       </c>
       <c r="K101" s="17" t="s">
-        <v>196</v>
+        <v>284</v>
       </c>
       <c r="L101" s="17" t="str" cm="1">
         <f t="array" ref="L101">_xlfn.REGEXEXTRACT(B101,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I102)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B102" s="17" t="s">
-        <v>190</v>
+        <v>14</v>
       </c>
       <c r="C102" s="17">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="D102" s="17" t="s">
-        <v>220</v>
+        <v>99</v>
       </c>
       <c r="E102" s="17" t="s">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="F102" s="17" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="G102" s="17" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="H102" s="17" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="I102" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J102" s="17">
         <v>4</v>
       </c>
       <c r="K102" s="17" t="s">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="L102" s="17" t="str" cm="1">
         <f t="array" ref="L102">_xlfn.REGEXEXTRACT(B102,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I103)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B103" s="17" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C103" s="17">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D103" s="17" t="s">
-        <v>241</v>
+        <v>408</v>
       </c>
       <c r="E103" s="17" t="s">
-        <v>242</v>
+        <v>502</v>
       </c>
       <c r="F103" s="17" t="s">
-        <v>237</v>
+        <v>280</v>
       </c>
       <c r="G103" s="17" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="H103" s="17" t="s">
-        <v>109</v>
+        <v>741</v>
       </c>
       <c r="I103" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J103" s="17">
         <v>4</v>
       </c>
       <c r="K103" s="17" t="s">
-        <v>243</v>
+        <v>281</v>
       </c>
       <c r="L103" s="17" t="str" cm="1">
         <f t="array" ref="L103">_xlfn.REGEXEXTRACT(B103,"(?&lt;=//)[^/]+")</f>
-        <v>txxx.me</v>
+        <v>txxx.com</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I104)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B104" s="17" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C104" s="17">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="D104" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E104" s="17" t="s">
-        <v>508</v>
+        <v>258</v>
       </c>
       <c r="F104" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G104" s="17" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="H104" s="17" t="s">
-        <v>752</v>
+        <v>742</v>
       </c>
       <c r="I104" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J104" s="17">
         <v>4</v>
       </c>
       <c r="K104" s="17" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
       <c r="L104" s="17" t="str" cm="1">
         <f t="array" ref="L104">_xlfn.REGEXEXTRACT(B104,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I105)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B105" s="17" t="s">
-        <v>409</v>
+        <v>45</v>
       </c>
       <c r="C105" s="17">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D105" s="17" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="E105" s="17" t="s">
-        <v>411</v>
+        <v>118</v>
       </c>
       <c r="F105" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G105" s="17" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="H105" s="17" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
       <c r="I105" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J105" s="17">
         <v>4</v>
       </c>
       <c r="K105" s="17" t="s">
-        <v>442</v>
+        <v>194</v>
       </c>
       <c r="L105" s="17" t="str" cm="1">
         <f t="array" ref="L105">_xlfn.REGEXEXTRACT(B105,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="106" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="17" t="str">
-        <f t="shared" ref="A106:A137" si="4">IF(ISBLANK(I106)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I106)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B106" s="17" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C106" s="17">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D106" s="17" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E106" s="17" t="s">
-        <v>211</v>
+        <v>247</v>
       </c>
       <c r="F106" s="17" t="s">
-        <v>93</v>
+        <v>222</v>
       </c>
       <c r="G106" s="17" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="H106" s="17" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="I106" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J106" s="17">
         <v>4</v>
       </c>
       <c r="K106" s="17" t="s">
-        <v>214</v>
+        <v>248</v>
       </c>
       <c r="L106" s="17" t="str" cm="1">
         <f t="array" ref="L106">_xlfn.REGEXEXTRACT(B106,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>pornxp.com</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I107)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B107" s="17" t="s">
-        <v>4</v>
+        <v>177</v>
       </c>
       <c r="C107" s="17">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D107" s="17" t="s">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="E107" s="17" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="F107" s="17" t="s">
-        <v>93</v>
+        <v>235</v>
       </c>
       <c r="G107" s="17" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="H107" s="17" t="s">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="I107" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J107" s="17">
         <v>4</v>
       </c>
       <c r="K107" s="17" t="s">
-        <v>213</v>
+        <v>241</v>
       </c>
       <c r="L107" s="17" t="str" cm="1">
         <f t="array" ref="L107">_xlfn.REGEXEXTRACT(B107,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>txxx.me</v>
       </c>
     </row>
     <row r="108" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I108)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B108" s="17" t="s">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="C108" s="17">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D108" s="17" t="s">
-        <v>206</v>
+        <v>96</v>
       </c>
       <c r="E108" s="17" t="s">
-        <v>106</v>
+        <v>503</v>
       </c>
       <c r="F108" s="17" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="G108" s="17" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="H108" s="17" t="s">
-        <v>755</v>
+        <v>745</v>
       </c>
       <c r="I108" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J108" s="17">
         <v>4</v>
       </c>
       <c r="K108" s="17" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="L108" s="17" t="str" cm="1">
         <f t="array" ref="L108">_xlfn.REGEXEXTRACT(B108,"(?&lt;=//)[^/]+")</f>
-        <v>www.porndead.org</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I109)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B109" s="17" t="s">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="C109" s="17">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D109" s="17" t="s">
-        <v>271</v>
+        <v>154</v>
       </c>
       <c r="E109" s="17" t="s">
-        <v>201</v>
+        <v>407</v>
       </c>
       <c r="F109" s="17" t="s">
-        <v>225</v>
+        <v>110</v>
       </c>
       <c r="G109" s="17" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="H109" s="17" t="s">
-        <v>756</v>
+        <v>746</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J109" s="17">
         <v>4</v>
       </c>
       <c r="K109" s="17" t="s">
-        <v>202</v>
+        <v>438</v>
       </c>
       <c r="L109" s="17" t="str" cm="1">
         <f t="array" ref="L109">_xlfn.REGEXEXTRACT(B109,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster18.desi</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A110" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I110)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B110" s="17" t="s">
-        <v>9</v>
+        <v>183</v>
       </c>
       <c r="C110" s="17">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D110" s="17" t="s">
-        <v>446</v>
+        <v>210</v>
       </c>
       <c r="E110" s="17" t="s">
-        <v>343</v>
+        <v>209</v>
       </c>
       <c r="F110" s="17" t="s">
-        <v>418</v>
+        <v>91</v>
       </c>
       <c r="G110" s="17" t="s">
-        <v>521</v>
+        <v>613</v>
       </c>
       <c r="H110" s="17" t="s">
-        <v>521</v>
+        <v>747</v>
       </c>
       <c r="I110" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J110" s="17">
         <v>4</v>
       </c>
       <c r="K110" s="17" t="s">
-        <v>348</v>
+        <v>212</v>
       </c>
       <c r="L110" s="17" t="str" cm="1">
         <f t="array" ref="L110">_xlfn.REGEXEXTRACT(B110,"(?&lt;=//)[^/]+")</f>
-        <v>netfapx.net</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I111)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B111" s="17" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C111" s="17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D111" s="17" t="s">
-        <v>446</v>
+        <v>210</v>
       </c>
       <c r="E111" s="17" t="s">
-        <v>343</v>
+        <v>208</v>
       </c>
       <c r="F111" s="17" t="s">
-        <v>418</v>
+        <v>91</v>
       </c>
       <c r="G111" s="17" t="s">
-        <v>521</v>
+        <v>614</v>
       </c>
       <c r="H111" s="17" t="s">
-        <v>521</v>
+        <v>259</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J111" s="17">
         <v>4</v>
       </c>
       <c r="K111" s="17" t="s">
-        <v>351</v>
+        <v>211</v>
       </c>
       <c r="L111" s="17" t="str" cm="1">
         <f t="array" ref="L111">_xlfn.REGEXEXTRACT(B111,"(?&lt;=//)[^/]+")</f>
-        <v>pornzog</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I112)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B112" s="17" t="s">
-        <v>388</v>
+        <v>190</v>
       </c>
       <c r="C112" s="17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D112" s="17" t="s">
-        <v>446</v>
+        <v>204</v>
       </c>
       <c r="E112" s="17" t="s">
-        <v>343</v>
+        <v>104</v>
       </c>
       <c r="F112" s="17" t="s">
-        <v>112</v>
+        <v>222</v>
       </c>
       <c r="G112" s="17" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="H112" s="17" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="I112" s="17" t="s">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="J112" s="17">
         <v>4</v>
       </c>
       <c r="K112" s="17" t="s">
-        <v>389</v>
+        <v>205</v>
       </c>
       <c r="L112" s="17" t="str" cm="1">
         <f t="array" ref="L112">_xlfn.REGEXEXTRACT(B112,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubegalore.com</v>
+        <v>www.porndead.org</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I113)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B113" s="17" t="s">
-        <v>451</v>
+        <v>0</v>
       </c>
       <c r="C113" s="17">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="D113" s="17" t="s">
-        <v>381</v>
+        <v>269</v>
       </c>
       <c r="E113" s="17" t="s">
-        <v>456</v>
+        <v>199</v>
       </c>
       <c r="F113" s="17" t="s">
-        <v>112</v>
+        <v>223</v>
       </c>
       <c r="G113" s="17" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="H113" s="17" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J113" s="17">
         <v>4</v>
       </c>
       <c r="K113" s="17" t="s">
-        <v>457</v>
+        <v>200</v>
       </c>
       <c r="L113" s="17" t="str" cm="1">
         <f t="array" ref="L113">_xlfn.REGEXEXTRACT(B113,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="114" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>xhamster18.desi</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A114" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I114)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B114" s="17" t="s">
-        <v>454</v>
+        <v>821</v>
       </c>
       <c r="C114" s="17">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="D114" s="17" t="s">
-        <v>381</v>
+        <v>819</v>
       </c>
       <c r="E114" s="17" t="s">
-        <v>509</v>
+        <v>816</v>
       </c>
       <c r="F114" s="17" t="s">
-        <v>112</v>
+        <v>414</v>
       </c>
       <c r="G114" s="17" t="s">
-        <v>624</v>
+        <v>820</v>
       </c>
       <c r="H114" s="17" t="s">
-        <v>758</v>
+        <v>691</v>
       </c>
       <c r="I114" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J114" s="17">
         <v>4</v>
       </c>
       <c r="K114" s="17" t="s">
-        <v>463</v>
+        <v>345</v>
       </c>
       <c r="L114" s="17" t="str" cm="1">
         <f t="array" ref="L114">_xlfn.REGEXEXTRACT(B114,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntry.com</v>
-      </c>
-    </row>
-    <row r="115" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>netfapx.net</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I115)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B115" s="17" t="s">
-        <v>390</v>
+        <v>822</v>
       </c>
       <c r="C115" s="17">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D115" s="17" t="s">
-        <v>412</v>
+        <v>819</v>
       </c>
       <c r="E115" s="17" t="s">
-        <v>494</v>
+        <v>816</v>
       </c>
       <c r="F115" s="17" t="s">
-        <v>112</v>
+        <v>414</v>
       </c>
       <c r="G115" s="17" t="s">
-        <v>625</v>
+        <v>820</v>
       </c>
       <c r="H115" s="17" t="s">
-        <v>759</v>
+        <v>691</v>
       </c>
       <c r="I115" s="17" t="s">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="J115" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K115" s="17" t="s">
-        <v>394</v>
+        <v>348</v>
       </c>
       <c r="L115" s="17" t="str" cm="1">
         <f t="array" ref="L115">_xlfn.REGEXEXTRACT(B115,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="116" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>pornzog.com</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I116)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B116" s="17" t="s">
-        <v>36</v>
+        <v>385</v>
       </c>
       <c r="C116" s="17">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="D116" s="17" t="s">
-        <v>152</v>
+        <v>819</v>
       </c>
       <c r="E116" s="17" t="s">
-        <v>277</v>
+        <v>816</v>
       </c>
       <c r="F116" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G116" s="17" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="H116" s="17" t="s">
-        <v>760</v>
+        <v>750</v>
       </c>
       <c r="I116" s="17" t="s">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="J116" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K116" s="17" t="s">
-        <v>137</v>
+        <v>386</v>
       </c>
       <c r="L116" s="17" t="str" cm="1">
         <f t="array" ref="L116">_xlfn.REGEXEXTRACT(B116,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>www.tubegalore.com</v>
       </c>
     </row>
     <row r="117" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I117)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B117" s="17" t="s">
-        <v>188</v>
+        <v>446</v>
       </c>
       <c r="C117" s="17">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D117" s="17" t="s">
-        <v>98</v>
+        <v>378</v>
       </c>
       <c r="E117" s="17" t="s">
-        <v>245</v>
+        <v>451</v>
       </c>
       <c r="F117" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G117" s="17" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="H117" s="17" t="s">
-        <v>109</v>
+        <v>725</v>
       </c>
       <c r="I117" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J117" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K117" s="17" t="s">
-        <v>316</v>
+        <v>452</v>
       </c>
       <c r="L117" s="17" t="str" cm="1">
         <f t="array" ref="L117">_xlfn.REGEXEXTRACT(B117,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
-      </c>
-    </row>
-    <row r="118" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>www.porntry.com</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I118)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B118" s="17" t="s">
-        <v>62</v>
+        <v>449</v>
       </c>
       <c r="C118" s="17">
-        <v>77</v>
+        <v>42</v>
       </c>
       <c r="D118" s="17" t="s">
-        <v>101</v>
+        <v>378</v>
       </c>
       <c r="E118" s="17" t="s">
-        <v>356</v>
+        <v>504</v>
       </c>
       <c r="F118" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G118" s="17" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="H118" s="17" t="s">
-        <v>761</v>
+        <v>751</v>
       </c>
       <c r="I118" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J118" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K118" s="17" t="s">
-        <v>358</v>
+        <v>458</v>
       </c>
       <c r="L118" s="17" t="str" cm="1">
         <f t="array" ref="L118">_xlfn.REGEXEXTRACT(B118,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>www.porntry.com</v>
       </c>
     </row>
     <row r="119" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I119)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B119" s="17" t="s">
-        <v>64</v>
+        <v>387</v>
       </c>
       <c r="C119" s="17">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="D119" s="17" t="s">
-        <v>270</v>
+        <v>408</v>
       </c>
       <c r="E119" s="17" t="s">
-        <v>510</v>
+        <v>489</v>
       </c>
       <c r="F119" s="17" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="G119" s="17" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="H119" s="17" t="s">
-        <v>762</v>
+        <v>752</v>
       </c>
       <c r="I119" s="17" t="s">
-        <v>84</v>
+        <v>372</v>
       </c>
       <c r="J119" s="17">
         <v>3</v>
       </c>
       <c r="K119" s="17" t="s">
-        <v>142</v>
+        <v>390</v>
       </c>
       <c r="L119" s="17" t="str" cm="1">
         <f t="array" ref="L119">_xlfn.REGEXEXTRACT(B119,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="120" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I120)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B120" s="17" t="s">
-        <v>310</v>
+        <v>34</v>
       </c>
       <c r="C120" s="17">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="D120" s="17" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="E120" s="17" t="s">
-        <v>311</v>
+        <v>275</v>
       </c>
       <c r="F120" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G120" s="17" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="H120" s="17" t="s">
-        <v>705</v>
+        <v>753</v>
       </c>
       <c r="I120" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J120" s="17">
         <v>3</v>
       </c>
       <c r="K120" s="17" t="s">
-        <v>416</v>
+        <v>135</v>
       </c>
       <c r="L120" s="17" t="str" cm="1">
         <f t="array" ref="L120">_xlfn.REGEXEXTRACT(B120,"(?&lt;=//)[^/]+")</f>
-        <v>pervtube.net</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="121" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I121)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B121" s="17" t="s">
-        <v>116</v>
+        <v>186</v>
       </c>
       <c r="C121" s="17">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D121" s="17" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E121" s="17" t="s">
-        <v>117</v>
+        <v>243</v>
       </c>
       <c r="F121" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G121" s="17" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="H121" s="17" t="s">
-        <v>732</v>
+        <v>107</v>
       </c>
       <c r="I121" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J121" s="17">
         <v>3</v>
       </c>
       <c r="K121" s="17" t="s">
-        <v>145</v>
+        <v>314</v>
       </c>
       <c r="L121" s="17" t="str" cm="1">
         <f t="array" ref="L121">_xlfn.REGEXEXTRACT(B121,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>curebdsm.com</v>
       </c>
     </row>
     <row r="122" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I122)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B122" s="17" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="C122" s="17">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="D122" s="17" t="s">
-        <v>197</v>
+        <v>99</v>
       </c>
       <c r="E122" s="17" t="s">
-        <v>290</v>
+        <v>353</v>
       </c>
       <c r="F122" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G122" s="17" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="H122" s="17" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="I122" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J122" s="17">
         <v>3</v>
       </c>
       <c r="K122" s="17" t="s">
-        <v>291</v>
+        <v>355</v>
       </c>
       <c r="L122" s="17" t="str" cm="1">
         <f t="array" ref="L122">_xlfn.REGEXEXTRACT(B122,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="123" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I123)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B123" s="17" t="s">
-        <v>415</v>
+        <v>62</v>
       </c>
       <c r="C123" s="17">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="D123" s="17" t="s">
-        <v>412</v>
+        <v>268</v>
       </c>
       <c r="E123" s="17" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="F123" s="17" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
       <c r="G123" s="17" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
       <c r="H123" s="17" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="I123" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J123" s="17">
         <v>3</v>
       </c>
       <c r="K123" s="17" t="s">
-        <v>297</v>
+        <v>140</v>
       </c>
       <c r="L123" s="17" t="str" cm="1">
         <f t="array" ref="L123">_xlfn.REGEXEXTRACT(B123,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="124" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I124)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B124" s="17" t="s">
-        <v>122</v>
+        <v>308</v>
       </c>
       <c r="C124" s="17">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D124" s="17" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E124" s="17" t="s">
-        <v>124</v>
+        <v>309</v>
       </c>
       <c r="F124" s="17" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="G124" s="17" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="H124" s="17" t="s">
-        <v>765</v>
+        <v>698</v>
       </c>
       <c r="I124" s="17" t="s">
-        <v>131</v>
+        <v>82</v>
       </c>
       <c r="J124" s="17">
         <v>3</v>
       </c>
       <c r="K124" s="17" t="s">
-        <v>146</v>
+        <v>412</v>
       </c>
       <c r="L124" s="17" t="str" cm="1">
         <f t="array" ref="L124">_xlfn.REGEXEXTRACT(B124,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
-      </c>
-    </row>
-    <row r="125" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>pervtube.net</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I125)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B125" s="17" t="s">
-        <v>178</v>
+        <v>114</v>
       </c>
       <c r="C125" s="17">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D125" s="17" t="s">
-        <v>280</v>
+        <v>108</v>
       </c>
       <c r="E125" s="17" t="s">
-        <v>239</v>
+        <v>115</v>
       </c>
       <c r="F125" s="17" t="s">
-        <v>224</v>
+        <v>110</v>
       </c>
       <c r="G125" s="17" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="H125" s="17" t="s">
-        <v>766</v>
+        <v>725</v>
       </c>
       <c r="I125" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J125" s="17">
         <v>3</v>
       </c>
       <c r="K125" s="17" t="s">
-        <v>281</v>
+        <v>143</v>
       </c>
       <c r="L125" s="17" t="str" cm="1">
         <f t="array" ref="L125">_xlfn.REGEXEXTRACT(B125,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
-      </c>
-    </row>
-    <row r="126" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I126)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B126" s="17" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C126" s="17">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D126" s="17" t="s">
-        <v>263</v>
+        <v>195</v>
       </c>
       <c r="E126" s="17" t="s">
-        <v>106</v>
+        <v>288</v>
       </c>
       <c r="F126" s="17" t="s">
-        <v>224</v>
+        <v>91</v>
       </c>
       <c r="G126" s="17" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="H126" s="17" t="s">
-        <v>767</v>
+        <v>756</v>
       </c>
       <c r="I126" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J126" s="17">
         <v>3</v>
       </c>
       <c r="K126" s="17" t="s">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="L126" s="17" t="str" cm="1">
         <f t="array" ref="L126">_xlfn.REGEXEXTRACT(B126,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="127" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I127)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B127" s="17" t="s">
-        <v>193</v>
+        <v>411</v>
       </c>
       <c r="C127" s="17">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>251</v>
+        <v>408</v>
       </c>
       <c r="E127" s="17" t="s">
-        <v>252</v>
+        <v>506</v>
       </c>
       <c r="F127" s="17" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="G127" s="17" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="H127" s="17" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
       <c r="I127" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J127" s="17">
         <v>3</v>
       </c>
       <c r="K127" s="17" t="s">
-        <v>253</v>
+        <v>295</v>
       </c>
       <c r="L127" s="17" t="str" cm="1">
         <f t="array" ref="L127">_xlfn.REGEXEXTRACT(B127,"(?&lt;=//)[^/]+")</f>
-        <v>pornxp.com</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>spankbang.com</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I128)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B128" s="17" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="C128" s="17">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D128" s="17" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="E128" s="17" t="s">
-        <v>512</v>
+        <v>122</v>
       </c>
       <c r="F128" s="17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G128" s="17" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="H128" s="17" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
       <c r="I128" s="17" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="J128" s="17">
         <v>3</v>
       </c>
       <c r="K128" s="17" t="s">
-        <v>244</v>
+        <v>144</v>
       </c>
       <c r="L128" s="17" t="str" cm="1">
         <f t="array" ref="L128">_xlfn.REGEXEXTRACT(B128,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmstreak.com</v>
       </c>
     </row>
     <row r="129" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I129)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B129" s="17" t="s">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="C129" s="17">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D129" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="E129" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="F129" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="E129" s="17" t="s">
-        <v>513</v>
-      </c>
-      <c r="F129" s="17" t="s">
-        <v>237</v>
-      </c>
       <c r="G129" s="17" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="H129" s="17" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="I129" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J129" s="17">
         <v>3</v>
       </c>
       <c r="K129" s="17" t="s">
-        <v>236</v>
+        <v>279</v>
       </c>
       <c r="L129" s="17" t="str" cm="1">
         <f t="array" ref="L129">_xlfn.REGEXEXTRACT(B129,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>spankbang.com</v>
       </c>
     </row>
     <row r="130" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I130)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B130" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C130" s="17">
         <v>42</v>
       </c>
-      <c r="C130" s="17">
-        <v>30</v>
-      </c>
       <c r="D130" s="17" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="E130" s="17" t="s">
-        <v>239</v>
+        <v>104</v>
       </c>
       <c r="F130" s="17" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G130" s="17" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
       <c r="H130" s="17" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
       <c r="I130" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J130" s="17">
         <v>3</v>
       </c>
       <c r="K130" s="17" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="L130" s="17" t="str" cm="1">
         <f t="array" ref="L130">_xlfn.REGEXEXTRACT(B130,"(?&lt;=//)[^/]+")</f>
@@ -8205,798 +8266,798 @@
     </row>
     <row r="131" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I131)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B131" s="17" t="s">
-        <v>2</v>
+        <v>191</v>
       </c>
       <c r="C131" s="17">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="D131" s="17" t="s">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="E131" s="17" t="s">
-        <v>106</v>
+        <v>250</v>
       </c>
       <c r="F131" s="17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G131" s="17" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="H131" s="17" t="s">
-        <v>772</v>
+        <v>761</v>
       </c>
       <c r="I131" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J131" s="17">
         <v>3</v>
       </c>
       <c r="K131" s="17" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="L131" s="17" t="str" cm="1">
         <f t="array" ref="L131">_xlfn.REGEXEXTRACT(B131,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>pornxp.com</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I132)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B132" s="17" t="s">
-        <v>161</v>
+        <v>70</v>
       </c>
       <c r="C132" s="17">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D132" s="17" t="s">
-        <v>98</v>
+        <v>126</v>
       </c>
       <c r="E132" s="17" t="s">
-        <v>273</v>
+        <v>507</v>
       </c>
       <c r="F132" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G132" s="17" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="H132" s="17" t="s">
-        <v>773</v>
+        <v>762</v>
       </c>
       <c r="I132" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J132" s="17">
         <v>3</v>
       </c>
       <c r="K132" s="17" t="s">
-        <v>218</v>
+        <v>242</v>
       </c>
       <c r="L132" s="17" t="str" cm="1">
         <f t="array" ref="L132">_xlfn.REGEXEXTRACT(B132,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I133)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B133" s="17" t="s">
-        <v>127</v>
+        <v>72</v>
       </c>
       <c r="C133" s="17">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D133" s="17" t="s">
-        <v>128</v>
+        <v>220</v>
       </c>
       <c r="E133" s="17" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="F133" s="17" t="s">
-        <v>94</v>
+        <v>235</v>
       </c>
       <c r="G133" s="17" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="H133" s="17" t="s">
-        <v>148</v>
+        <v>763</v>
       </c>
       <c r="I133" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J133" s="17">
         <v>3</v>
       </c>
       <c r="K133" s="17" t="s">
-        <v>149</v>
+        <v>234</v>
       </c>
       <c r="L133" s="17" t="str" cm="1">
         <f t="array" ref="L133">_xlfn.REGEXEXTRACT(B133,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="134" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>tube.perverzija.com</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A134" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I134)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B134" s="17" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C134" s="17">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D134" s="17" t="s">
-        <v>212</v>
+        <v>236</v>
       </c>
       <c r="E134" s="17" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="F134" s="17" t="s">
-        <v>93</v>
+        <v>223</v>
       </c>
       <c r="G134" s="17" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="H134" s="17" t="s">
-        <v>95</v>
+        <v>764</v>
       </c>
       <c r="I134" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J134" s="17">
         <v>3</v>
       </c>
       <c r="K134" s="17" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
       <c r="L134" s="17" t="str" cm="1">
         <f t="array" ref="L134">_xlfn.REGEXEXTRACT(B134,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhub.com</v>
       </c>
     </row>
     <row r="135" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I135)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B135" s="17" t="s">
-        <v>189</v>
+        <v>2</v>
       </c>
       <c r="C135" s="17">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="E135" s="17" t="s">
-        <v>204</v>
+        <v>104</v>
       </c>
       <c r="F135" s="17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G135" s="17" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="H135" s="17" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="I135" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J135" s="17">
         <v>3</v>
       </c>
       <c r="K135" s="17" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="L135" s="17" t="str" cm="1">
         <f t="array" ref="L135">_xlfn.REGEXEXTRACT(B135,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
-      </c>
-    </row>
-    <row r="136" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I136)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B136" s="17" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="C136" s="17">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="E136" s="17" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F136" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G136" s="17" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="H136" s="17" t="s">
-        <v>88</v>
+        <v>766</v>
       </c>
       <c r="I136" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J136" s="17">
         <v>3</v>
       </c>
       <c r="K136" s="17" t="s">
-        <v>90</v>
+        <v>216</v>
       </c>
       <c r="L136" s="17" t="str" cm="1">
         <f t="array" ref="L136">_xlfn.REGEXEXTRACT(B136,"(?&lt;=//)[^/]+")</f>
-        <v>anyporn.com</v>
-      </c>
-    </row>
-    <row r="137" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(I137)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B137" s="17" t="s">
-        <v>427</v>
+        <v>125</v>
       </c>
       <c r="C137" s="17">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="D137" s="17" t="s">
-        <v>412</v>
+        <v>126</v>
       </c>
       <c r="E137" s="17" t="s">
-        <v>412</v>
+        <v>509</v>
       </c>
       <c r="F137" s="17" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="G137" s="17" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="H137" s="17" t="s">
-        <v>265</v>
+        <v>146</v>
       </c>
       <c r="I137" s="17" t="s">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="J137" s="17">
         <v>3</v>
       </c>
       <c r="K137" s="17" t="s">
-        <v>437</v>
+        <v>147</v>
       </c>
       <c r="L137" s="17" t="str" cm="1">
         <f t="array" ref="L137">_xlfn.REGEXEXTRACT(B137,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="138" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="17" t="str">
-        <f t="shared" ref="A138:A154" si="5">IF(ISBLANK(I138)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I138)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B138" s="17" t="s">
-        <v>408</v>
+        <v>6</v>
       </c>
       <c r="C138" s="17">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D138" s="17" t="s">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="E138" s="17" t="s">
-        <v>410</v>
+        <v>213</v>
       </c>
       <c r="F138" s="17" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="G138" s="17" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="H138" s="17" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="I138" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J138" s="17">
         <v>3</v>
       </c>
       <c r="K138" s="17" t="s">
-        <v>435</v>
+        <v>214</v>
       </c>
       <c r="L138" s="17" t="str" cm="1">
         <f t="array" ref="L138">_xlfn.REGEXEXTRACT(B138,"(?&lt;=//)[^/]+")</f>
-        <v>www.porntopedia.com</v>
-      </c>
-    </row>
-    <row r="139" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I139)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B139" s="17" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C139" s="17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D139" s="17" t="s">
-        <v>446</v>
+        <v>201</v>
       </c>
       <c r="E139" s="17" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="F139" s="17" t="s">
-        <v>93</v>
+        <v>222</v>
       </c>
       <c r="G139" s="17" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="H139" s="17" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="I139" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J139" s="17">
         <v>3</v>
       </c>
       <c r="K139" s="17" t="s">
-        <v>346</v>
+        <v>203</v>
       </c>
       <c r="L139" s="17" t="str" cm="1">
         <f t="array" ref="L139">_xlfn.REGEXEXTRACT(B139,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>www.tnaflix.com</v>
       </c>
     </row>
     <row r="140" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I140)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B140" s="17" t="s">
-        <v>183</v>
+        <v>38</v>
       </c>
       <c r="C140" s="17">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D140" s="17" t="s">
-        <v>446</v>
+        <v>87</v>
       </c>
       <c r="E140" s="17" t="s">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="F140" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G140" s="17" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="H140" s="17" t="s">
-        <v>776</v>
+        <v>86</v>
       </c>
       <c r="I140" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J140" s="17">
         <v>3</v>
       </c>
       <c r="K140" s="17" t="s">
-        <v>347</v>
+        <v>88</v>
       </c>
       <c r="L140" s="17" t="str" cm="1">
         <f t="array" ref="L140">_xlfn.REGEXEXTRACT(B140,"(?&lt;=//)[^/]+")</f>
-        <v>curebdsm.com</v>
+        <v>anyporn.com</v>
       </c>
     </row>
     <row r="141" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I141)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B141" s="17" t="s">
-        <v>172</v>
+        <v>423</v>
       </c>
       <c r="C141" s="17">
-        <v>64</v>
+        <v>5</v>
       </c>
       <c r="D141" s="17" t="s">
-        <v>338</v>
+        <v>408</v>
       </c>
       <c r="E141" s="17" t="s">
-        <v>340</v>
+        <v>408</v>
       </c>
       <c r="F141" s="17" t="s">
-        <v>224</v>
+        <v>110</v>
       </c>
       <c r="G141" s="17" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="H141" s="17" t="s">
-        <v>777</v>
+        <v>263</v>
       </c>
       <c r="I141" s="17" t="s">
-        <v>84</v>
+        <v>432</v>
       </c>
       <c r="J141" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K141" s="17" t="s">
-        <v>339</v>
+        <v>433</v>
       </c>
       <c r="L141" s="17" t="str" cm="1">
         <f t="array" ref="L141">_xlfn.REGEXEXTRACT(B141,"(?&lt;=//)[^/]+")</f>
-        <v>www.peekvids.com</v>
-      </c>
-    </row>
-    <row r="142" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A142" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I142)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B142" s="17" t="s">
-        <v>71</v>
+        <v>404</v>
       </c>
       <c r="C142" s="17">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="D142" s="17" t="s">
-        <v>327</v>
+        <v>108</v>
       </c>
       <c r="E142" s="17" t="s">
-        <v>328</v>
+        <v>406</v>
       </c>
       <c r="F142" s="17" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="G142" s="17" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="H142" s="17" t="s">
-        <v>778</v>
+        <v>107</v>
       </c>
       <c r="I142" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J142" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K142" s="17" t="s">
-        <v>329</v>
+        <v>431</v>
       </c>
       <c r="L142" s="17" t="str" cm="1">
         <f t="array" ref="L142">_xlfn.REGEXEXTRACT(B142,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="143" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>www.porntopedia.com</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I143)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B143" s="17" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C143" s="17">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D143" s="17" t="s">
-        <v>289</v>
+        <v>819</v>
       </c>
       <c r="E143" s="17" t="s">
-        <v>515</v>
+        <v>209</v>
       </c>
       <c r="F143" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G143" s="17" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="H143" s="17" t="s">
-        <v>779</v>
+        <v>768</v>
       </c>
       <c r="I143" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J143" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K143" s="17" t="s">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="L143" s="17" t="str" cm="1">
         <f t="array" ref="L143">_xlfn.REGEXEXTRACT(B143,"(?&lt;=//)[^/]+")</f>
-        <v>www.omg.xxx</v>
+        <v>curebdsm.com</v>
       </c>
     </row>
     <row r="144" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I144)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B144" s="17" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="C144" s="17">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="D144" s="17" t="s">
-        <v>150</v>
+        <v>819</v>
       </c>
       <c r="E144" s="17" t="s">
-        <v>516</v>
+        <v>243</v>
       </c>
       <c r="F144" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G144" s="17" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="H144" s="17" t="s">
-        <v>780</v>
+        <v>769</v>
       </c>
       <c r="I144" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J144" s="17">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K144" s="17" t="s">
-        <v>299</v>
+        <v>344</v>
       </c>
       <c r="L144" s="17" t="str" cm="1">
         <f t="array" ref="L144">_xlfn.REGEXEXTRACT(B144,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>curebdsm.com</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I145)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B145" s="17" t="s">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="C145" s="17">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="D145" s="17" t="s">
-        <v>101</v>
+        <v>336</v>
       </c>
       <c r="E145" s="17" t="s">
-        <v>120</v>
+        <v>338</v>
       </c>
       <c r="F145" s="17" t="s">
-        <v>94</v>
+        <v>222</v>
       </c>
       <c r="G145" s="17" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
       <c r="H145" s="17" t="s">
-        <v>781</v>
+        <v>770</v>
       </c>
       <c r="I145" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J145" s="17">
         <v>2</v>
       </c>
       <c r="K145" s="17" t="s">
-        <v>284</v>
+        <v>337</v>
       </c>
       <c r="L145" s="17" t="str" cm="1">
         <f t="array" ref="L145">_xlfn.REGEXEXTRACT(B145,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>www.peekvids.com</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I146)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B146" s="17" t="s">
-        <v>181</v>
+        <v>69</v>
       </c>
       <c r="C146" s="17">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="D146" s="17" t="s">
-        <v>98</v>
+        <v>325</v>
       </c>
       <c r="E146" s="17" t="s">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="F146" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G146" s="17" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="H146" s="17" t="s">
-        <v>322</v>
+        <v>771</v>
       </c>
       <c r="I146" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J146" s="17">
         <v>2</v>
       </c>
       <c r="K146" s="17" t="s">
-        <v>246</v>
+        <v>327</v>
       </c>
       <c r="L146" s="17" t="str" cm="1">
         <f t="array" ref="L146">_xlfn.REGEXEXTRACT(B146,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I147)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B147" s="17" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C147" s="17">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="D147" s="17" t="s">
-        <v>128</v>
+        <v>287</v>
       </c>
       <c r="E147" s="17" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="F147" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G147" s="17" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="H147" s="17" t="s">
-        <v>109</v>
+        <v>772</v>
       </c>
       <c r="I147" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J147" s="17">
         <v>2</v>
       </c>
       <c r="K147" s="17" t="s">
-        <v>217</v>
+        <v>328</v>
       </c>
       <c r="L147" s="17" t="str" cm="1">
         <f t="array" ref="L147">_xlfn.REGEXEXTRACT(B147,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.omg.xxx</v>
       </c>
     </row>
     <row r="148" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I148)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B148" s="17" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="C148" s="17">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="D148" s="17" t="s">
-        <v>412</v>
+        <v>148</v>
       </c>
       <c r="E148" s="17" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="F148" s="17" t="s">
         <v>92</v>
       </c>
       <c r="G148" s="17" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="H148" s="17" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="I148" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J148" s="17">
         <v>2</v>
       </c>
       <c r="K148" s="17" t="s">
-        <v>414</v>
+        <v>297</v>
       </c>
       <c r="L148" s="17" t="str" cm="1">
         <f t="array" ref="L148">_xlfn.REGEXEXTRACT(B148,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>m.hqporner.com</v>
       </c>
     </row>
     <row r="149" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I149)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B149" s="17" t="s">
-        <v>155</v>
+        <v>46</v>
       </c>
       <c r="C149" s="17">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D149" s="17" t="s">
-        <v>156</v>
+        <v>99</v>
       </c>
       <c r="E149" s="17" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="F149" s="17" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="G149" s="17" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="H149" s="17" t="s">
-        <v>109</v>
+        <v>774</v>
       </c>
       <c r="I149" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J149" s="17">
         <v>2</v>
       </c>
       <c r="K149" s="17" t="s">
-        <v>413</v>
+        <v>282</v>
       </c>
       <c r="L149" s="17" t="str" cm="1">
         <f t="array" ref="L149">_xlfn.REGEXEXTRACT(B149,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I150)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B150" s="17" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="C150" s="17">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D150" s="17" t="s">
-        <v>128</v>
+        <v>96</v>
       </c>
       <c r="E150" s="17" t="s">
-        <v>128</v>
+        <v>243</v>
       </c>
       <c r="F150" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G150" s="17" t="s">
-        <v>296</v>
+        <v>651</v>
       </c>
       <c r="H150" s="17" t="s">
-        <v>783</v>
+        <v>320</v>
       </c>
       <c r="I150" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J150" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K150" s="17" t="s">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="L150" s="17" t="str" cm="1">
         <f t="array" ref="L150">_xlfn.REGEXEXTRACT(B150,"(?&lt;=//)[^/]+")</f>
@@ -9005,189 +9066,189 @@
     </row>
     <row r="151" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I151)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B151" s="17" t="s">
-        <v>125</v>
+        <v>193</v>
       </c>
       <c r="C151" s="17">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D151" s="17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E151" s="17" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F151" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G151" s="17" t="s">
-        <v>660</v>
+        <v>652</v>
       </c>
       <c r="H151" s="17" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="I151" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J151" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K151" s="17" t="s">
-        <v>130</v>
+        <v>215</v>
       </c>
       <c r="L151" s="17" t="str" cm="1">
         <f t="array" ref="L151">_xlfn.REGEXEXTRACT(B151,"(?&lt;=//)[^/]+")</f>
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A152" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I152)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B152" s="17" t="s">
-        <v>3</v>
+        <v>156</v>
       </c>
       <c r="C152" s="17">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="D152" s="17" t="s">
-        <v>208</v>
+        <v>408</v>
       </c>
       <c r="E152" s="17" t="s">
-        <v>106</v>
+        <v>513</v>
       </c>
       <c r="F152" s="17" t="s">
-        <v>224</v>
+        <v>90</v>
       </c>
       <c r="G152" s="17" t="s">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="H152" s="17" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="I152" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J152" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K152" s="17" t="s">
-        <v>209</v>
+        <v>410</v>
       </c>
       <c r="L152" s="17" t="str" cm="1">
         <f t="array" ref="L152">_xlfn.REGEXEXTRACT(B152,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhub.com</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I153)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B153" s="17" t="s">
-        <v>482</v>
+        <v>153</v>
       </c>
       <c r="C153" s="17">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D153" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="E153" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="F153" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="E153" s="17" t="s">
-        <v>412</v>
-      </c>
-      <c r="F153" s="17" t="s">
-        <v>112</v>
-      </c>
       <c r="G153" s="17" t="s">
-        <v>808</v>
+        <v>654</v>
       </c>
       <c r="H153" s="17" t="s">
-        <v>807</v>
+        <v>107</v>
       </c>
       <c r="I153" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J153" s="17">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K153" s="17" t="s">
-        <v>809</v>
+        <v>409</v>
       </c>
       <c r="L153" s="17" t="str" cm="1">
         <f t="array" ref="L153">_xlfn.REGEXEXTRACT(B153,"(?&lt;=//)[^/]+")</f>
-        <v>www.fapcat.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="154" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="17" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(I154)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B154" s="17" t="s">
-        <v>471</v>
+        <v>158</v>
       </c>
       <c r="C154" s="17">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D154" s="17" t="s">
-        <v>381</v>
+        <v>126</v>
       </c>
       <c r="E154" s="17" t="s">
-        <v>519</v>
+        <v>126</v>
       </c>
       <c r="F154" s="17" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="G154" s="17" t="s">
-        <v>804</v>
+        <v>294</v>
       </c>
       <c r="H154" s="17" t="s">
-        <v>803</v>
+        <v>776</v>
       </c>
       <c r="I154" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J154" s="17">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K154" s="17" t="s">
-        <v>806</v>
+        <v>298</v>
       </c>
       <c r="L154" s="17" t="str" cm="1">
         <f t="array" ref="L154">_xlfn.REGEXEXTRACT(B154,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="17" t="str">
         <f>IF(ISBLANK(I155)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B155" s="17" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C155" s="17">
         <v>51</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E155" s="17" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="F155" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G155" s="17" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="H155" s="17" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="I155" s="17"/>
       <c r="J155" s="17"/>
@@ -9197,31 +9258,31 @@
         <v>tube.perverzija.com</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="17" t="str">
         <f>IF(ISBLANK(I156)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B156" s="17" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="C156" s="17">
         <v>53</v>
       </c>
       <c r="D156" s="17" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E156" s="17" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F156" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G156" s="17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H156" s="17" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="I156" s="17"/>
       <c r="J156" s="17"/>
@@ -9231,31 +9292,31 @@
         <v>abxxx.com</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="str">
         <f>IF(ISBLANK(I157)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B157" s="17" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C157" s="17">
         <v>54</v>
       </c>
       <c r="D157" s="17" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E157" s="17" t="s">
-        <v>805</v>
+        <v>798</v>
       </c>
       <c r="F157" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G157" s="17" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H157" s="17" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="I157" s="17"/>
       <c r="J157" s="17"/>
@@ -9265,52 +9326,317 @@
         <v>www.eporner.com</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="17" t="str">
         <f>IF(ISBLANK(I158)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B158" s="17" t="s">
-        <v>472</v>
+        <v>803</v>
       </c>
       <c r="C158" s="17">
-        <v>99</v>
+        <v>58</v>
       </c>
       <c r="D158" s="17" t="s">
-        <v>412</v>
+        <v>108</v>
       </c>
       <c r="E158" s="17" t="s">
-        <v>412</v>
+        <v>810</v>
       </c>
       <c r="F158" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="G158" s="17" t="s">
-        <v>521</v>
-      </c>
-      <c r="H158" s="17" t="s">
-        <v>521</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="G158" s="17"/>
+      <c r="H158" s="17"/>
       <c r="I158" s="17"/>
       <c r="J158" s="17"/>
       <c r="K158" s="17"/>
       <c r="L158" s="17" t="str" cm="1">
         <f t="array" ref="L158">_xlfn.REGEXEXTRACT(B158,"(?&lt;=//)[^/]+")</f>
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="17" t="str">
+        <f>IF(ISBLANK(I159)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B159" s="17" t="s">
+        <v>804</v>
+      </c>
+      <c r="C159" s="17">
+        <v>64</v>
+      </c>
+      <c r="D159" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E159" s="17" t="s">
+        <v>811</v>
+      </c>
+      <c r="F159" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="G159" s="17"/>
+      <c r="H159" s="17"/>
+      <c r="I159" s="17"/>
+      <c r="J159" s="17"/>
+      <c r="K159" s="17"/>
+      <c r="L159" s="17" t="str" cm="1">
+        <f t="array" ref="L159">_xlfn.REGEXEXTRACT(B159,"(?&lt;=//)[^/]+")</f>
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="17" t="str">
+        <f>IF(ISBLANK(I160)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B160" s="17" t="s">
+        <v>805</v>
+      </c>
+      <c r="C160" s="17">
+        <v>56</v>
+      </c>
+      <c r="D160" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E160" s="17" t="s">
+        <v>812</v>
+      </c>
+      <c r="F160" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="G160" s="17"/>
+      <c r="H160" s="17"/>
+      <c r="I160" s="17"/>
+      <c r="J160" s="17"/>
+      <c r="K160" s="17"/>
+      <c r="L160" s="17" t="str" cm="1">
+        <f t="array" ref="L160">_xlfn.REGEXEXTRACT(B160,"(?&lt;=//)[^/]+")</f>
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" ht="45" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="17" t="str">
+        <f>IF(ISBLANK(I161)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B161" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="C161" s="17">
+        <v>52</v>
+      </c>
+      <c r="D161" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E161" s="17" t="s">
+        <v>813</v>
+      </c>
+      <c r="F161" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="G161" s="17"/>
+      <c r="H161" s="17"/>
+      <c r="I161" s="17"/>
+      <c r="J161" s="17"/>
+      <c r="K161" s="17"/>
+      <c r="L161" s="17" t="str" cm="1">
+        <f t="array" ref="L161">_xlfn.REGEXEXTRACT(B161,"(?&lt;=//)[^/]+")</f>
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="17" t="str">
+        <f>IF(ISBLANK(I162)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B162" s="17" t="s">
+        <v>807</v>
+      </c>
+      <c r="C162" s="17">
+        <v>48</v>
+      </c>
+      <c r="D162" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E162" s="17" t="s">
+        <v>814</v>
+      </c>
+      <c r="F162" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="G162" s="17"/>
+      <c r="H162" s="17"/>
+      <c r="I162" s="17"/>
+      <c r="J162" s="17"/>
+      <c r="K162" s="17"/>
+      <c r="L162" s="17" t="str" cm="1">
+        <f t="array" ref="L162">_xlfn.REGEXEXTRACT(B162,"(?&lt;=//)[^/]+")</f>
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="17" t="str">
+        <f>IF(ISBLANK(I163)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B163" s="17" t="s">
+        <v>808</v>
+      </c>
+      <c r="C163" s="17">
+        <v>64</v>
+      </c>
+      <c r="D163" s="17" t="s">
+        <v>108</v>
+      </c>
+      <c r="E163" s="17" t="s">
+        <v>815</v>
+      </c>
+      <c r="F163" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="G163" s="17"/>
+      <c r="H163" s="17"/>
+      <c r="I163" s="17"/>
+      <c r="J163" s="17"/>
+      <c r="K163" s="17"/>
+      <c r="L163" s="17" t="str" cm="1">
+        <f t="array" ref="L163">_xlfn.REGEXEXTRACT(B163,"(?&lt;=//)[^/]+")</f>
+        <v>www.pornhits.com</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A164" s="17" t="str">
+        <f>IF(ISBLANK(I164)=TRUE,"Pending","Done")</f>
+        <v>Done</v>
+      </c>
+      <c r="B164" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C164" s="17">
+        <v>34</v>
+      </c>
+      <c r="D164" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="E164" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="F164" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="G164" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="H164" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="I164" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="J164" s="17">
+        <v>1</v>
+      </c>
+      <c r="K164" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="L164" s="17" t="str" cm="1">
+        <f t="array" ref="L164">_xlfn.REGEXEXTRACT(B164,"(?&lt;=//)[^/]+")</f>
+        <v>heavyfetish.com</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A165" s="17" t="str">
+        <f>IF(ISBLANK(I165)=TRUE,"Pending","Done")</f>
+        <v>Done</v>
+      </c>
+      <c r="B165" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C165" s="17">
+        <v>11</v>
+      </c>
+      <c r="D165" s="17" t="s">
+        <v>206</v>
+      </c>
+      <c r="E165" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="F165" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="G165" s="17" t="s">
+        <v>656</v>
+      </c>
+      <c r="H165" s="17" t="s">
+        <v>777</v>
+      </c>
+      <c r="I165" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="J165" s="17">
+        <v>1</v>
+      </c>
+      <c r="K165" s="17" t="s">
+        <v>207</v>
+      </c>
+      <c r="L165" s="17" t="str" cm="1">
+        <f t="array" ref="L165">_xlfn.REGEXEXTRACT(B165,"(?&lt;=//)[^/]+")</f>
+        <v>www.pornhub.com</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" ht="30" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A166" s="17" t="str">
+        <f>IF(ISBLANK(I166)=TRUE,"Pending","Done")</f>
+        <v>Pending</v>
+      </c>
+      <c r="B166" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="C166" s="17">
+        <v>99</v>
+      </c>
+      <c r="D166" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="E166" s="17" t="s">
+        <v>408</v>
+      </c>
+      <c r="F166" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G166" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="H166" s="17" t="s">
+        <v>516</v>
+      </c>
+      <c r="I166" s="17"/>
+      <c r="J166" s="17"/>
+      <c r="K166" s="17"/>
+      <c r="L166" s="17" t="str" cm="1">
+        <f t="array" ref="L166">_xlfn.REGEXEXTRACT(B166,"(?&lt;=//)[^/]+")</f>
         <v>xhamster44.desi</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L158" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A155:L158">
-      <sortCondition ref="C1:C158"/>
+  <autoFilter ref="A1:L166" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Done"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L165">
+      <sortCondition descending="1" ref="J1:J166"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L158">
-    <sortCondition descending="1" ref="J1:J158"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L166">
+    <sortCondition descending="1" ref="J1:J166"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="H1:L2 I3:L125 H159:XFD1048576 A1:G1048576 H3:H158 I126:XFD158">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+  <conditionalFormatting sqref="H1:L2 I3:L125 H167:XFD1048576 A1:G1048576 I126:XFD166 H3:H166">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9353,13 +9679,13 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>229</v>
       </c>
       <c r="D1" s="7" t="str">
         <f>_xlfn.CONCAT(A1,"-",B1,"-",C1)</f>
@@ -9368,112 +9694,112 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D2" s="7" t="str">
         <f t="shared" ref="D2:D6" si="0">_xlfn.CONCAT(A2,"-",B2,"-",C2)</f>
         <v>bdsm-soft-femdom</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H2" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="I2" s="13" t="s">
         <v>233</v>
-      </c>
-      <c r="I2" s="13" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D3" s="7" t="str">
         <f t="shared" si="0"/>
         <v>bdsm-soft-lesdom</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>228</v>
-      </c>
       <c r="C4" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D4" s="6" t="str">
         <f t="shared" si="0"/>
         <v>bdsm-hard-maledom</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>230</v>
       </c>
       <c r="D5" s="6" t="str">
         <f t="shared" si="0"/>
         <v>bdsm-hard-femdom</v>
       </c>
       <c r="I5" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>228</v>
-      </c>
       <c r="C6" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D6" s="6" t="str">
         <f t="shared" si="0"/>
         <v>bdsm-hard-lesdom</v>
       </c>
       <c r="I6" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="C7" s="13" t="s">
         <v>233</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>235</v>
       </c>
       <c r="D7" s="6" t="str">
         <f>_xlfn.CONCAT(A7,"-",B7,"-",C7)</f>
@@ -9482,76 +9808,76 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D8" s="6" t="str">
         <f t="shared" ref="D8:D16" si="1">_xlfn.CONCAT(A8,"-",B8,"-",C8)</f>
         <v>normal-rough-maledom</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H8" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="I8" s="10" t="s">
         <v>227</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D9" s="6" t="str">
         <f t="shared" si="1"/>
         <v>normal-rough-femdom</v>
       </c>
       <c r="H9" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="I9" s="11" t="s">
         <v>228</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D10" s="6" t="str">
         <f t="shared" si="1"/>
         <v>normal-rough-lesdom</v>
       </c>
       <c r="I10" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D11" s="6" t="str">
         <f t="shared" si="1"/>
@@ -9560,13 +9886,13 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="C12" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D12" s="7" t="str">
         <f t="shared" si="1"/>
@@ -9575,13 +9901,13 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="C13" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D13" s="7" t="str">
         <f t="shared" si="1"/>
@@ -9590,13 +9916,13 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="C14" s="11" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D14" s="7" t="str">
         <f t="shared" si="1"/>
@@ -9605,13 +9931,13 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="C15" s="12" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D15" s="7" t="str">
         <f t="shared" si="1"/>
@@ -9620,13 +9946,13 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>234</v>
-      </c>
       <c r="C16" s="14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D16" s="7" t="str">
         <f t="shared" si="1"/>
@@ -9649,151 +9975,151 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A18">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/master_links.xlsx
+++ b/data/master_links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0A5A66-1616-4A17-B085-77FE3E98BF88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85BF21D-0803-40AC-A8D3-377F17970C8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="314" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3478,7 +3478,7 @@
         <v>846</v>
       </c>
       <c r="C2" s="7" t="str">
-        <f t="shared" ref="C2:C23" si="0">IF(ISBLANK(K2)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(K2)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D2" s="7" t="s">
@@ -3524,7 +3524,7 @@
         <v>846</v>
       </c>
       <c r="C3" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K3)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -3570,7 +3570,7 @@
         <v>846</v>
       </c>
       <c r="C4" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K4)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D4" s="7" t="s">
@@ -3616,7 +3616,7 @@
         <v>847</v>
       </c>
       <c r="C5" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K5)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D5" s="7" t="s">
@@ -3662,7 +3662,7 @@
         <v>846</v>
       </c>
       <c r="C6" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K6)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -3706,7 +3706,7 @@
         <v>847</v>
       </c>
       <c r="C7" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K7)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -3752,7 +3752,7 @@
         <v>847</v>
       </c>
       <c r="C8" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K8)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -3798,7 +3798,7 @@
         <v>847</v>
       </c>
       <c r="C9" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K9)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D9" s="7" t="s">
@@ -3844,7 +3844,7 @@
         <v>847</v>
       </c>
       <c r="C10" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K10)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D10" s="7" t="s">
@@ -3890,7 +3890,7 @@
         <v>847</v>
       </c>
       <c r="C11" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K11)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D11" s="7" t="s">
@@ -3936,7 +3936,7 @@
         <v>847</v>
       </c>
       <c r="C12" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K12)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D12" s="7" t="s">
@@ -3982,7 +3982,7 @@
         <v>847</v>
       </c>
       <c r="C13" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K13)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D13" s="7" t="s">
@@ -4028,7 +4028,7 @@
         <v>847</v>
       </c>
       <c r="C14" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K14)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -4072,7 +4072,7 @@
         <v>847</v>
       </c>
       <c r="C15" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K15)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D15" s="7" t="s">
@@ -4118,7 +4118,7 @@
         <v>847</v>
       </c>
       <c r="C16" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K16)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D16" s="7" t="s">
@@ -4164,7 +4164,7 @@
         <v>847</v>
       </c>
       <c r="C17" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K17)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D17" s="7" t="s">
@@ -4210,7 +4210,7 @@
         <v>847</v>
       </c>
       <c r="C18" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K18)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D18" s="7" t="s">
@@ -4256,7 +4256,7 @@
         <v>847</v>
       </c>
       <c r="C19" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K19)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D19" s="7" t="s">
@@ -4302,7 +4302,7 @@
         <v>847</v>
       </c>
       <c r="C20" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K20)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D20" s="7" t="s">
@@ -4348,7 +4348,7 @@
         <v>847</v>
       </c>
       <c r="C21" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K21)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D21" s="7" t="s">
@@ -4394,7 +4394,7 @@
         <v>847</v>
       </c>
       <c r="C22" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K22)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D22" s="7" t="s">
@@ -4440,7 +4440,7 @@
         <v>847</v>
       </c>
       <c r="C23" s="7" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(K23)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D23" s="7" t="s">
@@ -4532,7 +4532,7 @@
         <v>847</v>
       </c>
       <c r="C25" s="7" t="str">
-        <f t="shared" ref="C25:C56" si="1">IF(ISBLANK(K25)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(K25)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D25" s="7" t="s">
@@ -4578,7 +4578,7 @@
         <v>847</v>
       </c>
       <c r="C26" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K26)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D26" s="7" t="s">
@@ -4624,7 +4624,7 @@
         <v>847</v>
       </c>
       <c r="C27" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K27)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D27" s="7" t="s">
@@ -4670,7 +4670,7 @@
         <v>847</v>
       </c>
       <c r="C28" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K28)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D28" s="7" t="s">
@@ -4716,7 +4716,7 @@
         <v>847</v>
       </c>
       <c r="C29" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K29)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D29" s="7" t="s">
@@ -4762,7 +4762,7 @@
         <v>847</v>
       </c>
       <c r="C30" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K30)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D30" s="7" t="s">
@@ -4808,7 +4808,7 @@
         <v>847</v>
       </c>
       <c r="C31" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K31)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D31" s="7" t="s">
@@ -4854,7 +4854,7 @@
         <v>847</v>
       </c>
       <c r="C32" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K32)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D32" s="7" t="s">
@@ -4900,7 +4900,7 @@
         <v>847</v>
       </c>
       <c r="C33" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K33)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D33" s="7" t="s">
@@ -4946,7 +4946,7 @@
         <v>847</v>
       </c>
       <c r="C34" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K34)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D34" s="7" t="s">
@@ -4992,7 +4992,7 @@
         <v>847</v>
       </c>
       <c r="C35" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K35)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D35" s="7" t="s">
@@ -5038,7 +5038,7 @@
         <v>847</v>
       </c>
       <c r="C36" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K36)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D36" s="7" t="s">
@@ -5084,7 +5084,7 @@
         <v>847</v>
       </c>
       <c r="C37" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K37)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D37" s="7" t="s">
@@ -5130,7 +5130,7 @@
         <v>847</v>
       </c>
       <c r="C38" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K38)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D38" s="7" t="s">
@@ -5176,7 +5176,7 @@
         <v>847</v>
       </c>
       <c r="C39" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K39)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D39" s="7" t="s">
@@ -5222,7 +5222,7 @@
         <v>847</v>
       </c>
       <c r="C40" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K40)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D40" s="7" t="s">
@@ -5268,7 +5268,7 @@
         <v>847</v>
       </c>
       <c r="C41" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K41)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D41" s="7" t="s">
@@ -5314,7 +5314,7 @@
         <v>847</v>
       </c>
       <c r="C42" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K42)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D42" s="7" t="s">
@@ -5360,7 +5360,7 @@
         <v>847</v>
       </c>
       <c r="C43" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K43)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D43" s="7" t="s">
@@ -5406,7 +5406,7 @@
         <v>847</v>
       </c>
       <c r="C44" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K44)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D44" s="7" t="s">
@@ -5452,7 +5452,7 @@
         <v>847</v>
       </c>
       <c r="C45" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K45)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D45" s="7" t="s">
@@ -5498,7 +5498,7 @@
         <v>847</v>
       </c>
       <c r="C46" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K46)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D46" s="7" t="s">
@@ -5544,7 +5544,7 @@
         <v>847</v>
       </c>
       <c r="C47" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K47)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D47" s="7" t="s">
@@ -5590,7 +5590,7 @@
         <v>847</v>
       </c>
       <c r="C48" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K48)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D48" s="7" t="s">
@@ -5636,7 +5636,7 @@
         <v>847</v>
       </c>
       <c r="C49" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K49)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D49" s="7" t="s">
@@ -5682,7 +5682,7 @@
         <v>847</v>
       </c>
       <c r="C50" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K50)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D50" s="7" t="s">
@@ -5728,7 +5728,7 @@
         <v>847</v>
       </c>
       <c r="C51" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K51)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D51" s="7" t="s">
@@ -5774,7 +5774,7 @@
         <v>847</v>
       </c>
       <c r="C52" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K52)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D52" s="7" t="s">
@@ -5820,7 +5820,7 @@
         <v>847</v>
       </c>
       <c r="C53" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K53)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D53" s="7" t="s">
@@ -5866,7 +5866,7 @@
         <v>847</v>
       </c>
       <c r="C54" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K54)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D54" s="7" t="s">
@@ -5912,7 +5912,7 @@
         <v>847</v>
       </c>
       <c r="C55" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K55)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D55" s="7" t="s">
@@ -5958,7 +5958,7 @@
         <v>847</v>
       </c>
       <c r="C56" s="7" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(K56)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D56" s="7" t="s">
@@ -6004,7 +6004,7 @@
         <v>847</v>
       </c>
       <c r="C57" s="7" t="str">
-        <f t="shared" ref="C57:C88" si="2">IF(ISBLANK(K57)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(K57)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D57" s="7" t="s">
@@ -6050,7 +6050,7 @@
         <v>847</v>
       </c>
       <c r="C58" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K58)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D58" s="7" t="s">
@@ -6096,7 +6096,7 @@
         <v>847</v>
       </c>
       <c r="C59" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K59)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D59" s="7" t="s">
@@ -6142,7 +6142,7 @@
         <v>847</v>
       </c>
       <c r="C60" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K60)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D60" s="7" t="s">
@@ -6188,7 +6188,7 @@
         <v>847</v>
       </c>
       <c r="C61" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K61)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D61" s="7" t="s">
@@ -6234,7 +6234,7 @@
         <v>847</v>
       </c>
       <c r="C62" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K62)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D62" s="7" t="s">
@@ -6280,7 +6280,7 @@
         <v>847</v>
       </c>
       <c r="C63" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K63)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D63" s="7" t="s">
@@ -6326,7 +6326,7 @@
         <v>847</v>
       </c>
       <c r="C64" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K64)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D64" s="7" t="s">
@@ -6372,7 +6372,7 @@
         <v>847</v>
       </c>
       <c r="C65" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K65)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D65" s="7" t="s">
@@ -6418,7 +6418,7 @@
         <v>847</v>
       </c>
       <c r="C66" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K66)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D66" s="7" t="s">
@@ -6464,7 +6464,7 @@
         <v>847</v>
       </c>
       <c r="C67" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K67)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D67" s="7" t="s">
@@ -6510,7 +6510,7 @@
         <v>847</v>
       </c>
       <c r="C68" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K68)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D68" s="7" t="s">
@@ -6556,7 +6556,7 @@
         <v>847</v>
       </c>
       <c r="C69" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K69)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D69" s="7" t="s">
@@ -6602,7 +6602,7 @@
         <v>847</v>
       </c>
       <c r="C70" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K70)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D70" s="7" t="s">
@@ -6648,7 +6648,7 @@
         <v>847</v>
       </c>
       <c r="C71" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K71)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D71" s="7" t="s">
@@ -6694,7 +6694,7 @@
         <v>847</v>
       </c>
       <c r="C72" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K72)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D72" s="7" t="s">
@@ -6740,7 +6740,7 @@
         <v>847</v>
       </c>
       <c r="C73" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K73)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D73" s="7" t="s">
@@ -6786,7 +6786,7 @@
         <v>847</v>
       </c>
       <c r="C74" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K74)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D74" s="7" t="s">
@@ -6832,7 +6832,7 @@
         <v>847</v>
       </c>
       <c r="C75" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K75)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D75" s="7" t="s">
@@ -6878,7 +6878,7 @@
         <v>847</v>
       </c>
       <c r="C76" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K76)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D76" s="7" t="s">
@@ -6924,7 +6924,7 @@
         <v>847</v>
       </c>
       <c r="C77" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K77)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -6970,7 +6970,7 @@
         <v>847</v>
       </c>
       <c r="C78" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K78)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D78" s="7" t="s">
@@ -7016,7 +7016,7 @@
         <v>847</v>
       </c>
       <c r="C79" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K79)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D79" s="7" t="s">
@@ -7062,7 +7062,7 @@
         <v>847</v>
       </c>
       <c r="C80" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K80)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D80" s="7" t="s">
@@ -7108,7 +7108,7 @@
         <v>847</v>
       </c>
       <c r="C81" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K81)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D81" s="7" t="s">
@@ -7154,7 +7154,7 @@
         <v>847</v>
       </c>
       <c r="C82" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K82)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D82" s="7" t="s">
@@ -7200,7 +7200,7 @@
         <v>847</v>
       </c>
       <c r="C83" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K83)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D83" s="7" t="s">
@@ -7246,7 +7246,7 @@
         <v>847</v>
       </c>
       <c r="C84" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K84)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D84" s="7" t="s">
@@ -7292,7 +7292,7 @@
         <v>847</v>
       </c>
       <c r="C85" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K85)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D85" s="7" t="s">
@@ -7338,7 +7338,7 @@
         <v>847</v>
       </c>
       <c r="C86" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K86)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D86" s="7" t="s">
@@ -7384,7 +7384,7 @@
         <v>847</v>
       </c>
       <c r="C87" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K87)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D87" s="7" t="s">
@@ -7430,7 +7430,7 @@
         <v>847</v>
       </c>
       <c r="C88" s="7" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(K88)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D88" s="7" t="s">
@@ -7476,7 +7476,7 @@
         <v>847</v>
       </c>
       <c r="C89" s="7" t="str">
-        <f t="shared" ref="C89:C120" si="3">IF(ISBLANK(K89)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(K89)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D89" s="7" t="s">
@@ -7522,7 +7522,7 @@
         <v>847</v>
       </c>
       <c r="C90" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K90)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D90" s="7" t="s">
@@ -7568,7 +7568,7 @@
         <v>847</v>
       </c>
       <c r="C91" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K91)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D91" s="7" t="s">
@@ -7614,7 +7614,7 @@
         <v>847</v>
       </c>
       <c r="C92" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K92)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D92" s="7" t="s">
@@ -7660,7 +7660,7 @@
         <v>847</v>
       </c>
       <c r="C93" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K93)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D93" s="7" t="s">
@@ -7706,7 +7706,7 @@
         <v>847</v>
       </c>
       <c r="C94" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K94)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D94" s="7" t="s">
@@ -7752,7 +7752,7 @@
         <v>847</v>
       </c>
       <c r="C95" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K95)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D95" s="7" t="s">
@@ -7798,7 +7798,7 @@
         <v>847</v>
       </c>
       <c r="C96" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K96)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D96" s="7" t="s">
@@ -7844,7 +7844,7 @@
         <v>847</v>
       </c>
       <c r="C97" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K97)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D97" s="7" t="s">
@@ -7890,7 +7890,7 @@
         <v>847</v>
       </c>
       <c r="C98" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K98)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D98" s="7" t="s">
@@ -7936,7 +7936,7 @@
         <v>847</v>
       </c>
       <c r="C99" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K99)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D99" s="7" t="s">
@@ -7982,7 +7982,7 @@
         <v>847</v>
       </c>
       <c r="C100" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K100)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D100" s="7" t="s">
@@ -8028,7 +8028,7 @@
         <v>847</v>
       </c>
       <c r="C101" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K101)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D101" s="7" t="s">
@@ -8074,7 +8074,7 @@
         <v>847</v>
       </c>
       <c r="C102" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K102)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D102" s="7" t="s">
@@ -8120,7 +8120,7 @@
         <v>847</v>
       </c>
       <c r="C103" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K103)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D103" s="7" t="s">
@@ -8166,7 +8166,7 @@
         <v>847</v>
       </c>
       <c r="C104" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K104)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D104" s="7" t="s">
@@ -8212,7 +8212,7 @@
         <v>847</v>
       </c>
       <c r="C105" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K105)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D105" s="7" t="s">
@@ -8258,7 +8258,7 @@
         <v>847</v>
       </c>
       <c r="C106" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K106)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D106" s="7" t="s">
@@ -8304,7 +8304,7 @@
         <v>847</v>
       </c>
       <c r="C107" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K107)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D107" s="7" t="s">
@@ -8350,7 +8350,7 @@
         <v>847</v>
       </c>
       <c r="C108" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K108)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D108" s="7" t="s">
@@ -8396,7 +8396,7 @@
         <v>847</v>
       </c>
       <c r="C109" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K109)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D109" s="7" t="s">
@@ -8442,7 +8442,7 @@
         <v>847</v>
       </c>
       <c r="C110" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K110)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D110" s="7" t="s">
@@ -8488,7 +8488,7 @@
         <v>847</v>
       </c>
       <c r="C111" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K111)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D111" s="7" t="s">
@@ -8534,7 +8534,7 @@
         <v>847</v>
       </c>
       <c r="C112" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K112)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D112" s="7" t="s">
@@ -8580,7 +8580,7 @@
         <v>847</v>
       </c>
       <c r="C113" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K113)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D113" s="7" t="s">
@@ -8626,7 +8626,7 @@
         <v>847</v>
       </c>
       <c r="C114" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K114)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D114" s="7" t="s">
@@ -8672,7 +8672,7 @@
         <v>847</v>
       </c>
       <c r="C115" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K115)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D115" s="7" t="s">
@@ -8718,7 +8718,7 @@
         <v>847</v>
       </c>
       <c r="C116" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K116)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D116" s="7" t="s">
@@ -8764,7 +8764,7 @@
         <v>847</v>
       </c>
       <c r="C117" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K117)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D117" s="7" t="s">
@@ -8810,7 +8810,7 @@
         <v>847</v>
       </c>
       <c r="C118" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K118)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D118" s="7" t="s">
@@ -8856,7 +8856,7 @@
         <v>847</v>
       </c>
       <c r="C119" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K119)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D119" s="7" t="s">
@@ -8902,7 +8902,7 @@
         <v>847</v>
       </c>
       <c r="C120" s="7" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(K120)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D120" s="7" t="s">
@@ -8948,7 +8948,7 @@
         <v>847</v>
       </c>
       <c r="C121" s="7" t="str">
-        <f t="shared" ref="C121:C152" si="4">IF(ISBLANK(K121)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(K121)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D121" s="7" t="s">
@@ -8994,7 +8994,7 @@
         <v>847</v>
       </c>
       <c r="C122" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K122)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D122" s="7" t="s">
@@ -9040,7 +9040,7 @@
         <v>847</v>
       </c>
       <c r="C123" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K123)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D123" s="7" t="s">
@@ -9086,7 +9086,7 @@
         <v>847</v>
       </c>
       <c r="C124" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K124)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D124" s="7" t="s">
@@ -9132,7 +9132,7 @@
         <v>847</v>
       </c>
       <c r="C125" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K125)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D125" s="7" t="s">
@@ -9178,7 +9178,7 @@
         <v>847</v>
       </c>
       <c r="C126" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K126)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D126" s="7" t="s">
@@ -9224,7 +9224,7 @@
         <v>847</v>
       </c>
       <c r="C127" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K127)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D127" s="7" t="s">
@@ -9270,7 +9270,7 @@
         <v>847</v>
       </c>
       <c r="C128" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K128)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D128" s="7" t="s">
@@ -9316,7 +9316,7 @@
         <v>847</v>
       </c>
       <c r="C129" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K129)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D129" s="7" t="s">
@@ -9362,7 +9362,7 @@
         <v>847</v>
       </c>
       <c r="C130" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K130)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D130" s="7" t="s">
@@ -9408,7 +9408,7 @@
         <v>847</v>
       </c>
       <c r="C131" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K131)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D131" s="7" t="s">
@@ -9454,7 +9454,7 @@
         <v>847</v>
       </c>
       <c r="C132" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K132)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D132" s="7" t="s">
@@ -9500,7 +9500,7 @@
         <v>847</v>
       </c>
       <c r="C133" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K133)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D133" s="7" t="s">
@@ -9546,7 +9546,7 @@
         <v>847</v>
       </c>
       <c r="C134" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K134)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D134" s="7" t="s">
@@ -9592,7 +9592,7 @@
         <v>847</v>
       </c>
       <c r="C135" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K135)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D135" s="7" t="s">
@@ -9638,7 +9638,7 @@
         <v>847</v>
       </c>
       <c r="C136" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K136)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D136" s="7" t="s">
@@ -9684,7 +9684,7 @@
         <v>847</v>
       </c>
       <c r="C137" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K137)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D137" s="7" t="s">
@@ -9730,7 +9730,7 @@
         <v>847</v>
       </c>
       <c r="C138" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K138)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D138" s="7" t="s">
@@ -9776,7 +9776,7 @@
         <v>847</v>
       </c>
       <c r="C139" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K139)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D139" s="7" t="s">
@@ -9822,7 +9822,7 @@
         <v>847</v>
       </c>
       <c r="C140" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K140)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D140" s="7" t="s">
@@ -9868,7 +9868,7 @@
         <v>847</v>
       </c>
       <c r="C141" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K141)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D141" s="7" t="s">
@@ -9914,7 +9914,7 @@
         <v>847</v>
       </c>
       <c r="C142" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K142)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D142" s="7" t="s">
@@ -9960,7 +9960,7 @@
         <v>847</v>
       </c>
       <c r="C143" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K143)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D143" s="7" t="s">
@@ -10006,7 +10006,7 @@
         <v>847</v>
       </c>
       <c r="C144" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K144)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D144" s="7" t="s">
@@ -10052,7 +10052,7 @@
         <v>847</v>
       </c>
       <c r="C145" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K145)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D145" s="7" t="s">
@@ -10098,7 +10098,7 @@
         <v>847</v>
       </c>
       <c r="C146" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K146)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D146" s="7" t="s">
@@ -10144,7 +10144,7 @@
         <v>847</v>
       </c>
       <c r="C147" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K147)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D147" s="7" t="s">
@@ -10190,7 +10190,7 @@
         <v>847</v>
       </c>
       <c r="C148" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K148)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D148" s="7" t="s">
@@ -10236,7 +10236,7 @@
         <v>847</v>
       </c>
       <c r="C149" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K149)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D149" s="7" t="s">
@@ -10282,7 +10282,7 @@
         <v>847</v>
       </c>
       <c r="C150" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K150)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D150" s="7" t="s">
@@ -10328,7 +10328,7 @@
         <v>847</v>
       </c>
       <c r="C151" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K151)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D151" s="7" t="s">
@@ -10374,7 +10374,7 @@
         <v>847</v>
       </c>
       <c r="C152" s="7" t="str">
-        <f t="shared" si="4"/>
+        <f>IF(ISBLANK(K152)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D152" s="7" t="s">
@@ -10420,7 +10420,7 @@
         <v>847</v>
       </c>
       <c r="C153" s="7" t="str">
-        <f t="shared" ref="C153:C180" si="5">IF(ISBLANK(K153)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(K153)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D153" s="7" t="s">
@@ -10466,7 +10466,7 @@
         <v>847</v>
       </c>
       <c r="C154" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K154)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D154" s="7" t="s">
@@ -10512,7 +10512,7 @@
         <v>847</v>
       </c>
       <c r="C155" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K155)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D155" s="7" t="s">
@@ -10558,7 +10558,7 @@
         <v>847</v>
       </c>
       <c r="C156" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K156)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D156" s="7" t="s">
@@ -10604,7 +10604,7 @@
         <v>847</v>
       </c>
       <c r="C157" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K157)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D157" s="7" t="s">
@@ -10650,7 +10650,7 @@
         <v>847</v>
       </c>
       <c r="C158" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K158)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D158" s="7" t="s">
@@ -10696,7 +10696,7 @@
         <v>847</v>
       </c>
       <c r="C159" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K159)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D159" s="7" t="s">
@@ -10742,7 +10742,7 @@
         <v>847</v>
       </c>
       <c r="C160" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K160)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D160" s="7" t="s">
@@ -10788,7 +10788,7 @@
         <v>847</v>
       </c>
       <c r="C161" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K161)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D161" s="7" t="s">
@@ -10834,7 +10834,7 @@
         <v>847</v>
       </c>
       <c r="C162" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K162)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D162" s="7" t="s">
@@ -10880,7 +10880,7 @@
         <v>847</v>
       </c>
       <c r="C163" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K163)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D163" s="7" t="s">
@@ -10926,7 +10926,7 @@
         <v>847</v>
       </c>
       <c r="C164" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K164)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D164" s="7" t="s">
@@ -10972,7 +10972,7 @@
         <v>847</v>
       </c>
       <c r="C165" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K165)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D165" s="7" t="s">
@@ -11018,7 +11018,7 @@
         <v>847</v>
       </c>
       <c r="C166" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K166)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D166" s="7" t="s">
@@ -11064,7 +11064,7 @@
         <v>847</v>
       </c>
       <c r="C167" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K167)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D167" s="7" t="s">
@@ -11110,7 +11110,7 @@
         <v>847</v>
       </c>
       <c r="C168" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K168)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D168" s="7" t="s">
@@ -11156,7 +11156,7 @@
         <v>847</v>
       </c>
       <c r="C169" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K169)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D169" s="7" t="s">
@@ -11202,7 +11202,7 @@
         <v>847</v>
       </c>
       <c r="C170" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K170)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D170" s="7" t="s">
@@ -11248,7 +11248,7 @@
         <v>847</v>
       </c>
       <c r="C171" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K171)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D171" s="7" t="s">
@@ -11294,7 +11294,7 @@
         <v>847</v>
       </c>
       <c r="C172" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K172)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D172" s="7" t="s">
@@ -11340,7 +11340,7 @@
         <v>847</v>
       </c>
       <c r="C173" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K173)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D173" s="7" t="s">
@@ -11386,7 +11386,7 @@
         <v>847</v>
       </c>
       <c r="C174" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K174)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D174" s="7" t="s">
@@ -11432,7 +11432,7 @@
         <v>847</v>
       </c>
       <c r="C175" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K175)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D175" s="7" t="s">
@@ -11478,7 +11478,7 @@
         <v>847</v>
       </c>
       <c r="C176" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K176)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D176" s="7" t="s">
@@ -11524,7 +11524,7 @@
         <v>847</v>
       </c>
       <c r="C177" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K177)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D177" s="7" t="s">
@@ -11570,7 +11570,7 @@
         <v>847</v>
       </c>
       <c r="C178" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K178)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D178" s="7" t="s">
@@ -11616,7 +11616,7 @@
         <v>847</v>
       </c>
       <c r="C179" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K179)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D179" s="7" t="s">
@@ -11662,7 +11662,7 @@
         <v>847</v>
       </c>
       <c r="C180" s="7" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(ISBLANK(K180)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="D180" s="7" t="s">
@@ -11700,7 +11700,7 @@
         <v>heavyfetish.com</v>
       </c>
     </row>
-    <row r="181" spans="1:14" ht="30" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
         <v>361</v>
       </c>
@@ -11708,112 +11708,106 @@
         <v>847</v>
       </c>
       <c r="C181" s="7" t="str">
-        <f t="shared" ref="C181:C187" si="6">IF(ISBLANK(K181)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(K181)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="D181" s="7" t="s">
-        <v>905</v>
+        <v>838</v>
       </c>
       <c r="E181" s="7">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F181" s="7" t="s">
-        <v>136</v>
+        <v>254</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>906</v>
+        <v>549</v>
       </c>
       <c r="H181" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="I181" s="7" t="s">
-        <v>908</v>
-      </c>
-      <c r="J181" s="7" t="s">
-        <v>910</v>
-      </c>
+      <c r="I181" s="7"/>
+      <c r="J181" s="7"/>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
-      <c r="M181" s="7" t="s">
-        <v>909</v>
-      </c>
+      <c r="M181" s="7"/>
       <c r="N181" s="7" t="str" cm="1">
         <f t="array" ref="N181">_xlfn.REGEXEXTRACT(D181,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
-      </c>
-    </row>
-    <row r="182" spans="1:14" ht="45" x14ac:dyDescent="0.25">
+        <v>www.eporner.com</v>
+      </c>
+    </row>
+    <row r="182" spans="1:14" ht="60" x14ac:dyDescent="0.25">
       <c r="A182" s="7" t="s">
-        <v>361</v>
+        <v>902</v>
       </c>
       <c r="B182" s="7" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C182" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(ISBLANK(K182)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>838</v>
+        <v>857</v>
       </c>
       <c r="E182" s="7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>254</v>
+        <v>92</v>
       </c>
       <c r="G182" s="7" t="s">
-        <v>549</v>
+        <v>858</v>
       </c>
       <c r="H182" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="I182" s="7"/>
+      <c r="I182" s="7" t="s">
+        <v>859</v>
+      </c>
       <c r="J182" s="7"/>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c r="M182" s="7"/>
       <c r="N182" s="7" t="str" cm="1">
         <f t="array" ref="N182">_xlfn.REGEXEXTRACT(D182,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
-      </c>
-    </row>
-    <row r="183" spans="1:14" ht="60" x14ac:dyDescent="0.25">
+        <v>bdsmstreak.com</v>
+      </c>
+    </row>
+    <row r="183" spans="1:14" ht="30" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>902</v>
+        <v>361</v>
       </c>
       <c r="B183" s="7" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C183" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(ISBLANK(K183)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="D183" s="7" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="E183" s="7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>92</v>
+        <v>254</v>
       </c>
       <c r="G183" s="7" t="s">
-        <v>858</v>
+        <v>549</v>
       </c>
       <c r="H183" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="I183" s="7" t="s">
-        <v>859</v>
-      </c>
+      <c r="I183" s="7"/>
       <c r="J183" s="7"/>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c r="M183" s="7"/>
       <c r="N183" s="7" t="str" cm="1">
         <f t="array" ref="N183">_xlfn.REGEXEXTRACT(D183,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>www.eporner.com</v>
       </c>
     </row>
     <row r="184" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -11824,20 +11818,20 @@
         <v>847</v>
       </c>
       <c r="C184" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(ISBLANK(K184)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="D184" s="7" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E184" s="7">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F184" s="7" t="s">
         <v>254</v>
       </c>
       <c r="G184" s="7" t="s">
-        <v>549</v>
+        <v>907</v>
       </c>
       <c r="H184" s="7" t="s">
         <v>88</v>
@@ -11860,32 +11854,38 @@
         <v>847</v>
       </c>
       <c r="C185" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(ISBLANK(K185)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="D185" s="7" t="s">
-        <v>852</v>
+        <v>905</v>
       </c>
       <c r="E185" s="7">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F185" s="7" t="s">
-        <v>254</v>
+        <v>136</v>
       </c>
       <c r="G185" s="7" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H185" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="I185" s="7"/>
-      <c r="J185" s="7"/>
+      <c r="I185" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="J185" s="7" t="s">
+        <v>910</v>
+      </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
-      <c r="M185" s="7"/>
+      <c r="M185" s="7" t="s">
+        <v>909</v>
+      </c>
       <c r="N185" s="7" t="str" cm="1">
         <f t="array" ref="N185">_xlfn.REGEXEXTRACT(D185,"(?&lt;=//)[^/]+")</f>
-        <v>www.eporner.com</v>
+        <v>heavyfetish.com</v>
       </c>
     </row>
     <row r="186" spans="1:14" ht="30" x14ac:dyDescent="0.25">
@@ -11896,7 +11896,7 @@
         <v>847</v>
       </c>
       <c r="C186" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(ISBLANK(K186)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="D186" s="7" t="s">
@@ -11932,7 +11932,7 @@
         <v>847</v>
       </c>
       <c r="C187" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f>IF(ISBLANK(K187)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="D187" s="7" t="s">
@@ -11967,8 +11967,8 @@
         <filter val="Pending"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N180">
-      <sortCondition descending="1" ref="L1:L187"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:N187">
+      <sortCondition ref="E1:E187"/>
     </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N187">

--- a/data/master_links.xlsx
+++ b/data/master_links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23675D99-7B00-4A37-9962-ECAC756CEC29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD1CFFE8-B53F-4894-8264-57E078C17DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="314" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2669,9 +2669,6 @@
     <t>melody marks in gentle femdom</t>
   </si>
   <si>
-    <t>https://www.kink.com/shoot/7295</t>
-  </si>
-  <si>
     <t>isis love,jessie cox, ami emerson</t>
   </si>
   <si>
@@ -2750,9 +2747,6 @@
     <t>downloaded</t>
   </si>
   <si>
-    <t>invalid</t>
-  </si>
-  <si>
     <t>real_name</t>
   </si>
   <si>
@@ -3099,6 +3093,12 @@
   </si>
   <si>
     <t>bent over at 25m,chain inside pussy and ass at 41m</t>
+  </si>
+  <si>
+    <t>z-not-applicable</t>
+  </si>
+  <si>
+    <t>https://bdsmstreak.com/video/93110/jessie-cox-ami-emerson-and-isis-love-part-1-of-4-of-the-september-live-feed</t>
   </si>
 </sst>
 </file>
@@ -3416,13 +3416,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
@@ -3436,6 +3429,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF6161"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="1" tint="4.9989318521683403E-2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3722,7 +3722,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:R202"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3783,40 +3782,40 @@
         <v>76</v>
       </c>
       <c r="M1" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>896</v>
-      </c>
       <c r="Q1" s="2" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="R1" s="2" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" s="25" customFormat="1" ht="90" hidden="1" x14ac:dyDescent="0.25">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" s="25" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="str">
         <f>IF(ISBLANK(I2)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C2" s="2">
         <v>61</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>89</v>
@@ -3831,7 +3830,7 @@
         <v>82</v>
       </c>
       <c r="J2" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>810</v>
@@ -3844,56 +3843,56 @@
         <v>813</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="O2" s="2" t="str" cm="1">
-        <f t="array" ref="O2">IF(N2&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N2,"\d+(?=p)"),"invalid")</f>
+        <f t="array" ref="O2">IF(N2&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N2,"\d+(?=p)"),"z-not-applicable")</f>
         <v>720</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" s="25" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="str">
         <f>IF(ISBLANK(I3)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C3" s="2">
         <v>72</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J3" s="2">
+        <v>10</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>981</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="J3" s="2">
-        <v>9</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>983</v>
       </c>
       <c r="L3" s="2" t="str" cm="1">
         <f t="array" ref="L3">_xlfn.REGEXEXTRACT(B3,"(?&lt;=//)[^/]+")</f>
@@ -3903,283 +3902,283 @@
         <v>813</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="O3" s="2" t="str" cm="1">
-        <f t="array" ref="O3">IF(N3&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N3,"\d+(?=p)"),"invalid")</f>
+        <f t="array" ref="O3">IF(N3&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N3,"\d+(?=p)"),"z-not-applicable")</f>
         <v>720</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" s="25" customFormat="1" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="str">
         <f>IF(ISBLANK(I4)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>984</v>
+        <v>898</v>
       </c>
       <c r="C4" s="2">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>821</v>
+        <v>900</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>987</v>
+        <v>973</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>985</v>
+        <v>972</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>82</v>
       </c>
       <c r="J4" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="L4" s="2" t="str" cm="1">
         <f t="array" ref="L4">_xlfn.REGEXEXTRACT(B4,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>bdsmlust.com</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="O4" s="2" t="str" cm="1">
-        <f t="array" ref="O4">IF(N4&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N4,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O4">IF(N4&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N4,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>720</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" s="25" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
         <f>IF(ISBLANK(I5)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>887</v>
+        <v>863</v>
       </c>
       <c r="C5" s="2">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>524</v>
+        <v>995</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>529</v>
+        <v>208</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>888</v>
+        <v>880</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>889</v>
+        <v>859</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>82</v>
       </c>
       <c r="J5" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>890</v>
+        <v>879</v>
       </c>
       <c r="L5" s="2" t="str" cm="1">
         <f t="array" ref="L5">_xlfn.REGEXEXTRACT(B5,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmlust.com</v>
+        <v>bdsmmansion.com</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>895</v>
+        <v>875</v>
       </c>
       <c r="O5" s="2" t="str" cm="1">
-        <f t="array" ref="O5">IF(N5&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N5,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O5">IF(N5&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N5,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>1080</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>895</v>
+        <v>905</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" s="25" customFormat="1" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="str">
         <f>IF(ISBLANK(I6)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>900</v>
+        <v>987</v>
       </c>
       <c r="C6" s="2">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>1004</v>
+        <v>995</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>902</v>
+        <v>986</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>975</v>
+        <v>991</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>974</v>
+        <v>98</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>82</v>
       </c>
       <c r="J6" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>976</v>
+        <v>992</v>
       </c>
       <c r="L6" s="2" t="str" cm="1">
         <f t="array" ref="L6">_xlfn.REGEXEXTRACT(B6,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmlust.com</v>
+        <v>www.tnaflix.com</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>813</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>901</v>
+        <v>989</v>
       </c>
       <c r="O6" s="2" t="str" cm="1">
-        <f t="array" ref="O6">IF(N6&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N6,"\d+(?=p)"),"invalid")</f>
+        <f t="array" ref="O6">IF(N6&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N6,"\d+(?=p)"),"z-not-applicable")</f>
         <v>720</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>904</v>
+        <v>988</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>903</v>
+        <v>990</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="str">
         <f>IF(ISBLANK(I7)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>863</v>
+        <v>152</v>
       </c>
       <c r="C7" s="2">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>997</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>208</v>
+        <v>291</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>881</v>
+        <v>784</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>859</v>
+        <v>747</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>82</v>
       </c>
       <c r="J7" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>880</v>
+        <v>954</v>
       </c>
       <c r="L7" s="2" t="str" cm="1">
         <f t="array" ref="L7">_xlfn.REGEXEXTRACT(B7,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
+        <v>heavyfetish.com</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>813</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="O7" s="2" t="str" cm="1">
-        <f t="array" ref="O7">IF(N7&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N7,"\d+(?=p)"),"invalid")</f>
-        <v>1080</v>
+        <f t="array" ref="O7">IF(N7&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N7,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>720</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="str">
         <f>IF(ISBLANK(I8)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>820</v>
+        <v>982</v>
       </c>
       <c r="C8" s="2">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>997</v>
+        <v>1006</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>821</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>824</v>
+        <v>985</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>825</v>
+        <v>983</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>82</v>
@@ -4188,57 +4187,57 @@
         <v>9</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>826</v>
+        <v>984</v>
       </c>
       <c r="L8" s="2" t="str" cm="1">
         <f t="array" ref="L8">_xlfn.REGEXEXTRACT(B8,"(?&lt;=//)[^/]+")</f>
-        <v>www.hqbdsm.com</v>
+        <v>heavyfetish.com</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O8" s="2" t="str" cm="1">
-        <f t="array" ref="O8">IF(N8&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N8,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O8">IF(N8&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N8,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
         <f>IF(ISBLANK(I9)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>989</v>
+        <v>886</v>
       </c>
       <c r="C9" s="2">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>997</v>
+        <v>524</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>988</v>
+        <v>529</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>993</v>
+        <v>887</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>98</v>
+        <v>888</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>82</v>
@@ -4247,57 +4246,57 @@
         <v>9</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>994</v>
+        <v>889</v>
       </c>
       <c r="L9" s="2" t="str" cm="1">
         <f t="array" ref="L9">_xlfn.REGEXEXTRACT(B9,"(?&lt;=//)[^/]+")</f>
-        <v>www.tnaflix.com</v>
+        <v>bdsmlust.com</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>991</v>
+        <v>1010</v>
       </c>
       <c r="O9" s="2" t="str" cm="1">
-        <f t="array" ref="O9">IF(N9&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N9,"\d+(?=p)"),"invalid")</f>
-        <v>720</v>
+        <f t="array" ref="O9">IF(N9&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N9,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>990</v>
+        <v>1010</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>992</v>
+        <v>1010</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
         <f>IF(ISBLANK(I10)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>152</v>
+        <v>820</v>
       </c>
       <c r="C10" s="2">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>291</v>
+        <v>821</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>784</v>
+        <v>824</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>747</v>
+        <v>825</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>82</v>
@@ -4306,116 +4305,116 @@
         <v>9</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>956</v>
+        <v>826</v>
       </c>
       <c r="L10" s="2" t="str" cm="1">
         <f t="array" ref="L10">_xlfn.REGEXEXTRACT(B10,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.hqbdsm.com</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>875</v>
+        <v>1010</v>
       </c>
       <c r="O10" s="2" t="str" cm="1">
-        <f t="array" ref="O10">IF(N10&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N10,"\d+(?=p)"),"invalid")</f>
-        <v>720</v>
+        <f t="array" ref="O10">IF(N10&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N10,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>905</v>
+        <v>1010</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>898</v>
+        <v>1010</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
         <f>IF(ISBLANK(I11)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>935</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>1008</v>
+        <v>524</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>873</v>
+        <v>147</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>89</v>
+        <v>148</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>944</v>
+        <v>411</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>936</v>
+        <v>708</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>82</v>
       </c>
       <c r="J11" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>937</v>
+        <v>149</v>
       </c>
       <c r="L11" s="2" t="str" cm="1">
         <f t="array" ref="L11">_xlfn.REGEXEXTRACT(B11,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>spankbang.com</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O11" s="2" t="str" cm="1">
-        <f t="array" ref="O11">IF(N11&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N11,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O11">IF(N11&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N11,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
         <f>IF(ISBLANK(I12)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>314</v>
+        <v>933</v>
       </c>
       <c r="C12" s="2">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>524</v>
+        <v>1006</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>529</v>
+        <v>872</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>538</v>
+        <v>942</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>433</v>
+        <v>934</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>82</v>
@@ -4424,39 +4423,39 @@
         <v>8</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>333</v>
+        <v>935</v>
       </c>
       <c r="L12" s="2" t="str" cm="1">
         <f t="array" ref="L12">_xlfn.REGEXEXTRACT(B12,"(?&lt;=//)[^/]+")</f>
-        <v>www.fuq.com</v>
+        <v>bdsmstreak.com</v>
       </c>
       <c r="M12" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O12" s="2" t="str" cm="1">
-        <f t="array" ref="O12">IF(N12&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N12,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O12">IF(N12&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N12,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
         <f>IF(ISBLANK(I13)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>369</v>
+        <v>314</v>
       </c>
       <c r="C13" s="2">
         <v>0</v>
@@ -4468,13 +4467,13 @@
         <v>529</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>409</v>
+        <v>538</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>82</v>
@@ -4483,39 +4482,39 @@
         <v>8</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>378</v>
+        <v>333</v>
       </c>
       <c r="L13" s="2" t="str" cm="1">
         <f t="array" ref="L13">_xlfn.REGEXEXTRACT(B13,"(?&lt;=//)[^/]+")</f>
-        <v>www.tubebdsm.com</v>
+        <v>www.fuq.com</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O13" s="2" t="str" cm="1">
-        <f t="array" ref="O13">IF(N13&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N13,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O13">IF(N13&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N13,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
         <f>IF(ISBLANK(I14)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C14" s="2">
         <v>0</v>
@@ -4527,13 +4526,13 @@
         <v>529</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>542</v>
+        <v>409</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>742</v>
+        <v>434</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>82</v>
@@ -4542,7 +4541,7 @@
         <v>8</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>491</v>
+        <v>378</v>
       </c>
       <c r="L14" s="2" t="str" cm="1">
         <f t="array" ref="L14">_xlfn.REGEXEXTRACT(B14,"(?&lt;=//)[^/]+")</f>
@@ -4552,47 +4551,47 @@
         <v>814</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O14" s="2" t="str" cm="1">
-        <f t="array" ref="O14">IF(N14&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N14,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O14">IF(N14&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N14,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
         <f>IF(ISBLANK(I15)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C15" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1006</v>
+        <v>524</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>552</v>
+        <v>542</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>82</v>
@@ -4601,57 +4600,57 @@
         <v>8</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>558</v>
+        <v>491</v>
       </c>
       <c r="L15" s="2" t="str" cm="1">
         <f t="array" ref="L15">_xlfn.REGEXEXTRACT(B15,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
+        <v>www.tubebdsm.com</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O15" s="2" t="str" cm="1">
-        <f t="array" ref="O15">IF(N15&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N15,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O15">IF(N15&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N15,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
         <f>IF(ISBLANK(I16)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>860</v>
+        <v>367</v>
       </c>
       <c r="C16" s="2">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>861</v>
+        <v>531</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>971</v>
+        <v>552</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>969</v>
+        <v>745</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>82</v>
@@ -4660,57 +4659,57 @@
         <v>8</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>970</v>
+        <v>558</v>
       </c>
       <c r="L16" s="2" t="str" cm="1">
         <f t="array" ref="L16">_xlfn.REGEXEXTRACT(B16,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>xhamster44.desi</v>
       </c>
       <c r="M16" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O16" s="2" t="str" cm="1">
-        <f t="array" ref="O16">IF(N16&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N16,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O16">IF(N16&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N16,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
         <f>IF(ISBLANK(I17)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>796</v>
+        <v>860</v>
       </c>
       <c r="C17" s="2">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>798</v>
+        <v>861</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>804</v>
+        <v>969</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>803</v>
+        <v>967</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>82</v>
@@ -4719,57 +4718,57 @@
         <v>8</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>805</v>
+        <v>968</v>
       </c>
       <c r="L17" s="2" t="str" cm="1">
         <f t="array" ref="L17">_xlfn.REGEXEXTRACT(B17,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
+        <v>heavyfetish.com</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O17" s="2" t="str" cm="1">
-        <f t="array" ref="O17">IF(N17&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N17,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O17">IF(N17&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N17,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
         <f>IF(ISBLANK(I18)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>73</v>
+        <v>796</v>
       </c>
       <c r="C18" s="2">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>529</v>
+        <v>798</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>596</v>
+        <v>804</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>432</v>
+        <v>803</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>82</v>
@@ -4778,57 +4777,57 @@
         <v>8</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>280</v>
+        <v>805</v>
       </c>
       <c r="L18" s="2" t="str" cm="1">
         <f t="array" ref="L18">_xlfn.REGEXEXTRACT(B18,"(?&lt;=//)[^/]+")</f>
-        <v>tube.perverzija.com</v>
+        <v>abxxx.com</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O18" s="2" t="str" cm="1">
-        <f t="array" ref="O18">IF(N18&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N18,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O18">IF(N18&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N18,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
         <f>IF(ISBLANK(I19)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>376</v>
+        <v>73</v>
       </c>
       <c r="C19" s="2">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>377</v>
+        <v>529</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>566</v>
+        <v>596</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>756</v>
+        <v>432</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>82</v>
@@ -4837,116 +4836,116 @@
         <v>8</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>603</v>
+        <v>280</v>
       </c>
       <c r="L19" s="2" t="str" cm="1">
         <f t="array" ref="L19">_xlfn.REGEXEXTRACT(B19,"(?&lt;=//)[^/]+")</f>
-        <v>abxxx.com</v>
+        <v>tube.perverzija.com</v>
       </c>
       <c r="M19" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O19" s="2" t="str" cm="1">
-        <f t="array" ref="O19">IF(N19&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N19,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O19">IF(N19&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N19,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
         <f>IF(ISBLANK(I20)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>143</v>
+        <v>376</v>
       </c>
       <c r="C20" s="2">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>266</v>
+        <v>377</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>674</v>
+        <v>566</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>704</v>
+        <v>756</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>82</v>
       </c>
       <c r="J20" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>760</v>
+        <v>603</v>
       </c>
       <c r="L20" s="2" t="str" cm="1">
         <f t="array" ref="L20">_xlfn.REGEXEXTRACT(B20,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>abxxx.com</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O20" s="2" t="str" cm="1">
-        <f t="array" ref="O20">IF(N20&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N20,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O20">IF(N20&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N20,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
         <f>IF(ISBLANK(I21)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>43</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>229</v>
+        <v>266</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>809</v>
+        <v>674</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>832</v>
+        <v>704</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>82</v>
@@ -4955,57 +4954,57 @@
         <v>7</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>95</v>
+        <v>760</v>
       </c>
       <c r="L21" s="2" t="str" cm="1">
         <f t="array" ref="L21">_xlfn.REGEXEXTRACT(B21,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmstreak.com</v>
+        <v>m.hqporner.com</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O21" s="2" t="str" cm="1">
-        <f t="array" ref="O21">IF(N21&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N21,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O21">IF(N21&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N21,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
         <f>IF(ISBLANK(I22)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="C22" s="2">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>670</v>
+        <v>809</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>436</v>
+        <v>832</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>82</v>
@@ -5014,57 +5013,57 @@
         <v>7</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>957</v>
+        <v>95</v>
       </c>
       <c r="L22" s="2" t="str" cm="1">
         <f t="array" ref="L22">_xlfn.REGEXEXTRACT(B22,"(?&lt;=//)[^/]+")</f>
-        <v>m.hqporner.com</v>
+        <v>bdsmstreak.com</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O22" s="2" t="str" cm="1">
-        <f t="array" ref="O22">IF(N22&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N22,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O22">IF(N22&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N22,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
         <f>IF(ISBLANK(I23)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>818</v>
+        <v>145</v>
       </c>
       <c r="C23" s="2">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>819</v>
+        <v>257</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>884</v>
+        <v>670</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>882</v>
+        <v>436</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>82</v>
@@ -5073,57 +5072,57 @@
         <v>7</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>883</v>
+        <v>955</v>
       </c>
       <c r="L23" s="2" t="str" cm="1">
         <f t="array" ref="L23">_xlfn.REGEXEXTRACT(B23,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>m.hqporner.com</v>
       </c>
       <c r="M23" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O23" s="2" t="str" cm="1">
-        <f t="array" ref="O23">IF(N23&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N23,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O23">IF(N23&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N23,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
         <f>IF(ISBLANK(I24)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>65</v>
+        <v>818</v>
       </c>
       <c r="C24" s="2">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>526</v>
+        <v>1006</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>531</v>
+        <v>819</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>576</v>
+        <v>883</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>761</v>
+        <v>881</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>82</v>
@@ -5132,42 +5131,42 @@
         <v>7</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>609</v>
+        <v>882</v>
       </c>
       <c r="L24" s="2" t="str" cm="1">
         <f t="array" ref="L24">_xlfn.REGEXEXTRACT(B24,"(?&lt;=//)[^/]+")</f>
-        <v>punishworld.com</v>
+        <v>heavyfetish.com</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O24" s="2" t="str" cm="1">
-        <f t="array" ref="O24">IF(N24&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N24,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O24">IF(N24&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N24,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
         <f>IF(ISBLANK(I25)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>364</v>
+        <v>65</v>
       </c>
       <c r="C25" s="2">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>526</v>
@@ -5179,10 +5178,10 @@
         <v>88</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>593</v>
+        <v>576</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>751</v>
+        <v>761</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>82</v>
@@ -5191,57 +5190,57 @@
         <v>7</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="L25" s="2" t="str" cm="1">
         <f t="array" ref="L25">_xlfn.REGEXEXTRACT(B25,"(?&lt;=//)[^/]+")</f>
-        <v>xhamster44.desi</v>
+        <v>punishworld.com</v>
       </c>
       <c r="M25" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O25" s="2" t="str" cm="1">
-        <f t="array" ref="O25">IF(N25&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N25,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O25">IF(N25&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N25,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
         <f>IF(ISBLANK(I26)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>502</v>
+        <v>364</v>
       </c>
       <c r="C26" s="2">
-        <v>48</v>
+        <v>99</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>1007</v>
+        <v>526</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>623</v>
+        <v>593</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>735</v>
+        <v>751</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>82</v>
@@ -5250,57 +5249,57 @@
         <v>7</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>554</v>
+        <v>613</v>
       </c>
       <c r="L26" s="2" t="str" cm="1">
         <f t="array" ref="L26">_xlfn.REGEXEXTRACT(B26,"(?&lt;=//)[^/]+")</f>
-        <v>www.pornhits.com</v>
+        <v>xhamster44.desi</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O26" s="2" t="str" cm="1">
-        <f t="array" ref="O26">IF(N26&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N26,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O26">IF(N26&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N26,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
         <f>IF(ISBLANK(I27)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>321</v>
+        <v>502</v>
       </c>
       <c r="C27" s="2">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>266</v>
+        <v>509</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>100</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>547</v>
+        <v>623</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>711</v>
+        <v>735</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>82</v>
@@ -5309,57 +5308,57 @@
         <v>7</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>544</v>
+        <v>554</v>
       </c>
       <c r="L27" s="2" t="str" cm="1">
         <f t="array" ref="L27">_xlfn.REGEXEXTRACT(B27,"(?&lt;=//)[^/]+")</f>
-        <v>heavyfetish.com</v>
+        <v>www.pornhits.com</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O27" s="2" t="str" cm="1">
-        <f t="array" ref="O27">IF(N27&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N27,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O27">IF(N27&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N27,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
         <f>IF(ISBLANK(I28)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>374</v>
+        <v>321</v>
       </c>
       <c r="C28" s="2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>531</v>
+        <v>266</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>100</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>571</v>
+        <v>547</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>487</v>
+        <v>711</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>82</v>
@@ -5368,57 +5367,57 @@
         <v>7</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>606</v>
+        <v>544</v>
       </c>
       <c r="L28" s="2" t="str" cm="1">
         <f t="array" ref="L28">_xlfn.REGEXEXTRACT(B28,"(?&lt;=//)[^/]+")</f>
-        <v>www.fapcat.com</v>
+        <v>heavyfetish.com</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O28" s="2" t="str" cm="1">
-        <f t="array" ref="O28">IF(N28&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N28,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O28">IF(N28&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N28,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
         <f>IF(ISBLANK(I29)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>795</v>
+        <v>374</v>
       </c>
       <c r="C29" s="2">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>526</v>
+        <v>1005</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>531</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>238</v>
+        <v>100</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>799</v>
+        <v>571</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>940</v>
+        <v>487</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>82</v>
@@ -5427,57 +5426,57 @@
         <v>7</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>939</v>
+        <v>606</v>
       </c>
       <c r="L29" s="2" t="str" cm="1">
         <f t="array" ref="L29">_xlfn.REGEXEXTRACT(B29,"(?&lt;=//)[^/]+")</f>
-        <v>www.amateur8.com</v>
+        <v>www.fapcat.com</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O29" s="2" t="str" cm="1">
-        <f t="array" ref="O29">IF(N29&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N29,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O29">IF(N29&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N29,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
         <f>IF(ISBLANK(I30)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>872</v>
+        <v>795</v>
       </c>
       <c r="C30" s="2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>873</v>
+        <v>531</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>88</v>
+        <v>238</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>877</v>
+        <v>799</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>879</v>
+        <v>938</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>82</v>
@@ -5486,39 +5485,39 @@
         <v>7</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>874</v>
+        <v>937</v>
       </c>
       <c r="L30" s="2" t="str" cm="1">
         <f t="array" ref="L30">_xlfn.REGEXEXTRACT(B30,"(?&lt;=//)[^/]+")</f>
-        <v>bdsmmansion.com</v>
+        <v>www.amateur8.com</v>
       </c>
       <c r="M30" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O30" s="2" t="str" cm="1">
-        <f t="array" ref="O30">IF(N30&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N30,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O30">IF(N30&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N30,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
         <f>IF(ISBLANK(I31)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>311</v>
+        <v>871</v>
       </c>
       <c r="C31" s="2">
         <v>0</v>
@@ -5527,16 +5526,16 @@
         <v>524</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>529</v>
+        <v>872</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>330</v>
+        <v>88</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>524</v>
+        <v>876</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>449</v>
+        <v>878</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>82</v>
@@ -5545,57 +5544,57 @@
         <v>7</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>341</v>
+        <v>873</v>
       </c>
       <c r="L31" s="2" t="str" cm="1">
         <f t="array" ref="L31">_xlfn.REGEXEXTRACT(B31,"(?&lt;=//)[^/]+")</f>
-        <v>beeg.com</v>
+        <v>bdsmmansion.com</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O31" s="2" t="str" cm="1">
-        <f t="array" ref="O31">IF(N31&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N31,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O31">IF(N31&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N31,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
         <f>IF(ISBLANK(I32)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2">
         <v>0</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>529</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>100</v>
+        <v>330</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>849</v>
+        <v>524</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>710</v>
+        <v>449</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>82</v>
@@ -5604,7 +5603,7 @@
         <v>7</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="L32" s="2" t="str" cm="1">
         <f t="array" ref="L32">_xlfn.REGEXEXTRACT(B32,"(?&lt;=//)[^/]+")</f>
@@ -5614,47 +5613,47 @@
         <v>814</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O32" s="2" t="str" cm="1">
-        <f t="array" ref="O32">IF(N32&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N32,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O32">IF(N32&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N32,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
         <f>IF(ISBLANK(I33)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>146</v>
+        <v>313</v>
       </c>
       <c r="C33" s="2">
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>147</v>
+        <v>529</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>411</v>
+        <v>849</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>82</v>
@@ -5663,33 +5662,33 @@
         <v>7</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>149</v>
+        <v>332</v>
       </c>
       <c r="L33" s="2" t="str" cm="1">
         <f t="array" ref="L33">_xlfn.REGEXEXTRACT(B33,"(?&lt;=//)[^/]+")</f>
-        <v>spankbang.com</v>
+        <v>beeg.com</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O33" s="2" t="str" cm="1">
-        <f t="array" ref="O33">IF(N33&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N33,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O33">IF(N33&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N33,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
         <f>IF(ISBLANK(I34)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -5732,23 +5731,23 @@
         <v>814</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O34" s="2" t="str" cm="1">
-        <f t="array" ref="O34">IF(N34&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N34,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O34">IF(N34&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N34,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="str">
         <f>IF(ISBLANK(I35)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -5760,7 +5759,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>529</v>
@@ -5791,23 +5790,23 @@
         <v>814</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O35" s="2" t="str" cm="1">
-        <f t="array" ref="O35">IF(N35&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N35,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O35">IF(N35&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N35,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="str">
         <f>IF(ISBLANK(I36)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -5850,23 +5849,23 @@
         <v>814</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O36" s="2" t="str" cm="1">
-        <f t="array" ref="O36">IF(N36&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N36,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O36">IF(N36&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N36,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P36" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="str">
         <f>IF(ISBLANK(I37)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -5878,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>529</v>
@@ -5909,23 +5908,23 @@
         <v>814</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O37" s="2" t="str" cm="1">
-        <f t="array" ref="O37">IF(N37&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N37,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O37">IF(N37&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N37,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q37" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R37" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="str">
         <f>IF(ISBLANK(I38)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -5968,23 +5967,23 @@
         <v>814</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O38" s="2" t="str" cm="1">
-        <f t="array" ref="O38">IF(N38&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N38,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O38">IF(N38&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N38,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q38" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R38" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="str">
         <f>IF(ISBLANK(I39)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6027,23 +6026,23 @@
         <v>814</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O39" s="2" t="str" cm="1">
-        <f t="array" ref="O39">IF(N39&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N39,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O39">IF(N39&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N39,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q39" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R39" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="40" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="str">
         <f>IF(ISBLANK(I40)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6055,7 +6054,7 @@
         <v>46</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>384</v>
@@ -6086,23 +6085,23 @@
         <v>814</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O40" s="2" t="str" cm="1">
-        <f t="array" ref="O40">IF(N40&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N40,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O40">IF(N40&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N40,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P40" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q40" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R40" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="41" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="str">
         <f>IF(ISBLANK(I41)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6145,35 +6144,35 @@
         <v>814</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O41" s="2" t="str" cm="1">
-        <f t="array" ref="O41">IF(N41&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N41,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O41">IF(N41&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N41,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P41" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q41" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R41" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="42" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="str">
         <f>IF(ISBLANK(I42)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="C42" s="2">
         <v>57</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>338</v>
@@ -6204,23 +6203,23 @@
         <v>814</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O42" s="2" t="str" cm="1">
-        <f t="array" ref="O42">IF(N42&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N42,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O42">IF(N42&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N42,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q42" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R42" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="43" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="str">
         <f>IF(ISBLANK(I43)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6232,7 +6231,7 @@
         <v>51</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>862</v>
@@ -6241,10 +6240,10 @@
         <v>88</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>82</v>
@@ -6253,7 +6252,7 @@
         <v>7</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="L43" s="2" t="str" cm="1">
         <f t="array" ref="L43">_xlfn.REGEXEXTRACT(B43,"(?&lt;=//)[^/]+")</f>
@@ -6263,23 +6262,23 @@
         <v>814</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O43" s="2" t="str" cm="1">
-        <f t="array" ref="O43">IF(N43&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N43,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O43">IF(N43&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N43,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q43" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R43" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="44" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="str">
         <f>IF(ISBLANK(I44)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6291,7 +6290,7 @@
         <v>73</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>290</v>
@@ -6322,23 +6321,23 @@
         <v>814</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O44" s="2" t="str" cm="1">
-        <f t="array" ref="O44">IF(N44&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N44,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O44">IF(N44&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N44,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q44" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R44" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="str">
         <f>IF(ISBLANK(I45)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6350,7 +6349,7 @@
         <v>85</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>383</v>
@@ -6381,23 +6380,23 @@
         <v>814</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O45" s="2" t="str" cm="1">
-        <f t="array" ref="O45">IF(N45&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N45,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O45">IF(N45&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N45,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q45" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R45" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="46" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="str">
         <f>IF(ISBLANK(I46)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6409,7 +6408,7 @@
         <v>51</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>532</v>
@@ -6440,47 +6439,47 @@
         <v>814</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O46" s="2" t="str" cm="1">
-        <f t="array" ref="O46">IF(N46&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N46,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O46">IF(N46&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N46,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q46" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R46" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="str">
         <f>IF(ISBLANK(I47)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C47" s="2">
         <v>51</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G47" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>966</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>968</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>82</v>
@@ -6489,7 +6488,7 @@
         <v>7</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="L47" s="2" t="str" cm="1">
         <f t="array" ref="L47">_xlfn.REGEXEXTRACT(B47,"(?&lt;=//)[^/]+")</f>
@@ -6499,23 +6498,23 @@
         <v>814</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O47" s="2" t="str" cm="1">
-        <f t="array" ref="O47">IF(N47&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N47,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O47">IF(N47&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N47,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q47" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R47" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="str">
         <f>IF(ISBLANK(I48)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6527,7 +6526,7 @@
         <v>56</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>264</v>
@@ -6558,23 +6557,23 @@
         <v>814</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O48" s="2" t="str" cm="1">
-        <f t="array" ref="O48">IF(N48&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N48,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O48">IF(N48&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N48,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R48" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="str">
         <f>IF(ISBLANK(I49)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6586,7 +6585,7 @@
         <v>53</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>230</v>
@@ -6617,47 +6616,47 @@
         <v>814</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O49" s="2" t="str" cm="1">
-        <f t="array" ref="O49">IF(N49&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N49,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O49">IF(N49&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N49,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q49" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R49" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="50" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="str">
         <f>IF(ISBLANK(I50)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C50" s="2">
         <v>39</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>82</v>
@@ -6666,7 +6665,7 @@
         <v>6</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="L50" s="2" t="str" cm="1">
         <f t="array" ref="L50">_xlfn.REGEXEXTRACT(B50,"(?&lt;=//)[^/]+")</f>
@@ -6676,23 +6675,23 @@
         <v>814</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O50" s="2" t="str" cm="1">
-        <f t="array" ref="O50">IF(N50&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N50,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O50">IF(N50&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N50,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P50" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q50" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R50" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="51" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="str">
         <f>IF(ISBLANK(I51)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6704,7 +6703,7 @@
         <v>64</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>510</v>
@@ -6735,23 +6734,23 @@
         <v>814</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O51" s="2" t="str" cm="1">
-        <f t="array" ref="O51">IF(N51&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N51,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O51">IF(N51&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N51,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q51" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R51" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="str">
         <f>IF(ISBLANK(I52)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6763,7 +6762,7 @@
         <v>58</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>505</v>
@@ -6794,29 +6793,29 @@
         <v>814</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O52" s="2" t="str" cm="1">
-        <f t="array" ref="O52">IF(N52&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N52,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O52">IF(N52&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N52,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P52" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q52" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R52" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="53" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="str">
         <f>IF(ISBLANK(I53)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="C53" s="2">
         <v>12</v>
@@ -6825,13 +6824,13 @@
         <v>525</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="F53" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>835</v>
@@ -6843,7 +6842,7 @@
         <v>6</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
       <c r="L53" s="2" t="str" cm="1">
         <f t="array" ref="L53">_xlfn.REGEXEXTRACT(B53,"(?&lt;=//)[^/]+")</f>
@@ -6853,29 +6852,29 @@
         <v>814</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O53" s="2" t="str" cm="1">
-        <f t="array" ref="O53">IF(N53&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N53,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O53">IF(N53&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N53,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P53" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q53" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R53" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="54" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="str">
         <f>IF(ISBLANK(I54)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="C54" s="2">
         <v>3</v>
@@ -6884,13 +6883,13 @@
         <v>525</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>835</v>
@@ -6902,7 +6901,7 @@
         <v>6</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="L54" s="2" t="str" cm="1">
         <f t="array" ref="L54">_xlfn.REGEXEXTRACT(B54,"(?&lt;=//)[^/]+")</f>
@@ -6912,23 +6911,23 @@
         <v>814</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O54" s="2" t="str" cm="1">
-        <f t="array" ref="O54">IF(N54&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N54,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O54">IF(N54&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N54,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q54" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R54" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="55" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="str">
         <f>IF(ISBLANK(I55)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6971,23 +6970,23 @@
         <v>814</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O55" s="2" t="str" cm="1">
-        <f t="array" ref="O55">IF(N55&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N55,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O55">IF(N55&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N55,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q55" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R55" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="56" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="str">
         <f>IF(ISBLANK(I56)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -6999,7 +6998,7 @@
         <v>0</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>529</v>
@@ -7030,23 +7029,23 @@
         <v>814</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O56" s="2" t="str" cm="1">
-        <f t="array" ref="O56">IF(N56&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N56,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O56">IF(N56&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N56,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q56" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R56" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="57" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="str">
         <f>IF(ISBLANK(I57)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7058,7 +7057,7 @@
         <v>0</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>529</v>
@@ -7089,23 +7088,23 @@
         <v>814</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O57" s="2" t="str" cm="1">
-        <f t="array" ref="O57">IF(N57&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N57,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O57">IF(N57&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N57,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q57" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R57" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="58" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="str">
         <f>IF(ISBLANK(I58)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7148,23 +7147,23 @@
         <v>814</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O58" s="2" t="str" cm="1">
-        <f t="array" ref="O58">IF(N58&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N58,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O58">IF(N58&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N58,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P58" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q58" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R58" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="59" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="str">
         <f>IF(ISBLANK(I59)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7207,23 +7206,23 @@
         <v>814</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O59" s="2" t="str" cm="1">
-        <f t="array" ref="O59">IF(N59&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N59,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O59">IF(N59&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N59,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P59" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q59" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R59" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="60" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="str">
         <f>IF(ISBLANK(I60)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7266,23 +7265,23 @@
         <v>814</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O60" s="2" t="str" cm="1">
-        <f t="array" ref="O60">IF(N60&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N60,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O60">IF(N60&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N60,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P60" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q60" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R60" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="61" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="str">
         <f>IF(ISBLANK(I61)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7325,23 +7324,23 @@
         <v>814</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O61" s="2" t="str" cm="1">
-        <f t="array" ref="O61">IF(N61&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N61,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O61">IF(N61&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N61,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P61" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q61" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R61" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="62" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="str">
         <f>IF(ISBLANK(I62)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7374,7 +7373,7 @@
         <v>6</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="L62" s="2" t="str" cm="1">
         <f t="array" ref="L62">_xlfn.REGEXEXTRACT(B62,"(?&lt;=//)[^/]+")</f>
@@ -7384,23 +7383,23 @@
         <v>814</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O62" s="2" t="str" cm="1">
-        <f t="array" ref="O62">IF(N62&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N62,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O62">IF(N62&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N62,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P62" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q62" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R62" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="63" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="str">
         <f>IF(ISBLANK(I63)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7443,23 +7442,23 @@
         <v>814</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O63" s="2" t="str" cm="1">
-        <f t="array" ref="O63">IF(N63&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N63,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O63">IF(N63&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N63,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P63" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q63" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R63" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="64" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="str">
         <f>IF(ISBLANK(I64)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7502,23 +7501,23 @@
         <v>814</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O64" s="2" t="str" cm="1">
-        <f t="array" ref="O64">IF(N64&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N64,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O64">IF(N64&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N64,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P64" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q64" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R64" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="65" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="str">
         <f>IF(ISBLANK(I65)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7561,23 +7560,23 @@
         <v>814</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O65" s="2" t="str" cm="1">
-        <f t="array" ref="O65">IF(N65&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N65,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O65">IF(N65&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N65,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P65" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q65" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R65" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="66" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="str">
         <f>IF(ISBLANK(I66)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7620,23 +7619,23 @@
         <v>814</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O66" s="2" t="str" cm="1">
-        <f t="array" ref="O66">IF(N66&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N66,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O66">IF(N66&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N66,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P66" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q66" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R66" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="67" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="str">
         <f>IF(ISBLANK(I67)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7679,23 +7678,23 @@
         <v>814</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O67" s="2" t="str" cm="1">
-        <f t="array" ref="O67">IF(N67&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N67,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O67">IF(N67&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N67,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P67" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q67" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R67" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="68" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="str">
         <f>IF(ISBLANK(I68)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7738,23 +7737,23 @@
         <v>814</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O68" s="2" t="str" cm="1">
-        <f t="array" ref="O68">IF(N68&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N68,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O68">IF(N68&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N68,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P68" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q68" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R68" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="69" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="str">
         <f>IF(ISBLANK(I69)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7797,23 +7796,23 @@
         <v>814</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O69" s="2" t="str" cm="1">
-        <f t="array" ref="O69">IF(N69&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N69,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O69">IF(N69&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N69,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P69" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q69" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R69" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="70" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="str">
         <f>IF(ISBLANK(I70)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7856,23 +7855,23 @@
         <v>814</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O70" s="2" t="str" cm="1">
-        <f t="array" ref="O70">IF(N70&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N70,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O70">IF(N70&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N70,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P70" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q70" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R70" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="71" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="str">
         <f>IF(ISBLANK(I71)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7915,23 +7914,23 @@
         <v>814</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O71" s="2" t="str" cm="1">
-        <f t="array" ref="O71">IF(N71&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N71,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O71">IF(N71&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N71,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P71" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q71" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R71" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="str">
         <f>IF(ISBLANK(I72)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -7974,23 +7973,23 @@
         <v>814</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O72" s="2" t="str" cm="1">
-        <f t="array" ref="O72">IF(N72&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N72,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O72">IF(N72&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N72,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P72" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q72" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R72" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="73" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="str">
         <f>IF(ISBLANK(I73)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8033,23 +8032,23 @@
         <v>814</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O73" s="2" t="str" cm="1">
-        <f t="array" ref="O73">IF(N73&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N73,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O73">IF(N73&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N73,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P73" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q73" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R73" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="str">
         <f>IF(ISBLANK(I74)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8092,23 +8091,23 @@
         <v>814</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O74" s="2" t="str" cm="1">
-        <f t="array" ref="O74">IF(N74&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N74,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O74">IF(N74&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N74,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P74" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q74" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R74" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="75" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="str">
         <f>IF(ISBLANK(I75)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8120,7 +8119,7 @@
         <v>66</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>284</v>
@@ -8151,23 +8150,23 @@
         <v>814</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O75" s="2" t="str" cm="1">
-        <f t="array" ref="O75">IF(N75&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N75,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O75">IF(N75&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N75,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P75" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q75" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R75" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="76" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="str">
         <f>IF(ISBLANK(I76)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8210,23 +8209,23 @@
         <v>814</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O76" s="2" t="str" cm="1">
-        <f t="array" ref="O76">IF(N76&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N76,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O76">IF(N76&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N76,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P76" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q76" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R76" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="77" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="str">
         <f>IF(ISBLANK(I77)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8269,23 +8268,23 @@
         <v>814</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O77" s="2" t="str" cm="1">
-        <f t="array" ref="O77">IF(N77&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N77,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O77">IF(N77&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N77,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P77" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q77" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R77" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="78" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="str">
         <f>IF(ISBLANK(I78)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8297,7 +8296,7 @@
         <v>45</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>182</v>
@@ -8328,23 +8327,23 @@
         <v>814</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O78" s="2" t="str" cm="1">
-        <f t="array" ref="O78">IF(N78&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N78,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O78">IF(N78&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N78,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P78" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q78" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R78" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="79" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="str">
         <f>IF(ISBLANK(I79)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8356,7 +8355,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>529</v>
@@ -8387,23 +8386,23 @@
         <v>814</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O79" s="2" t="str" cm="1">
-        <f t="array" ref="O79">IF(N79&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N79,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O79">IF(N79&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N79,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P79" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q79" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R79" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="str">
         <f>IF(ISBLANK(I80)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8415,7 +8414,7 @@
         <v>51</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>232</v>
@@ -8446,23 +8445,23 @@
         <v>814</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O80" s="2" t="str" cm="1">
-        <f t="array" ref="O80">IF(N80&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N80,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O80">IF(N80&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N80,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P80" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q80" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R80" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="81" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="str">
         <f>IF(ISBLANK(I81)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8474,7 +8473,7 @@
         <v>50</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>408</v>
@@ -8505,23 +8504,23 @@
         <v>814</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O81" s="2" t="str" cm="1">
-        <f t="array" ref="O81">IF(N81&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N81,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O81">IF(N81&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N81,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P81" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q81" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R81" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="82" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="str">
         <f>IF(ISBLANK(I82)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8533,7 +8532,7 @@
         <v>0</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>529</v>
@@ -8564,23 +8563,23 @@
         <v>814</v>
       </c>
       <c r="N82" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O82" s="2" t="str" cm="1">
-        <f t="array" ref="O82">IF(N82&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N82,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O82">IF(N82&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N82,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P82" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q82" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R82" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="83" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="str">
         <f>IF(ISBLANK(I83)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8592,7 +8591,7 @@
         <v>0</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>529</v>
@@ -8623,23 +8622,23 @@
         <v>814</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O83" s="2" t="str" cm="1">
-        <f t="array" ref="O83">IF(N83&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N83,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O83">IF(N83&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N83,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P83" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q83" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R83" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="84" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="str">
         <f>IF(ISBLANK(I84)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8651,7 +8650,7 @@
         <v>83</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>229</v>
@@ -8682,23 +8681,23 @@
         <v>814</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O84" s="2" t="str" cm="1">
-        <f t="array" ref="O84">IF(N84&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N84,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O84">IF(N84&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N84,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P84" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q84" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R84" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="85" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="str">
         <f>IF(ISBLANK(I85)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8710,7 +8709,7 @@
         <v>57</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>269</v>
@@ -8741,23 +8740,23 @@
         <v>814</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O85" s="2" t="str" cm="1">
-        <f t="array" ref="O85">IF(N85&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N85,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O85">IF(N85&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N85,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P85" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q85" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R85" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="86" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="str">
         <f>IF(ISBLANK(I86)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8769,7 +8768,7 @@
         <v>89</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>386</v>
@@ -8778,7 +8777,7 @@
         <v>88</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>454</v>
@@ -8800,23 +8799,23 @@
         <v>814</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O86" s="2" t="str" cm="1">
-        <f t="array" ref="O86">IF(N86&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N86,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O86">IF(N86&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N86,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P86" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q86" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R86" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="87" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="str">
         <f>IF(ISBLANK(I87)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8828,7 +8827,7 @@
         <v>58</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>387</v>
@@ -8859,23 +8858,23 @@
         <v>814</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O87" s="2" t="str" cm="1">
-        <f t="array" ref="O87">IF(N87&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N87,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O87">IF(N87&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N87,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P87" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q87" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R87" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="88" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="str">
         <f>IF(ISBLANK(I88)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8887,7 +8886,7 @@
         <v>55</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>208</v>
@@ -8918,23 +8917,23 @@
         <v>814</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O88" s="2" t="str" cm="1">
-        <f t="array" ref="O88">IF(N88&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N88,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O88">IF(N88&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N88,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P88" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q88" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R88" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="89" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="str">
         <f>IF(ISBLANK(I89)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -8946,7 +8945,7 @@
         <v>46</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>248</v>
@@ -8967,7 +8966,7 @@
         <v>5</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="L89" s="2" t="str" cm="1">
         <f t="array" ref="L89">_xlfn.REGEXEXTRACT(B89,"(?&lt;=//)[^/]+")</f>
@@ -8977,23 +8976,23 @@
         <v>814</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O89" s="2" t="str" cm="1">
-        <f t="array" ref="O89">IF(N89&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N89,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O89">IF(N89&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N89,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P89" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q89" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R89" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="90" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="str">
         <f>IF(ISBLANK(I90)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9005,7 +9004,7 @@
         <v>64</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>506</v>
@@ -9036,23 +9035,23 @@
         <v>814</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O90" s="2" t="str" cm="1">
-        <f t="array" ref="O90">IF(N90&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N90,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O90">IF(N90&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N90,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P90" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q90" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R90" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="91" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="str">
         <f>IF(ISBLANK(I91)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9064,7 +9063,7 @@
         <v>57</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>232</v>
@@ -9095,23 +9094,23 @@
         <v>814</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O91" s="2" t="str" cm="1">
-        <f t="array" ref="O91">IF(N91&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N91,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O91">IF(N91&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N91,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P91" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q91" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R91" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="92" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="str">
         <f>IF(ISBLANK(I92)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9123,7 +9122,7 @@
         <v>54</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>362</v>
@@ -9154,23 +9153,23 @@
         <v>814</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O92" s="2" t="str" cm="1">
-        <f t="array" ref="O92">IF(N92&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N92,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O92">IF(N92&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N92,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P92" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q92" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R92" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="93" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="str">
         <f>IF(ISBLANK(I93)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9213,23 +9212,23 @@
         <v>814</v>
       </c>
       <c r="N93" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O93" s="2" t="str" cm="1">
-        <f t="array" ref="O93">IF(N93&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N93,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O93">IF(N93&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N93,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P93" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q93" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R93" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="94" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="str">
         <f>IF(ISBLANK(I94)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9272,23 +9271,23 @@
         <v>814</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O94" s="2" t="str" cm="1">
-        <f t="array" ref="O94">IF(N94&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N94,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O94">IF(N94&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N94,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P94" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q94" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R94" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="95" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="str">
         <f>IF(ISBLANK(I95)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9331,23 +9330,23 @@
         <v>814</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O95" s="2" t="str" cm="1">
-        <f t="array" ref="O95">IF(N95&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N95,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O95">IF(N95&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N95,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P95" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q95" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R95" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="96" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="str">
         <f>IF(ISBLANK(I96)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9362,7 +9361,7 @@
         <v>224</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>88</v>
@@ -9390,23 +9389,23 @@
         <v>814</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O96" s="2" t="str" cm="1">
-        <f t="array" ref="O96">IF(N96&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N96,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O96">IF(N96&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N96,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P96" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q96" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R96" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="97" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="str">
         <f>IF(ISBLANK(I97)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9449,23 +9448,23 @@
         <v>814</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O97" s="2" t="str" cm="1">
-        <f t="array" ref="O97">IF(N97&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N97,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O97">IF(N97&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N97,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P97" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q97" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R97" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="98" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="str">
         <f>IF(ISBLANK(I98)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9477,7 +9476,7 @@
         <v>65</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>276</v>
@@ -9508,23 +9507,23 @@
         <v>814</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O98" s="2" t="str" cm="1">
-        <f t="array" ref="O98">IF(N98&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N98,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O98">IF(N98&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N98,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P98" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q98" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R98" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="99" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="str">
         <f>IF(ISBLANK(I99)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9536,7 +9535,7 @@
         <v>62</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>275</v>
@@ -9567,23 +9566,23 @@
         <v>814</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O99" s="2" t="str" cm="1">
-        <f t="array" ref="O99">IF(N99&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N99,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O99">IF(N99&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N99,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P99" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q99" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R99" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="100" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="str">
         <f>IF(ISBLANK(I100)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9595,7 +9594,7 @@
         <v>51</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>255</v>
@@ -9626,23 +9625,23 @@
         <v>814</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O100" s="2" t="str" cm="1">
-        <f t="array" ref="O100">IF(N100&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N100,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O100">IF(N100&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N100,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P100" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q100" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R100" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="101" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="101" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="str">
         <f>IF(ISBLANK(I101)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9654,7 +9653,7 @@
         <v>43</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>388</v>
@@ -9685,23 +9684,23 @@
         <v>814</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O101" s="2" t="str" cm="1">
-        <f t="array" ref="O101">IF(N101&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N101,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O101">IF(N101&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N101,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P101" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q101" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R101" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="102" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="102" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="str">
         <f>IF(ISBLANK(I102)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9744,23 +9743,23 @@
         <v>814</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O102" s="2" t="str" cm="1">
-        <f t="array" ref="O102">IF(N102&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N102,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O102">IF(N102&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N102,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P102" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q102" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R102" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="103" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="103" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="str">
         <f>IF(ISBLANK(I103)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9803,23 +9802,23 @@
         <v>814</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O103" s="2" t="str" cm="1">
-        <f t="array" ref="O103">IF(N103&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N103,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O103">IF(N103&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N103,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P103" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q103" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R103" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="104" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="104" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="str">
         <f>IF(ISBLANK(I104)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9862,23 +9861,23 @@
         <v>814</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O104" s="2" t="str" cm="1">
-        <f t="array" ref="O104">IF(N104&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N104,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O104">IF(N104&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N104,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P104" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q104" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R104" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="105" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="105" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="str">
         <f>IF(ISBLANK(I105)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9921,23 +9920,23 @@
         <v>814</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O105" s="2" t="str" cm="1">
-        <f t="array" ref="O105">IF(N105&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N105,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O105">IF(N105&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N105,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P105" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q105" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R105" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="106" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="str">
         <f>IF(ISBLANK(I106)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -9980,23 +9979,23 @@
         <v>814</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O106" s="2" t="str" cm="1">
-        <f t="array" ref="O106">IF(N106&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N106,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O106">IF(N106&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N106,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P106" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q106" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R106" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="107" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="107" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="str">
         <f>IF(ISBLANK(I107)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10039,23 +10038,23 @@
         <v>814</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O107" s="2" t="str" cm="1">
-        <f t="array" ref="O107">IF(N107&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N107,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O107">IF(N107&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N107,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P107" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q107" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R107" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="108" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="108" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="str">
         <f>IF(ISBLANK(I108)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10098,23 +10097,23 @@
         <v>814</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O108" s="2" t="str" cm="1">
-        <f t="array" ref="O108">IF(N108&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N108,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O108">IF(N108&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N108,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P108" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q108" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R108" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="109" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="109" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="str">
         <f>IF(ISBLANK(I109)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10157,23 +10156,23 @@
         <v>814</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O109" s="2" t="str" cm="1">
-        <f t="array" ref="O109">IF(N109&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N109,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O109">IF(N109&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N109,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P109" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q109" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R109" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="110" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="110" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="str">
         <f>IF(ISBLANK(I110)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10216,23 +10215,23 @@
         <v>814</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O110" s="2" t="str" cm="1">
-        <f t="array" ref="O110">IF(N110&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N110,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O110">IF(N110&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N110,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P110" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q110" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R110" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="111" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="111" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="str">
         <f>IF(ISBLANK(I111)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10275,23 +10274,23 @@
         <v>814</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O111" s="2" t="str" cm="1">
-        <f t="array" ref="O111">IF(N111&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N111,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O111">IF(N111&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N111,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P111" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q111" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R111" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="112" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="112" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="str">
         <f>IF(ISBLANK(I112)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10334,23 +10333,23 @@
         <v>814</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O112" s="2" t="str" cm="1">
-        <f t="array" ref="O112">IF(N112&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N112,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O112">IF(N112&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N112,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P112" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q112" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R112" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="113" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="113" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="str">
         <f>IF(ISBLANK(I113)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10362,7 +10361,7 @@
         <v>54</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E113" s="2" t="s">
         <v>496</v>
@@ -10393,23 +10392,23 @@
         <v>814</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O113" s="2" t="str" cm="1">
-        <f t="array" ref="O113">IF(N113&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N113,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O113">IF(N113&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N113,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P113" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q113" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R113" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="114" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="114" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="str">
         <f>IF(ISBLANK(I114)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10421,7 +10420,7 @@
         <v>46</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E114" s="2" t="s">
         <v>340</v>
@@ -10452,23 +10451,23 @@
         <v>814</v>
       </c>
       <c r="N114" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O114" s="2" t="str" cm="1">
-        <f t="array" ref="O114">IF(N114&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N114,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O114">IF(N114&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N114,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P114" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q114" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R114" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="115" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="115" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="str">
         <f>IF(ISBLANK(I115)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10480,7 +10479,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>530</v>
@@ -10511,47 +10510,47 @@
         <v>814</v>
       </c>
       <c r="N115" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O115" s="2" t="str" cm="1">
-        <f t="array" ref="O115">IF(N115&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N115,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O115">IF(N115&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N115,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P115" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q115" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R115" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="116" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="116" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="str">
         <f>IF(ISBLANK(I116)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C116" s="2">
         <v>47</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="H116" s="2" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>82</v>
@@ -10560,7 +10559,7 @@
         <v>5</v>
       </c>
       <c r="K116" s="2" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="L116" s="2" t="str" cm="1">
         <f t="array" ref="L116">_xlfn.REGEXEXTRACT(B116,"(?&lt;=//)[^/]+")</f>
@@ -10570,23 +10569,23 @@
         <v>814</v>
       </c>
       <c r="N116" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O116" s="2" t="str" cm="1">
-        <f t="array" ref="O116">IF(N116&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N116,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O116">IF(N116&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N116,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P116" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q116" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R116" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="117" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="117" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="str">
         <f>IF(ISBLANK(I117)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10598,7 +10597,7 @@
         <v>47</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E117" s="2" t="s">
         <v>359</v>
@@ -10629,23 +10628,23 @@
         <v>814</v>
       </c>
       <c r="N117" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O117" s="2" t="str" cm="1">
-        <f t="array" ref="O117">IF(N117&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N117,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O117">IF(N117&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N117,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P117" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q117" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R117" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="118" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="118" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="str">
         <f>IF(ISBLANK(I118)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10657,10 +10656,10 @@
         <v>44</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>100</v>
@@ -10688,23 +10687,23 @@
         <v>814</v>
       </c>
       <c r="N118" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O118" s="2" t="str" cm="1">
-        <f t="array" ref="O118">IF(N118&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N118,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O118">IF(N118&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N118,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P118" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q118" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R118" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="119" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="119" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="str">
         <f>IF(ISBLANK(I119)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10716,7 +10715,7 @@
         <v>4</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>175</v>
@@ -10737,7 +10736,7 @@
         <v>5</v>
       </c>
       <c r="K119" s="2" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="L119" s="2" t="str" cm="1">
         <f t="array" ref="L119">_xlfn.REGEXEXTRACT(B119,"(?&lt;=//)[^/]+")</f>
@@ -10747,23 +10746,23 @@
         <v>814</v>
       </c>
       <c r="N119" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O119" s="2" t="str" cm="1">
-        <f t="array" ref="O119">IF(N119&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N119,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O119">IF(N119&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N119,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P119" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q119" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R119" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="120" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="120" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="str">
         <f>IF(ISBLANK(I120)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10775,7 +10774,7 @@
         <v>60</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E120" s="2" t="s">
         <v>274</v>
@@ -10806,23 +10805,23 @@
         <v>814</v>
       </c>
       <c r="N120" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O120" s="2" t="str" cm="1">
-        <f t="array" ref="O120">IF(N120&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N120,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O120">IF(N120&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N120,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P120" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q120" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R120" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="121" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="121" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="str">
         <f>IF(ISBLANK(I121)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10834,7 +10833,7 @@
         <v>50</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E121" s="2" t="s">
         <v>229</v>
@@ -10865,23 +10864,23 @@
         <v>814</v>
       </c>
       <c r="N121" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O121" s="2" t="str" cm="1">
-        <f t="array" ref="O121">IF(N121&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N121,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O121">IF(N121&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N121,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P121" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q121" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R121" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="122" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="str">
         <f>IF(ISBLANK(I122)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10893,7 +10892,7 @@
         <v>58</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>396</v>
@@ -10924,23 +10923,23 @@
         <v>814</v>
       </c>
       <c r="N122" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O122" s="2" t="str" cm="1">
-        <f t="array" ref="O122">IF(N122&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N122,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O122">IF(N122&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N122,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P122" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q122" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R122" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="123" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="123" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="str">
         <f>IF(ISBLANK(I123)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -10952,7 +10951,7 @@
         <v>42</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E123" s="2" t="s">
         <v>219</v>
@@ -10983,23 +10982,23 @@
         <v>814</v>
       </c>
       <c r="N123" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O123" s="2" t="str" cm="1">
-        <f t="array" ref="O123">IF(N123&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N123,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O123">IF(N123&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N123,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P123" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q123" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R123" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="124" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="124" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="str">
         <f>IF(ISBLANK(I124)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11011,7 +11010,7 @@
         <v>27</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E124" s="2" t="s">
         <v>397</v>
@@ -11042,23 +11041,23 @@
         <v>814</v>
       </c>
       <c r="N124" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O124" s="2" t="str" cm="1">
-        <f t="array" ref="O124">IF(N124&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N124,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O124">IF(N124&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N124,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P124" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q124" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R124" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="125" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="125" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="str">
         <f>IF(ISBLANK(I125)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11070,7 +11069,7 @@
         <v>5</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>531</v>
@@ -11101,23 +11100,23 @@
         <v>814</v>
       </c>
       <c r="N125" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O125" s="2" t="str" cm="1">
-        <f t="array" ref="O125">IF(N125&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N125,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O125">IF(N125&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N125,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P125" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q125" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R125" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="126" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="126" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="str">
         <f>IF(ISBLANK(I126)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11129,7 +11128,7 @@
         <v>48</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>823</v>
@@ -11138,7 +11137,7 @@
         <v>88</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>835</v>
@@ -11150,7 +11149,7 @@
         <v>4</v>
       </c>
       <c r="K126" s="2" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="L126" s="2" t="str" cm="1">
         <f t="array" ref="L126">_xlfn.REGEXEXTRACT(B126,"(?&lt;=//)[^/]+")</f>
@@ -11160,23 +11159,23 @@
         <v>814</v>
       </c>
       <c r="N126" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O126" s="2" t="str" cm="1">
-        <f t="array" ref="O126">IF(N126&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N126,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O126">IF(N126&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N126,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P126" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q126" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R126" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="127" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="127" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="str">
         <f>IF(ISBLANK(I127)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11188,19 +11187,19 @@
         <v>49</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="I127" s="2" t="s">
         <v>82</v>
@@ -11209,7 +11208,7 @@
         <v>4</v>
       </c>
       <c r="K127" s="2" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="L127" s="2" t="str" cm="1">
         <f t="array" ref="L127">_xlfn.REGEXEXTRACT(B127,"(?&lt;=//)[^/]+")</f>
@@ -11219,23 +11218,23 @@
         <v>814</v>
       </c>
       <c r="N127" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O127" s="2" t="str" cm="1">
-        <f t="array" ref="O127">IF(N127&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N127,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O127">IF(N127&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N127,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P127" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q127" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R127" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="128" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="str">
         <f>IF(ISBLANK(I128)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11247,7 +11246,7 @@
         <v>67</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E128" s="2" t="s">
         <v>99</v>
@@ -11278,23 +11277,23 @@
         <v>814</v>
       </c>
       <c r="N128" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O128" s="2" t="str" cm="1">
-        <f t="array" ref="O128">IF(N128&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N128,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O128">IF(N128&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N128,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P128" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q128" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R128" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="129" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="129" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="str">
         <f>IF(ISBLANK(I129)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11306,7 +11305,7 @@
         <v>52</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E129" s="2" t="s">
         <v>508</v>
@@ -11337,23 +11336,23 @@
         <v>814</v>
       </c>
       <c r="N129" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O129" s="2" t="str" cm="1">
-        <f t="array" ref="O129">IF(N129&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N129,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O129">IF(N129&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N129,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P129" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q129" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R129" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="130" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="130" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="str">
         <f>IF(ISBLANK(I130)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11396,23 +11395,23 @@
         <v>814</v>
       </c>
       <c r="N130" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O130" s="2" t="str" cm="1">
-        <f t="array" ref="O130">IF(N130&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N130,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O130">IF(N130&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N130,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P130" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q130" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R130" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="131" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="131" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="str">
         <f>IF(ISBLANK(I131)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11455,23 +11454,23 @@
         <v>814</v>
       </c>
       <c r="N131" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O131" s="2" t="str" cm="1">
-        <f t="array" ref="O131">IF(N131&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N131,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O131">IF(N131&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N131,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P131" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q131" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R131" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="132" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="132" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="str">
         <f>IF(ISBLANK(I132)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11514,23 +11513,23 @@
         <v>814</v>
       </c>
       <c r="N132" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O132" s="2" t="str" cm="1">
-        <f t="array" ref="O132">IF(N132&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N132,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O132">IF(N132&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N132,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P132" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q132" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R132" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="133" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="133" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="str">
         <f>IF(ISBLANK(I133)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11542,7 +11541,7 @@
         <v>80</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="E133" s="2" t="s">
         <v>393</v>
@@ -11573,23 +11572,23 @@
         <v>814</v>
       </c>
       <c r="N133" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O133" s="2" t="str" cm="1">
-        <f t="array" ref="O133">IF(N133&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N133,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O133">IF(N133&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N133,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P133" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q133" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R133" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="134" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="134" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="str">
         <f>IF(ISBLANK(I134)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11610,7 +11609,7 @@
         <v>89</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>468</v>
@@ -11622,7 +11621,7 @@
         <v>4</v>
       </c>
       <c r="K134" s="2" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="L134" s="2" t="str" cm="1">
         <f t="array" ref="L134">_xlfn.REGEXEXTRACT(B134,"(?&lt;=//)[^/]+")</f>
@@ -11632,23 +11631,23 @@
         <v>814</v>
       </c>
       <c r="N134" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O134" s="2" t="str" cm="1">
-        <f t="array" ref="O134">IF(N134&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N134,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O134">IF(N134&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N134,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P134" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q134" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R134" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="135" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="135" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="str">
         <f>IF(ISBLANK(I135)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11691,23 +11690,23 @@
         <v>814</v>
       </c>
       <c r="N135" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O135" s="2" t="str" cm="1">
-        <f t="array" ref="O135">IF(N135&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N135,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O135">IF(N135&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N135,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P135" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q135" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R135" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="136" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="str">
         <f>IF(ISBLANK(I136)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11719,7 +11718,7 @@
         <v>66</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E136" s="2" t="s">
         <v>287</v>
@@ -11750,23 +11749,23 @@
         <v>814</v>
       </c>
       <c r="N136" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O136" s="2" t="str" cm="1">
-        <f t="array" ref="O136">IF(N136&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N136,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O136">IF(N136&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N136,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P136" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q136" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R136" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="137" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="str">
         <f>IF(ISBLANK(I137)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11778,7 +11777,7 @@
         <v>53</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E137" s="2" t="s">
         <v>261</v>
@@ -11809,23 +11808,23 @@
         <v>814</v>
       </c>
       <c r="N137" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O137" s="2" t="str" cm="1">
-        <f t="array" ref="O137">IF(N137&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N137,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O137">IF(N137&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N137,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P137" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q137" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R137" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="138" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="138" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="str">
         <f>IF(ISBLANK(I138)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11837,7 +11836,7 @@
         <v>45</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>241</v>
@@ -11868,23 +11867,23 @@
         <v>814</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O138" s="2" t="str" cm="1">
-        <f t="array" ref="O138">IF(N138&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N138,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O138">IF(N138&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N138,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P138" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q138" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R138" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="139" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="139" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="str">
         <f>IF(ISBLANK(I139)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11927,23 +11926,23 @@
         <v>814</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O139" s="2" t="str" cm="1">
-        <f t="array" ref="O139">IF(N139&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N139,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O139">IF(N139&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N139,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P139" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q139" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R139" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="140" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="140" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="str">
         <f>IF(ISBLANK(I140)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -11986,23 +11985,23 @@
         <v>814</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O140" s="2" t="str" cm="1">
-        <f t="array" ref="O140">IF(N140&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N140,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O140">IF(N140&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N140,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P140" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q140" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R140" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="141" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="141" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="str">
         <f>IF(ISBLANK(I141)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12045,23 +12044,23 @@
         <v>814</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O141" s="2" t="str" cm="1">
-        <f t="array" ref="O141">IF(N141&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N141,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O141">IF(N141&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N141,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P141" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q141" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R141" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="142" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="142" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="str">
         <f>IF(ISBLANK(I142)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12104,23 +12103,23 @@
         <v>814</v>
       </c>
       <c r="N142" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O142" s="2" t="str" cm="1">
-        <f t="array" ref="O142">IF(N142&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N142,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O142">IF(N142&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N142,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P142" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q142" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R142" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="143" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="143" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="str">
         <f>IF(ISBLANK(I143)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12163,23 +12162,23 @@
         <v>814</v>
       </c>
       <c r="N143" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O143" s="2" t="str" cm="1">
-        <f t="array" ref="O143">IF(N143&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N143,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O143">IF(N143&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N143,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P143" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q143" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R143" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="144" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="144" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="str">
         <f>IF(ISBLANK(I144)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12222,23 +12221,23 @@
         <v>814</v>
       </c>
       <c r="N144" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O144" s="2" t="str" cm="1">
-        <f t="array" ref="O144">IF(N144&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N144,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O144">IF(N144&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N144,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P144" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q144" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R144" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="145" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="145" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="str">
         <f>IF(ISBLANK(I145)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12250,7 +12249,7 @@
         <v>53</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>523</v>
@@ -12281,23 +12280,23 @@
         <v>814</v>
       </c>
       <c r="N145" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O145" s="2" t="str" cm="1">
-        <f t="array" ref="O145">IF(N145&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N145,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O145">IF(N145&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N145,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P145" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q145" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R145" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="146" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="str">
         <f>IF(ISBLANK(I146)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12318,7 +12317,7 @@
         <v>192</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>472</v>
@@ -12340,35 +12339,35 @@
         <v>814</v>
       </c>
       <c r="N146" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O146" s="2" t="str" cm="1">
-        <f t="array" ref="O146">IF(N146&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N146,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O146">IF(N146&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N146,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P146" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q146" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R146" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="147" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="147" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="str">
         <f>IF(ISBLANK(I147)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="C147" s="2">
         <v>45</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>798</v>
@@ -12377,10 +12376,10 @@
         <v>88</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="H147" s="2" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="I147" s="2" t="s">
         <v>82</v>
@@ -12389,7 +12388,7 @@
         <v>4</v>
       </c>
       <c r="K147" s="2" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
       <c r="L147" s="2" t="str" cm="1">
         <f t="array" ref="L147">_xlfn.REGEXEXTRACT(B147,"(?&lt;=//)[^/]+")</f>
@@ -12399,23 +12398,23 @@
         <v>814</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O147" s="2" t="str" cm="1">
-        <f t="array" ref="O147">IF(N147&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N147,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O147">IF(N147&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N147,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P147" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q147" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R147" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="148" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="148" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="str">
         <f>IF(ISBLANK(I148)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12436,7 +12435,7 @@
         <v>89</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>788</v>
@@ -12448,7 +12447,7 @@
         <v>4</v>
       </c>
       <c r="K148" s="2" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="L148" s="2" t="str" cm="1">
         <f t="array" ref="L148">_xlfn.REGEXEXTRACT(B148,"(?&lt;=//)[^/]+")</f>
@@ -12458,23 +12457,23 @@
         <v>814</v>
       </c>
       <c r="N148" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O148" s="2" t="str" cm="1">
-        <f t="array" ref="O148">IF(N148&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N148,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O148">IF(N148&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N148,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P148" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q148" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R148" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="149" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="149" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="str">
         <f>IF(ISBLANK(I149)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12517,23 +12516,23 @@
         <v>814</v>
       </c>
       <c r="N149" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O149" s="2" t="str" cm="1">
-        <f t="array" ref="O149">IF(N149&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N149,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O149">IF(N149&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N149,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P149" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q149" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R149" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="150" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="150" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="str">
         <f>IF(ISBLANK(I150)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12576,23 +12575,23 @@
         <v>814</v>
       </c>
       <c r="N150" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O150" s="2" t="str" cm="1">
-        <f t="array" ref="O150">IF(N150&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N150,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O150">IF(N150&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N150,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P150" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q150" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R150" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="151" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="151" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="str">
         <f>IF(ISBLANK(I151)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12635,23 +12634,23 @@
         <v>814</v>
       </c>
       <c r="N151" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O151" s="2" t="str" cm="1">
-        <f t="array" ref="O151">IF(N151&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N151,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O151">IF(N151&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N151,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P151" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q151" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R151" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="152" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="152" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="str">
         <f>IF(ISBLANK(I152)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12666,7 +12665,7 @@
         <v>227</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>193</v>
@@ -12694,23 +12693,23 @@
         <v>814</v>
       </c>
       <c r="N152" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O152" s="2" t="str" cm="1">
-        <f t="array" ref="O152">IF(N152&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N152,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O152">IF(N152&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N152,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P152" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q152" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R152" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="153" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="153" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="str">
         <f>IF(ISBLANK(I153)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12753,23 +12752,23 @@
         <v>814</v>
       </c>
       <c r="N153" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O153" s="2" t="str" cm="1">
-        <f t="array" ref="O153">IF(N153&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N153,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O153">IF(N153&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N153,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P153" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q153" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R153" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="154" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="154" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="str">
         <f>IF(ISBLANK(I154)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12812,23 +12811,23 @@
         <v>814</v>
       </c>
       <c r="N154" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O154" s="2" t="str" cm="1">
-        <f t="array" ref="O154">IF(N154&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N154,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O154">IF(N154&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N154,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P154" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q154" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R154" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="155" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="155" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="str">
         <f>IF(ISBLANK(I155)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12871,23 +12870,23 @@
         <v>814</v>
       </c>
       <c r="N155" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O155" s="2" t="str" cm="1">
-        <f t="array" ref="O155">IF(N155&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N155,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O155">IF(N155&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N155,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P155" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q155" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R155" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="156" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="156" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="str">
         <f>IF(ISBLANK(I156)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12899,7 +12898,7 @@
         <v>44</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>358</v>
@@ -12930,23 +12929,23 @@
         <v>814</v>
       </c>
       <c r="N156" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O156" s="2" t="str" cm="1">
-        <f t="array" ref="O156">IF(N156&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N156,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O156">IF(N156&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N156,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P156" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q156" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R156" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="157" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="157" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="str">
         <f>IF(ISBLANK(I157)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -12958,7 +12957,7 @@
         <v>42</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>398</v>
@@ -12989,23 +12988,23 @@
         <v>814</v>
       </c>
       <c r="N157" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O157" s="2" t="str" cm="1">
-        <f t="array" ref="O157">IF(N157&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N157,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O157">IF(N157&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N157,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P157" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q157" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R157" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="158" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="158" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="str">
         <f>IF(ISBLANK(I158)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13017,7 +13016,7 @@
         <v>60</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>394</v>
@@ -13048,23 +13047,23 @@
         <v>814</v>
       </c>
       <c r="N158" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O158" s="2" t="str" cm="1">
-        <f t="array" ref="O158">IF(N158&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N158,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O158">IF(N158&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N158,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P158" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q158" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R158" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="159" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="159" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="str">
         <f>IF(ISBLANK(I159)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13076,7 +13075,7 @@
         <v>59</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>395</v>
@@ -13107,23 +13106,23 @@
         <v>814</v>
       </c>
       <c r="N159" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O159" s="2" t="str" cm="1">
-        <f t="array" ref="O159">IF(N159&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N159,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O159">IF(N159&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N159,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P159" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q159" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R159" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="160" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="160" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="str">
         <f>IF(ISBLANK(I160)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13135,7 +13134,7 @@
         <v>80</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>208</v>
@@ -13166,23 +13165,23 @@
         <v>814</v>
       </c>
       <c r="N160" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O160" s="2" t="str" cm="1">
-        <f t="array" ref="O160">IF(N160&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N160,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O160">IF(N160&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N160,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P160" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q160" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R160" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="161" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="161" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="str">
         <f>IF(ISBLANK(I161)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13194,7 +13193,7 @@
         <v>25</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>229</v>
@@ -13225,23 +13224,23 @@
         <v>814</v>
       </c>
       <c r="N161" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O161" s="2" t="str" cm="1">
-        <f t="array" ref="O161">IF(N161&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N161,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O161">IF(N161&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N161,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P161" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q161" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R161" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="162" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="162" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="str">
         <f>IF(ISBLANK(I162)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13253,7 +13252,7 @@
         <v>56</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>507</v>
@@ -13284,23 +13283,23 @@
         <v>814</v>
       </c>
       <c r="N162" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O162" s="2" t="str" cm="1">
-        <f t="array" ref="O162">IF(N162&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N162,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O162">IF(N162&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N162,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P162" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q162" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R162" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="163" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="163" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="str">
         <f>IF(ISBLANK(I163)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13312,7 +13311,7 @@
         <v>53</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>260</v>
@@ -13343,23 +13342,23 @@
         <v>814</v>
       </c>
       <c r="N163" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O163" s="2" t="str" cm="1">
-        <f t="array" ref="O163">IF(N163&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N163,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O163">IF(N163&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N163,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P163" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q163" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R163" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="164" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="164" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="str">
         <f>IF(ISBLANK(I164)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13371,7 +13370,7 @@
         <v>49</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>104</v>
@@ -13402,23 +13401,23 @@
         <v>814</v>
       </c>
       <c r="N164" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O164" s="2" t="str" cm="1">
-        <f t="array" ref="O164">IF(N164&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N164,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O164">IF(N164&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N164,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P164" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q164" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R164" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="165" spans="1:18" ht="90" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="165" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="str">
         <f>IF(ISBLANK(I165)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13430,7 +13429,7 @@
         <v>4</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E165" s="2" t="s">
         <v>324</v>
@@ -13461,44 +13460,44 @@
         <v>814</v>
       </c>
       <c r="N165" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O165" s="2" t="str" cm="1">
-        <f t="array" ref="O165">IF(N165&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N165,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O165">IF(N165&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N165,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P165" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q165" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R165" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="166" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="166" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="str">
         <f>IF(ISBLANK(I166)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C166" s="2">
         <v>55</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F166" s="2" t="s">
         <v>100</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>743</v>
@@ -13510,7 +13509,7 @@
         <v>3</v>
       </c>
       <c r="K166" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="L166" s="2" t="str" cm="1">
         <f t="array" ref="L166">_xlfn.REGEXEXTRACT(B166,"(?&lt;=//)[^/]+")</f>
@@ -13520,23 +13519,23 @@
         <v>814</v>
       </c>
       <c r="N166" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O166" s="2" t="str" cm="1">
-        <f t="array" ref="O166">IF(N166&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N166,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O166">IF(N166&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N166,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P166" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q166" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R166" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="167" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="167" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="str">
         <f>IF(ISBLANK(I167)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13579,23 +13578,23 @@
         <v>814</v>
       </c>
       <c r="N167" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O167" s="2" t="str" cm="1">
-        <f t="array" ref="O167">IF(N167&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N167,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O167">IF(N167&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N167,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P167" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q167" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R167" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="168" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="168" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="str">
         <f>IF(ISBLANK(I168)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13638,23 +13637,23 @@
         <v>814</v>
       </c>
       <c r="N168" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O168" s="2" t="str" cm="1">
-        <f t="array" ref="O168">IF(N168&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N168,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O168">IF(N168&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N168,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P168" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q168" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R168" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="169" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="169" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="str">
         <f>IF(ISBLANK(I169)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13697,23 +13696,23 @@
         <v>814</v>
       </c>
       <c r="N169" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O169" s="2" t="str" cm="1">
-        <f t="array" ref="O169">IF(N169&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N169,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O169">IF(N169&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N169,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P169" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q169" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R169" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="170" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="170" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="str">
         <f>IF(ISBLANK(I170)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13756,23 +13755,23 @@
         <v>814</v>
       </c>
       <c r="N170" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O170" s="2" t="str" cm="1">
-        <f t="array" ref="O170">IF(N170&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N170,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O170">IF(N170&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N170,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P170" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q170" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R170" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="171" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="171" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="str">
         <f>IF(ISBLANK(I171)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13784,7 +13783,7 @@
         <v>44</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="E171" s="2" t="s">
         <v>111</v>
@@ -13815,23 +13814,23 @@
         <v>814</v>
       </c>
       <c r="N171" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O171" s="2" t="str" cm="1">
-        <f t="array" ref="O171">IF(N171&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N171,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O171">IF(N171&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N171,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P171" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q171" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R171" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="172" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="172" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="str">
         <f>IF(ISBLANK(I172)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13874,23 +13873,23 @@
         <v>814</v>
       </c>
       <c r="N172" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O172" s="2" t="str" cm="1">
-        <f t="array" ref="O172">IF(N172&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N172,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O172">IF(N172&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N172,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P172" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q172" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R172" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="173" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="173" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="str">
         <f>IF(ISBLANK(I173)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13933,23 +13932,23 @@
         <v>814</v>
       </c>
       <c r="N173" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O173" s="2" t="str" cm="1">
-        <f t="array" ref="O173">IF(N173&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N173,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O173">IF(N173&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N173,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P173" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q173" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R173" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="174" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="174" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="str">
         <f>IF(ISBLANK(I174)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -13992,23 +13991,23 @@
         <v>814</v>
       </c>
       <c r="N174" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O174" s="2" t="str" cm="1">
-        <f t="array" ref="O174">IF(N174&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N174,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O174">IF(N174&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N174,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P174" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q174" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R174" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="175" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="175" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="str">
         <f>IF(ISBLANK(I175)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14051,23 +14050,23 @@
         <v>814</v>
       </c>
       <c r="N175" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O175" s="2" t="str" cm="1">
-        <f t="array" ref="O175">IF(N175&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N175,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O175">IF(N175&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N175,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P175" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q175" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R175" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="176" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="176" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="str">
         <f>IF(ISBLANK(I176)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14110,23 +14109,23 @@
         <v>814</v>
       </c>
       <c r="N176" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O176" s="2" t="str" cm="1">
-        <f t="array" ref="O176">IF(N176&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N176,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O176">IF(N176&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N176,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P176" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q176" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R176" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="177" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="177" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="str">
         <f>IF(ISBLANK(I177)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14169,23 +14168,23 @@
         <v>814</v>
       </c>
       <c r="N177" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O177" s="2" t="str" cm="1">
-        <f t="array" ref="O177">IF(N177&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N177,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O177">IF(N177&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N177,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P177" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q177" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R177" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="178" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="178" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="str">
         <f>IF(ISBLANK(I178)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14228,23 +14227,23 @@
         <v>814</v>
       </c>
       <c r="N178" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O178" s="2" t="str" cm="1">
-        <f t="array" ref="O178">IF(N178&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N178,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O178">IF(N178&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N178,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P178" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q178" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R178" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="179" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="179" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="str">
         <f>IF(ISBLANK(I179)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14287,23 +14286,23 @@
         <v>814</v>
       </c>
       <c r="N179" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O179" s="2" t="str" cm="1">
-        <f t="array" ref="O179">IF(N179&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N179,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O179">IF(N179&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N179,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P179" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q179" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R179" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="180" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="180" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="str">
         <f>IF(ISBLANK(I180)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14346,23 +14345,23 @@
         <v>814</v>
       </c>
       <c r="N180" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O180" s="2" t="str" cm="1">
-        <f t="array" ref="O180">IF(N180&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N180,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O180">IF(N180&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N180,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P180" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q180" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R180" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="181" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="181" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="str">
         <f>IF(ISBLANK(I181)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14374,7 +14373,7 @@
         <v>46</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="E181" s="2" t="s">
         <v>244</v>
@@ -14405,23 +14404,23 @@
         <v>814</v>
       </c>
       <c r="N181" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O181" s="2" t="str" cm="1">
-        <f t="array" ref="O181">IF(N181&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N181,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O181">IF(N181&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N181,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P181" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q181" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R181" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="182" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="182" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="str">
         <f>IF(ISBLANK(I182)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14464,23 +14463,23 @@
         <v>814</v>
       </c>
       <c r="N182" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O182" s="2" t="str" cm="1">
-        <f t="array" ref="O182">IF(N182&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N182,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O182">IF(N182&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N182,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P182" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q182" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R182" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="183" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="183" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="str">
         <f>IF(ISBLANK(I183)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14523,23 +14522,23 @@
         <v>814</v>
       </c>
       <c r="N183" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O183" s="2" t="str" cm="1">
-        <f t="array" ref="O183">IF(N183&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N183,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O183">IF(N183&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N183,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P183" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q183" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R183" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="184" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="184" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="str">
         <f>IF(ISBLANK(I184)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14582,23 +14581,23 @@
         <v>814</v>
       </c>
       <c r="N184" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O184" s="2" t="str" cm="1">
-        <f t="array" ref="O184">IF(N184&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N184,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O184">IF(N184&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N184,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P184" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q184" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R184" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="185" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="185" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="str">
         <f>IF(ISBLANK(I185)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14641,23 +14640,23 @@
         <v>814</v>
       </c>
       <c r="N185" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O185" s="2" t="str" cm="1">
-        <f t="array" ref="O185">IF(N185&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N185,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O185">IF(N185&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N185,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P185" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q185" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R185" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="186" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="186" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="str">
         <f>IF(ISBLANK(I186)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14700,23 +14699,23 @@
         <v>814</v>
       </c>
       <c r="N186" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O186" s="2" t="str" cm="1">
-        <f t="array" ref="O186">IF(N186&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N186,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O186">IF(N186&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N186,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P186" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q186" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R186" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="187" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="187" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="str">
         <f>IF(ISBLANK(I187)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14728,7 +14727,7 @@
         <v>70</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="E187" s="2" t="s">
         <v>399</v>
@@ -14749,7 +14748,7 @@
         <v>3</v>
       </c>
       <c r="K187" s="2" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="L187" s="2" t="str" cm="1">
         <f t="array" ref="L187">_xlfn.REGEXEXTRACT(B187,"(?&lt;=//)[^/]+")</f>
@@ -14759,23 +14758,23 @@
         <v>814</v>
       </c>
       <c r="N187" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O187" s="2" t="str" cm="1">
-        <f t="array" ref="O187">IF(N187&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N187,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O187">IF(N187&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N187,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P187" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q187" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R187" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="188" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="188" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="str">
         <f>IF(ISBLANK(I188)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14787,7 +14786,7 @@
         <v>32</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E188" s="2" t="s">
         <v>208</v>
@@ -14818,23 +14817,23 @@
         <v>814</v>
       </c>
       <c r="N188" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O188" s="2" t="str" cm="1">
-        <f t="array" ref="O188">IF(N188&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N188,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O188">IF(N188&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N188,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P188" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q188" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R188" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="189" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="189" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="str">
         <f>IF(ISBLANK(I189)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14846,7 +14845,7 @@
         <v>47</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="E189" s="2" t="s">
         <v>405</v>
@@ -14877,23 +14876,23 @@
         <v>814</v>
       </c>
       <c r="N189" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O189" s="2" t="str" cm="1">
-        <f t="array" ref="O189">IF(N189&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N189,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O189">IF(N189&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N189,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P189" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q189" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R189" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="190" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="190" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="str">
         <f>IF(ISBLANK(I190)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14936,23 +14935,23 @@
         <v>814</v>
       </c>
       <c r="N190" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O190" s="2" t="str" cm="1">
-        <f t="array" ref="O190">IF(N190&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N190,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O190">IF(N190&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N190,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P190" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q190" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R190" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="191" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="191" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="str">
         <f>IF(ISBLANK(I191)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -14964,7 +14963,7 @@
         <v>57</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>404</v>
@@ -14995,23 +14994,23 @@
         <v>814</v>
       </c>
       <c r="N191" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O191" s="2" t="str" cm="1">
-        <f t="array" ref="O191">IF(N191&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N191,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O191">IF(N191&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N191,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P191" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q191" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R191" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="192" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="192" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="str">
         <f>IF(ISBLANK(I192)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -15023,7 +15022,7 @@
         <v>57</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="E192" s="2" t="s">
         <v>271</v>
@@ -15054,23 +15053,23 @@
         <v>814</v>
       </c>
       <c r="N192" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O192" s="2" t="str" cm="1">
-        <f t="array" ref="O192">IF(N192&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N192,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O192">IF(N192&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N192,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P192" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q192" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R192" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="193" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="193" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="str">
         <f>IF(ISBLANK(I193)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -15113,23 +15112,23 @@
         <v>814</v>
       </c>
       <c r="N193" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O193" s="2" t="str" cm="1">
-        <f t="array" ref="O193">IF(N193&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N193,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O193">IF(N193&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N193,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P193" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q193" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R193" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="194" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="194" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="str">
         <f>IF(ISBLANK(I194)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -15172,23 +15171,23 @@
         <v>814</v>
       </c>
       <c r="N194" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O194" s="2" t="str" cm="1">
-        <f t="array" ref="O194">IF(N194&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N194,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O194">IF(N194&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N194,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P194" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q194" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R194" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="195" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="195" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="str">
         <f>IF(ISBLANK(I195)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -15231,23 +15230,23 @@
         <v>814</v>
       </c>
       <c r="N195" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O195" s="2" t="str" cm="1">
-        <f t="array" ref="O195">IF(N195&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N195,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O195">IF(N195&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N195,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P195" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q195" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R195" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="196" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="196" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="str">
         <f>IF(ISBLANK(I196)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -15290,23 +15289,23 @@
         <v>814</v>
       </c>
       <c r="N196" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O196" s="2" t="str" cm="1">
-        <f t="array" ref="O196">IF(N196&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N196,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O196">IF(N196&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N196,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P196" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q196" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R196" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="197" spans="1:18" ht="45" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="197" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="str">
         <f>IF(ISBLANK(I197)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -15349,23 +15348,23 @@
         <v>814</v>
       </c>
       <c r="N197" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O197" s="2" t="str" cm="1">
-        <f t="array" ref="O197">IF(N197&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N197,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O197">IF(N197&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N197,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P197" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q197" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R197" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="198" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="198" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="str">
         <f>IF(ISBLANK(I198)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -15408,23 +15407,23 @@
         <v>814</v>
       </c>
       <c r="N198" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O198" s="2" t="str" cm="1">
-        <f t="array" ref="O198">IF(N198&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N198,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O198">IF(N198&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N198,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P198" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q198" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R198" s="2" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="199" spans="1:18" ht="30" hidden="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="199" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="str">
         <f>IF(ISBLANK(I199)=TRUE,"Pending","Done")</f>
         <v>Done</v>
@@ -15467,20 +15466,20 @@
         <v>814</v>
       </c>
       <c r="N199" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O199" s="2" t="str" cm="1">
-        <f t="array" ref="O199">IF(N199&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N199,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O199">IF(N199&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N199,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P199" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q199" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R199" s="2" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="200" spans="1:18" ht="45" x14ac:dyDescent="0.25">
@@ -15489,22 +15488,22 @@
         <v>Pending</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>868</v>
+        <v>1011</v>
       </c>
       <c r="C200" s="2">
         <v>44</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>88</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
@@ -15512,26 +15511,26 @@
       <c r="K200" s="2"/>
       <c r="L200" s="2" t="str" cm="1">
         <f t="array" ref="L200">_xlfn.REGEXEXTRACT(B200,"(?&lt;=//)[^/]+")</f>
-        <v>www.kink.com</v>
+        <v>bdsmstreak.com</v>
       </c>
       <c r="M200" s="2" t="s">
         <v>814</v>
       </c>
       <c r="N200" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O200" s="2" t="str" cm="1">
-        <f t="array" ref="O200">IF(N200&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N200,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O200">IF(N200&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N200,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P200" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q200" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R200" s="2" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="201" spans="1:18" ht="45" x14ac:dyDescent="0.25">
@@ -15540,16 +15539,16 @@
         <v>Pending</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C201" s="2">
         <v>70</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="F201" s="2" t="s">
         <v>100</v>
@@ -15567,20 +15566,20 @@
         <v>814</v>
       </c>
       <c r="N201" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O201" s="2" t="str" cm="1">
-        <f t="array" ref="O201">IF(N201&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N201,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O201">IF(N201&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N201,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P201" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q201" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R201" s="2" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="202" spans="1:18" ht="45" x14ac:dyDescent="0.25">
@@ -15589,16 +15588,16 @@
         <v>Pending</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C202" s="2">
         <v>60</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="F202" s="2" t="s">
         <v>89</v>
@@ -15616,36 +15615,34 @@
         <v>814</v>
       </c>
       <c r="N202" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="O202" s="2" t="str" cm="1">
-        <f t="array" ref="O202">IF(N202&lt;&gt;"invalid",_xlfn.REGEXEXTRACT(N202,"\d+(?=p)"),"invalid")</f>
-        <v>invalid</v>
+        <f t="array" ref="O202">IF(N202&lt;&gt;"z-not-applicable",_xlfn.REGEXEXTRACT(N202,"\d+(?=p)"),"z-not-applicable")</f>
+        <v>z-not-applicable</v>
       </c>
       <c r="P202" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="Q202" s="2" t="s">
-        <v>895</v>
+        <v>1010</v>
       </c>
       <c r="R202" s="2" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:R202" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Pending"/>
-      </filters>
-    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R202">
+      <sortCondition descending="1" ref="J1:J202"/>
+    </sortState>
   </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R202">
     <sortCondition descending="1" ref="J1:J202"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:R202">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="3" priority="1">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15662,7 +15659,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:M174 L3:M202">
-    <cfRule type="cellIs" dxfId="3" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="17" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16129,12 +16126,12 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A18">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"-"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A19:E19">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$C19="Pending"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/data/master_links.xlsx
+++ b/data/master_links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F878ED-C452-47F6-9532-A31D698C03D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7309623E-18EF-4965-80DC-1217657E6652}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="314" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5318,21 +5318,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -5713,7 +5699,7 @@
     </row>
     <row r="2" spans="1:18" s="25" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="str">
-        <f t="shared" ref="A2:A65" si="0">IF(ISBLANK(I2)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I2)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -5772,7 +5758,7 @@
     </row>
     <row r="3" spans="1:18" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I3)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -5831,7 +5817,7 @@
     </row>
     <row r="4" spans="1:18" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I4)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -5890,7 +5876,7 @@
     </row>
     <row r="5" spans="1:18" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I5)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B5" s="2" t="s">
@@ -5949,7 +5935,7 @@
     </row>
     <row r="6" spans="1:18" s="25" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I6)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -6008,7 +5994,7 @@
     </row>
     <row r="7" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I7)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -6067,7 +6053,7 @@
     </row>
     <row r="8" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I8)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -6126,7 +6112,7 @@
     </row>
     <row r="9" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I9)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B9" s="2" t="s">
@@ -6185,7 +6171,7 @@
     </row>
     <row r="10" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I10)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B10" s="2" t="s">
@@ -6244,7 +6230,7 @@
     </row>
     <row r="11" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I11)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B11" s="2" t="s">
@@ -6303,7 +6289,7 @@
     </row>
     <row r="12" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I12)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B12" s="2" t="s">
@@ -6362,7 +6348,7 @@
     </row>
     <row r="13" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I13)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -6421,7 +6407,7 @@
     </row>
     <row r="14" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I14)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -6480,7 +6466,7 @@
     </row>
     <row r="15" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I15)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -6539,7 +6525,7 @@
     </row>
     <row r="16" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I16)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -6598,7 +6584,7 @@
     </row>
     <row r="17" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I17)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -6657,7 +6643,7 @@
     </row>
     <row r="18" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I18)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -6716,7 +6702,7 @@
     </row>
     <row r="19" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I19)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -6775,7 +6761,7 @@
     </row>
     <row r="20" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I20)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -6834,7 +6820,7 @@
     </row>
     <row r="21" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I21)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B21" s="2" t="s">
@@ -6893,7 +6879,7 @@
     </row>
     <row r="22" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I22)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -6952,7 +6938,7 @@
     </row>
     <row r="23" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I23)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B23" s="2" t="s">
@@ -7011,7 +6997,7 @@
     </row>
     <row r="24" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I24)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B24" s="2" t="s">
@@ -7070,7 +7056,7 @@
     </row>
     <row r="25" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I25)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B25" s="2" t="s">
@@ -7129,7 +7115,7 @@
     </row>
     <row r="26" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I26)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -7188,7 +7174,7 @@
     </row>
     <row r="27" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I27)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -7247,7 +7233,7 @@
     </row>
     <row r="28" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I28)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B28" s="2" t="s">
@@ -7306,7 +7292,7 @@
     </row>
     <row r="29" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I29)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B29" s="2" t="s">
@@ -7365,7 +7351,7 @@
     </row>
     <row r="30" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I30)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B30" s="2" t="s">
@@ -7424,7 +7410,7 @@
     </row>
     <row r="31" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I31)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B31" s="2" t="s">
@@ -7483,7 +7469,7 @@
     </row>
     <row r="32" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I32)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -7542,7 +7528,7 @@
     </row>
     <row r="33" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I33)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B33" s="2" t="s">
@@ -7601,7 +7587,7 @@
     </row>
     <row r="34" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I34)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B34" s="2" t="s">
@@ -7660,7 +7646,7 @@
     </row>
     <row r="35" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I35)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B35" s="2" t="s">
@@ -7719,7 +7705,7 @@
     </row>
     <row r="36" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I36)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B36" s="2" t="s">
@@ -7778,7 +7764,7 @@
     </row>
     <row r="37" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I37)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B37" s="2" t="s">
@@ -7837,7 +7823,7 @@
     </row>
     <row r="38" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I38)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B38" s="2" t="s">
@@ -7896,7 +7882,7 @@
     </row>
     <row r="39" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I39)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B39" s="2" t="s">
@@ -7955,7 +7941,7 @@
     </row>
     <row r="40" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I40)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B40" s="2" t="s">
@@ -8014,7 +8000,7 @@
     </row>
     <row r="41" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I41)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B41" s="2" t="s">
@@ -8073,7 +8059,7 @@
     </row>
     <row r="42" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I42)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B42" s="2" t="s">
@@ -8132,7 +8118,7 @@
     </row>
     <row r="43" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I43)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B43" s="2" t="s">
@@ -8191,7 +8177,7 @@
     </row>
     <row r="44" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I44)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B44" s="2" t="s">
@@ -8250,7 +8236,7 @@
     </row>
     <row r="45" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I45)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B45" s="2" t="s">
@@ -8309,7 +8295,7 @@
     </row>
     <row r="46" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I46)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B46" s="2" t="s">
@@ -8368,7 +8354,7 @@
     </row>
     <row r="47" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I47)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -8427,7 +8413,7 @@
     </row>
     <row r="48" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I48)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B48" s="2" t="s">
@@ -8486,7 +8472,7 @@
     </row>
     <row r="49" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I49)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B49" s="2" t="s">
@@ -8545,7 +8531,7 @@
     </row>
     <row r="50" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I50)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B50" s="2" t="s">
@@ -8604,7 +8590,7 @@
     </row>
     <row r="51" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I51)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B51" s="2" t="s">
@@ -8663,7 +8649,7 @@
     </row>
     <row r="52" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I52)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B52" s="2" t="s">
@@ -8722,7 +8708,7 @@
     </row>
     <row r="53" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I53)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B53" s="2" t="s">
@@ -8781,7 +8767,7 @@
     </row>
     <row r="54" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I54)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B54" s="2" t="s">
@@ -8840,7 +8826,7 @@
     </row>
     <row r="55" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I55)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B55" s="2" t="s">
@@ -8899,7 +8885,7 @@
     </row>
     <row r="56" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I56)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B56" s="2" t="s">
@@ -8958,7 +8944,7 @@
     </row>
     <row r="57" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I57)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B57" s="2" t="s">
@@ -9017,7 +9003,7 @@
     </row>
     <row r="58" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I58)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B58" s="2" t="s">
@@ -9076,7 +9062,7 @@
     </row>
     <row r="59" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I59)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B59" s="2" t="s">
@@ -9135,7 +9121,7 @@
     </row>
     <row r="60" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I60)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B60" s="2" t="s">
@@ -9194,7 +9180,7 @@
     </row>
     <row r="61" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I61)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B61" s="2" t="s">
@@ -9253,7 +9239,7 @@
     </row>
     <row r="62" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I62)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B62" s="2" t="s">
@@ -9312,7 +9298,7 @@
     </row>
     <row r="63" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I63)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B63" s="2" t="s">
@@ -9371,7 +9357,7 @@
     </row>
     <row r="64" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I64)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B64" s="2" t="s">
@@ -9430,7 +9416,7 @@
     </row>
     <row r="65" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="str">
-        <f t="shared" si="0"/>
+        <f>IF(ISBLANK(I65)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B65" s="2" t="s">
@@ -9489,7 +9475,7 @@
     </row>
     <row r="66" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="str">
-        <f t="shared" ref="A66:A129" si="1">IF(ISBLANK(I66)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I66)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B66" s="2" t="s">
@@ -9548,7 +9534,7 @@
     </row>
     <row r="67" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I67)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B67" s="2" t="s">
@@ -9607,7 +9593,7 @@
     </row>
     <row r="68" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I68)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B68" s="2" t="s">
@@ -9666,7 +9652,7 @@
     </row>
     <row r="69" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I69)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B69" s="2" t="s">
@@ -9725,7 +9711,7 @@
     </row>
     <row r="70" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I70)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B70" s="2" t="s">
@@ -9784,7 +9770,7 @@
     </row>
     <row r="71" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I71)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B71" s="2" t="s">
@@ -9843,7 +9829,7 @@
     </row>
     <row r="72" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I72)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B72" s="2" t="s">
@@ -9902,7 +9888,7 @@
     </row>
     <row r="73" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I73)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B73" s="2" t="s">
@@ -9961,7 +9947,7 @@
     </row>
     <row r="74" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I74)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B74" s="2" t="s">
@@ -10020,7 +10006,7 @@
     </row>
     <row r="75" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I75)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B75" s="2" t="s">
@@ -10079,7 +10065,7 @@
     </row>
     <row r="76" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I76)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B76" s="2" t="s">
@@ -10138,7 +10124,7 @@
     </row>
     <row r="77" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I77)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B77" s="2" t="s">
@@ -10197,7 +10183,7 @@
     </row>
     <row r="78" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I78)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B78" s="2" t="s">
@@ -10256,7 +10242,7 @@
     </row>
     <row r="79" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I79)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B79" s="2" t="s">
@@ -10315,7 +10301,7 @@
     </row>
     <row r="80" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I80)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B80" s="2" t="s">
@@ -10374,7 +10360,7 @@
     </row>
     <row r="81" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I81)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B81" s="2" t="s">
@@ -10433,7 +10419,7 @@
     </row>
     <row r="82" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I82)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B82" s="2" t="s">
@@ -10492,7 +10478,7 @@
     </row>
     <row r="83" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I83)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B83" s="2" t="s">
@@ -10551,7 +10537,7 @@
     </row>
     <row r="84" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I84)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B84" s="2" t="s">
@@ -10610,7 +10596,7 @@
     </row>
     <row r="85" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I85)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B85" s="2" t="s">
@@ -10669,7 +10655,7 @@
     </row>
     <row r="86" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I86)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B86" s="2" t="s">
@@ -10728,7 +10714,7 @@
     </row>
     <row r="87" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I87)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B87" s="2" t="s">
@@ -10787,7 +10773,7 @@
     </row>
     <row r="88" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I88)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B88" s="2" t="s">
@@ -10846,7 +10832,7 @@
     </row>
     <row r="89" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I89)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B89" s="2" t="s">
@@ -10905,7 +10891,7 @@
     </row>
     <row r="90" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I90)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B90" s="2" t="s">
@@ -10964,7 +10950,7 @@
     </row>
     <row r="91" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I91)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B91" s="2" t="s">
@@ -11023,7 +11009,7 @@
     </row>
     <row r="92" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I92)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B92" s="2" t="s">
@@ -11082,7 +11068,7 @@
     </row>
     <row r="93" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I93)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B93" s="2" t="s">
@@ -11141,7 +11127,7 @@
     </row>
     <row r="94" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I94)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B94" s="2" t="s">
@@ -11200,7 +11186,7 @@
     </row>
     <row r="95" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I95)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B95" s="2" t="s">
@@ -11259,7 +11245,7 @@
     </row>
     <row r="96" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I96)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B96" s="2" t="s">
@@ -11318,7 +11304,7 @@
     </row>
     <row r="97" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I97)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B97" s="2" t="s">
@@ -11377,7 +11363,7 @@
     </row>
     <row r="98" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I98)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B98" s="2" t="s">
@@ -11436,7 +11422,7 @@
     </row>
     <row r="99" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I99)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B99" s="2" t="s">
@@ -11495,7 +11481,7 @@
     </row>
     <row r="100" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I100)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B100" s="2" t="s">
@@ -11554,7 +11540,7 @@
     </row>
     <row r="101" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I101)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B101" s="2" t="s">
@@ -11613,7 +11599,7 @@
     </row>
     <row r="102" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I102)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B102" s="2" t="s">
@@ -11672,7 +11658,7 @@
     </row>
     <row r="103" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I103)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B103" s="2" t="s">
@@ -11731,7 +11717,7 @@
     </row>
     <row r="104" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I104)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B104" s="2" t="s">
@@ -11790,7 +11776,7 @@
     </row>
     <row r="105" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I105)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B105" s="2" t="s">
@@ -11849,7 +11835,7 @@
     </row>
     <row r="106" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I106)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B106" s="2" t="s">
@@ -11908,7 +11894,7 @@
     </row>
     <row r="107" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I107)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B107" s="2" t="s">
@@ -11967,7 +11953,7 @@
     </row>
     <row r="108" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I108)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B108" s="2" t="s">
@@ -12026,7 +12012,7 @@
     </row>
     <row r="109" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I109)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B109" s="2" t="s">
@@ -12085,7 +12071,7 @@
     </row>
     <row r="110" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I110)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B110" s="2" t="s">
@@ -12144,7 +12130,7 @@
     </row>
     <row r="111" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I111)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B111" s="2" t="s">
@@ -12203,7 +12189,7 @@
     </row>
     <row r="112" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I112)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B112" s="2" t="s">
@@ -12262,7 +12248,7 @@
     </row>
     <row r="113" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I113)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B113" s="2" t="s">
@@ -12321,7 +12307,7 @@
     </row>
     <row r="114" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I114)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B114" s="2" t="s">
@@ -12380,7 +12366,7 @@
     </row>
     <row r="115" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I115)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B115" s="2" t="s">
@@ -12439,7 +12425,7 @@
     </row>
     <row r="116" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I116)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B116" s="2" t="s">
@@ -12498,7 +12484,7 @@
     </row>
     <row r="117" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I117)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B117" s="2" t="s">
@@ -12557,7 +12543,7 @@
     </row>
     <row r="118" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I118)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B118" s="2" t="s">
@@ -12616,7 +12602,7 @@
     </row>
     <row r="119" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I119)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B119" s="2" t="s">
@@ -12675,7 +12661,7 @@
     </row>
     <row r="120" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I120)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B120" s="2" t="s">
@@ -12734,7 +12720,7 @@
     </row>
     <row r="121" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I121)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B121" s="2" t="s">
@@ -12793,7 +12779,7 @@
     </row>
     <row r="122" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I122)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B122" s="2" t="s">
@@ -12852,7 +12838,7 @@
     </row>
     <row r="123" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I123)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B123" s="2" t="s">
@@ -12911,7 +12897,7 @@
     </row>
     <row r="124" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I124)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B124" s="2" t="s">
@@ -12970,7 +12956,7 @@
     </row>
     <row r="125" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I125)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B125" s="2" t="s">
@@ -13029,7 +13015,7 @@
     </row>
     <row r="126" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I126)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B126" s="2" t="s">
@@ -13088,7 +13074,7 @@
     </row>
     <row r="127" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I127)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B127" s="2" t="s">
@@ -13147,7 +13133,7 @@
     </row>
     <row r="128" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I128)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B128" s="2" t="s">
@@ -13206,7 +13192,7 @@
     </row>
     <row r="129" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(ISBLANK(I129)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B129" s="2" t="s">
@@ -13265,7 +13251,7 @@
     </row>
     <row r="130" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="str">
-        <f t="shared" ref="A130:A193" si="2">IF(ISBLANK(I130)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I130)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B130" s="2" t="s">
@@ -13324,7 +13310,7 @@
     </row>
     <row r="131" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I131)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B131" s="2" t="s">
@@ -13383,7 +13369,7 @@
     </row>
     <row r="132" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I132)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B132" s="2" t="s">
@@ -13442,7 +13428,7 @@
     </row>
     <row r="133" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I133)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B133" s="2" t="s">
@@ -13501,7 +13487,7 @@
     </row>
     <row r="134" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I134)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B134" s="2" t="s">
@@ -13560,7 +13546,7 @@
     </row>
     <row r="135" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I135)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B135" s="2" t="s">
@@ -13619,7 +13605,7 @@
     </row>
     <row r="136" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I136)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B136" s="2" t="s">
@@ -13678,7 +13664,7 @@
     </row>
     <row r="137" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I137)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B137" s="2" t="s">
@@ -13737,7 +13723,7 @@
     </row>
     <row r="138" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I138)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B138" s="2" t="s">
@@ -13796,7 +13782,7 @@
     </row>
     <row r="139" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I139)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B139" s="2" t="s">
@@ -13855,7 +13841,7 @@
     </row>
     <row r="140" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I140)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B140" s="2" t="s">
@@ -13914,7 +13900,7 @@
     </row>
     <row r="141" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I141)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B141" s="2" t="s">
@@ -13973,7 +13959,7 @@
     </row>
     <row r="142" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I142)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B142" s="2" t="s">
@@ -14032,7 +14018,7 @@
     </row>
     <row r="143" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I143)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B143" s="2" t="s">
@@ -14091,7 +14077,7 @@
     </row>
     <row r="144" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I144)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B144" s="2" t="s">
@@ -14150,7 +14136,7 @@
     </row>
     <row r="145" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I145)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B145" s="2" t="s">
@@ -14209,7 +14195,7 @@
     </row>
     <row r="146" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I146)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B146" s="2" t="s">
@@ -14268,7 +14254,7 @@
     </row>
     <row r="147" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I147)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B147" s="2" t="s">
@@ -14327,7 +14313,7 @@
     </row>
     <row r="148" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I148)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B148" s="2" t="s">
@@ -14386,7 +14372,7 @@
     </row>
     <row r="149" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I149)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B149" s="2" t="s">
@@ -14445,7 +14431,7 @@
     </row>
     <row r="150" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I150)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B150" s="2" t="s">
@@ -14504,7 +14490,7 @@
     </row>
     <row r="151" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I151)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B151" s="2" t="s">
@@ -14563,7 +14549,7 @@
     </row>
     <row r="152" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I152)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B152" s="2" t="s">
@@ -14622,7 +14608,7 @@
     </row>
     <row r="153" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I153)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B153" s="2" t="s">
@@ -14681,7 +14667,7 @@
     </row>
     <row r="154" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I154)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B154" s="2" t="s">
@@ -14740,7 +14726,7 @@
     </row>
     <row r="155" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I155)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B155" s="2" t="s">
@@ -14799,7 +14785,7 @@
     </row>
     <row r="156" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I156)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B156" s="2" t="s">
@@ -14858,7 +14844,7 @@
     </row>
     <row r="157" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I157)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B157" s="2" t="s">
@@ -14917,7 +14903,7 @@
     </row>
     <row r="158" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I158)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B158" s="2" t="s">
@@ -14976,7 +14962,7 @@
     </row>
     <row r="159" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I159)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B159" s="2" t="s">
@@ -15035,7 +15021,7 @@
     </row>
     <row r="160" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I160)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B160" s="2" t="s">
@@ -15094,7 +15080,7 @@
     </row>
     <row r="161" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I161)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B161" s="2" t="s">
@@ -15153,7 +15139,7 @@
     </row>
     <row r="162" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I162)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B162" s="2" t="s">
@@ -15212,7 +15198,7 @@
     </row>
     <row r="163" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I163)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B163" s="2" t="s">
@@ -15271,7 +15257,7 @@
     </row>
     <row r="164" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I164)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B164" s="2" t="s">
@@ -15330,7 +15316,7 @@
     </row>
     <row r="165" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I165)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B165" s="2" t="s">
@@ -15389,7 +15375,7 @@
     </row>
     <row r="166" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I166)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B166" s="2" t="s">
@@ -15448,7 +15434,7 @@
     </row>
     <row r="167" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I167)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B167" s="2" t="s">
@@ -15507,7 +15493,7 @@
     </row>
     <row r="168" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I168)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B168" s="2" t="s">
@@ -15566,7 +15552,7 @@
     </row>
     <row r="169" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I169)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B169" s="2" t="s">
@@ -15625,7 +15611,7 @@
     </row>
     <row r="170" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I170)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B170" s="2" t="s">
@@ -15684,7 +15670,7 @@
     </row>
     <row r="171" spans="1:18" ht="90" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I171)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B171" s="2" t="s">
@@ -15743,7 +15729,7 @@
     </row>
     <row r="172" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I172)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B172" s="2" t="s">
@@ -15802,7 +15788,7 @@
     </row>
     <row r="173" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I173)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B173" s="2" t="s">
@@ -15861,7 +15847,7 @@
     </row>
     <row r="174" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I174)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B174" s="2" t="s">
@@ -15920,7 +15906,7 @@
     </row>
     <row r="175" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I175)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B175" s="2" t="s">
@@ -15979,7 +15965,7 @@
     </row>
     <row r="176" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I176)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B176" s="2" t="s">
@@ -16038,7 +16024,7 @@
     </row>
     <row r="177" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I177)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B177" s="2" t="s">
@@ -16097,7 +16083,7 @@
     </row>
     <row r="178" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I178)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B178" s="2" t="s">
@@ -16156,7 +16142,7 @@
     </row>
     <row r="179" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I179)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B179" s="2" t="s">
@@ -16215,7 +16201,7 @@
     </row>
     <row r="180" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I180)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B180" s="2" t="s">
@@ -16274,7 +16260,7 @@
     </row>
     <row r="181" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I181)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B181" s="2" t="s">
@@ -16333,7 +16319,7 @@
     </row>
     <row r="182" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I182)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B182" s="2" t="s">
@@ -16392,7 +16378,7 @@
     </row>
     <row r="183" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I183)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B183" s="2" t="s">
@@ -16451,7 +16437,7 @@
     </row>
     <row r="184" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I184)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B184" s="2" t="s">
@@ -16510,7 +16496,7 @@
     </row>
     <row r="185" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I185)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B185" s="2" t="s">
@@ -16569,7 +16555,7 @@
     </row>
     <row r="186" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I186)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B186" s="2" t="s">
@@ -16628,7 +16614,7 @@
     </row>
     <row r="187" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I187)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B187" s="2" t="s">
@@ -16687,7 +16673,7 @@
     </row>
     <row r="188" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I188)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B188" s="2" t="s">
@@ -16746,7 +16732,7 @@
     </row>
     <row r="189" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I189)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B189" s="2" t="s">
@@ -16805,7 +16791,7 @@
     </row>
     <row r="190" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I190)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B190" s="2" t="s">
@@ -16864,7 +16850,7 @@
     </row>
     <row r="191" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I191)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B191" s="2" t="s">
@@ -16923,7 +16909,7 @@
     </row>
     <row r="192" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I192)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B192" s="2" t="s">
@@ -16982,7 +16968,7 @@
     </row>
     <row r="193" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="str">
-        <f t="shared" si="2"/>
+        <f>IF(ISBLANK(I193)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B193" s="2" t="s">
@@ -17041,7 +17027,7 @@
     </row>
     <row r="194" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="str">
-        <f t="shared" ref="A194:A205" si="3">IF(ISBLANK(I194)=TRUE,"Pending","Done")</f>
+        <f>IF(ISBLANK(I194)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B194" s="2" t="s">
@@ -17100,7 +17086,7 @@
     </row>
     <row r="195" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I195)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B195" s="2" t="s">
@@ -17159,7 +17145,7 @@
     </row>
     <row r="196" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I196)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B196" s="2" t="s">
@@ -17218,7 +17204,7 @@
     </row>
     <row r="197" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I197)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B197" s="2" t="s">
@@ -17277,7 +17263,7 @@
     </row>
     <row r="198" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I198)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B198" s="2" t="s">
@@ -17336,7 +17322,7 @@
     </row>
     <row r="199" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I199)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B199" s="2" t="s">
@@ -17395,7 +17381,7 @@
     </row>
     <row r="200" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I200)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B200" s="2" t="s">
@@ -17454,7 +17440,7 @@
     </row>
     <row r="201" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I201)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B201" s="2" t="s">
@@ -17513,7 +17499,7 @@
     </row>
     <row r="202" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I202)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B202" s="2" t="s">
@@ -17572,7 +17558,7 @@
     </row>
     <row r="203" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I203)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B203" s="2" t="s">
@@ -17631,7 +17617,7 @@
     </row>
     <row r="204" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I204)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B204" s="2" t="s">
@@ -17690,7 +17676,7 @@
     </row>
     <row r="205" spans="1:18" ht="30" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="str">
-        <f t="shared" si="3"/>
+        <f>IF(ISBLANK(I205)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B205" s="2" t="s">
@@ -17752,25 +17738,8 @@
     <sortCondition descending="1" ref="J1:J205"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:A205 M1:R205">
-    <cfRule type="expression" dxfId="3" priority="5">
-      <formula>$A1="Pending"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J206:J1048576">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:G205 I1:L205">
-    <cfRule type="expression" dxfId="1" priority="2">
+  <conditionalFormatting sqref="A1:R205">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17786,9 +17755,16 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H1:H205">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$A1="Pending"</formula>
+  <conditionalFormatting sqref="J206:J1048576">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -22882,7 +22858,7 @@
     <sortCondition ref="A223:A297"/>
   </sortState>
   <conditionalFormatting sqref="A1:B1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/data/master_links.xlsx
+++ b/data/master_links.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Cryo\Private\OTGX\LinkBoardApplication\LinkBoardV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCBE6979-6A0E-4861-A703-281474C7967E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2E0F575-9D12-4202-8981-24C7FF83958B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="258" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6956,14 +6956,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1" tint="4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -7254,6 +7247,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:U466"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7347,7 +7341,7 @@
     </row>
     <row r="2" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str">
-        <f>IF(ISBLANK(I2)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A2:A65" si="0">IF(ISBLANK(I2)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -7398,7 +7392,7 @@
         <v>675</v>
       </c>
       <c r="Q2" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E2))</f>
+        <f t="shared" ref="Q2:Q65" si="1">ISNUMBER(SEARCH(",",E2))</f>
         <v>0</v>
       </c>
       <c r="R2" s="1" t="s">
@@ -7416,7 +7410,7 @@
     </row>
     <row r="3" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
-        <f>IF(ISBLANK(I3)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -7467,7 +7461,7 @@
         <v>676</v>
       </c>
       <c r="Q3" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E3))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R3" s="1" t="s">
@@ -7485,7 +7479,7 @@
     </row>
     <row r="4" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
-        <f>IF(ISBLANK(I4)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -7536,7 +7530,7 @@
         <v>676</v>
       </c>
       <c r="Q4" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E4))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R4" s="1" t="s">
@@ -7554,7 +7548,7 @@
     </row>
     <row r="5" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
-        <f>IF(ISBLANK(I5)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -7605,7 +7599,7 @@
         <v>676</v>
       </c>
       <c r="Q5" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E5))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R5" s="1" t="s">
@@ -7623,7 +7617,7 @@
     </row>
     <row r="6" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
-        <f>IF(ISBLANK(I6)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -7674,7 +7668,7 @@
         <v>1679</v>
       </c>
       <c r="Q6" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E6))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R6" s="1" t="s">
@@ -7692,7 +7686,7 @@
     </row>
     <row r="7" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
-        <f>IF(ISBLANK(I7)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -7743,7 +7737,7 @@
         <v>676</v>
       </c>
       <c r="Q7" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E7))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R7" s="1" t="s">
@@ -7761,7 +7755,7 @@
     </row>
     <row r="8" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
-        <f>IF(ISBLANK(I8)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -7812,7 +7806,7 @@
         <v>1678</v>
       </c>
       <c r="Q8" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E8))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R8" s="1" t="s">
@@ -7830,7 +7824,7 @@
     </row>
     <row r="9" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
-        <f>IF(ISBLANK(I9)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -7881,7 +7875,7 @@
         <v>1836</v>
       </c>
       <c r="Q9" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E9))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R9" s="1" t="s">
@@ -7899,7 +7893,7 @@
     </row>
     <row r="10" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
-        <f>IF(ISBLANK(I10)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -7950,7 +7944,7 @@
         <v>1836</v>
       </c>
       <c r="Q10" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E10))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R10" s="1" t="s">
@@ -7968,7 +7962,7 @@
     </row>
     <row r="11" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
-        <f>IF(ISBLANK(I11)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -8019,7 +8013,7 @@
         <v>1836</v>
       </c>
       <c r="Q11" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E11))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R11" s="1" t="s">
@@ -8037,7 +8031,7 @@
     </row>
     <row r="12" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
-        <f>IF(ISBLANK(I12)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -8088,7 +8082,7 @@
         <v>1836</v>
       </c>
       <c r="Q12" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E12))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R12" s="1" t="s">
@@ -8106,7 +8100,7 @@
     </row>
     <row r="13" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
-        <f>IF(ISBLANK(I13)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -8157,7 +8151,7 @@
         <v>1836</v>
       </c>
       <c r="Q13" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E13))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R13" s="1" t="s">
@@ -8175,7 +8169,7 @@
     </row>
     <row r="14" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
-        <f>IF(ISBLANK(I14)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -8226,7 +8220,7 @@
         <v>709</v>
       </c>
       <c r="Q14" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E14))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R14" s="1" t="s">
@@ -8244,7 +8238,7 @@
     </row>
     <row r="15" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
-        <f>IF(ISBLANK(I15)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -8295,7 +8289,7 @@
         <v>1836</v>
       </c>
       <c r="Q15" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E15))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R15" s="1" t="s">
@@ -8313,7 +8307,7 @@
     </row>
     <row r="16" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
-        <f>IF(ISBLANK(I16)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -8364,7 +8358,7 @@
         <v>1836</v>
       </c>
       <c r="Q16" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E16))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R16" s="1" t="s">
@@ -8382,7 +8376,7 @@
     </row>
     <row r="17" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
-        <f>IF(ISBLANK(I17)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -8433,7 +8427,7 @@
         <v>1836</v>
       </c>
       <c r="Q17" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E17))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R17" s="1" t="s">
@@ -8451,7 +8445,7 @@
     </row>
     <row r="18" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
-        <f>IF(ISBLANK(I18)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -8502,7 +8496,7 @@
         <v>1836</v>
       </c>
       <c r="Q18" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E18))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R18" s="1" t="s">
@@ -8520,7 +8514,7 @@
     </row>
     <row r="19" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
-        <f>IF(ISBLANK(I19)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -8571,7 +8565,7 @@
         <v>1836</v>
       </c>
       <c r="Q19" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E19))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R19" s="1" t="s">
@@ -8589,7 +8583,7 @@
     </row>
     <row r="20" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
-        <f>IF(ISBLANK(I20)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -8640,7 +8634,7 @@
         <v>1678</v>
       </c>
       <c r="Q20" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E20))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R20" s="1" t="s">
@@ -8658,7 +8652,7 @@
     </row>
     <row r="21" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="str">
-        <f>IF(ISBLANK(I21)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -8709,7 +8703,7 @@
         <v>1836</v>
       </c>
       <c r="Q21" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E21))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R21" s="1" t="s">
@@ -8727,7 +8721,7 @@
     </row>
     <row r="22" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="str">
-        <f>IF(ISBLANK(I22)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -8778,7 +8772,7 @@
         <v>1836</v>
       </c>
       <c r="Q22" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E22))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R22" s="1" t="s">
@@ -8796,7 +8790,7 @@
     </row>
     <row r="23" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="str">
-        <f>IF(ISBLANK(I23)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -8847,7 +8841,7 @@
         <v>1836</v>
       </c>
       <c r="Q23" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E23))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R23" s="1" t="s">
@@ -8865,7 +8859,7 @@
     </row>
     <row r="24" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
-        <f>IF(ISBLANK(I24)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -8916,7 +8910,7 @@
         <v>1836</v>
       </c>
       <c r="Q24" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E24))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R24" s="1" t="s">
@@ -8934,7 +8928,7 @@
     </row>
     <row r="25" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
-        <f>IF(ISBLANK(I25)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -8985,7 +8979,7 @@
         <v>1836</v>
       </c>
       <c r="Q25" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E25))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R25" s="1" t="s">
@@ -9003,7 +8997,7 @@
     </row>
     <row r="26" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="str">
-        <f>IF(ISBLANK(I26)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -9054,7 +9048,7 @@
         <v>1836</v>
       </c>
       <c r="Q26" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E26))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R26" s="1" t="s">
@@ -9072,7 +9066,7 @@
     </row>
     <row r="27" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
-        <f>IF(ISBLANK(I27)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -9123,7 +9117,7 @@
         <v>1836</v>
       </c>
       <c r="Q27" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E27))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R27" s="1" t="s">
@@ -9141,7 +9135,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
-        <f>IF(ISBLANK(I28)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -9192,7 +9186,7 @@
         <v>1836</v>
       </c>
       <c r="Q28" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E28))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R28" s="1" t="s">
@@ -9210,7 +9204,7 @@
     </row>
     <row r="29" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
-        <f>IF(ISBLANK(I29)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B29" s="1" t="s">
@@ -9261,7 +9255,7 @@
         <v>1836</v>
       </c>
       <c r="Q29" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E29))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R29" s="1" t="s">
@@ -9279,7 +9273,7 @@
     </row>
     <row r="30" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="str">
-        <f>IF(ISBLANK(I30)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B30" s="1" t="s">
@@ -9330,7 +9324,7 @@
         <v>1836</v>
       </c>
       <c r="Q30" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E30))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R30" s="1" t="s">
@@ -9348,7 +9342,7 @@
     </row>
     <row r="31" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="str">
-        <f>IF(ISBLANK(I31)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -9399,7 +9393,7 @@
         <v>1836</v>
       </c>
       <c r="Q31" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E31))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R31" s="1" t="s">
@@ -9417,7 +9411,7 @@
     </row>
     <row r="32" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
-        <f>IF(ISBLANK(I32)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -9468,7 +9462,7 @@
         <v>1836</v>
       </c>
       <c r="Q32" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E32))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R32" s="1" t="s">
@@ -9486,7 +9480,7 @@
     </row>
     <row r="33" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="str">
-        <f>IF(ISBLANK(I33)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -9537,7 +9531,7 @@
         <v>1836</v>
       </c>
       <c r="Q33" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E33))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R33" s="1" t="s">
@@ -9555,7 +9549,7 @@
     </row>
     <row r="34" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="str">
-        <f>IF(ISBLANK(I34)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -9606,7 +9600,7 @@
         <v>1836</v>
       </c>
       <c r="Q34" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E34))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R34" s="1" t="s">
@@ -9624,7 +9618,7 @@
     </row>
     <row r="35" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
-        <f>IF(ISBLANK(I35)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -9675,7 +9669,7 @@
         <v>1836</v>
       </c>
       <c r="Q35" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E35))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R35" s="1" t="s">
@@ -9693,7 +9687,7 @@
     </row>
     <row r="36" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="str">
-        <f>IF(ISBLANK(I36)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -9744,7 +9738,7 @@
         <v>1836</v>
       </c>
       <c r="Q36" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E36))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R36" s="1" t="s">
@@ -9762,7 +9756,7 @@
     </row>
     <row r="37" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="str">
-        <f>IF(ISBLANK(I37)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B37" s="1" t="s">
@@ -9813,7 +9807,7 @@
         <v>1836</v>
       </c>
       <c r="Q37" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E37))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R37" s="1" t="s">
@@ -9831,7 +9825,7 @@
     </row>
     <row r="38" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="str">
-        <f>IF(ISBLANK(I38)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B38" s="1" t="s">
@@ -9882,7 +9876,7 @@
         <v>1836</v>
       </c>
       <c r="Q38" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E38))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R38" s="1" t="s">
@@ -9900,7 +9894,7 @@
     </row>
     <row r="39" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
-        <f>IF(ISBLANK(I39)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B39" s="1" t="s">
@@ -9951,7 +9945,7 @@
         <v>1836</v>
       </c>
       <c r="Q39" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E39))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R39" s="1" t="s">
@@ -9969,7 +9963,7 @@
     </row>
     <row r="40" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="str">
-        <f>IF(ISBLANK(I40)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B40" s="1" t="s">
@@ -10020,7 +10014,7 @@
         <v>1836</v>
       </c>
       <c r="Q40" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E40))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R40" s="1" t="s">
@@ -10038,7 +10032,7 @@
     </row>
     <row r="41" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="str">
-        <f>IF(ISBLANK(I41)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B41" s="1" t="s">
@@ -10089,7 +10083,7 @@
         <v>1836</v>
       </c>
       <c r="Q41" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E41))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R41" s="1" t="s">
@@ -10107,7 +10101,7 @@
     </row>
     <row r="42" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="str">
-        <f>IF(ISBLANK(I42)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B42" s="1" t="s">
@@ -10158,7 +10152,7 @@
         <v>1836</v>
       </c>
       <c r="Q42" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E42))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R42" s="1" t="s">
@@ -10176,7 +10170,7 @@
     </row>
     <row r="43" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="str">
-        <f>IF(ISBLANK(I43)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B43" s="1" t="s">
@@ -10227,7 +10221,7 @@
         <v>1836</v>
       </c>
       <c r="Q43" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E43))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R43" s="1" t="s">
@@ -10245,7 +10239,7 @@
     </row>
     <row r="44" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="str">
-        <f>IF(ISBLANK(I44)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B44" s="1" t="s">
@@ -10296,7 +10290,7 @@
         <v>1836</v>
       </c>
       <c r="Q44" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E44))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R44" s="1" t="s">
@@ -10314,7 +10308,7 @@
     </row>
     <row r="45" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="str">
-        <f>IF(ISBLANK(I45)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B45" s="1" t="s">
@@ -10365,7 +10359,7 @@
         <v>1836</v>
       </c>
       <c r="Q45" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E45))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R45" s="1" t="s">
@@ -10383,7 +10377,7 @@
     </row>
     <row r="46" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="str">
-        <f>IF(ISBLANK(I46)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B46" s="1" t="s">
@@ -10434,7 +10428,7 @@
         <v>1836</v>
       </c>
       <c r="Q46" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E46))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R46" s="1" t="s">
@@ -10452,7 +10446,7 @@
     </row>
     <row r="47" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="str">
-        <f>IF(ISBLANK(I47)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B47" s="1" t="s">
@@ -10503,7 +10497,7 @@
         <v>1836</v>
       </c>
       <c r="Q47" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E47))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R47" s="1" t="s">
@@ -10521,7 +10515,7 @@
     </row>
     <row r="48" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="str">
-        <f>IF(ISBLANK(I48)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -10572,7 +10566,7 @@
         <v>1836</v>
       </c>
       <c r="Q48" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E48))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R48" s="1" t="s">
@@ -10590,7 +10584,7 @@
     </row>
     <row r="49" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="str">
-        <f>IF(ISBLANK(I49)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -10641,7 +10635,7 @@
         <v>1836</v>
       </c>
       <c r="Q49" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E49))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R49" s="1" t="s">
@@ -10659,7 +10653,7 @@
     </row>
     <row r="50" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="str">
-        <f>IF(ISBLANK(I50)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B50" s="1" t="s">
@@ -10710,7 +10704,7 @@
         <v>1836</v>
       </c>
       <c r="Q50" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E50))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R50" s="1" t="s">
@@ -10728,7 +10722,7 @@
     </row>
     <row r="51" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
-        <f>IF(ISBLANK(I51)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -10779,7 +10773,7 @@
         <v>1836</v>
       </c>
       <c r="Q51" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E51))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R51" s="1" t="s">
@@ -10797,7 +10791,7 @@
     </row>
     <row r="52" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="str">
-        <f>IF(ISBLANK(I52)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B52" s="1" t="s">
@@ -10848,7 +10842,7 @@
         <v>1836</v>
       </c>
       <c r="Q52" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E52))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R52" s="1" t="s">
@@ -10866,7 +10860,7 @@
     </row>
     <row r="53" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="str">
-        <f>IF(ISBLANK(I53)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -10917,7 +10911,7 @@
         <v>1836</v>
       </c>
       <c r="Q53" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E53))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R53" s="1" t="s">
@@ -10935,7 +10929,7 @@
     </row>
     <row r="54" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="str">
-        <f>IF(ISBLANK(I54)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B54" s="1" t="s">
@@ -10986,7 +10980,7 @@
         <v>1836</v>
       </c>
       <c r="Q54" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E54))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R54" s="1" t="s">
@@ -11004,7 +10998,7 @@
     </row>
     <row r="55" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="str">
-        <f>IF(ISBLANK(I55)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -11055,7 +11049,7 @@
         <v>1836</v>
       </c>
       <c r="Q55" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E55))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R55" s="1" t="s">
@@ -11073,7 +11067,7 @@
     </row>
     <row r="56" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="str">
-        <f>IF(ISBLANK(I56)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B56" s="1" t="s">
@@ -11124,7 +11118,7 @@
         <v>1836</v>
       </c>
       <c r="Q56" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E56))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R56" s="1" t="s">
@@ -11142,7 +11136,7 @@
     </row>
     <row r="57" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="str">
-        <f>IF(ISBLANK(I57)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -11193,7 +11187,7 @@
         <v>1836</v>
       </c>
       <c r="Q57" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E57))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R57" s="1" t="s">
@@ -11211,7 +11205,7 @@
     </row>
     <row r="58" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="str">
-        <f>IF(ISBLANK(I58)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B58" s="1" t="s">
@@ -11262,7 +11256,7 @@
         <v>1836</v>
       </c>
       <c r="Q58" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E58))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R58" s="1" t="s">
@@ -11280,7 +11274,7 @@
     </row>
     <row r="59" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="str">
-        <f>IF(ISBLANK(I59)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -11331,7 +11325,7 @@
         <v>1836</v>
       </c>
       <c r="Q59" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E59))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R59" s="1" t="s">
@@ -11349,7 +11343,7 @@
     </row>
     <row r="60" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="str">
-        <f>IF(ISBLANK(I60)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B60" s="1" t="s">
@@ -11400,7 +11394,7 @@
         <v>1836</v>
       </c>
       <c r="Q60" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E60))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R60" s="1" t="s">
@@ -11418,7 +11412,7 @@
     </row>
     <row r="61" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="str">
-        <f>IF(ISBLANK(I61)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -11469,7 +11463,7 @@
         <v>1836</v>
       </c>
       <c r="Q61" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E61))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R61" s="1" t="s">
@@ -11487,7 +11481,7 @@
     </row>
     <row r="62" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="str">
-        <f>IF(ISBLANK(I62)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B62" s="1" t="s">
@@ -11538,7 +11532,7 @@
         <v>1836</v>
       </c>
       <c r="Q62" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E62))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R62" s="1" t="s">
@@ -11556,7 +11550,7 @@
     </row>
     <row r="63" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="str">
-        <f>IF(ISBLANK(I63)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B63" s="1" t="s">
@@ -11607,7 +11601,7 @@
         <v>1836</v>
       </c>
       <c r="Q63" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E63))</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="R63" s="1" t="s">
@@ -11625,7 +11619,7 @@
     </row>
     <row r="64" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="str">
-        <f>IF(ISBLANK(I64)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B64" s="1" t="s">
@@ -11676,7 +11670,7 @@
         <v>1836</v>
       </c>
       <c r="Q64" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E64))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R64" s="1" t="s">
@@ -11694,7 +11688,7 @@
     </row>
     <row r="65" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="str">
-        <f>IF(ISBLANK(I65)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="0"/>
         <v>Done</v>
       </c>
       <c r="B65" s="1" t="s">
@@ -11745,7 +11739,7 @@
         <v>1836</v>
       </c>
       <c r="Q65" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E65))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="R65" s="1" t="s">
@@ -11763,7 +11757,7 @@
     </row>
     <row r="66" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="str">
-        <f>IF(ISBLANK(I66)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A66:A129" si="2">IF(ISBLANK(I66)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B66" s="1" t="s">
@@ -11814,7 +11808,7 @@
         <v>1836</v>
       </c>
       <c r="Q66" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E66))</f>
+        <f t="shared" ref="Q66:Q129" si="3">ISNUMBER(SEARCH(",",E66))</f>
         <v>0</v>
       </c>
       <c r="R66" s="1" t="s">
@@ -11830,9 +11824,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="67" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" ht="75" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="str">
-        <f>IF(ISBLANK(I67)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B67" s="1" t="s">
@@ -11883,7 +11877,7 @@
         <v>1836</v>
       </c>
       <c r="Q67" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E67))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R67" s="1" t="s">
@@ -11901,7 +11895,7 @@
     </row>
     <row r="68" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="str">
-        <f>IF(ISBLANK(I68)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B68" s="1" t="s">
@@ -11952,7 +11946,7 @@
         <v>1836</v>
       </c>
       <c r="Q68" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E68))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R68" s="1" t="s">
@@ -11970,7 +11964,7 @@
     </row>
     <row r="69" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="str">
-        <f>IF(ISBLANK(I69)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B69" s="1" t="s">
@@ -12021,7 +12015,7 @@
         <v>1836</v>
       </c>
       <c r="Q69" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E69))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R69" s="1" t="s">
@@ -12039,7 +12033,7 @@
     </row>
     <row r="70" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="str">
-        <f>IF(ISBLANK(I70)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B70" s="1" t="s">
@@ -12090,7 +12084,7 @@
         <v>1836</v>
       </c>
       <c r="Q70" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E70))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R70" s="1" t="s">
@@ -12108,7 +12102,7 @@
     </row>
     <row r="71" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="str">
-        <f>IF(ISBLANK(I71)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B71" s="1" t="s">
@@ -12159,7 +12153,7 @@
         <v>1836</v>
       </c>
       <c r="Q71" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E71))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R71" s="1" t="s">
@@ -12177,7 +12171,7 @@
     </row>
     <row r="72" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="str">
-        <f>IF(ISBLANK(I72)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B72" s="1" t="s">
@@ -12228,7 +12222,7 @@
         <v>1836</v>
       </c>
       <c r="Q72" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E72))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R72" s="1" t="s">
@@ -12246,7 +12240,7 @@
     </row>
     <row r="73" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="str">
-        <f>IF(ISBLANK(I73)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B73" s="1" t="s">
@@ -12297,7 +12291,7 @@
         <v>1836</v>
       </c>
       <c r="Q73" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E73))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R73" s="1" t="s">
@@ -12315,7 +12309,7 @@
     </row>
     <row r="74" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="str">
-        <f>IF(ISBLANK(I74)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B74" s="1" t="s">
@@ -12366,7 +12360,7 @@
         <v>1836</v>
       </c>
       <c r="Q74" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E74))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R74" s="1" t="s">
@@ -12384,7 +12378,7 @@
     </row>
     <row r="75" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="str">
-        <f>IF(ISBLANK(I75)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B75" s="1" t="s">
@@ -12435,7 +12429,7 @@
         <v>1836</v>
       </c>
       <c r="Q75" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E75))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R75" s="1" t="s">
@@ -12453,7 +12447,7 @@
     </row>
     <row r="76" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="str">
-        <f>IF(ISBLANK(I76)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B76" s="1" t="s">
@@ -12504,7 +12498,7 @@
         <v>1836</v>
       </c>
       <c r="Q76" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E76))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R76" s="1" t="s">
@@ -12522,7 +12516,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="str">
-        <f>IF(ISBLANK(I77)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B77" s="1" t="s">
@@ -12573,7 +12567,7 @@
         <v>1836</v>
       </c>
       <c r="Q77" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E77))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R77" s="1" t="s">
@@ -12591,7 +12585,7 @@
     </row>
     <row r="78" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="str">
-        <f>IF(ISBLANK(I78)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B78" s="1" t="s">
@@ -12642,7 +12636,7 @@
         <v>1836</v>
       </c>
       <c r="Q78" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E78))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R78" s="1" t="s">
@@ -12660,7 +12654,7 @@
     </row>
     <row r="79" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="str">
-        <f>IF(ISBLANK(I79)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B79" s="1" t="s">
@@ -12711,7 +12705,7 @@
         <v>1836</v>
       </c>
       <c r="Q79" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E79))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R79" s="1" t="s">
@@ -12729,7 +12723,7 @@
     </row>
     <row r="80" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="str">
-        <f>IF(ISBLANK(I80)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B80" s="1" t="s">
@@ -12780,7 +12774,7 @@
         <v>1836</v>
       </c>
       <c r="Q80" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E80))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R80" s="1" t="s">
@@ -12798,7 +12792,7 @@
     </row>
     <row r="81" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="str">
-        <f>IF(ISBLANK(I81)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B81" s="1" t="s">
@@ -12849,7 +12843,7 @@
         <v>1836</v>
       </c>
       <c r="Q81" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E81))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R81" s="1" t="s">
@@ -12867,7 +12861,7 @@
     </row>
     <row r="82" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="str">
-        <f>IF(ISBLANK(I82)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B82" s="1" t="s">
@@ -12918,7 +12912,7 @@
         <v>1836</v>
       </c>
       <c r="Q82" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E82))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R82" s="1" t="s">
@@ -12936,7 +12930,7 @@
     </row>
     <row r="83" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="str">
-        <f>IF(ISBLANK(I83)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B83" s="1" t="s">
@@ -12987,7 +12981,7 @@
         <v>1836</v>
       </c>
       <c r="Q83" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E83))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R83" s="1" t="s">
@@ -13005,7 +12999,7 @@
     </row>
     <row r="84" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="str">
-        <f>IF(ISBLANK(I84)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B84" s="1" t="s">
@@ -13056,7 +13050,7 @@
         <v>1836</v>
       </c>
       <c r="Q84" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E84))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R84" s="1" t="s">
@@ -13074,7 +13068,7 @@
     </row>
     <row r="85" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="str">
-        <f>IF(ISBLANK(I85)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B85" s="1" t="s">
@@ -13125,7 +13119,7 @@
         <v>1836</v>
       </c>
       <c r="Q85" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E85))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R85" s="1" t="s">
@@ -13143,7 +13137,7 @@
     </row>
     <row r="86" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="str">
-        <f>IF(ISBLANK(I86)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B86" s="1" t="s">
@@ -13194,7 +13188,7 @@
         <v>1836</v>
       </c>
       <c r="Q86" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E86))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R86" s="1" t="s">
@@ -13212,7 +13206,7 @@
     </row>
     <row r="87" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="str">
-        <f>IF(ISBLANK(I87)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B87" s="1" t="s">
@@ -13263,7 +13257,7 @@
         <v>1836</v>
       </c>
       <c r="Q87" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E87))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R87" s="1" t="s">
@@ -13281,7 +13275,7 @@
     </row>
     <row r="88" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="str">
-        <f>IF(ISBLANK(I88)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B88" s="1" t="s">
@@ -13332,7 +13326,7 @@
         <v>1836</v>
       </c>
       <c r="Q88" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E88))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R88" s="1" t="s">
@@ -13350,7 +13344,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="str">
-        <f>IF(ISBLANK(I89)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B89" s="1" t="s">
@@ -13401,7 +13395,7 @@
         <v>1836</v>
       </c>
       <c r="Q89" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E89))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R89" s="1" t="s">
@@ -13419,7 +13413,7 @@
     </row>
     <row r="90" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="str">
-        <f>IF(ISBLANK(I90)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B90" s="1" t="s">
@@ -13470,7 +13464,7 @@
         <v>1836</v>
       </c>
       <c r="Q90" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E90))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R90" s="1" t="s">
@@ -13488,7 +13482,7 @@
     </row>
     <row r="91" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="str">
-        <f>IF(ISBLANK(I91)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -13539,7 +13533,7 @@
         <v>1836</v>
       </c>
       <c r="Q91" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E91))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R91" s="1" t="s">
@@ -13557,7 +13551,7 @@
     </row>
     <row r="92" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="str">
-        <f>IF(ISBLANK(I92)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B92" s="1" t="s">
@@ -13608,7 +13602,7 @@
         <v>1836</v>
       </c>
       <c r="Q92" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E92))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R92" s="1" t="s">
@@ -13626,7 +13620,7 @@
     </row>
     <row r="93" spans="1:21" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="str">
-        <f>IF(ISBLANK(I93)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B93" s="1" t="s">
@@ -13677,7 +13671,7 @@
         <v>1836</v>
       </c>
       <c r="Q93" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E93))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R93" s="1" t="s">
@@ -13695,7 +13689,7 @@
     </row>
     <row r="94" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="str">
-        <f>IF(ISBLANK(I94)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B94" s="1" t="s">
@@ -13746,7 +13740,7 @@
         <v>1836</v>
       </c>
       <c r="Q94" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E94))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R94" s="1" t="s">
@@ -13764,7 +13758,7 @@
     </row>
     <row r="95" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="str">
-        <f>IF(ISBLANK(I95)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B95" s="1" t="s">
@@ -13815,7 +13809,7 @@
         <v>1836</v>
       </c>
       <c r="Q95" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E95))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R95" s="1" t="s">
@@ -13833,7 +13827,7 @@
     </row>
     <row r="96" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="str">
-        <f>IF(ISBLANK(I96)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B96" s="1" t="s">
@@ -13884,7 +13878,7 @@
         <v>1836</v>
       </c>
       <c r="Q96" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E96))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R96" s="1" t="s">
@@ -13902,7 +13896,7 @@
     </row>
     <row r="97" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="str">
-        <f>IF(ISBLANK(I97)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B97" s="1" t="s">
@@ -13953,7 +13947,7 @@
         <v>709</v>
       </c>
       <c r="Q97" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E97))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R97" s="1" t="s">
@@ -13971,7 +13965,7 @@
     </row>
     <row r="98" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="str">
-        <f>IF(ISBLANK(I98)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B98" s="1" t="s">
@@ -14022,7 +14016,7 @@
         <v>1836</v>
       </c>
       <c r="Q98" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E98))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R98" s="1" t="s">
@@ -14040,7 +14034,7 @@
     </row>
     <row r="99" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="str">
-        <f>IF(ISBLANK(I99)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B99" s="1" t="s">
@@ -14091,7 +14085,7 @@
         <v>1836</v>
       </c>
       <c r="Q99" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E99))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R99" s="1" t="s">
@@ -14109,7 +14103,7 @@
     </row>
     <row r="100" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="str">
-        <f>IF(ISBLANK(I100)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B100" s="1" t="s">
@@ -14160,7 +14154,7 @@
         <v>1836</v>
       </c>
       <c r="Q100" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E100))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R100" s="1" t="s">
@@ -14178,7 +14172,7 @@
     </row>
     <row r="101" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="str">
-        <f>IF(ISBLANK(I101)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B101" s="1" t="s">
@@ -14229,7 +14223,7 @@
         <v>1836</v>
       </c>
       <c r="Q101" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E101))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R101" s="1" t="s">
@@ -14247,7 +14241,7 @@
     </row>
     <row r="102" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="str">
-        <f>IF(ISBLANK(I102)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B102" s="1" t="s">
@@ -14298,7 +14292,7 @@
         <v>1836</v>
       </c>
       <c r="Q102" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E102))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R102" s="1" t="s">
@@ -14316,7 +14310,7 @@
     </row>
     <row r="103" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="str">
-        <f>IF(ISBLANK(I103)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B103" s="1" t="s">
@@ -14367,7 +14361,7 @@
         <v>1836</v>
       </c>
       <c r="Q103" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E103))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R103" s="1" t="s">
@@ -14385,7 +14379,7 @@
     </row>
     <row r="104" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="str">
-        <f>IF(ISBLANK(I104)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B104" s="1" t="s">
@@ -14436,7 +14430,7 @@
         <v>1836</v>
       </c>
       <c r="Q104" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E104))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R104" s="1" t="s">
@@ -14454,7 +14448,7 @@
     </row>
     <row r="105" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="str">
-        <f>IF(ISBLANK(I105)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B105" s="1" t="s">
@@ -14505,7 +14499,7 @@
         <v>1836</v>
       </c>
       <c r="Q105" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E105))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R105" s="1" t="s">
@@ -14523,7 +14517,7 @@
     </row>
     <row r="106" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="str">
-        <f>IF(ISBLANK(I106)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B106" s="1" t="s">
@@ -14574,7 +14568,7 @@
         <v>1836</v>
       </c>
       <c r="Q106" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E106))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R106" s="1" t="s">
@@ -14592,7 +14586,7 @@
     </row>
     <row r="107" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="str">
-        <f>IF(ISBLANK(I107)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B107" s="1" t="s">
@@ -14643,7 +14637,7 @@
         <v>1836</v>
       </c>
       <c r="Q107" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E107))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R107" s="1" t="s">
@@ -14661,7 +14655,7 @@
     </row>
     <row r="108" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="str">
-        <f>IF(ISBLANK(I108)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B108" s="1" t="s">
@@ -14712,7 +14706,7 @@
         <v>1836</v>
       </c>
       <c r="Q108" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E108))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R108" s="1" t="s">
@@ -14730,7 +14724,7 @@
     </row>
     <row r="109" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="str">
-        <f>IF(ISBLANK(I109)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B109" s="1" t="s">
@@ -14781,7 +14775,7 @@
         <v>709</v>
       </c>
       <c r="Q109" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E109))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R109" s="1" t="s">
@@ -14799,7 +14793,7 @@
     </row>
     <row r="110" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="str">
-        <f>IF(ISBLANK(I110)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B110" s="1" t="s">
@@ -14850,7 +14844,7 @@
         <v>1836</v>
       </c>
       <c r="Q110" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E110))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R110" s="1" t="s">
@@ -14868,7 +14862,7 @@
     </row>
     <row r="111" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="str">
-        <f>IF(ISBLANK(I111)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B111" s="1" t="s">
@@ -14919,7 +14913,7 @@
         <v>1836</v>
       </c>
       <c r="Q111" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E111))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R111" s="1" t="s">
@@ -14937,7 +14931,7 @@
     </row>
     <row r="112" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="str">
-        <f>IF(ISBLANK(I112)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B112" s="1" t="s">
@@ -14988,7 +14982,7 @@
         <v>1836</v>
       </c>
       <c r="Q112" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E112))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R112" s="1" t="s">
@@ -15006,7 +15000,7 @@
     </row>
     <row r="113" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="str">
-        <f>IF(ISBLANK(I113)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B113" s="1" t="s">
@@ -15057,7 +15051,7 @@
         <v>1836</v>
       </c>
       <c r="Q113" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E113))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R113" s="1" t="s">
@@ -15075,7 +15069,7 @@
     </row>
     <row r="114" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="str">
-        <f>IF(ISBLANK(I114)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B114" s="1" t="s">
@@ -15126,7 +15120,7 @@
         <v>1836</v>
       </c>
       <c r="Q114" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E114))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R114" s="1" t="s">
@@ -15144,7 +15138,7 @@
     </row>
     <row r="115" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="str">
-        <f>IF(ISBLANK(I115)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B115" s="1" t="s">
@@ -15195,7 +15189,7 @@
         <v>1836</v>
       </c>
       <c r="Q115" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E115))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R115" s="1" t="s">
@@ -15213,7 +15207,7 @@
     </row>
     <row r="116" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="str">
-        <f>IF(ISBLANK(I116)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B116" s="1" t="s">
@@ -15264,7 +15258,7 @@
         <v>1836</v>
       </c>
       <c r="Q116" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E116))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R116" s="1" t="s">
@@ -15282,7 +15276,7 @@
     </row>
     <row r="117" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="str">
-        <f>IF(ISBLANK(I117)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B117" s="1" t="s">
@@ -15333,7 +15327,7 @@
         <v>1836</v>
       </c>
       <c r="Q117" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E117))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R117" s="1" t="s">
@@ -15351,7 +15345,7 @@
     </row>
     <row r="118" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="str">
-        <f>IF(ISBLANK(I118)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B118" s="1" t="s">
@@ -15402,7 +15396,7 @@
         <v>1836</v>
       </c>
       <c r="Q118" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E118))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R118" s="1" t="s">
@@ -15420,7 +15414,7 @@
     </row>
     <row r="119" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="str">
-        <f>IF(ISBLANK(I119)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B119" s="1" t="s">
@@ -15471,7 +15465,7 @@
         <v>1836</v>
       </c>
       <c r="Q119" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E119))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R119" s="1" t="s">
@@ -15489,7 +15483,7 @@
     </row>
     <row r="120" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="str">
-        <f>IF(ISBLANK(I120)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B120" s="1" t="s">
@@ -15540,7 +15534,7 @@
         <v>1836</v>
       </c>
       <c r="Q120" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E120))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R120" s="1" t="s">
@@ -15558,7 +15552,7 @@
     </row>
     <row r="121" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="str">
-        <f>IF(ISBLANK(I121)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B121" s="1" t="s">
@@ -15609,7 +15603,7 @@
         <v>1836</v>
       </c>
       <c r="Q121" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E121))</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R121" s="1" t="s">
@@ -15627,7 +15621,7 @@
     </row>
     <row r="122" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="str">
-        <f>IF(ISBLANK(I122)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B122" s="1" t="s">
@@ -15678,7 +15672,7 @@
         <v>1836</v>
       </c>
       <c r="Q122" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E122))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R122" s="1" t="s">
@@ -15696,7 +15690,7 @@
     </row>
     <row r="123" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="str">
-        <f>IF(ISBLANK(I123)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B123" s="1" t="s">
@@ -15747,7 +15741,7 @@
         <v>1836</v>
       </c>
       <c r="Q123" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E123))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R123" s="1" t="s">
@@ -15765,7 +15759,7 @@
     </row>
     <row r="124" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="str">
-        <f>IF(ISBLANK(I124)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B124" s="1" t="s">
@@ -15816,7 +15810,7 @@
         <v>1836</v>
       </c>
       <c r="Q124" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E124))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R124" s="1" t="s">
@@ -15834,7 +15828,7 @@
     </row>
     <row r="125" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="str">
-        <f>IF(ISBLANK(I125)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B125" s="1" t="s">
@@ -15885,7 +15879,7 @@
         <v>1836</v>
       </c>
       <c r="Q125" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E125))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R125" s="1" t="s">
@@ -15903,7 +15897,7 @@
     </row>
     <row r="126" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="str">
-        <f>IF(ISBLANK(I126)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B126" s="1" t="s">
@@ -15954,7 +15948,7 @@
         <v>1836</v>
       </c>
       <c r="Q126" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E126))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R126" s="1" t="s">
@@ -15972,7 +15966,7 @@
     </row>
     <row r="127" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="str">
-        <f>IF(ISBLANK(I127)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B127" s="1" t="s">
@@ -16023,7 +16017,7 @@
         <v>1836</v>
       </c>
       <c r="Q127" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E127))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R127" s="1" t="s">
@@ -16041,7 +16035,7 @@
     </row>
     <row r="128" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="str">
-        <f>IF(ISBLANK(I128)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B128" s="1" t="s">
@@ -16092,7 +16086,7 @@
         <v>1836</v>
       </c>
       <c r="Q128" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E128))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R128" s="1" t="s">
@@ -16110,7 +16104,7 @@
     </row>
     <row r="129" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="str">
-        <f>IF(ISBLANK(I129)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="2"/>
         <v>Done</v>
       </c>
       <c r="B129" s="1" t="s">
@@ -16161,7 +16155,7 @@
         <v>1836</v>
       </c>
       <c r="Q129" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E129))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="R129" s="1" t="s">
@@ -16179,7 +16173,7 @@
     </row>
     <row r="130" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="str">
-        <f>IF(ISBLANK(I130)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A130:A193" si="4">IF(ISBLANK(I130)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B130" s="1" t="s">
@@ -16230,7 +16224,7 @@
         <v>1836</v>
       </c>
       <c r="Q130" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E130))</f>
+        <f t="shared" ref="Q130:Q193" si="5">ISNUMBER(SEARCH(",",E130))</f>
         <v>0</v>
       </c>
       <c r="R130" s="1" t="s">
@@ -16248,7 +16242,7 @@
     </row>
     <row r="131" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="str">
-        <f>IF(ISBLANK(I131)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B131" s="1" t="s">
@@ -16299,7 +16293,7 @@
         <v>1836</v>
       </c>
       <c r="Q131" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E131))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R131" s="1" t="s">
@@ -16317,7 +16311,7 @@
     </row>
     <row r="132" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="str">
-        <f>IF(ISBLANK(I132)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B132" s="1" t="s">
@@ -16368,7 +16362,7 @@
         <v>1836</v>
       </c>
       <c r="Q132" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E132))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R132" s="1" t="s">
@@ -16386,7 +16380,7 @@
     </row>
     <row r="133" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="str">
-        <f>IF(ISBLANK(I133)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B133" s="1" t="s">
@@ -16437,7 +16431,7 @@
         <v>1836</v>
       </c>
       <c r="Q133" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E133))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R133" s="1" t="s">
@@ -16455,7 +16449,7 @@
     </row>
     <row r="134" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="str">
-        <f>IF(ISBLANK(I134)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B134" s="1" t="s">
@@ -16506,7 +16500,7 @@
         <v>1836</v>
       </c>
       <c r="Q134" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E134))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R134" s="1" t="s">
@@ -16524,7 +16518,7 @@
     </row>
     <row r="135" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="str">
-        <f>IF(ISBLANK(I135)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B135" s="1" t="s">
@@ -16575,7 +16569,7 @@
         <v>1836</v>
       </c>
       <c r="Q135" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E135))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R135" s="1" t="s">
@@ -16593,7 +16587,7 @@
     </row>
     <row r="136" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="str">
-        <f>IF(ISBLANK(I136)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B136" s="1" t="s">
@@ -16644,7 +16638,7 @@
         <v>1836</v>
       </c>
       <c r="Q136" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E136))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R136" s="1" t="s">
@@ -16662,7 +16656,7 @@
     </row>
     <row r="137" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="str">
-        <f>IF(ISBLANK(I137)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B137" s="1" t="s">
@@ -16713,7 +16707,7 @@
         <v>1836</v>
       </c>
       <c r="Q137" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E137))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R137" s="1" t="s">
@@ -16731,7 +16725,7 @@
     </row>
     <row r="138" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="str">
-        <f>IF(ISBLANK(I138)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B138" s="1" t="s">
@@ -16782,7 +16776,7 @@
         <v>1836</v>
       </c>
       <c r="Q138" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E138))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R138" s="1" t="s">
@@ -16800,7 +16794,7 @@
     </row>
     <row r="139" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="str">
-        <f>IF(ISBLANK(I139)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B139" s="1" t="s">
@@ -16851,7 +16845,7 @@
         <v>1836</v>
       </c>
       <c r="Q139" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E139))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R139" s="1" t="s">
@@ -16869,7 +16863,7 @@
     </row>
     <row r="140" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="str">
-        <f>IF(ISBLANK(I140)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B140" s="1" t="s">
@@ -16920,7 +16914,7 @@
         <v>1836</v>
       </c>
       <c r="Q140" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E140))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R140" s="1" t="s">
@@ -16938,7 +16932,7 @@
     </row>
     <row r="141" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="str">
-        <f>IF(ISBLANK(I141)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B141" s="1" t="s">
@@ -16989,7 +16983,7 @@
         <v>1836</v>
       </c>
       <c r="Q141" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E141))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R141" s="1" t="s">
@@ -17007,7 +17001,7 @@
     </row>
     <row r="142" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="str">
-        <f>IF(ISBLANK(I142)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B142" s="1" t="s">
@@ -17058,7 +17052,7 @@
         <v>1836</v>
       </c>
       <c r="Q142" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E142))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R142" s="1" t="s">
@@ -17076,7 +17070,7 @@
     </row>
     <row r="143" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="str">
-        <f>IF(ISBLANK(I143)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B143" s="1" t="s">
@@ -17127,7 +17121,7 @@
         <v>1836</v>
       </c>
       <c r="Q143" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E143))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R143" s="1" t="s">
@@ -17145,7 +17139,7 @@
     </row>
     <row r="144" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="str">
-        <f>IF(ISBLANK(I144)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B144" s="1" t="s">
@@ -17196,7 +17190,7 @@
         <v>1836</v>
       </c>
       <c r="Q144" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E144))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R144" s="1" t="s">
@@ -17214,7 +17208,7 @@
     </row>
     <row r="145" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="str">
-        <f>IF(ISBLANK(I145)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B145" s="1" t="s">
@@ -17265,7 +17259,7 @@
         <v>1836</v>
       </c>
       <c r="Q145" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E145))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R145" s="1" t="s">
@@ -17283,7 +17277,7 @@
     </row>
     <row r="146" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="str">
-        <f>IF(ISBLANK(I146)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B146" s="1" t="s">
@@ -17334,7 +17328,7 @@
         <v>1836</v>
       </c>
       <c r="Q146" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E146))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R146" s="1" t="s">
@@ -17352,7 +17346,7 @@
     </row>
     <row r="147" spans="1:21" ht="75" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="str">
-        <f>IF(ISBLANK(I147)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B147" s="1" t="s">
@@ -17403,7 +17397,7 @@
         <v>1836</v>
       </c>
       <c r="Q147" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E147))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R147" s="1" t="s">
@@ -17421,7 +17415,7 @@
     </row>
     <row r="148" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="str">
-        <f>IF(ISBLANK(I148)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B148" s="1" t="s">
@@ -17472,7 +17466,7 @@
         <v>1836</v>
       </c>
       <c r="Q148" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E148))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R148" s="1" t="s">
@@ -17490,7 +17484,7 @@
     </row>
     <row r="149" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="str">
-        <f>IF(ISBLANK(I149)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B149" s="1" t="s">
@@ -17541,7 +17535,7 @@
         <v>1836</v>
       </c>
       <c r="Q149" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E149))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R149" s="1" t="s">
@@ -17559,7 +17553,7 @@
     </row>
     <row r="150" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="str">
-        <f>IF(ISBLANK(I150)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B150" s="1" t="s">
@@ -17610,7 +17604,7 @@
         <v>1836</v>
       </c>
       <c r="Q150" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E150))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R150" s="1" t="s">
@@ -17628,7 +17622,7 @@
     </row>
     <row r="151" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="str">
-        <f>IF(ISBLANK(I151)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B151" s="1" t="s">
@@ -17679,7 +17673,7 @@
         <v>1836</v>
       </c>
       <c r="Q151" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E151))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R151" s="1" t="s">
@@ -17697,7 +17691,7 @@
     </row>
     <row r="152" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="str">
-        <f>IF(ISBLANK(I152)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B152" s="1" t="s">
@@ -17748,7 +17742,7 @@
         <v>1836</v>
       </c>
       <c r="Q152" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E152))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R152" s="1" t="s">
@@ -17766,7 +17760,7 @@
     </row>
     <row r="153" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="str">
-        <f>IF(ISBLANK(I153)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B153" s="1" t="s">
@@ -17817,7 +17811,7 @@
         <v>1836</v>
       </c>
       <c r="Q153" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E153))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R153" s="1" t="s">
@@ -17835,7 +17829,7 @@
     </row>
     <row r="154" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="str">
-        <f>IF(ISBLANK(I154)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B154" s="1" t="s">
@@ -17886,7 +17880,7 @@
         <v>1836</v>
       </c>
       <c r="Q154" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E154))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R154" s="1" t="s">
@@ -17904,7 +17898,7 @@
     </row>
     <row r="155" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="str">
-        <f>IF(ISBLANK(I155)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B155" s="1" t="s">
@@ -17955,7 +17949,7 @@
         <v>1836</v>
       </c>
       <c r="Q155" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E155))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R155" s="1" t="s">
@@ -17973,7 +17967,7 @@
     </row>
     <row r="156" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="str">
-        <f>IF(ISBLANK(I156)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B156" s="1" t="s">
@@ -18024,7 +18018,7 @@
         <v>709</v>
       </c>
       <c r="Q156" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E156))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R156" s="1" t="s">
@@ -18042,7 +18036,7 @@
     </row>
     <row r="157" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="str">
-        <f>IF(ISBLANK(I157)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B157" s="1" t="s">
@@ -18093,7 +18087,7 @@
         <v>1836</v>
       </c>
       <c r="Q157" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E157))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R157" s="1" t="s">
@@ -18111,7 +18105,7 @@
     </row>
     <row r="158" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="str">
-        <f>IF(ISBLANK(I158)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B158" s="1" t="s">
@@ -18162,7 +18156,7 @@
         <v>1836</v>
       </c>
       <c r="Q158" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E158))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R158" s="1" t="s">
@@ -18180,7 +18174,7 @@
     </row>
     <row r="159" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="str">
-        <f>IF(ISBLANK(I159)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B159" s="1" t="s">
@@ -18231,7 +18225,7 @@
         <v>1836</v>
       </c>
       <c r="Q159" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E159))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R159" s="1" t="s">
@@ -18249,7 +18243,7 @@
     </row>
     <row r="160" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="str">
-        <f>IF(ISBLANK(I160)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B160" s="1" t="s">
@@ -18300,7 +18294,7 @@
         <v>1836</v>
       </c>
       <c r="Q160" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E160))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R160" s="1" t="s">
@@ -18318,7 +18312,7 @@
     </row>
     <row r="161" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="str">
-        <f>IF(ISBLANK(I161)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B161" s="1" t="s">
@@ -18369,7 +18363,7 @@
         <v>1836</v>
       </c>
       <c r="Q161" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E161))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R161" s="1" t="s">
@@ -18387,7 +18381,7 @@
     </row>
     <row r="162" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="str">
-        <f>IF(ISBLANK(I162)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B162" s="1" t="s">
@@ -18438,7 +18432,7 @@
         <v>1836</v>
       </c>
       <c r="Q162" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E162))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R162" s="1" t="s">
@@ -18456,7 +18450,7 @@
     </row>
     <row r="163" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="str">
-        <f>IF(ISBLANK(I163)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B163" s="1" t="s">
@@ -18507,7 +18501,7 @@
         <v>1836</v>
       </c>
       <c r="Q163" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E163))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R163" s="1" t="s">
@@ -18525,7 +18519,7 @@
     </row>
     <row r="164" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="str">
-        <f>IF(ISBLANK(I164)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B164" s="1" t="s">
@@ -18576,7 +18570,7 @@
         <v>1836</v>
       </c>
       <c r="Q164" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E164))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R164" s="1" t="s">
@@ -18594,7 +18588,7 @@
     </row>
     <row r="165" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="str">
-        <f>IF(ISBLANK(I165)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B165" s="1" t="s">
@@ -18645,7 +18639,7 @@
         <v>1836</v>
       </c>
       <c r="Q165" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E165))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R165" s="1" t="s">
@@ -18663,7 +18657,7 @@
     </row>
     <row r="166" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="str">
-        <f>IF(ISBLANK(I166)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B166" s="1" t="s">
@@ -18714,7 +18708,7 @@
         <v>1836</v>
       </c>
       <c r="Q166" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E166))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R166" s="1" t="s">
@@ -18732,7 +18726,7 @@
     </row>
     <row r="167" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="str">
-        <f>IF(ISBLANK(I167)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B167" s="1" t="s">
@@ -18783,7 +18777,7 @@
         <v>1836</v>
       </c>
       <c r="Q167" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E167))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R167" s="1" t="s">
@@ -18801,7 +18795,7 @@
     </row>
     <row r="168" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="str">
-        <f>IF(ISBLANK(I168)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B168" s="1" t="s">
@@ -18852,7 +18846,7 @@
         <v>1836</v>
       </c>
       <c r="Q168" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E168))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R168" s="1" t="s">
@@ -18870,7 +18864,7 @@
     </row>
     <row r="169" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="str">
-        <f>IF(ISBLANK(I169)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B169" s="1" t="s">
@@ -18921,7 +18915,7 @@
         <v>1836</v>
       </c>
       <c r="Q169" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E169))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R169" s="1" t="s">
@@ -18939,7 +18933,7 @@
     </row>
     <row r="170" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="str">
-        <f>IF(ISBLANK(I170)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B170" s="1" t="s">
@@ -18990,7 +18984,7 @@
         <v>1836</v>
       </c>
       <c r="Q170" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E170))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R170" s="1" t="s">
@@ -19008,7 +19002,7 @@
     </row>
     <row r="171" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="str">
-        <f>IF(ISBLANK(I171)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B171" s="1" t="s">
@@ -19059,7 +19053,7 @@
         <v>1836</v>
       </c>
       <c r="Q171" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E171))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R171" s="1" t="s">
@@ -19077,7 +19071,7 @@
     </row>
     <row r="172" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="str">
-        <f>IF(ISBLANK(I172)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B172" s="1" t="s">
@@ -19128,7 +19122,7 @@
         <v>1836</v>
       </c>
       <c r="Q172" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E172))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R172" s="1" t="s">
@@ -19146,7 +19140,7 @@
     </row>
     <row r="173" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="str">
-        <f>IF(ISBLANK(I173)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B173" s="1" t="s">
@@ -19197,7 +19191,7 @@
         <v>1836</v>
       </c>
       <c r="Q173" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E173))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R173" s="1" t="s">
@@ -19215,7 +19209,7 @@
     </row>
     <row r="174" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="str">
-        <f>IF(ISBLANK(I174)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B174" s="1" t="s">
@@ -19266,7 +19260,7 @@
         <v>1836</v>
       </c>
       <c r="Q174" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E174))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R174" s="1" t="s">
@@ -19284,7 +19278,7 @@
     </row>
     <row r="175" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="str">
-        <f>IF(ISBLANK(I175)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B175" s="1" t="s">
@@ -19335,7 +19329,7 @@
         <v>1836</v>
       </c>
       <c r="Q175" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E175))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R175" s="1" t="s">
@@ -19353,7 +19347,7 @@
     </row>
     <row r="176" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="str">
-        <f>IF(ISBLANK(I176)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B176" s="1" t="s">
@@ -19404,7 +19398,7 @@
         <v>1836</v>
       </c>
       <c r="Q176" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E176))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R176" s="1" t="s">
@@ -19422,7 +19416,7 @@
     </row>
     <row r="177" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="str">
-        <f>IF(ISBLANK(I177)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B177" s="1" t="s">
@@ -19473,7 +19467,7 @@
         <v>1836</v>
       </c>
       <c r="Q177" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E177))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R177" s="1" t="s">
@@ -19491,7 +19485,7 @@
     </row>
     <row r="178" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="str">
-        <f>IF(ISBLANK(I178)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B178" s="1" t="s">
@@ -19542,7 +19536,7 @@
         <v>1836</v>
       </c>
       <c r="Q178" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E178))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R178" s="1" t="s">
@@ -19560,7 +19554,7 @@
     </row>
     <row r="179" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="str">
-        <f>IF(ISBLANK(I179)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B179" s="1" t="s">
@@ -19611,7 +19605,7 @@
         <v>1836</v>
       </c>
       <c r="Q179" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E179))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R179" s="1" t="s">
@@ -19629,7 +19623,7 @@
     </row>
     <row r="180" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="str">
-        <f>IF(ISBLANK(I180)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B180" s="1" t="s">
@@ -19680,7 +19674,7 @@
         <v>1836</v>
       </c>
       <c r="Q180" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E180))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R180" s="1" t="s">
@@ -19698,7 +19692,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="str">
-        <f>IF(ISBLANK(I181)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B181" s="1" t="s">
@@ -19749,7 +19743,7 @@
         <v>1836</v>
       </c>
       <c r="Q181" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E181))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R181" s="1" t="s">
@@ -19767,7 +19761,7 @@
     </row>
     <row r="182" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="str">
-        <f>IF(ISBLANK(I182)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B182" s="1" t="s">
@@ -19818,7 +19812,7 @@
         <v>1836</v>
       </c>
       <c r="Q182" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E182))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R182" s="1" t="s">
@@ -19836,7 +19830,7 @@
     </row>
     <row r="183" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="str">
-        <f>IF(ISBLANK(I183)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B183" s="1" t="s">
@@ -19887,7 +19881,7 @@
         <v>1836</v>
       </c>
       <c r="Q183" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E183))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R183" s="1" t="s">
@@ -19905,7 +19899,7 @@
     </row>
     <row r="184" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="str">
-        <f>IF(ISBLANK(I184)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B184" s="1" t="s">
@@ -19956,7 +19950,7 @@
         <v>1836</v>
       </c>
       <c r="Q184" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E184))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R184" s="1" t="s">
@@ -19974,7 +19968,7 @@
     </row>
     <row r="185" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="str">
-        <f>IF(ISBLANK(I185)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B185" s="1" t="s">
@@ -20025,7 +20019,7 @@
         <v>1836</v>
       </c>
       <c r="Q185" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E185))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R185" s="1" t="s">
@@ -20043,7 +20037,7 @@
     </row>
     <row r="186" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="str">
-        <f>IF(ISBLANK(I186)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B186" s="1" t="s">
@@ -20094,7 +20088,7 @@
         <v>1836</v>
       </c>
       <c r="Q186" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E186))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R186" s="1" t="s">
@@ -20112,7 +20106,7 @@
     </row>
     <row r="187" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="str">
-        <f>IF(ISBLANK(I187)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B187" s="1" t="s">
@@ -20163,7 +20157,7 @@
         <v>1836</v>
       </c>
       <c r="Q187" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E187))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R187" s="1" t="s">
@@ -20181,7 +20175,7 @@
     </row>
     <row r="188" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="str">
-        <f>IF(ISBLANK(I188)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B188" s="1" t="s">
@@ -20232,7 +20226,7 @@
         <v>1836</v>
       </c>
       <c r="Q188" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E188))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R188" s="1" t="s">
@@ -20250,7 +20244,7 @@
     </row>
     <row r="189" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="str">
-        <f>IF(ISBLANK(I189)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B189" s="1" t="s">
@@ -20301,7 +20295,7 @@
         <v>1836</v>
       </c>
       <c r="Q189" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E189))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R189" s="1" t="s">
@@ -20319,7 +20313,7 @@
     </row>
     <row r="190" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="str">
-        <f>IF(ISBLANK(I190)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B190" s="1" t="s">
@@ -20370,7 +20364,7 @@
         <v>1836</v>
       </c>
       <c r="Q190" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E190))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R190" s="1" t="s">
@@ -20388,7 +20382,7 @@
     </row>
     <row r="191" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="str">
-        <f>IF(ISBLANK(I191)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B191" s="1" t="s">
@@ -20439,7 +20433,7 @@
         <v>1836</v>
       </c>
       <c r="Q191" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E191))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R191" s="1" t="s">
@@ -20457,7 +20451,7 @@
     </row>
     <row r="192" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="str">
-        <f>IF(ISBLANK(I192)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B192" s="1" t="s">
@@ -20508,7 +20502,7 @@
         <v>1836</v>
       </c>
       <c r="Q192" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E192))</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="R192" s="1" t="s">
@@ -20526,7 +20520,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="str">
-        <f>IF(ISBLANK(I193)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="4"/>
         <v>Done</v>
       </c>
       <c r="B193" s="1" t="s">
@@ -20577,7 +20571,7 @@
         <v>1836</v>
       </c>
       <c r="Q193" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E193))</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="R193" s="1" t="s">
@@ -20595,7 +20589,7 @@
     </row>
     <row r="194" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="str">
-        <f>IF(ISBLANK(I194)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A194:A215" si="6">IF(ISBLANK(I194)=TRUE,"Pending","Done")</f>
         <v>Done</v>
       </c>
       <c r="B194" s="1" t="s">
@@ -20646,7 +20640,7 @@
         <v>1836</v>
       </c>
       <c r="Q194" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E194))</f>
+        <f t="shared" ref="Q194:Q215" si="7">ISNUMBER(SEARCH(",",E194))</f>
         <v>0</v>
       </c>
       <c r="R194" s="1" t="s">
@@ -20664,7 +20658,7 @@
     </row>
     <row r="195" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="str">
-        <f>IF(ISBLANK(I195)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B195" s="1" t="s">
@@ -20715,7 +20709,7 @@
         <v>1836</v>
       </c>
       <c r="Q195" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E195))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R195" s="1" t="s">
@@ -20733,7 +20727,7 @@
     </row>
     <row r="196" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="str">
-        <f>IF(ISBLANK(I196)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B196" s="1" t="s">
@@ -20784,7 +20778,7 @@
         <v>1836</v>
       </c>
       <c r="Q196" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E196))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R196" s="1" t="s">
@@ -20802,7 +20796,7 @@
     </row>
     <row r="197" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="str">
-        <f>IF(ISBLANK(I197)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B197" s="1" t="s">
@@ -20853,7 +20847,7 @@
         <v>1836</v>
       </c>
       <c r="Q197" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E197))</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R197" s="1" t="s">
@@ -20871,7 +20865,7 @@
     </row>
     <row r="198" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="str">
-        <f>IF(ISBLANK(I198)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B198" s="1" t="s">
@@ -20922,7 +20916,7 @@
         <v>1836</v>
       </c>
       <c r="Q198" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E198))</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R198" s="1" t="s">
@@ -20940,7 +20934,7 @@
     </row>
     <row r="199" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="str">
-        <f>IF(ISBLANK(I199)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B199" s="1" t="s">
@@ -20991,7 +20985,7 @@
         <v>1836</v>
       </c>
       <c r="Q199" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E199))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R199" s="1" t="s">
@@ -21009,7 +21003,7 @@
     </row>
     <row r="200" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="str">
-        <f>IF(ISBLANK(I200)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B200" s="1" t="s">
@@ -21060,7 +21054,7 @@
         <v>1836</v>
       </c>
       <c r="Q200" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E200))</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R200" s="1" t="s">
@@ -21078,7 +21072,7 @@
     </row>
     <row r="201" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="str">
-        <f>IF(ISBLANK(I201)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B201" s="1" t="s">
@@ -21129,7 +21123,7 @@
         <v>1836</v>
       </c>
       <c r="Q201" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E201))</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R201" s="1" t="s">
@@ -21147,7 +21141,7 @@
     </row>
     <row r="202" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="str">
-        <f>IF(ISBLANK(I202)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B202" s="1" t="s">
@@ -21198,7 +21192,7 @@
         <v>1836</v>
       </c>
       <c r="Q202" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E202))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R202" s="1" t="s">
@@ -21216,7 +21210,7 @@
     </row>
     <row r="203" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="str">
-        <f>IF(ISBLANK(I203)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B203" s="1" t="s">
@@ -21267,7 +21261,7 @@
         <v>1836</v>
       </c>
       <c r="Q203" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E203))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R203" s="1" t="s">
@@ -21285,7 +21279,7 @@
     </row>
     <row r="204" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="str">
-        <f>IF(ISBLANK(I204)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B204" s="1" t="s">
@@ -21336,7 +21330,7 @@
         <v>1836</v>
       </c>
       <c r="Q204" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E204))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R204" s="1" t="s">
@@ -21354,7 +21348,7 @@
     </row>
     <row r="205" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="str">
-        <f>IF(ISBLANK(I205)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B205" s="1" t="s">
@@ -21405,7 +21399,7 @@
         <v>1836</v>
       </c>
       <c r="Q205" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E205))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R205" s="1" t="s">
@@ -21423,7 +21417,7 @@
     </row>
     <row r="206" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="str">
-        <f>IF(ISBLANK(I206)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B206" s="1" t="s">
@@ -21474,7 +21468,7 @@
         <v>1836</v>
       </c>
       <c r="Q206" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E206))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R206" s="1" t="s">
@@ -21492,7 +21486,7 @@
     </row>
     <row r="207" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="str">
-        <f>IF(ISBLANK(I207)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B207" s="1" t="s">
@@ -21543,7 +21537,7 @@
         <v>1836</v>
       </c>
       <c r="Q207" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E207))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R207" s="1" t="s">
@@ -21561,7 +21555,7 @@
     </row>
     <row r="208" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="str">
-        <f>IF(ISBLANK(I208)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B208" s="1" t="s">
@@ -21612,7 +21606,7 @@
         <v>1836</v>
       </c>
       <c r="Q208" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E208))</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R208" s="1" t="s">
@@ -21630,7 +21624,7 @@
     </row>
     <row r="209" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="str">
-        <f>IF(ISBLANK(I209)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B209" s="1" t="s">
@@ -21681,7 +21675,7 @@
         <v>1836</v>
       </c>
       <c r="Q209" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E209))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R209" s="1" t="s">
@@ -21699,7 +21693,7 @@
     </row>
     <row r="210" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="str">
-        <f>IF(ISBLANK(I210)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B210" s="1" t="s">
@@ -21750,7 +21744,7 @@
         <v>1836</v>
       </c>
       <c r="Q210" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E210))</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R210" s="1" t="s">
@@ -21768,7 +21762,7 @@
     </row>
     <row r="211" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="str">
-        <f>IF(ISBLANK(I211)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B211" s="1" t="s">
@@ -21819,7 +21813,7 @@
         <v>1836</v>
       </c>
       <c r="Q211" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E211))</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R211" s="1" t="s">
@@ -21837,7 +21831,7 @@
     </row>
     <row r="212" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="str">
-        <f>IF(ISBLANK(I212)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B212" s="1" t="s">
@@ -21888,7 +21882,7 @@
         <v>1836</v>
       </c>
       <c r="Q212" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E212))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R212" s="1" t="s">
@@ -21906,7 +21900,7 @@
     </row>
     <row r="213" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="str">
-        <f>IF(ISBLANK(I213)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B213" s="1" t="s">
@@ -21957,7 +21951,7 @@
         <v>1836</v>
       </c>
       <c r="Q213" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E213))</f>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="R213" s="1" t="s">
@@ -21975,7 +21969,7 @@
     </row>
     <row r="214" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="str">
-        <f>IF(ISBLANK(I214)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B214" s="1" t="s">
@@ -22026,7 +22020,7 @@
         <v>1836</v>
       </c>
       <c r="Q214" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E214))</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R214" s="1" t="s">
@@ -22044,7 +22038,7 @@
     </row>
     <row r="215" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="str">
-        <f>IF(ISBLANK(I215)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="6"/>
         <v>Done</v>
       </c>
       <c r="B215" s="1" t="s">
@@ -22095,7 +22089,7 @@
         <v>1836</v>
       </c>
       <c r="Q215" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E215))</f>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="R215" s="1" t="s">
@@ -22111,9 +22105,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="216" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="str">
-        <f>IF(ISBLANK(I216)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A216:A257" si="8">IF(ISBLANK(I216)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B216" s="1" t="s">
@@ -22156,7 +22150,7 @@
         <v>1836</v>
       </c>
       <c r="Q216" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E216))</f>
+        <f t="shared" ref="Q216:Q257" si="9">ISNUMBER(SEARCH(",",E216))</f>
         <v>0</v>
       </c>
       <c r="R216" s="1" t="s">
@@ -22172,9 +22166,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="217" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="str">
-        <f>IF(ISBLANK(I217)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B217" s="1" t="s">
@@ -22217,7 +22211,7 @@
         <v>1836</v>
       </c>
       <c r="Q217" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E217))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R217" s="1" t="s">
@@ -22233,9 +22227,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="218" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="str">
-        <f>IF(ISBLANK(I218)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B218" s="1" t="s">
@@ -22278,7 +22272,7 @@
         <v>1836</v>
       </c>
       <c r="Q218" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E218))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R218" s="1" t="s">
@@ -22294,9 +22288,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="219" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="str">
-        <f>IF(ISBLANK(I219)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B219" s="1" t="s">
@@ -22341,7 +22335,7 @@
         <v>1836</v>
       </c>
       <c r="Q219" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E219))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R219" s="1" t="s">
@@ -22357,9 +22351,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="220" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="str">
-        <f>IF(ISBLANK(I220)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B220" s="1" t="s">
@@ -22404,7 +22398,7 @@
         <v>1836</v>
       </c>
       <c r="Q220" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E220))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R220" s="1" t="s">
@@ -22420,9 +22414,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="221" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="str">
-        <f>IF(ISBLANK(I221)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B221" s="1" t="s">
@@ -22467,7 +22461,7 @@
         <v>1836</v>
       </c>
       <c r="Q221" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E221))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R221" s="1" t="s">
@@ -22483,9 +22477,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="222" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="str">
-        <f>IF(ISBLANK(I222)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B222" s="1" t="s">
@@ -22528,7 +22522,7 @@
         <v>1836</v>
       </c>
       <c r="Q222" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E222))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R222" s="1" t="s">
@@ -22544,9 +22538,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="223" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="str">
-        <f>IF(ISBLANK(I223)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B223" s="1" t="s">
@@ -22591,7 +22585,7 @@
         <v>1836</v>
       </c>
       <c r="Q223" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E223))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R223" s="1" t="s">
@@ -22607,9 +22601,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="224" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="str">
-        <f>IF(ISBLANK(I224)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B224" s="1" t="s">
@@ -22654,7 +22648,7 @@
         <v>1836</v>
       </c>
       <c r="Q224" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E224))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R224" s="1" t="s">
@@ -22670,9 +22664,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="225" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="str">
-        <f>IF(ISBLANK(I225)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B225" s="1" t="s">
@@ -22719,7 +22713,7 @@
         <v>1836</v>
       </c>
       <c r="Q225" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E225))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R225" s="1" t="s">
@@ -22735,9 +22729,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="226" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="str">
-        <f>IF(ISBLANK(I226)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B226" s="1" t="s">
@@ -22782,7 +22776,7 @@
         <v>1836</v>
       </c>
       <c r="Q226" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E226))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R226" s="1" t="s">
@@ -22798,9 +22792,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="227" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="str">
-        <f>IF(ISBLANK(I227)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B227" s="1" t="s">
@@ -22845,7 +22839,7 @@
         <v>1836</v>
       </c>
       <c r="Q227" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E227))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R227" s="1" t="s">
@@ -22861,9 +22855,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="228" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="str">
-        <f>IF(ISBLANK(I228)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B228" s="1" t="s">
@@ -22906,7 +22900,7 @@
         <v>1836</v>
       </c>
       <c r="Q228" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E228))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R228" s="1" t="s">
@@ -22922,9 +22916,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="229" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="str">
-        <f>IF(ISBLANK(I229)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B229" s="1" t="s">
@@ -22969,7 +22963,7 @@
         <v>1836</v>
       </c>
       <c r="Q229" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E229))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R229" s="1" t="s">
@@ -22985,9 +22979,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="230" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="str">
-        <f>IF(ISBLANK(I230)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B230" s="1" t="s">
@@ -23034,7 +23028,7 @@
         <v>1836</v>
       </c>
       <c r="Q230" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E230))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R230" s="1" t="s">
@@ -23050,9 +23044,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="231" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="str">
-        <f>IF(ISBLANK(I231)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B231" s="1" t="s">
@@ -23099,7 +23093,7 @@
         <v>1836</v>
       </c>
       <c r="Q231" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E231))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R231" s="1" t="s">
@@ -23115,9 +23109,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="232" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="str">
-        <f>IF(ISBLANK(I232)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B232" s="1" t="s">
@@ -23160,7 +23154,7 @@
         <v>1836</v>
       </c>
       <c r="Q232" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E232))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R232" s="1" t="s">
@@ -23176,9 +23170,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="233" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="str">
-        <f>IF(ISBLANK(I233)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B233" s="1" t="s">
@@ -23221,7 +23215,7 @@
         <v>1836</v>
       </c>
       <c r="Q233" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E233))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R233" s="1" t="s">
@@ -23237,9 +23231,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="234" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="str">
-        <f>IF(ISBLANK(I234)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B234" s="1" t="s">
@@ -23282,7 +23276,7 @@
         <v>1836</v>
       </c>
       <c r="Q234" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E234))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R234" s="1" t="s">
@@ -23298,9 +23292,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="235" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="str">
-        <f>IF(ISBLANK(I235)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B235" s="1" t="s">
@@ -23345,7 +23339,7 @@
         <v>1836</v>
       </c>
       <c r="Q235" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E235))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R235" s="1" t="s">
@@ -23361,9 +23355,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="236" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="str">
-        <f>IF(ISBLANK(I236)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B236" s="1" t="s">
@@ -23408,7 +23402,7 @@
         <v>1836</v>
       </c>
       <c r="Q236" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E236))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R236" s="1" t="s">
@@ -23424,9 +23418,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="237" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="str">
-        <f>IF(ISBLANK(I237)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B237" s="1" t="s">
@@ -23471,7 +23465,7 @@
         <v>1836</v>
       </c>
       <c r="Q237" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E237))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R237" s="1" t="s">
@@ -23487,9 +23481,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="238" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="str">
-        <f>IF(ISBLANK(I238)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B238" s="1" t="s">
@@ -23532,7 +23526,7 @@
         <v>1836</v>
       </c>
       <c r="Q238" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E238))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R238" s="1" t="s">
@@ -23548,9 +23542,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="239" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="str">
-        <f>IF(ISBLANK(I239)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B239" s="1" t="s">
@@ -23595,7 +23589,7 @@
         <v>1836</v>
       </c>
       <c r="Q239" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E239))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R239" s="1" t="s">
@@ -23611,9 +23605,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="240" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="str">
-        <f>IF(ISBLANK(I240)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B240" s="1" t="s">
@@ -23656,7 +23650,7 @@
         <v>1836</v>
       </c>
       <c r="Q240" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E240))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R240" s="1" t="s">
@@ -23672,9 +23666,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="241" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="str">
-        <f>IF(ISBLANK(I241)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B241" s="1" t="s">
@@ -23719,7 +23713,7 @@
         <v>1836</v>
       </c>
       <c r="Q241" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E241))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R241" s="1" t="s">
@@ -23735,9 +23729,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="242" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="str">
-        <f>IF(ISBLANK(I242)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B242" s="1" t="s">
@@ -23782,7 +23776,7 @@
         <v>1836</v>
       </c>
       <c r="Q242" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E242))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R242" s="1" t="s">
@@ -23798,9 +23792,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="243" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="str">
-        <f>IF(ISBLANK(I243)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B243" s="1" t="s">
@@ -23843,7 +23837,7 @@
         <v>1836</v>
       </c>
       <c r="Q243" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E243))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R243" s="1" t="s">
@@ -23859,9 +23853,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="244" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="str">
-        <f>IF(ISBLANK(I244)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B244" s="1" t="s">
@@ -23906,7 +23900,7 @@
         <v>1836</v>
       </c>
       <c r="Q244" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E244))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R244" s="1" t="s">
@@ -23922,9 +23916,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="245" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:21" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="str">
-        <f>IF(ISBLANK(I245)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B245" s="1" t="s">
@@ -23969,7 +23963,7 @@
         <v>1836</v>
       </c>
       <c r="Q245" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E245))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R245" s="1" t="s">
@@ -23985,9 +23979,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="246" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="str">
-        <f>IF(ISBLANK(I246)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B246" s="1" t="s">
@@ -24028,7 +24022,7 @@
         <v>1836</v>
       </c>
       <c r="Q246" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E246))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R246" s="1" t="s">
@@ -24044,9 +24038,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="247" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="str">
-        <f>IF(ISBLANK(I247)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B247" s="1" t="s">
@@ -24087,7 +24081,7 @@
         <v>1836</v>
       </c>
       <c r="Q247" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E247))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R247" s="1" t="s">
@@ -24103,9 +24097,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="248" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="str">
-        <f>IF(ISBLANK(I248)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B248" s="1" t="s">
@@ -24152,7 +24146,7 @@
         <v>1836</v>
       </c>
       <c r="Q248" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E248))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R248" s="1" t="s">
@@ -24168,9 +24162,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="249" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="str">
-        <f>IF(ISBLANK(I249)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B249" s="1" t="s">
@@ -24213,7 +24207,7 @@
         <v>1836</v>
       </c>
       <c r="Q249" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E249))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R249" s="1" t="s">
@@ -24229,9 +24223,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="250" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="str">
-        <f>IF(ISBLANK(I250)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B250" s="1" t="s">
@@ -24274,7 +24268,7 @@
         <v>1836</v>
       </c>
       <c r="Q250" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E250))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R250" s="1" t="s">
@@ -24290,9 +24284,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="251" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:21" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="str">
-        <f>IF(ISBLANK(I251)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B251" s="1" t="s">
@@ -24337,7 +24331,7 @@
         <v>1836</v>
       </c>
       <c r="Q251" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E251))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R251" s="1" t="s">
@@ -24353,9 +24347,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="252" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="str">
-        <f>IF(ISBLANK(I252)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B252" s="1" t="s">
@@ -24398,7 +24392,7 @@
         <v>1836</v>
       </c>
       <c r="Q252" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E252))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R252" s="1" t="s">
@@ -24414,9 +24408,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="253" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="str">
-        <f>IF(ISBLANK(I253)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B253" s="1" t="s">
@@ -24459,7 +24453,7 @@
         <v>1836</v>
       </c>
       <c r="Q253" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E253))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R253" s="1" t="s">
@@ -24475,9 +24469,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="254" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="str">
-        <f>IF(ISBLANK(I254)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B254" s="1" t="s">
@@ -24520,7 +24514,7 @@
         <v>1836</v>
       </c>
       <c r="Q254" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E254))</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="R254" s="1" t="s">
@@ -24536,9 +24530,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="255" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="str">
-        <f>IF(ISBLANK(I255)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B255" s="1" t="s">
@@ -24579,7 +24573,7 @@
         <v>1836</v>
       </c>
       <c r="Q255" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E255))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R255" s="1" t="s">
@@ -24595,9 +24589,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="256" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:21" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="str">
-        <f>IF(ISBLANK(I256)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B256" s="1" t="s">
@@ -24638,7 +24632,7 @@
         <v>1836</v>
       </c>
       <c r="Q256" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E256))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R256" s="1" t="s">
@@ -24654,9 +24648,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="257" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:21" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="str">
-        <f>IF(ISBLANK(I257)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="8"/>
         <v>Pending</v>
       </c>
       <c r="B257" s="1" t="s">
@@ -24697,7 +24691,7 @@
         <v>1836</v>
       </c>
       <c r="Q257" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E257))</f>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="R257" s="1" t="s">
@@ -24713,9 +24707,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="258" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="str">
-        <f>IF(ISBLANK(I258)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A258:A321" si="10">IF(ISBLANK(I258)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B258" s="1" t="s">
@@ -24756,7 +24750,7 @@
         <v>1836</v>
       </c>
       <c r="Q258" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E258))</f>
+        <f t="shared" ref="Q258:Q321" si="11">ISNUMBER(SEARCH(",",E258))</f>
         <v>0</v>
       </c>
       <c r="R258" s="1" t="s">
@@ -24772,9 +24766,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="259" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="str">
-        <f>IF(ISBLANK(I259)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B259" s="1" t="s">
@@ -24817,7 +24811,7 @@
         <v>1836</v>
       </c>
       <c r="Q259" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E259))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R259" s="1" t="s">
@@ -24833,9 +24827,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="260" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="str">
-        <f>IF(ISBLANK(I260)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B260" s="1" t="s">
@@ -24876,7 +24870,7 @@
         <v>1836</v>
       </c>
       <c r="Q260" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E260))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R260" s="1" t="s">
@@ -24892,9 +24886,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="261" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="str">
-        <f>IF(ISBLANK(I261)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B261" s="1" t="s">
@@ -24937,7 +24931,7 @@
         <v>1836</v>
       </c>
       <c r="Q261" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E261))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R261" s="1" t="s">
@@ -24953,9 +24947,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="262" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="str">
-        <f>IF(ISBLANK(I262)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B262" s="1" t="s">
@@ -24998,7 +24992,7 @@
         <v>1836</v>
       </c>
       <c r="Q262" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E262))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R262" s="1" t="s">
@@ -25014,9 +25008,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="263" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="str">
-        <f>IF(ISBLANK(I263)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B263" s="1" t="s">
@@ -25061,7 +25055,7 @@
         <v>1836</v>
       </c>
       <c r="Q263" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E263))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R263" s="1" t="s">
@@ -25077,9 +25071,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="264" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="str">
-        <f>IF(ISBLANK(I264)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B264" s="1" t="s">
@@ -25124,7 +25118,7 @@
         <v>1836</v>
       </c>
       <c r="Q264" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E264))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R264" s="1" t="s">
@@ -25140,9 +25134,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="265" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="str">
-        <f>IF(ISBLANK(I265)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B265" s="1" t="s">
@@ -25187,7 +25181,7 @@
         <v>1836</v>
       </c>
       <c r="Q265" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E265))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R265" s="1" t="s">
@@ -25203,9 +25197,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="266" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="str">
-        <f>IF(ISBLANK(I266)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B266" s="1" t="s">
@@ -25250,7 +25244,7 @@
         <v>1836</v>
       </c>
       <c r="Q266" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E266))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R266" s="1" t="s">
@@ -25266,9 +25260,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="267" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="str">
-        <f>IF(ISBLANK(I267)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B267" s="1" t="s">
@@ -25311,7 +25305,7 @@
         <v>1836</v>
       </c>
       <c r="Q267" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E267))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R267" s="1" t="s">
@@ -25327,9 +25321,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="268" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="str">
-        <f>IF(ISBLANK(I268)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B268" s="1" t="s">
@@ -25372,7 +25366,7 @@
         <v>1836</v>
       </c>
       <c r="Q268" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E268))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R268" s="1" t="s">
@@ -25388,9 +25382,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="269" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="str">
-        <f>IF(ISBLANK(I269)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B269" s="1" t="s">
@@ -25435,7 +25429,7 @@
         <v>1836</v>
       </c>
       <c r="Q269" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E269))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R269" s="1" t="s">
@@ -25451,9 +25445,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="270" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="str">
-        <f>IF(ISBLANK(I270)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B270" s="1" t="s">
@@ -25498,7 +25492,7 @@
         <v>1836</v>
       </c>
       <c r="Q270" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E270))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R270" s="1" t="s">
@@ -25514,9 +25508,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="271" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="str">
-        <f>IF(ISBLANK(I271)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B271" s="1" t="s">
@@ -25559,7 +25553,7 @@
         <v>1836</v>
       </c>
       <c r="Q271" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E271))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R271" s="1" t="s">
@@ -25575,9 +25569,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="272" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="str">
-        <f>IF(ISBLANK(I272)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B272" s="1" t="s">
@@ -25620,7 +25614,7 @@
         <v>1836</v>
       </c>
       <c r="Q272" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E272))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R272" s="1" t="s">
@@ -25636,9 +25630,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="273" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="str">
-        <f>IF(ISBLANK(I273)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B273" s="1" t="s">
@@ -25683,7 +25677,7 @@
         <v>1836</v>
       </c>
       <c r="Q273" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E273))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R273" s="1" t="s">
@@ -25699,9 +25693,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="274" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="str">
-        <f>IF(ISBLANK(I274)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B274" s="1" t="s">
@@ -25744,7 +25738,7 @@
         <v>1836</v>
       </c>
       <c r="Q274" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E274))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R274" s="1" t="s">
@@ -25760,9 +25754,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="275" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="str">
-        <f>IF(ISBLANK(I275)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B275" s="1" t="s">
@@ -25805,7 +25799,7 @@
         <v>1836</v>
       </c>
       <c r="Q275" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E275))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R275" s="1" t="s">
@@ -25821,9 +25815,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="276" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="str">
-        <f>IF(ISBLANK(I276)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B276" s="1" t="s">
@@ -25866,7 +25860,7 @@
         <v>1836</v>
       </c>
       <c r="Q276" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E276))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R276" s="1" t="s">
@@ -25882,9 +25876,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="277" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="str">
-        <f>IF(ISBLANK(I277)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B277" s="1" t="s">
@@ -25925,7 +25919,7 @@
         <v>1836</v>
       </c>
       <c r="Q277" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E277))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R277" s="1" t="s">
@@ -25941,9 +25935,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="278" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="str">
-        <f>IF(ISBLANK(I278)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B278" s="1" t="s">
@@ -25988,7 +25982,7 @@
         <v>1836</v>
       </c>
       <c r="Q278" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E278))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R278" s="1" t="s">
@@ -26004,9 +25998,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="279" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="str">
-        <f>IF(ISBLANK(I279)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B279" s="1" t="s">
@@ -26051,7 +26045,7 @@
         <v>1836</v>
       </c>
       <c r="Q279" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E279))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R279" s="1" t="s">
@@ -26067,9 +26061,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="280" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="str">
-        <f>IF(ISBLANK(I280)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B280" s="1" t="s">
@@ -26112,7 +26106,7 @@
         <v>1836</v>
       </c>
       <c r="Q280" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E280))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R280" s="1" t="s">
@@ -26128,9 +26122,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="281" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="str">
-        <f>IF(ISBLANK(I281)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B281" s="1" t="s">
@@ -26173,7 +26167,7 @@
         <v>1836</v>
       </c>
       <c r="Q281" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E281))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R281" s="1" t="s">
@@ -26189,9 +26183,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="282" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="str">
-        <f>IF(ISBLANK(I282)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B282" s="1" t="s">
@@ -26234,7 +26228,7 @@
         <v>1836</v>
       </c>
       <c r="Q282" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E282))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R282" s="1" t="s">
@@ -26250,9 +26244,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="283" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="str">
-        <f>IF(ISBLANK(I283)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B283" s="1" t="s">
@@ -26293,7 +26287,7 @@
         <v>1836</v>
       </c>
       <c r="Q283" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E283))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R283" s="1" t="s">
@@ -26309,9 +26303,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="284" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="str">
-        <f>IF(ISBLANK(I284)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B284" s="1" t="s">
@@ -26352,7 +26346,7 @@
         <v>1836</v>
       </c>
       <c r="Q284" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E284))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R284" s="1" t="s">
@@ -26368,9 +26362,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="285" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="str">
-        <f>IF(ISBLANK(I285)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B285" s="1" t="s">
@@ -26413,7 +26407,7 @@
         <v>1836</v>
       </c>
       <c r="Q285" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E285))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R285" s="1" t="s">
@@ -26429,9 +26423,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="286" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="str">
-        <f>IF(ISBLANK(I286)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B286" s="1" t="s">
@@ -26474,7 +26468,7 @@
         <v>1836</v>
       </c>
       <c r="Q286" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E286))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R286" s="1" t="s">
@@ -26490,9 +26484,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="287" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="str">
-        <f>IF(ISBLANK(I287)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B287" s="1" t="s">
@@ -26537,7 +26531,7 @@
         <v>1836</v>
       </c>
       <c r="Q287" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E287))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R287" s="1" t="s">
@@ -26553,9 +26547,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="288" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="str">
-        <f>IF(ISBLANK(I288)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B288" s="1" t="s">
@@ -26596,7 +26590,7 @@
         <v>1836</v>
       </c>
       <c r="Q288" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E288))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R288" s="1" t="s">
@@ -26612,9 +26606,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="289" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="str">
-        <f>IF(ISBLANK(I289)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B289" s="1" t="s">
@@ -26655,7 +26649,7 @@
         <v>1836</v>
       </c>
       <c r="Q289" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E289))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R289" s="1" t="s">
@@ -26671,9 +26665,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="290" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="str">
-        <f>IF(ISBLANK(I290)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B290" s="1" t="s">
@@ -26716,7 +26710,7 @@
         <v>1836</v>
       </c>
       <c r="Q290" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E290))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R290" s="1" t="s">
@@ -26732,9 +26726,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="291" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="str">
-        <f>IF(ISBLANK(I291)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B291" s="1" t="s">
@@ -26777,7 +26771,7 @@
         <v>1836</v>
       </c>
       <c r="Q291" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E291))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R291" s="1" t="s">
@@ -26793,9 +26787,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="292" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="str">
-        <f>IF(ISBLANK(I292)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B292" s="1" t="s">
@@ -26838,7 +26832,7 @@
         <v>1836</v>
       </c>
       <c r="Q292" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E292))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R292" s="1" t="s">
@@ -26854,9 +26848,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="293" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="str">
-        <f>IF(ISBLANK(I293)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B293" s="1" t="s">
@@ -26897,7 +26891,7 @@
         <v>1836</v>
       </c>
       <c r="Q293" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E293))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R293" s="1" t="s">
@@ -26913,9 +26907,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="294" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="str">
-        <f>IF(ISBLANK(I294)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B294" s="1" t="s">
@@ -26956,7 +26950,7 @@
         <v>1836</v>
       </c>
       <c r="Q294" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E294))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R294" s="1" t="s">
@@ -26972,9 +26966,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="295" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="str">
-        <f>IF(ISBLANK(I295)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B295" s="1" t="s">
@@ -27015,7 +27009,7 @@
         <v>1836</v>
       </c>
       <c r="Q295" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E295))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R295" s="1" t="s">
@@ -27031,9 +27025,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="296" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="str">
-        <f>IF(ISBLANK(I296)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B296" s="1" t="s">
@@ -27074,7 +27068,7 @@
         <v>1836</v>
       </c>
       <c r="Q296" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E296))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R296" s="1" t="s">
@@ -27090,9 +27084,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="297" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="str">
-        <f>IF(ISBLANK(I297)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B297" s="1" t="s">
@@ -27137,7 +27131,7 @@
         <v>1836</v>
       </c>
       <c r="Q297" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E297))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R297" s="1" t="s">
@@ -27153,9 +27147,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="298" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="str">
-        <f>IF(ISBLANK(I298)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B298" s="1" t="s">
@@ -27198,7 +27192,7 @@
         <v>1836</v>
       </c>
       <c r="Q298" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E298))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R298" s="1" t="s">
@@ -27214,9 +27208,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="299" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="str">
-        <f>IF(ISBLANK(I299)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B299" s="1" t="s">
@@ -27259,7 +27253,7 @@
         <v>1836</v>
       </c>
       <c r="Q299" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E299))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R299" s="1" t="s">
@@ -27275,9 +27269,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="300" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="str">
-        <f>IF(ISBLANK(I300)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B300" s="1" t="s">
@@ -27318,7 +27312,7 @@
         <v>1836</v>
       </c>
       <c r="Q300" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E300))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R300" s="1" t="s">
@@ -27334,9 +27328,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="301" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="str">
-        <f>IF(ISBLANK(I301)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B301" s="1" t="s">
@@ -27377,7 +27371,7 @@
         <v>1836</v>
       </c>
       <c r="Q301" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E301))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R301" s="1" t="s">
@@ -27393,9 +27387,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="302" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="str">
-        <f>IF(ISBLANK(I302)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B302" s="1" t="s">
@@ -27438,7 +27432,7 @@
         <v>1836</v>
       </c>
       <c r="Q302" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E302))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R302" s="1" t="s">
@@ -27454,9 +27448,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="303" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="str">
-        <f>IF(ISBLANK(I303)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B303" s="1" t="s">
@@ -27501,7 +27495,7 @@
         <v>1836</v>
       </c>
       <c r="Q303" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E303))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R303" s="1" t="s">
@@ -27517,9 +27511,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="304" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="str">
-        <f>IF(ISBLANK(I304)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B304" s="1" t="s">
@@ -27562,7 +27556,7 @@
         <v>1836</v>
       </c>
       <c r="Q304" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E304))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R304" s="1" t="s">
@@ -27578,9 +27572,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="305" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="str">
-        <f>IF(ISBLANK(I305)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B305" s="1" t="s">
@@ -27621,7 +27615,7 @@
         <v>1836</v>
       </c>
       <c r="Q305" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E305))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R305" s="1" t="s">
@@ -27637,9 +27631,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="306" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="str">
-        <f>IF(ISBLANK(I306)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B306" s="1" t="s">
@@ -27680,7 +27674,7 @@
         <v>1836</v>
       </c>
       <c r="Q306" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E306))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R306" s="1" t="s">
@@ -27696,9 +27690,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="307" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="str">
-        <f>IF(ISBLANK(I307)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B307" s="1" t="s">
@@ -27741,7 +27735,7 @@
         <v>1836</v>
       </c>
       <c r="Q307" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E307))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R307" s="1" t="s">
@@ -27757,9 +27751,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="308" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="str">
-        <f>IF(ISBLANK(I308)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B308" s="1" t="s">
@@ -27802,7 +27796,7 @@
         <v>1836</v>
       </c>
       <c r="Q308" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E308))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R308" s="1" t="s">
@@ -27818,9 +27812,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="309" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="str">
-        <f>IF(ISBLANK(I309)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B309" s="1" t="s">
@@ -27863,7 +27857,7 @@
         <v>1836</v>
       </c>
       <c r="Q309" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E309))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R309" s="1" t="s">
@@ -27879,9 +27873,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="310" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="str">
-        <f>IF(ISBLANK(I310)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B310" s="1" t="s">
@@ -27924,7 +27918,7 @@
         <v>1836</v>
       </c>
       <c r="Q310" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E310))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R310" s="1" t="s">
@@ -27940,9 +27934,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="311" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="str">
-        <f>IF(ISBLANK(I311)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B311" s="1" t="s">
@@ -27983,7 +27977,7 @@
         <v>1836</v>
       </c>
       <c r="Q311" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E311))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R311" s="1" t="s">
@@ -27999,9 +27993,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="312" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="str">
-        <f>IF(ISBLANK(I312)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B312" s="1" t="s">
@@ -28046,7 +28040,7 @@
         <v>1836</v>
       </c>
       <c r="Q312" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E312))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R312" s="1" t="s">
@@ -28062,9 +28056,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="313" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="str">
-        <f>IF(ISBLANK(I313)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B313" s="1" t="s">
@@ -28105,7 +28099,7 @@
         <v>1836</v>
       </c>
       <c r="Q313" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E313))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R313" s="1" t="s">
@@ -28121,9 +28115,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="314" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="str">
-        <f>IF(ISBLANK(I314)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B314" s="1" t="s">
@@ -28164,7 +28158,7 @@
         <v>1836</v>
       </c>
       <c r="Q314" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E314))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R314" s="1" t="s">
@@ -28180,9 +28174,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="315" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="str">
-        <f>IF(ISBLANK(I315)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B315" s="1" t="s">
@@ -28223,7 +28217,7 @@
         <v>1836</v>
       </c>
       <c r="Q315" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E315))</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="R315" s="1" t="s">
@@ -28239,9 +28233,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="316" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="str">
-        <f>IF(ISBLANK(I316)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B316" s="1" t="s">
@@ -28282,7 +28276,7 @@
         <v>1836</v>
       </c>
       <c r="Q316" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E316))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R316" s="1" t="s">
@@ -28298,9 +28292,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="317" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="str">
-        <f>IF(ISBLANK(I317)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B317" s="1" t="s">
@@ -28343,7 +28337,7 @@
         <v>1836</v>
       </c>
       <c r="Q317" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E317))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R317" s="1" t="s">
@@ -28359,9 +28353,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="318" spans="1:21" ht="60" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:21" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="str">
-        <f>IF(ISBLANK(I318)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B318" s="1" t="s">
@@ -28406,7 +28400,7 @@
         <v>1836</v>
       </c>
       <c r="Q318" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E318))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R318" s="1" t="s">
@@ -28422,9 +28416,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="319" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="str">
-        <f>IF(ISBLANK(I319)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B319" s="1" t="s">
@@ -28465,7 +28459,7 @@
         <v>1836</v>
       </c>
       <c r="Q319" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E319))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R319" s="1" t="s">
@@ -28481,9 +28475,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="320" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="str">
-        <f>IF(ISBLANK(I320)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B320" s="1" t="s">
@@ -28526,7 +28520,7 @@
         <v>1836</v>
       </c>
       <c r="Q320" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E320))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R320" s="1" t="s">
@@ -28542,9 +28536,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="321" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="str">
-        <f>IF(ISBLANK(I321)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="10"/>
         <v>Pending</v>
       </c>
       <c r="B321" s="1" t="s">
@@ -28587,7 +28581,7 @@
         <v>1836</v>
       </c>
       <c r="Q321" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E321))</f>
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
       <c r="R321" s="1" t="s">
@@ -28603,9 +28597,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="322" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="str">
-        <f>IF(ISBLANK(I322)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A322:A385" si="12">IF(ISBLANK(I322)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B322" s="1" t="s">
@@ -28648,7 +28642,7 @@
         <v>1836</v>
       </c>
       <c r="Q322" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E322))</f>
+        <f t="shared" ref="Q322:Q385" si="13">ISNUMBER(SEARCH(",",E322))</f>
         <v>1</v>
       </c>
       <c r="R322" s="1" t="s">
@@ -28664,9 +28658,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="323" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="str">
-        <f>IF(ISBLANK(I323)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B323" s="1" t="s">
@@ -28709,7 +28703,7 @@
         <v>1836</v>
       </c>
       <c r="Q323" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E323))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R323" s="1" t="s">
@@ -28725,9 +28719,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="324" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="str">
-        <f>IF(ISBLANK(I324)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B324" s="1" t="s">
@@ -28772,7 +28766,7 @@
         <v>1836</v>
       </c>
       <c r="Q324" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E324))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R324" s="1" t="s">
@@ -28788,9 +28782,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="325" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="str">
-        <f>IF(ISBLANK(I325)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B325" s="1" t="s">
@@ -28833,7 +28827,7 @@
         <v>1836</v>
       </c>
       <c r="Q325" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E325))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R325" s="1" t="s">
@@ -28849,9 +28843,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="326" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="str">
-        <f>IF(ISBLANK(I326)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B326" s="1" t="s">
@@ -28896,7 +28890,7 @@
         <v>1836</v>
       </c>
       <c r="Q326" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E326))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R326" s="1" t="s">
@@ -28912,9 +28906,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="327" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="str">
-        <f>IF(ISBLANK(I327)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B327" s="1" t="s">
@@ -28959,7 +28953,7 @@
         <v>1836</v>
       </c>
       <c r="Q327" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E327))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R327" s="1" t="s">
@@ -28975,9 +28969,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="328" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="str">
-        <f>IF(ISBLANK(I328)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B328" s="1" t="s">
@@ -29022,7 +29016,7 @@
         <v>1836</v>
       </c>
       <c r="Q328" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E328))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R328" s="1" t="s">
@@ -29038,9 +29032,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="329" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="str">
-        <f>IF(ISBLANK(I329)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B329" s="1" t="s">
@@ -29085,7 +29079,7 @@
         <v>1836</v>
       </c>
       <c r="Q329" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E329))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R329" s="1" t="s">
@@ -29101,9 +29095,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="330" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="str">
-        <f>IF(ISBLANK(I330)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B330" s="1" t="s">
@@ -29148,7 +29142,7 @@
         <v>1836</v>
       </c>
       <c r="Q330" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E330))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R330" s="1" t="s">
@@ -29164,9 +29158,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="331" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="str">
-        <f>IF(ISBLANK(I331)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B331" s="1" t="s">
@@ -29209,7 +29203,7 @@
         <v>1836</v>
       </c>
       <c r="Q331" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E331))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R331" s="1" t="s">
@@ -29225,9 +29219,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="332" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="str">
-        <f>IF(ISBLANK(I332)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B332" s="1" t="s">
@@ -29270,7 +29264,7 @@
         <v>1836</v>
       </c>
       <c r="Q332" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E332))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R332" s="1" t="s">
@@ -29286,9 +29280,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="333" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="str">
-        <f>IF(ISBLANK(I333)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B333" s="1" t="s">
@@ -29333,7 +29327,7 @@
         <v>1836</v>
       </c>
       <c r="Q333" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E333))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R333" s="1" t="s">
@@ -29349,9 +29343,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="334" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="str">
-        <f>IF(ISBLANK(I334)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B334" s="1" t="s">
@@ -29394,7 +29388,7 @@
         <v>1836</v>
       </c>
       <c r="Q334" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E334))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R334" s="1" t="s">
@@ -29410,9 +29404,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="335" spans="1:21" ht="90" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:21" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="str">
-        <f>IF(ISBLANK(I335)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B335" s="1" t="s">
@@ -29455,7 +29449,7 @@
         <v>1836</v>
       </c>
       <c r="Q335" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E335))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R335" s="1" t="s">
@@ -29471,9 +29465,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="336" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="str">
-        <f>IF(ISBLANK(I336)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B336" s="1" t="s">
@@ -29514,7 +29508,7 @@
         <v>1836</v>
       </c>
       <c r="Q336" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E336))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R336" s="1" t="s">
@@ -29530,9 +29524,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="337" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="str">
-        <f>IF(ISBLANK(I337)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B337" s="1" t="s">
@@ -29575,7 +29569,7 @@
         <v>1836</v>
       </c>
       <c r="Q337" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E337))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R337" s="1" t="s">
@@ -29591,9 +29585,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="338" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="str">
-        <f>IF(ISBLANK(I338)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B338" s="1" t="s">
@@ -29636,7 +29630,7 @@
         <v>1836</v>
       </c>
       <c r="Q338" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E338))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R338" s="1" t="s">
@@ -29652,9 +29646,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="339" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="str">
-        <f>IF(ISBLANK(I339)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B339" s="1" t="s">
@@ -29695,7 +29689,7 @@
         <v>1836</v>
       </c>
       <c r="Q339" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E339))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R339" s="1" t="s">
@@ -29711,9 +29705,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="340" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="str">
-        <f>IF(ISBLANK(I340)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B340" s="1" t="s">
@@ -29754,7 +29748,7 @@
         <v>1836</v>
       </c>
       <c r="Q340" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E340))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R340" s="1" t="s">
@@ -29770,9 +29764,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="341" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="str">
-        <f>IF(ISBLANK(I341)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B341" s="1" t="s">
@@ -29813,7 +29807,7 @@
         <v>1836</v>
       </c>
       <c r="Q341" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E341))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R341" s="1" t="s">
@@ -29829,9 +29823,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="342" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="str">
-        <f>IF(ISBLANK(I342)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B342" s="1" t="s">
@@ -29874,7 +29868,7 @@
         <v>1836</v>
       </c>
       <c r="Q342" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E342))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R342" s="1" t="s">
@@ -29890,9 +29884,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="343" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="str">
-        <f>IF(ISBLANK(I343)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B343" s="1" t="s">
@@ -29937,7 +29931,7 @@
         <v>1836</v>
       </c>
       <c r="Q343" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E343))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R343" s="1" t="s">
@@ -29953,9 +29947,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="344" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="str">
-        <f>IF(ISBLANK(I344)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B344" s="1" t="s">
@@ -29998,7 +29992,7 @@
         <v>1836</v>
       </c>
       <c r="Q344" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E344))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R344" s="1" t="s">
@@ -30014,9 +30008,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="345" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="str">
-        <f>IF(ISBLANK(I345)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B345" s="1" t="s">
@@ -30059,7 +30053,7 @@
         <v>1836</v>
       </c>
       <c r="Q345" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E345))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R345" s="1" t="s">
@@ -30075,9 +30069,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="346" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="str">
-        <f>IF(ISBLANK(I346)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B346" s="1" t="s">
@@ -30120,7 +30114,7 @@
         <v>1836</v>
       </c>
       <c r="Q346" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E346))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R346" s="1" t="s">
@@ -30136,9 +30130,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="347" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="str">
-        <f>IF(ISBLANK(I347)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B347" s="1" t="s">
@@ -30181,7 +30175,7 @@
         <v>1836</v>
       </c>
       <c r="Q347" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E347))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R347" s="1" t="s">
@@ -30197,9 +30191,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="348" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="str">
-        <f>IF(ISBLANK(I348)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B348" s="1" t="s">
@@ -30244,7 +30238,7 @@
         <v>1836</v>
       </c>
       <c r="Q348" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E348))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R348" s="1" t="s">
@@ -30260,9 +30254,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="349" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="str">
-        <f>IF(ISBLANK(I349)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B349" s="1" t="s">
@@ -30303,7 +30297,7 @@
         <v>1836</v>
       </c>
       <c r="Q349" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E349))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R349" s="1" t="s">
@@ -30319,9 +30313,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="350" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="str">
-        <f>IF(ISBLANK(I350)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B350" s="1" t="s">
@@ -30366,7 +30360,7 @@
         <v>1836</v>
       </c>
       <c r="Q350" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E350))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R350" s="1" t="s">
@@ -30382,9 +30376,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="351" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="str">
-        <f>IF(ISBLANK(I351)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B351" s="1" t="s">
@@ -30427,7 +30421,7 @@
         <v>1836</v>
       </c>
       <c r="Q351" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E351))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R351" s="1" t="s">
@@ -30443,9 +30437,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="352" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="str">
-        <f>IF(ISBLANK(I352)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B352" s="1" t="s">
@@ -30488,7 +30482,7 @@
         <v>1836</v>
       </c>
       <c r="Q352" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E352))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R352" s="1" t="s">
@@ -30504,9 +30498,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="353" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="str">
-        <f>IF(ISBLANK(I353)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B353" s="1" t="s">
@@ -30547,7 +30541,7 @@
         <v>1836</v>
       </c>
       <c r="Q353" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E353))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R353" s="1" t="s">
@@ -30563,9 +30557,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="354" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="str">
-        <f>IF(ISBLANK(I354)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B354" s="1" t="s">
@@ -30608,7 +30602,7 @@
         <v>1836</v>
       </c>
       <c r="Q354" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E354))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R354" s="1" t="s">
@@ -30624,9 +30618,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="355" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="str">
-        <f>IF(ISBLANK(I355)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B355" s="1" t="s">
@@ -30669,7 +30663,7 @@
         <v>1836</v>
       </c>
       <c r="Q355" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E355))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R355" s="1" t="s">
@@ -30685,9 +30679,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="356" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="str">
-        <f>IF(ISBLANK(I356)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B356" s="1" t="s">
@@ -30728,7 +30722,7 @@
         <v>1836</v>
       </c>
       <c r="Q356" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E356))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R356" s="1" t="s">
@@ -30744,9 +30738,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="357" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="str">
-        <f>IF(ISBLANK(I357)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B357" s="1" t="s">
@@ -30789,7 +30783,7 @@
         <v>1836</v>
       </c>
       <c r="Q357" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E357))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R357" s="1" t="s">
@@ -30805,9 +30799,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="358" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="str">
-        <f>IF(ISBLANK(I358)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B358" s="1" t="s">
@@ -30848,7 +30842,7 @@
         <v>1836</v>
       </c>
       <c r="Q358" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E358))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R358" s="1" t="s">
@@ -30864,9 +30858,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="359" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="str">
-        <f>IF(ISBLANK(I359)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B359" s="1" t="s">
@@ -30911,7 +30905,7 @@
         <v>1836</v>
       </c>
       <c r="Q359" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E359))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R359" s="1" t="s">
@@ -30927,9 +30921,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="360" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="str">
-        <f>IF(ISBLANK(I360)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B360" s="1" t="s">
@@ -30972,7 +30966,7 @@
         <v>1836</v>
       </c>
       <c r="Q360" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E360))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R360" s="1" t="s">
@@ -30988,9 +30982,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="361" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="str">
-        <f>IF(ISBLANK(I361)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B361" s="1" t="s">
@@ -31033,7 +31027,7 @@
         <v>1836</v>
       </c>
       <c r="Q361" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E361))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R361" s="1" t="s">
@@ -31049,9 +31043,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="362" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="str">
-        <f>IF(ISBLANK(I362)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B362" s="1" t="s">
@@ -31094,7 +31088,7 @@
         <v>1836</v>
       </c>
       <c r="Q362" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E362))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R362" s="1" t="s">
@@ -31110,9 +31104,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="363" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="str">
-        <f>IF(ISBLANK(I363)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B363" s="1" t="s">
@@ -31153,7 +31147,7 @@
         <v>1836</v>
       </c>
       <c r="Q363" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E363))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R363" s="1" t="s">
@@ -31169,9 +31163,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="364" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="str">
-        <f>IF(ISBLANK(I364)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B364" s="1" t="s">
@@ -31216,7 +31210,7 @@
         <v>1836</v>
       </c>
       <c r="Q364" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E364))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R364" s="1" t="s">
@@ -31232,9 +31226,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="365" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="str">
-        <f>IF(ISBLANK(I365)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B365" s="1" t="s">
@@ -31277,7 +31271,7 @@
         <v>1836</v>
       </c>
       <c r="Q365" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E365))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R365" s="1" t="s">
@@ -31293,9 +31287,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="366" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="str">
-        <f>IF(ISBLANK(I366)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B366" s="1" t="s">
@@ -31340,7 +31334,7 @@
         <v>1836</v>
       </c>
       <c r="Q366" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E366))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R366" s="1" t="s">
@@ -31356,9 +31350,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="367" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="str">
-        <f>IF(ISBLANK(I367)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B367" s="1" t="s">
@@ -31401,7 +31395,7 @@
         <v>1836</v>
       </c>
       <c r="Q367" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E367))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R367" s="1" t="s">
@@ -31417,9 +31411,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="368" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="str">
-        <f>IF(ISBLANK(I368)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B368" s="1" t="s">
@@ -31462,7 +31456,7 @@
         <v>1836</v>
       </c>
       <c r="Q368" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E368))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R368" s="1" t="s">
@@ -31478,9 +31472,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="369" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="str">
-        <f>IF(ISBLANK(I369)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B369" s="1" t="s">
@@ -31521,7 +31515,7 @@
         <v>1836</v>
       </c>
       <c r="Q369" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E369))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R369" s="1" t="s">
@@ -31537,9 +31531,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="370" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="str">
-        <f>IF(ISBLANK(I370)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B370" s="1" t="s">
@@ -31582,7 +31576,7 @@
         <v>1836</v>
       </c>
       <c r="Q370" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E370))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R370" s="1" t="s">
@@ -31598,9 +31592,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="371" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="str">
-        <f>IF(ISBLANK(I371)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B371" s="1" t="s">
@@ -31643,7 +31637,7 @@
         <v>1836</v>
       </c>
       <c r="Q371" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E371))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R371" s="1" t="s">
@@ -31659,9 +31653,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="372" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="str">
-        <f>IF(ISBLANK(I372)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B372" s="1" t="s">
@@ -31704,7 +31698,7 @@
         <v>1836</v>
       </c>
       <c r="Q372" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E372))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R372" s="1" t="s">
@@ -31720,9 +31714,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="373" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="str">
-        <f>IF(ISBLANK(I373)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B373" s="1" t="s">
@@ -31765,7 +31759,7 @@
         <v>1836</v>
       </c>
       <c r="Q373" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E373))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R373" s="1" t="s">
@@ -31781,9 +31775,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="374" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="str">
-        <f>IF(ISBLANK(I374)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B374" s="1" t="s">
@@ -31826,7 +31820,7 @@
         <v>1836</v>
       </c>
       <c r="Q374" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E374))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R374" s="1" t="s">
@@ -31842,9 +31836,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="375" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="str">
-        <f>IF(ISBLANK(I375)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B375" s="1" t="s">
@@ -31887,7 +31881,7 @@
         <v>1836</v>
       </c>
       <c r="Q375" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E375))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R375" s="1" t="s">
@@ -31903,9 +31897,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="376" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="str">
-        <f>IF(ISBLANK(I376)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B376" s="1" t="s">
@@ -31946,7 +31940,7 @@
         <v>1836</v>
       </c>
       <c r="Q376" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E376))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R376" s="1" t="s">
@@ -31962,9 +31956,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="377" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="str">
-        <f>IF(ISBLANK(I377)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B377" s="1" t="s">
@@ -32005,7 +31999,7 @@
         <v>1836</v>
       </c>
       <c r="Q377" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E377))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R377" s="1" t="s">
@@ -32021,9 +32015,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="378" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="str">
-        <f>IF(ISBLANK(I378)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B378" s="1" t="s">
@@ -32066,7 +32060,7 @@
         <v>1836</v>
       </c>
       <c r="Q378" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E378))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R378" s="1" t="s">
@@ -32082,9 +32076,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="379" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="str">
-        <f>IF(ISBLANK(I379)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B379" s="1" t="s">
@@ -32127,7 +32121,7 @@
         <v>1836</v>
       </c>
       <c r="Q379" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E379))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R379" s="1" t="s">
@@ -32143,9 +32137,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="380" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="str">
-        <f>IF(ISBLANK(I380)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B380" s="1" t="s">
@@ -32188,7 +32182,7 @@
         <v>1836</v>
       </c>
       <c r="Q380" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E380))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R380" s="1" t="s">
@@ -32204,9 +32198,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="381" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="str">
-        <f>IF(ISBLANK(I381)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B381" s="1" t="s">
@@ -32251,7 +32245,7 @@
         <v>1836</v>
       </c>
       <c r="Q381" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E381))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R381" s="1" t="s">
@@ -32267,9 +32261,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="382" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="str">
-        <f>IF(ISBLANK(I382)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B382" s="1" t="s">
@@ -32312,7 +32306,7 @@
         <v>1836</v>
       </c>
       <c r="Q382" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E382))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R382" s="1" t="s">
@@ -32328,9 +32322,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="383" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="str">
-        <f>IF(ISBLANK(I383)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B383" s="1" t="s">
@@ -32373,7 +32367,7 @@
         <v>1836</v>
       </c>
       <c r="Q383" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E383))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R383" s="1" t="s">
@@ -32389,9 +32383,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="384" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="str">
-        <f>IF(ISBLANK(I384)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B384" s="1" t="s">
@@ -32434,7 +32428,7 @@
         <v>1836</v>
       </c>
       <c r="Q384" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E384))</f>
+        <f t="shared" si="13"/>
         <v>1</v>
       </c>
       <c r="R384" s="1" t="s">
@@ -32450,9 +32444,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="385" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="str">
-        <f>IF(ISBLANK(I385)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="12"/>
         <v>Pending</v>
       </c>
       <c r="B385" s="1" t="s">
@@ -32497,7 +32491,7 @@
         <v>1836</v>
       </c>
       <c r="Q385" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E385))</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="R385" s="1" t="s">
@@ -32513,9 +32507,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="386" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="str">
-        <f>IF(ISBLANK(I386)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A386:A449" si="14">IF(ISBLANK(I386)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B386" s="1" t="s">
@@ -32556,7 +32550,7 @@
         <v>1836</v>
       </c>
       <c r="Q386" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E386))</f>
+        <f t="shared" ref="Q386:Q449" si="15">ISNUMBER(SEARCH(",",E386))</f>
         <v>0</v>
       </c>
       <c r="R386" s="1" t="s">
@@ -32572,9 +32566,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="387" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="str">
-        <f>IF(ISBLANK(I387)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B387" s="1" t="s">
@@ -32617,7 +32611,7 @@
         <v>1836</v>
       </c>
       <c r="Q387" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E387))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R387" s="1" t="s">
@@ -32633,9 +32627,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="388" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="str">
-        <f>IF(ISBLANK(I388)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B388" s="1" t="s">
@@ -32676,7 +32670,7 @@
         <v>1836</v>
       </c>
       <c r="Q388" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E388))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R388" s="1" t="s">
@@ -32692,9 +32686,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="389" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="str">
-        <f>IF(ISBLANK(I389)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B389" s="1" t="s">
@@ -32737,7 +32731,7 @@
         <v>1836</v>
       </c>
       <c r="Q389" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E389))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R389" s="1" t="s">
@@ -32753,9 +32747,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="390" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="str">
-        <f>IF(ISBLANK(I390)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B390" s="1" t="s">
@@ -32798,7 +32792,7 @@
         <v>1836</v>
       </c>
       <c r="Q390" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E390))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R390" s="1" t="s">
@@ -32814,9 +32808,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="391" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="str">
-        <f>IF(ISBLANK(I391)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B391" s="1" t="s">
@@ -32857,7 +32851,7 @@
         <v>1836</v>
       </c>
       <c r="Q391" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E391))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R391" s="1" t="s">
@@ -32873,9 +32867,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="392" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="str">
-        <f>IF(ISBLANK(I392)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B392" s="1" t="s">
@@ -32918,7 +32912,7 @@
         <v>1836</v>
       </c>
       <c r="Q392" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E392))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R392" s="1" t="s">
@@ -32934,9 +32928,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="393" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="str">
-        <f>IF(ISBLANK(I393)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B393" s="1" t="s">
@@ -32979,7 +32973,7 @@
         <v>1836</v>
       </c>
       <c r="Q393" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E393))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R393" s="1" t="s">
@@ -32995,9 +32989,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="394" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="str">
-        <f>IF(ISBLANK(I394)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B394" s="1" t="s">
@@ -33038,7 +33032,7 @@
         <v>1836</v>
       </c>
       <c r="Q394" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E394))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R394" s="1" t="s">
@@ -33054,9 +33048,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="395" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="str">
-        <f>IF(ISBLANK(I395)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B395" s="1" t="s">
@@ -33099,7 +33093,7 @@
         <v>1836</v>
       </c>
       <c r="Q395" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E395))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R395" s="1" t="s">
@@ -33115,9 +33109,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="396" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="str">
-        <f>IF(ISBLANK(I396)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B396" s="1" t="s">
@@ -33160,7 +33154,7 @@
         <v>1836</v>
       </c>
       <c r="Q396" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E396))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R396" s="1" t="s">
@@ -33176,9 +33170,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="397" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="str">
-        <f>IF(ISBLANK(I397)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B397" s="1" t="s">
@@ -33221,7 +33215,7 @@
         <v>1836</v>
       </c>
       <c r="Q397" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E397))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R397" s="1" t="s">
@@ -33237,9 +33231,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="398" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="str">
-        <f>IF(ISBLANK(I398)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B398" s="1" t="s">
@@ -33282,7 +33276,7 @@
         <v>1836</v>
       </c>
       <c r="Q398" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E398))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R398" s="1" t="s">
@@ -33298,9 +33292,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="399" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="str">
-        <f>IF(ISBLANK(I399)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B399" s="1" t="s">
@@ -33343,7 +33337,7 @@
         <v>1836</v>
       </c>
       <c r="Q399" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E399))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R399" s="1" t="s">
@@ -33359,9 +33353,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="400" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="str">
-        <f>IF(ISBLANK(I400)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B400" s="1" t="s">
@@ -33402,7 +33396,7 @@
         <v>1836</v>
       </c>
       <c r="Q400" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E400))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R400" s="1" t="s">
@@ -33418,9 +33412,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="401" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="str">
-        <f>IF(ISBLANK(I401)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B401" s="1" t="s">
@@ -33463,7 +33457,7 @@
         <v>1836</v>
       </c>
       <c r="Q401" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E401))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R401" s="1" t="s">
@@ -33479,9 +33473,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="402" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="str">
-        <f>IF(ISBLANK(I402)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B402" s="1" t="s">
@@ -33524,7 +33518,7 @@
         <v>1836</v>
       </c>
       <c r="Q402" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E402))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R402" s="1" t="s">
@@ -33540,9 +33534,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="403" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="str">
-        <f>IF(ISBLANK(I403)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B403" s="1" t="s">
@@ -33583,7 +33577,7 @@
         <v>1836</v>
       </c>
       <c r="Q403" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E403))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R403" s="1" t="s">
@@ -33599,9 +33593,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="404" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="str">
-        <f>IF(ISBLANK(I404)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B404" s="1" t="s">
@@ -33644,7 +33638,7 @@
         <v>1836</v>
       </c>
       <c r="Q404" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E404))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R404" s="1" t="s">
@@ -33660,9 +33654,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="405" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="str">
-        <f>IF(ISBLANK(I405)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B405" s="1" t="s">
@@ -33703,7 +33697,7 @@
         <v>1836</v>
       </c>
       <c r="Q405" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E405))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R405" s="1" t="s">
@@ -33719,9 +33713,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="406" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="str">
-        <f>IF(ISBLANK(I406)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B406" s="1" t="s">
@@ -33762,7 +33756,7 @@
         <v>1836</v>
       </c>
       <c r="Q406" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E406))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R406" s="1" t="s">
@@ -33778,9 +33772,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="407" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="str">
-        <f>IF(ISBLANK(I407)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B407" s="1" t="s">
@@ -33821,7 +33815,7 @@
         <v>1836</v>
       </c>
       <c r="Q407" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E407))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R407" s="1" t="s">
@@ -33837,9 +33831,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="408" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="str">
-        <f>IF(ISBLANK(I408)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B408" s="1" t="s">
@@ -33882,7 +33876,7 @@
         <v>1836</v>
       </c>
       <c r="Q408" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E408))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R408" s="1" t="s">
@@ -33898,9 +33892,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="409" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="str">
-        <f>IF(ISBLANK(I409)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B409" s="1" t="s">
@@ -33941,7 +33935,7 @@
         <v>1836</v>
       </c>
       <c r="Q409" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E409))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R409" s="1" t="s">
@@ -33957,9 +33951,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="410" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="str">
-        <f>IF(ISBLANK(I410)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B410" s="1" t="s">
@@ -34002,7 +33996,7 @@
         <v>1836</v>
       </c>
       <c r="Q410" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E410))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R410" s="1" t="s">
@@ -34018,9 +34012,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="411" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="str">
-        <f>IF(ISBLANK(I411)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B411" s="1" t="s">
@@ -34063,7 +34057,7 @@
         <v>1836</v>
       </c>
       <c r="Q411" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E411))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R411" s="1" t="s">
@@ -34079,9 +34073,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="412" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="str">
-        <f>IF(ISBLANK(I412)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B412" s="1" t="s">
@@ -34126,7 +34120,7 @@
         <v>1836</v>
       </c>
       <c r="Q412" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E412))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R412" s="1" t="s">
@@ -34142,9 +34136,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="413" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="str">
-        <f>IF(ISBLANK(I413)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B413" s="1" t="s">
@@ -34185,7 +34179,7 @@
         <v>1836</v>
       </c>
       <c r="Q413" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E413))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R413" s="1" t="s">
@@ -34201,9 +34195,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="414" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="str">
-        <f>IF(ISBLANK(I414)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B414" s="1" t="s">
@@ -34244,7 +34238,7 @@
         <v>1836</v>
       </c>
       <c r="Q414" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E414))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R414" s="1" t="s">
@@ -34260,9 +34254,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="415" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="str">
-        <f>IF(ISBLANK(I415)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B415" s="1" t="s">
@@ -34305,7 +34299,7 @@
         <v>1836</v>
       </c>
       <c r="Q415" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E415))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R415" s="1" t="s">
@@ -34321,9 +34315,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="416" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="str">
-        <f>IF(ISBLANK(I416)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B416" s="1" t="s">
@@ -34366,7 +34360,7 @@
         <v>1836</v>
       </c>
       <c r="Q416" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E416))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R416" s="1" t="s">
@@ -34382,9 +34376,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="417" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="str">
-        <f>IF(ISBLANK(I417)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B417" s="1" t="s">
@@ -34427,7 +34421,7 @@
         <v>1836</v>
       </c>
       <c r="Q417" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E417))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R417" s="1" t="s">
@@ -34443,9 +34437,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="418" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="str">
-        <f>IF(ISBLANK(I418)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B418" s="1" t="s">
@@ -34488,7 +34482,7 @@
         <v>1836</v>
       </c>
       <c r="Q418" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E418))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R418" s="1" t="s">
@@ -34504,9 +34498,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="419" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="str">
-        <f>IF(ISBLANK(I419)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B419" s="1" t="s">
@@ -34549,7 +34543,7 @@
         <v>1836</v>
       </c>
       <c r="Q419" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E419))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R419" s="1" t="s">
@@ -34565,9 +34559,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="420" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="str">
-        <f>IF(ISBLANK(I420)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B420" s="1" t="s">
@@ -34610,7 +34604,7 @@
         <v>1836</v>
       </c>
       <c r="Q420" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E420))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R420" s="1" t="s">
@@ -34626,9 +34620,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="421" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="str">
-        <f>IF(ISBLANK(I421)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B421" s="1" t="s">
@@ -34669,7 +34663,7 @@
         <v>1836</v>
       </c>
       <c r="Q421" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E421))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R421" s="1" t="s">
@@ -34685,9 +34679,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="422" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="str">
-        <f>IF(ISBLANK(I422)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B422" s="1" t="s">
@@ -34730,7 +34724,7 @@
         <v>1836</v>
       </c>
       <c r="Q422" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E422))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R422" s="1" t="s">
@@ -34746,9 +34740,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="423" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="str">
-        <f>IF(ISBLANK(I423)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B423" s="1" t="s">
@@ -34789,7 +34783,7 @@
         <v>1836</v>
       </c>
       <c r="Q423" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E423))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R423" s="1" t="s">
@@ -34805,9 +34799,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="424" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="str">
-        <f>IF(ISBLANK(I424)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B424" s="1" t="s">
@@ -34850,7 +34844,7 @@
         <v>1836</v>
       </c>
       <c r="Q424" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E424))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R424" s="1" t="s">
@@ -34866,9 +34860,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="425" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="str">
-        <f>IF(ISBLANK(I425)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B425" s="1" t="s">
@@ -34911,7 +34905,7 @@
         <v>1836</v>
       </c>
       <c r="Q425" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E425))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R425" s="1" t="s">
@@ -34927,9 +34921,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="426" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="str">
-        <f>IF(ISBLANK(I426)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B426" s="1" t="s">
@@ -34972,7 +34966,7 @@
         <v>1836</v>
       </c>
       <c r="Q426" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E426))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R426" s="1" t="s">
@@ -34988,9 +34982,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="427" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="str">
-        <f>IF(ISBLANK(I427)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B427" s="1" t="s">
@@ -35033,7 +35027,7 @@
         <v>1836</v>
       </c>
       <c r="Q427" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E427))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R427" s="1" t="s">
@@ -35049,9 +35043,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="428" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="str">
-        <f>IF(ISBLANK(I428)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B428" s="1" t="s">
@@ -35094,7 +35088,7 @@
         <v>1836</v>
       </c>
       <c r="Q428" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E428))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R428" s="1" t="s">
@@ -35110,9 +35104,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="429" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="str">
-        <f>IF(ISBLANK(I429)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B429" s="1" t="s">
@@ -35153,7 +35147,7 @@
         <v>1836</v>
       </c>
       <c r="Q429" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E429))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R429" s="1" t="s">
@@ -35169,9 +35163,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="430" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="str">
-        <f>IF(ISBLANK(I430)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B430" s="1" t="s">
@@ -35212,7 +35206,7 @@
         <v>1836</v>
       </c>
       <c r="Q430" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E430))</f>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="R430" s="1" t="s">
@@ -35228,9 +35222,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="431" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="str">
-        <f>IF(ISBLANK(I431)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B431" s="1" t="s">
@@ -35273,7 +35267,7 @@
         <v>1836</v>
       </c>
       <c r="Q431" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E431))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R431" s="1" t="s">
@@ -35289,9 +35283,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="432" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="str">
-        <f>IF(ISBLANK(I432)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B432" s="1" t="s">
@@ -35334,7 +35328,7 @@
         <v>1836</v>
       </c>
       <c r="Q432" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E432))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R432" s="1" t="s">
@@ -35350,9 +35344,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="433" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="str">
-        <f>IF(ISBLANK(I433)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B433" s="1" t="s">
@@ -35393,7 +35387,7 @@
         <v>1836</v>
       </c>
       <c r="Q433" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E433))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R433" s="1" t="s">
@@ -35409,9 +35403,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="434" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="str">
-        <f>IF(ISBLANK(I434)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B434" s="1" t="s">
@@ -35452,7 +35446,7 @@
         <v>1836</v>
       </c>
       <c r="Q434" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E434))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R434" s="1" t="s">
@@ -35468,9 +35462,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="435" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="str">
-        <f>IF(ISBLANK(I435)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B435" s="1" t="s">
@@ -35513,7 +35507,7 @@
         <v>1836</v>
       </c>
       <c r="Q435" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E435))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R435" s="1" t="s">
@@ -35529,9 +35523,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="436" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="str">
-        <f>IF(ISBLANK(I436)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B436" s="1" t="s">
@@ -35574,7 +35568,7 @@
         <v>1836</v>
       </c>
       <c r="Q436" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E436))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R436" s="1" t="s">
@@ -35590,9 +35584,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="437" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="str">
-        <f>IF(ISBLANK(I437)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B437" s="1" t="s">
@@ -35635,7 +35629,7 @@
         <v>1836</v>
       </c>
       <c r="Q437" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E437))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R437" s="1" t="s">
@@ -35651,9 +35645,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="438" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="str">
-        <f>IF(ISBLANK(I438)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B438" s="1" t="s">
@@ -35698,7 +35692,7 @@
         <v>1836</v>
       </c>
       <c r="Q438" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E438))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R438" s="1" t="s">
@@ -35714,9 +35708,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="439" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="str">
-        <f>IF(ISBLANK(I439)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B439" s="1" t="s">
@@ -35761,7 +35755,7 @@
         <v>1836</v>
       </c>
       <c r="Q439" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E439))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R439" s="1" t="s">
@@ -35777,9 +35771,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="440" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="str">
-        <f>IF(ISBLANK(I440)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B440" s="1" t="s">
@@ -35822,7 +35816,7 @@
         <v>1836</v>
       </c>
       <c r="Q440" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E440))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R440" s="1" t="s">
@@ -35838,9 +35832,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="441" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="str">
-        <f>IF(ISBLANK(I441)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B441" s="1" t="s">
@@ -35883,7 +35877,7 @@
         <v>1836</v>
       </c>
       <c r="Q441" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E441))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R441" s="1" t="s">
@@ -35899,9 +35893,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="442" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="str">
-        <f>IF(ISBLANK(I442)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B442" s="1" t="s">
@@ -35944,7 +35938,7 @@
         <v>1836</v>
       </c>
       <c r="Q442" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E442))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R442" s="1" t="s">
@@ -35960,9 +35954,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="443" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="str">
-        <f>IF(ISBLANK(I443)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B443" s="1" t="s">
@@ -36005,7 +35999,7 @@
         <v>1836</v>
       </c>
       <c r="Q443" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E443))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R443" s="1" t="s">
@@ -36021,9 +36015,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="444" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="str">
-        <f>IF(ISBLANK(I444)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B444" s="1" t="s">
@@ -36066,7 +36060,7 @@
         <v>1836</v>
       </c>
       <c r="Q444" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E444))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R444" s="1" t="s">
@@ -36082,9 +36076,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="445" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="str">
-        <f>IF(ISBLANK(I445)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B445" s="1" t="s">
@@ -36127,7 +36121,7 @@
         <v>1836</v>
       </c>
       <c r="Q445" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E445))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R445" s="1" t="s">
@@ -36143,9 +36137,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="446" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="str">
-        <f>IF(ISBLANK(I446)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B446" s="1" t="s">
@@ -36190,7 +36184,7 @@
         <v>1836</v>
       </c>
       <c r="Q446" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E446))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R446" s="1" t="s">
@@ -36206,9 +36200,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="447" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="str">
-        <f>IF(ISBLANK(I447)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B447" s="1" t="s">
@@ -36251,7 +36245,7 @@
         <v>1836</v>
       </c>
       <c r="Q447" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E447))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R447" s="1" t="s">
@@ -36267,9 +36261,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="448" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="str">
-        <f>IF(ISBLANK(I448)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B448" s="1" t="s">
@@ -36312,7 +36306,7 @@
         <v>1836</v>
       </c>
       <c r="Q448" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E448))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R448" s="1" t="s">
@@ -36328,9 +36322,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="449" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="str">
-        <f>IF(ISBLANK(I449)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="14"/>
         <v>Pending</v>
       </c>
       <c r="B449" s="1" t="s">
@@ -36373,7 +36367,7 @@
         <v>1836</v>
       </c>
       <c r="Q449" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E449))</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="R449" s="1" t="s">
@@ -36389,9 +36383,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="450" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="str">
-        <f>IF(ISBLANK(I450)=TRUE,"Pending","Done")</f>
+        <f t="shared" ref="A450:A466" si="16">IF(ISBLANK(I450)=TRUE,"Pending","Done")</f>
         <v>Pending</v>
       </c>
       <c r="B450" s="1" t="s">
@@ -36434,7 +36428,7 @@
         <v>1836</v>
       </c>
       <c r="Q450" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E450))</f>
+        <f t="shared" ref="Q450:Q466" si="17">ISNUMBER(SEARCH(",",E450))</f>
         <v>1</v>
       </c>
       <c r="R450" s="1" t="s">
@@ -36450,9 +36444,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="451" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="str">
-        <f>IF(ISBLANK(I451)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B451" s="1" t="s">
@@ -36495,7 +36489,7 @@
         <v>1836</v>
       </c>
       <c r="Q451" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E451))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R451" s="1" t="s">
@@ -36511,9 +36505,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="452" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="str">
-        <f>IF(ISBLANK(I452)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B452" s="1" t="s">
@@ -36558,7 +36552,7 @@
         <v>1836</v>
       </c>
       <c r="Q452" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E452))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R452" s="1" t="s">
@@ -36574,9 +36568,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="453" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="str">
-        <f>IF(ISBLANK(I453)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B453" s="1" t="s">
@@ -36619,7 +36613,7 @@
         <v>1836</v>
       </c>
       <c r="Q453" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E453))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R453" s="1" t="s">
@@ -36635,9 +36629,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="454" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="str">
-        <f>IF(ISBLANK(I454)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B454" s="1" t="s">
@@ -36680,7 +36674,7 @@
         <v>1836</v>
       </c>
       <c r="Q454" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E454))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R454" s="1" t="s">
@@ -36696,9 +36690,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="455" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="str">
-        <f>IF(ISBLANK(I455)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B455" s="1" t="s">
@@ -36741,7 +36735,7 @@
         <v>1836</v>
       </c>
       <c r="Q455" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E455))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R455" s="1" t="s">
@@ -36757,9 +36751,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="456" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="str">
-        <f>IF(ISBLANK(I456)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B456" s="1" t="s">
@@ -36800,7 +36794,7 @@
         <v>1836</v>
       </c>
       <c r="Q456" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E456))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="R456" s="1" t="s">
@@ -36816,9 +36810,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="457" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="str">
-        <f>IF(ISBLANK(I457)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B457" s="1" t="s">
@@ -36863,7 +36857,7 @@
         <v>1836</v>
       </c>
       <c r="Q457" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E457))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R457" s="1" t="s">
@@ -36879,9 +36873,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="458" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="str">
-        <f>IF(ISBLANK(I458)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B458" s="1" t="s">
@@ -36926,7 +36920,7 @@
         <v>1836</v>
       </c>
       <c r="Q458" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E458))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R458" s="1" t="s">
@@ -36942,9 +36936,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="459" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="str">
-        <f>IF(ISBLANK(I459)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B459" s="1" t="s">
@@ -36987,7 +36981,7 @@
         <v>1836</v>
       </c>
       <c r="Q459" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E459))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R459" s="1" t="s">
@@ -37003,9 +36997,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="460" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="str">
-        <f>IF(ISBLANK(I460)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B460" s="1" t="s">
@@ -37048,7 +37042,7 @@
         <v>1836</v>
       </c>
       <c r="Q460" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E460))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R460" s="1" t="s">
@@ -37064,9 +37058,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="461" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:21" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="str">
-        <f>IF(ISBLANK(I461)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B461" s="1" t="s">
@@ -37109,7 +37103,7 @@
         <v>1836</v>
       </c>
       <c r="Q461" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E461))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R461" s="1" t="s">
@@ -37125,9 +37119,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="462" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="str">
-        <f>IF(ISBLANK(I462)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B462" s="1" t="s">
@@ -37170,7 +37164,7 @@
         <v>1836</v>
       </c>
       <c r="Q462" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E462))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R462" s="1" t="s">
@@ -37186,9 +37180,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="463" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="str">
-        <f>IF(ISBLANK(I463)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B463" s="1" t="s">
@@ -37233,7 +37227,7 @@
         <v>1836</v>
       </c>
       <c r="Q463" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E463))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R463" s="1" t="s">
@@ -37249,9 +37243,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="464" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="str">
-        <f>IF(ISBLANK(I464)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B464" s="1" t="s">
@@ -37294,7 +37288,7 @@
         <v>1836</v>
       </c>
       <c r="Q464" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E464))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R464" s="1" t="s">
@@ -37310,9 +37304,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="465" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="str">
-        <f>IF(ISBLANK(I465)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B465" s="1" t="s">
@@ -37355,7 +37349,7 @@
         <v>1836</v>
       </c>
       <c r="Q465" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E465))</f>
+        <f t="shared" si="17"/>
         <v>1</v>
       </c>
       <c r="R465" s="1" t="s">
@@ -37371,9 +37365,9 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="466" spans="1:21" ht="30" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:21" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="str">
-        <f>IF(ISBLANK(I466)=TRUE,"Pending","Done")</f>
+        <f t="shared" si="16"/>
         <v>Pending</v>
       </c>
       <c r="B466" s="1" t="s">
@@ -37416,7 +37410,7 @@
         <v>1836</v>
       </c>
       <c r="Q466" s="1" t="b">
-        <f>ISNUMBER(SEARCH(",",E466))</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="R466" s="1" t="s">
@@ -37434,7 +37428,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:U466" xr:uid="{84BC93B7-B882-48B2-AAF6-D1E0B3702CB8}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U466">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Done"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:U215">
       <sortCondition descending="1" ref="J1:J466"/>
     </sortState>
   </autoFilter>
@@ -37443,7 +37442,7 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:U1048576">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$A1="Pending"</formula>
     </cfRule>
   </conditionalFormatting>
